--- a/Assets/StreamingAssets/Excel/ChatData.xlsx
+++ b/Assets/StreamingAssets/Excel/ChatData.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="175">
   <si>
     <t>小段</t>
   </si>
@@ -193,9 +193,6 @@
     </r>
   </si>
   <si>
-    <t>电流杂音</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -272,16 +269,6 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>流水声</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>那我该怎么帮你呢？</t>
     </r>
   </si>
@@ -377,16 +364,6 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>点击摄像头窗口后跳转到31</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>打开摄像头窗口</t>
     </r>
   </si>
@@ -540,16 +517,6 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>等待动画</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>好了。</t>
     </r>
   </si>
@@ -1573,26 +1540,18 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>存档销毁，返回开始界面，并弹出提示“你似乎忘记了什么很重要的事。”</t>
-    </r>
+    <t>其他_死亡</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -2215,11 +2174,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2808,7 +2764,7 @@
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3"/>
+      <c r="E2" s="2"/>
       <c r="G2">
         <v>9</v>
       </c>
@@ -2826,7 +2782,7 @@
       <c r="D3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G3">
@@ -2846,7 +2802,7 @@
       <c r="D4" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G4">
@@ -2866,7 +2822,7 @@
       <c r="D5" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G5">
@@ -2886,7 +2842,7 @@
       <c r="D6" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G6">
@@ -2906,7 +2862,7 @@
       <c r="D7" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G7">
@@ -2926,7 +2882,7 @@
       <c r="D8" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G8">
@@ -2946,7 +2902,7 @@
       <c r="D9" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="2" t="s">
         <v>20</v>
       </c>
       <c r="G9">
@@ -2966,7 +2922,7 @@
       <c r="D10" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="2" t="s">
         <v>21</v>
       </c>
       <c r="G10">
@@ -2986,7 +2942,7 @@
       <c r="D11" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G11">
@@ -3006,7 +2962,7 @@
       <c r="D12" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G12">
@@ -3026,7 +2982,7 @@
       <c r="D13" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G13">
@@ -3046,15 +3002,13 @@
       <c r="D14" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G14">
         <v>13</v>
       </c>
-      <c r="I14" s="2" t="s">
-        <v>26</v>
-      </c>
+      <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
@@ -3069,8 +3023,8 @@
       <c r="D15" t="s">
         <v>11</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>27</v>
+      <c r="F15" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="G15">
         <v>14</v>
@@ -3089,8 +3043,8 @@
       <c r="D16" t="s">
         <v>11</v>
       </c>
-      <c r="F16" s="3" t="s">
-        <v>28</v>
+      <c r="F16" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="G16">
         <v>15</v>
@@ -3109,8 +3063,8 @@
       <c r="D17" t="s">
         <v>16</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>29</v>
+      <c r="F17" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="G17">
         <v>17</v>
@@ -3129,8 +3083,8 @@
       <c r="D18" t="s">
         <v>16</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>30</v>
+      <c r="F18" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="G18">
         <v>17</v>
@@ -3149,8 +3103,8 @@
       <c r="D19" t="s">
         <v>11</v>
       </c>
-      <c r="F19" s="3" t="s">
-        <v>31</v>
+      <c r="F19" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="G19">
         <v>18</v>
@@ -3169,14 +3123,14 @@
       <c r="D20" t="s">
         <v>11</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>32</v>
+      <c r="F20" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="G20">
         <v>19</v>
       </c>
       <c r="H20">
-        <v>2</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -3192,15 +3146,13 @@
       <c r="D21" t="s">
         <v>11</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>33</v>
+      <c r="F21" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="G21">
         <v>20</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>34</v>
-      </c>
+      <c r="I21" s="2"/>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
@@ -3215,8 +3167,8 @@
       <c r="D22" t="s">
         <v>16</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>35</v>
+      <c r="F22" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="G22">
         <v>21</v>
@@ -3235,8 +3187,8 @@
       <c r="D23" t="s">
         <v>11</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>36</v>
+      <c r="F23" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="G23">
         <v>22</v>
@@ -3255,8 +3207,8 @@
       <c r="D24" t="s">
         <v>11</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>37</v>
+      <c r="F24" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="G24">
         <v>23</v>
@@ -3275,8 +3227,8 @@
       <c r="D25" t="s">
         <v>11</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>38</v>
+      <c r="F25" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="G25">
         <v>24</v>
@@ -3295,8 +3247,8 @@
       <c r="D26" t="s">
         <v>16</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>39</v>
+      <c r="F26" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="G26">
         <v>25</v>
@@ -3315,8 +3267,8 @@
       <c r="D27" t="s">
         <v>11</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>40</v>
+      <c r="F27" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="G27">
         <v>26</v>
@@ -3335,8 +3287,8 @@
       <c r="D28" t="s">
         <v>11</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>41</v>
+      <c r="F28" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="G28">
         <v>27</v>
@@ -3355,8 +3307,8 @@
       <c r="D29" t="s">
         <v>11</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>42</v>
+      <c r="F29" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="G29">
         <v>28</v>
@@ -3375,8 +3327,8 @@
       <c r="D30" t="s">
         <v>11</v>
       </c>
-      <c r="F30" s="3" t="s">
-        <v>43</v>
+      <c r="F30" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="G30">
         <v>29</v>
@@ -3395,8 +3347,8 @@
       <c r="D31" t="s">
         <v>11</v>
       </c>
-      <c r="F31" s="3" t="s">
-        <v>44</v>
+      <c r="F31" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="G31">
         <v>30</v>
@@ -3410,20 +3362,18 @@
         <v>9</v>
       </c>
       <c r="C32" t="s">
+        <v>43</v>
+      </c>
+      <c r="D32" t="s">
+        <v>44</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D32" t="s">
-        <v>46</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="G32">
         <v>31</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>48</v>
-      </c>
+      <c r="I32" s="2"/>
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
@@ -3438,11 +3388,11 @@
       <c r="D33" t="s">
         <v>11</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>50</v>
+      <c r="E33" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="G33">
         <v>32</v>
@@ -3461,8 +3411,8 @@
       <c r="D34" t="s">
         <v>11</v>
       </c>
-      <c r="F34" s="3" t="s">
-        <v>51</v>
+      <c r="F34" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="G34">
         <v>33</v>
@@ -3481,8 +3431,8 @@
       <c r="D35" t="s">
         <v>11</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>52</v>
+      <c r="F35" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="G35">
         <v>34</v>
@@ -3501,8 +3451,8 @@
       <c r="D36" t="s">
         <v>16</v>
       </c>
-      <c r="F36" s="3" t="s">
-        <v>53</v>
+      <c r="F36" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="G36">
         <v>35</v>
@@ -3521,8 +3471,8 @@
       <c r="D37" t="s">
         <v>11</v>
       </c>
-      <c r="F37" s="3" t="s">
-        <v>54</v>
+      <c r="F37" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="G37">
         <v>36</v>
@@ -3541,8 +3491,8 @@
       <c r="D38" t="s">
         <v>16</v>
       </c>
-      <c r="F38" s="3" t="s">
-        <v>55</v>
+      <c r="F38" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="G38">
         <v>39</v>
@@ -3561,8 +3511,8 @@
       <c r="D39" t="s">
         <v>16</v>
       </c>
-      <c r="F39" s="3" t="s">
-        <v>56</v>
+      <c r="F39" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="G39">
         <v>38</v>
@@ -3581,8 +3531,8 @@
       <c r="D40" t="s">
         <v>11</v>
       </c>
-      <c r="F40" s="3" t="s">
-        <v>57</v>
+      <c r="F40" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="G40">
         <v>39</v>
@@ -3601,8 +3551,8 @@
       <c r="D41" t="s">
         <v>11</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>58</v>
+      <c r="F41" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="G41">
         <v>40</v>
@@ -3621,8 +3571,8 @@
       <c r="D42" t="s">
         <v>11</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>59</v>
+      <c r="F42" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="G42">
         <v>41</v>
@@ -3641,8 +3591,8 @@
       <c r="D43" t="s">
         <v>11</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>60</v>
+      <c r="F43" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="G43">
         <v>42</v>
@@ -3656,13 +3606,13 @@
         <v>9</v>
       </c>
       <c r="C44" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D44" t="s">
-        <v>46</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>61</v>
+        <v>44</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="G44">
         <v>43</v>
@@ -3681,11 +3631,11 @@
       <c r="D45" t="s">
         <v>16</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>63</v>
+      <c r="E45" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="G45">
         <v>44</v>
@@ -3704,18 +3654,16 @@
       <c r="D46" t="s">
         <v>11</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>64</v>
+      <c r="F46" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="G46">
         <v>45</v>
       </c>
       <c r="H46">
-        <v>3</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>65</v>
-      </c>
+        <v>3000</v>
+      </c>
+      <c r="I46" s="2"/>
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
@@ -3730,8 +3678,8 @@
       <c r="D47" t="s">
         <v>11</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>66</v>
+      <c r="F47" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="G47">
         <v>46</v>
@@ -3750,8 +3698,8 @@
       <c r="D48" t="s">
         <v>11</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>67</v>
+      <c r="F48" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="G48">
         <v>47</v>
@@ -3770,8 +3718,8 @@
       <c r="D49" t="s">
         <v>11</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>68</v>
+      <c r="F49" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="G49">
         <v>48</v>
@@ -3785,13 +3733,13 @@
         <v>9</v>
       </c>
       <c r="C50" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D50" t="s">
-        <v>46</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>69</v>
+        <v>44</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="G50">
         <v>49</v>
@@ -3810,11 +3758,11 @@
       <c r="D51" t="s">
         <v>16</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>71</v>
+      <c r="E51" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="G51">
         <v>50</v>
@@ -3833,8 +3781,8 @@
       <c r="D52" t="s">
         <v>11</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>72</v>
+      <c r="F52" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="G52">
         <v>51</v>
@@ -3853,8 +3801,8 @@
       <c r="D53" t="s">
         <v>11</v>
       </c>
-      <c r="F53" s="3" t="s">
-        <v>73</v>
+      <c r="F53" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="G53">
         <v>52</v>
@@ -3873,8 +3821,8 @@
       <c r="D54" t="s">
         <v>11</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>74</v>
+      <c r="F54" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="G54">
         <v>53</v>
@@ -3893,8 +3841,8 @@
       <c r="D55" t="s">
         <v>11</v>
       </c>
-      <c r="F55" s="3" t="s">
-        <v>75</v>
+      <c r="F55" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="G55">
         <v>54</v>
@@ -3913,8 +3861,8 @@
       <c r="D56" t="s">
         <v>11</v>
       </c>
-      <c r="F56" s="3" t="s">
-        <v>76</v>
+      <c r="F56" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="G56">
         <v>55</v>
@@ -3933,8 +3881,8 @@
       <c r="D57" t="s">
         <v>11</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>77</v>
+      <c r="F57" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="G57">
         <v>56</v>
@@ -3948,13 +3896,13 @@
         <v>9</v>
       </c>
       <c r="C58" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D58" t="s">
-        <v>46</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>78</v>
+        <v>44</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="G58">
         <v>57</v>
@@ -3973,11 +3921,11 @@
       <c r="D59" t="s">
         <v>16</v>
       </c>
-      <c r="E59" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>80</v>
+      <c r="E59" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="G59">
         <v>58</v>
@@ -3996,8 +3944,8 @@
       <c r="D60" t="s">
         <v>11</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>81</v>
+      <c r="F60" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="G60">
         <v>59</v>
@@ -4016,8 +3964,8 @@
       <c r="D61" t="s">
         <v>11</v>
       </c>
-      <c r="F61" s="3" t="s">
-        <v>82</v>
+      <c r="F61" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="G61">
         <v>60</v>
@@ -4036,8 +3984,8 @@
       <c r="D62" t="s">
         <v>11</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>83</v>
+      <c r="F62" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="G62">
         <v>61</v>
@@ -4056,8 +4004,8 @@
       <c r="D63" t="s">
         <v>11</v>
       </c>
-      <c r="F63" s="3" t="s">
-        <v>84</v>
+      <c r="F63" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="G63">
         <v>62</v>
@@ -4076,8 +4024,8 @@
       <c r="D64" t="s">
         <v>11</v>
       </c>
-      <c r="F64" s="3" t="s">
-        <v>85</v>
+      <c r="F64" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="G64">
         <v>63</v>
@@ -4096,8 +4044,8 @@
       <c r="D65" t="s">
         <v>11</v>
       </c>
-      <c r="F65" s="3" t="s">
-        <v>86</v>
+      <c r="F65" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="G65">
         <v>64</v>
@@ -4116,8 +4064,8 @@
       <c r="D66" t="s">
         <v>11</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>87</v>
+      <c r="F66" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="G66">
         <v>65</v>
@@ -4136,8 +4084,8 @@
       <c r="D67" t="s">
         <v>11</v>
       </c>
-      <c r="F67" s="3" t="s">
-        <v>88</v>
+      <c r="F67" s="2" t="s">
+        <v>84</v>
       </c>
       <c r="G67">
         <v>66</v>
@@ -4156,8 +4104,8 @@
       <c r="D68" t="s">
         <v>11</v>
       </c>
-      <c r="F68" s="3" t="s">
-        <v>89</v>
+      <c r="F68" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="G68">
         <v>67</v>
@@ -4176,18 +4124,16 @@
       <c r="D69" t="s">
         <v>11</v>
       </c>
-      <c r="F69" s="3" t="s">
-        <v>90</v>
+      <c r="F69" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="G69">
         <v>68</v>
       </c>
       <c r="H69">
-        <v>3</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>65</v>
-      </c>
+        <v>3000</v>
+      </c>
+      <c r="I69" s="2"/>
     </row>
     <row r="70" spans="1:7">
       <c r="A70">
@@ -4202,8 +4148,8 @@
       <c r="D70" t="s">
         <v>11</v>
       </c>
-      <c r="F70" s="3" t="s">
-        <v>91</v>
+      <c r="F70" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="G70">
         <v>69</v>
@@ -4222,8 +4168,8 @@
       <c r="D71" t="s">
         <v>11</v>
       </c>
-      <c r="F71" s="3" t="s">
-        <v>92</v>
+      <c r="F71" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="G71">
         <v>70</v>
@@ -4242,8 +4188,8 @@
       <c r="D72" t="s">
         <v>11</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>93</v>
+      <c r="F72" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="G72">
         <v>71</v>
@@ -4257,13 +4203,13 @@
         <v>9</v>
       </c>
       <c r="C73" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D73" t="s">
-        <v>46</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>94</v>
+        <v>44</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="G73">
         <v>72</v>
@@ -4282,11 +4228,11 @@
       <c r="D74" t="s">
         <v>16</v>
       </c>
-      <c r="E74" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>96</v>
+      <c r="E74" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="G74">
         <v>73</v>
@@ -4305,8 +4251,8 @@
       <c r="D75" t="s">
         <v>11</v>
       </c>
-      <c r="F75" s="3" t="s">
-        <v>97</v>
+      <c r="F75" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="G75">
         <v>74</v>
@@ -4325,8 +4271,8 @@
       <c r="D76" t="s">
         <v>11</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>98</v>
+      <c r="F76" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="G76">
         <v>75</v>
@@ -4345,8 +4291,8 @@
       <c r="D77" t="s">
         <v>11</v>
       </c>
-      <c r="F77" s="3" t="s">
-        <v>99</v>
+      <c r="F77" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="G77">
         <v>76</v>
@@ -4365,8 +4311,8 @@
       <c r="D78" t="s">
         <v>11</v>
       </c>
-      <c r="F78" s="3" t="s">
-        <v>100</v>
+      <c r="F78" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="G78">
         <v>77</v>
@@ -4385,18 +4331,16 @@
       <c r="D79" t="s">
         <v>16</v>
       </c>
-      <c r="F79" s="3" t="s">
-        <v>101</v>
+      <c r="F79" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="G79">
         <v>78</v>
       </c>
       <c r="H79">
-        <v>3</v>
-      </c>
-      <c r="I79" s="3" t="s">
-        <v>65</v>
-      </c>
+        <v>3000</v>
+      </c>
+      <c r="I79" s="2"/>
     </row>
     <row r="80" spans="1:7">
       <c r="A80">
@@ -4411,8 +4355,8 @@
       <c r="D80" t="s">
         <v>11</v>
       </c>
-      <c r="F80" s="3" t="s">
-        <v>102</v>
+      <c r="F80" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="G80">
         <v>79</v>
@@ -4431,8 +4375,8 @@
       <c r="D81" t="s">
         <v>11</v>
       </c>
-      <c r="F81" s="3" t="s">
-        <v>103</v>
+      <c r="F81" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="G81">
         <v>80</v>
@@ -4451,8 +4395,8 @@
       <c r="D82" t="s">
         <v>11</v>
       </c>
-      <c r="F82" s="3" t="s">
-        <v>104</v>
+      <c r="F82" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="G82">
         <v>81</v>
@@ -4466,13 +4410,13 @@
         <v>9</v>
       </c>
       <c r="C83" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D83" t="s">
-        <v>46</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>105</v>
+        <v>44</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="G83">
         <v>82</v>
@@ -4491,21 +4435,19 @@
       <c r="D84" t="s">
         <v>16</v>
       </c>
-      <c r="E84" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>107</v>
+      <c r="E84" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="G84">
         <v>83</v>
       </c>
       <c r="H84">
-        <v>3</v>
-      </c>
-      <c r="I84" s="3" t="s">
-        <v>65</v>
-      </c>
+        <v>3000</v>
+      </c>
+      <c r="I84" s="2"/>
     </row>
     <row r="85" spans="1:7">
       <c r="A85">
@@ -4520,8 +4462,8 @@
       <c r="D85" t="s">
         <v>11</v>
       </c>
-      <c r="F85" s="3" t="s">
-        <v>108</v>
+      <c r="F85" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="G85">
         <v>84</v>
@@ -4540,8 +4482,8 @@
       <c r="D86" t="s">
         <v>11</v>
       </c>
-      <c r="F86" s="3" t="s">
-        <v>109</v>
+      <c r="F86" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="G86">
         <v>85</v>
@@ -4560,8 +4502,8 @@
       <c r="D87" t="s">
         <v>11</v>
       </c>
-      <c r="F87" s="3" t="s">
-        <v>110</v>
+      <c r="F87" s="2" t="s">
+        <v>106</v>
       </c>
       <c r="G87">
         <v>86</v>
@@ -4580,8 +4522,8 @@
       <c r="D88" t="s">
         <v>11</v>
       </c>
-      <c r="F88" s="3" t="s">
-        <v>111</v>
+      <c r="F88" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="G88">
         <v>87</v>
@@ -4600,8 +4542,8 @@
       <c r="D89" t="s">
         <v>11</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>112</v>
+      <c r="F89" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="G89">
         <v>88</v>
@@ -4620,8 +4562,8 @@
       <c r="D90" t="s">
         <v>16</v>
       </c>
-      <c r="F90" s="3" t="s">
-        <v>113</v>
+      <c r="F90" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="G90">
         <v>90</v>
@@ -4640,8 +4582,8 @@
       <c r="D91" t="s">
         <v>16</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>114</v>
+      <c r="F91" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="G91">
         <v>90</v>
@@ -4660,8 +4602,8 @@
       <c r="D92" t="s">
         <v>11</v>
       </c>
-      <c r="F92" s="3" t="s">
-        <v>115</v>
+      <c r="F92" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="G92">
         <v>91</v>
@@ -4680,8 +4622,8 @@
       <c r="D93" t="s">
         <v>11</v>
       </c>
-      <c r="F93" s="3" t="s">
-        <v>116</v>
+      <c r="F93" s="2" t="s">
+        <v>112</v>
       </c>
       <c r="G93">
         <v>92</v>
@@ -4700,8 +4642,8 @@
       <c r="D94" t="s">
         <v>11</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>117</v>
+      <c r="F94" s="2" t="s">
+        <v>113</v>
       </c>
       <c r="G94">
         <v>93</v>
@@ -4720,8 +4662,8 @@
       <c r="D95" t="s">
         <v>16</v>
       </c>
-      <c r="F95" s="3" t="s">
-        <v>118</v>
+      <c r="F95" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="G95">
         <v>94</v>
@@ -4740,8 +4682,8 @@
       <c r="D96" t="s">
         <v>11</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>119</v>
+      <c r="F96" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="G96">
         <v>95</v>
@@ -4760,8 +4702,8 @@
       <c r="D97" t="s">
         <v>11</v>
       </c>
-      <c r="F97" s="3" t="s">
-        <v>120</v>
+      <c r="F97" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="G97">
         <v>96</v>
@@ -4780,8 +4722,8 @@
       <c r="D98" t="s">
         <v>11</v>
       </c>
-      <c r="F98" s="3" t="s">
-        <v>121</v>
+      <c r="F98" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="G98">
         <v>97</v>
@@ -4800,8 +4742,8 @@
       <c r="D99" t="s">
         <v>11</v>
       </c>
-      <c r="F99" s="3" t="s">
-        <v>122</v>
+      <c r="F99" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="G99">
         <v>98</v>
@@ -4815,13 +4757,13 @@
         <v>9</v>
       </c>
       <c r="C100" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D100" t="s">
-        <v>46</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>123</v>
+        <v>44</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="G100">
         <v>99</v>
@@ -4840,11 +4782,11 @@
       <c r="D101" t="s">
         <v>16</v>
       </c>
-      <c r="E101" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>125</v>
+      <c r="E101" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>121</v>
       </c>
       <c r="G101">
         <v>100</v>
@@ -4863,8 +4805,8 @@
       <c r="D102" t="s">
         <v>11</v>
       </c>
-      <c r="F102" s="3" t="s">
-        <v>126</v>
+      <c r="F102" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="G102">
         <v>101</v>
@@ -4883,8 +4825,8 @@
       <c r="D103" t="s">
         <v>11</v>
       </c>
-      <c r="F103" s="3" t="s">
-        <v>127</v>
+      <c r="F103" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="G103">
         <v>102</v>
@@ -4903,8 +4845,8 @@
       <c r="D104" t="s">
         <v>11</v>
       </c>
-      <c r="F104" s="3" t="s">
-        <v>128</v>
+      <c r="F104" s="2" t="s">
+        <v>124</v>
       </c>
       <c r="G104">
         <v>103</v>
@@ -4918,13 +4860,13 @@
         <v>9</v>
       </c>
       <c r="C105" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D105" t="s">
-        <v>46</v>
-      </c>
-      <c r="F105" s="3" t="s">
-        <v>129</v>
+        <v>44</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="G105">
         <v>104</v>
@@ -4943,11 +4885,11 @@
       <c r="D106" t="s">
         <v>11</v>
       </c>
-      <c r="E106" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="F106" s="3" t="s">
-        <v>131</v>
+      <c r="E106" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="G106">
         <v>105</v>
@@ -4966,8 +4908,8 @@
       <c r="D107" t="s">
         <v>11</v>
       </c>
-      <c r="F107" s="3" t="s">
-        <v>132</v>
+      <c r="F107" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="G107">
         <v>106</v>
@@ -4981,13 +4923,13 @@
         <v>9</v>
       </c>
       <c r="C108" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D108" t="s">
-        <v>46</v>
-      </c>
-      <c r="F108" s="3" t="s">
-        <v>133</v>
+        <v>44</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="G108">
         <v>-1</v>
@@ -5045,10 +4987,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>131</v>
       </c>
       <c r="G2">
         <v>8</v>
@@ -5059,7 +5001,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
@@ -5067,8 +5009,8 @@
       <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>136</v>
+      <c r="F3" s="2" t="s">
+        <v>132</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -5079,7 +5021,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
@@ -5087,8 +5029,8 @@
       <c r="D4" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>137</v>
+      <c r="F4" s="2" t="s">
+        <v>133</v>
       </c>
       <c r="G4">
         <v>3</v>
@@ -5099,16 +5041,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>138</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -5119,7 +5061,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -5127,8 +5069,8 @@
       <c r="D6" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>139</v>
+      <c r="F6" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5139,7 +5081,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
@@ -5147,8 +5089,8 @@
       <c r="D7" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>67</v>
+      <c r="F7" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="G7">
         <v>6</v>
@@ -5159,7 +5101,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C8" t="s">
         <v>15</v>
@@ -5167,8 +5109,8 @@
       <c r="D8" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>140</v>
+      <c r="F8" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="G8">
         <v>7</v>
@@ -5179,19 +5121,19 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>141</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>139</v>
       </c>
       <c r="G9">
         <v>9</v>
@@ -5202,19 +5144,19 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
       </c>
       <c r="D10" t="s">
+        <v>137</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="G10">
         <v>11</v>
@@ -5225,16 +5167,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>146</v>
+        <v>44</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>142</v>
       </c>
       <c r="G11">
         <v>10</v>
@@ -5245,7 +5187,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
@@ -5253,11 +5195,11 @@
       <c r="D12" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>148</v>
+      <c r="E12" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="G12">
         <v>11</v>
@@ -5268,7 +5210,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C13" t="s">
         <v>15</v>
@@ -5276,8 +5218,8 @@
       <c r="D13" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>149</v>
+      <c r="F13" s="2" t="s">
+        <v>145</v>
       </c>
       <c r="G13">
         <v>12</v>
@@ -5288,7 +5230,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -5296,8 +5238,8 @@
       <c r="D14" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>150</v>
+      <c r="F14" s="2" t="s">
+        <v>146</v>
       </c>
       <c r="G14">
         <v>13</v>
@@ -5308,16 +5250,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>151</v>
+        <v>44</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="G15">
         <v>14</v>
@@ -5328,7 +5270,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C16" t="s">
         <v>10</v>
@@ -5336,11 +5278,11 @@
       <c r="D16" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>153</v>
+      <c r="E16" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>149</v>
       </c>
       <c r="G16">
         <v>15</v>
@@ -5351,7 +5293,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
@@ -5359,8 +5301,8 @@
       <c r="D17" t="s">
         <v>11</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>154</v>
+      <c r="F17" s="2" t="s">
+        <v>150</v>
       </c>
       <c r="G17">
         <v>16</v>
@@ -5371,7 +5313,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -5379,8 +5321,8 @@
       <c r="D18" t="s">
         <v>11</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>155</v>
+      <c r="F18" s="2" t="s">
+        <v>151</v>
       </c>
       <c r="G18">
         <v>17</v>
@@ -5391,7 +5333,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C19" t="s">
         <v>10</v>
@@ -5399,8 +5341,8 @@
       <c r="D19" t="s">
         <v>11</v>
       </c>
-      <c r="F19" s="3" t="s">
-        <v>156</v>
+      <c r="F19" s="2" t="s">
+        <v>152</v>
       </c>
       <c r="G19">
         <v>18</v>
@@ -5411,7 +5353,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
@@ -5419,8 +5361,8 @@
       <c r="D20" t="s">
         <v>11</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>157</v>
+      <c r="F20" s="2" t="s">
+        <v>153</v>
       </c>
       <c r="G20">
         <v>19</v>
@@ -5431,7 +5373,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C21" t="s">
         <v>10</v>
@@ -5439,8 +5381,8 @@
       <c r="D21" t="s">
         <v>11</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>158</v>
+      <c r="F21" s="2" t="s">
+        <v>154</v>
       </c>
       <c r="G21">
         <v>20</v>
@@ -5451,7 +5393,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C22" t="s">
         <v>10</v>
@@ -5459,8 +5401,8 @@
       <c r="D22" t="s">
         <v>11</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>159</v>
+      <c r="F22" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="G22">
         <v>21</v>
@@ -5471,7 +5413,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C23" t="s">
         <v>15</v>
@@ -5479,8 +5421,8 @@
       <c r="D23" t="s">
         <v>16</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>160</v>
+      <c r="F23" s="2" t="s">
+        <v>156</v>
       </c>
       <c r="G23">
         <v>26</v>
@@ -5491,7 +5433,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C24" t="s">
         <v>15</v>
@@ -5499,8 +5441,8 @@
       <c r="D24" t="s">
         <v>16</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>161</v>
+      <c r="F24" s="2" t="s">
+        <v>157</v>
       </c>
       <c r="G24">
         <v>26</v>
@@ -5511,7 +5453,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C25" t="s">
         <v>15</v>
@@ -5519,8 +5461,8 @@
       <c r="D25" t="s">
         <v>16</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>162</v>
+      <c r="F25" s="2" t="s">
+        <v>158</v>
       </c>
       <c r="G25">
         <v>24</v>
@@ -5531,7 +5473,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C26" t="s">
         <v>10</v>
@@ -5539,8 +5481,8 @@
       <c r="D26" t="s">
         <v>11</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>163</v>
+      <c r="F26" s="2" t="s">
+        <v>159</v>
       </c>
       <c r="G26">
         <v>25</v>
@@ -5551,7 +5493,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C27" t="s">
         <v>10</v>
@@ -5559,8 +5501,8 @@
       <c r="D27" t="s">
         <v>11</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>164</v>
+      <c r="F27" s="2" t="s">
+        <v>160</v>
       </c>
       <c r="G27">
         <v>26</v>
@@ -5571,7 +5513,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C28" t="s">
         <v>10</v>
@@ -5579,8 +5521,8 @@
       <c r="D28" t="s">
         <v>11</v>
       </c>
-      <c r="F28" s="3" t="s">
-        <v>165</v>
+      <c r="F28" s="2" t="s">
+        <v>161</v>
       </c>
       <c r="G28">
         <v>-1</v>
@@ -5633,165 +5575,165 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="1">
+      <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="G2" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="G3" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>166</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="G7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>162</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="G4" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>166</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="G8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="G5" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>166</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G6" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>166</v>
-      </c>
-      <c r="C7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="G7" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>166</v>
-      </c>
-      <c r="C8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="G8" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>166</v>
-      </c>
-      <c r="C9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="G9" s="1">
+      <c r="G9">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="1">
+      <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>
@@ -5799,19 +5741,19 @@
       <c r="D10" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="G10" s="1">
+      <c r="F10" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="G10">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="1">
+      <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C11" t="s">
         <v>15</v>
@@ -5819,19 +5761,19 @@
       <c r="D11" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G11" s="1">
+      <c r="F11" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="G11">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="1">
+      <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C12" t="s">
         <v>15</v>
@@ -5839,14 +5781,14 @@
       <c r="D12" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="G12" s="1">
+      <c r="F12" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="G12">
         <v>-1</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>178</v>
+      <c r="I12" s="1" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Excel/ChatData.xlsx
+++ b/Assets/StreamingAssets/Excel/ChatData.xlsx
@@ -5585,7 +5585,7 @@
         <v>163</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:7">

--- a/Assets/StreamingAssets/Excel/ChatData.xlsx
+++ b/Assets/StreamingAssets/Excel/ChatData.xlsx
@@ -4,12 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060" activeTab="2"/>
+    <workbookView windowWidth="22188" windowHeight="9060" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="一切的开始" sheetId="1" r:id="rId1"/>
     <sheet name="修理研究完毕" sheetId="2" r:id="rId2"/>
     <sheet name="死亡" sheetId="3" r:id="rId3"/>
+    <sheet name="第一次点开气密舱门" sheetId="4" r:id="rId4"/>
+    <sheet name="第一次进珊瑚礁海域" sheetId="5" r:id="rId5"/>
+    <sheet name="困了_01" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="235">
   <si>
     <t>小段</t>
   </si>
@@ -83,17 +86,37 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>呼…呼叫公司总台，呼叫公司总台！我是麦麦，这里是信天翁号，我们需要救援，我们需要救援！</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>有人吗？不是说好点这个“紧急呼救”就会有人应的吗？</t>
+      <t>呼…呼叫公司总台，呼叫公司总台！</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我是麦麦，这里是信天翁号。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我们需要救援，我们需要救援！</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>有人吗？不是说好点这个“紧急呼救”然后集中精力就能用脑电发送远程通讯了吗？</t>
     </r>
   </si>
   <si>
@@ -129,17 +152,27 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>啊，有人接了。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我是麦麦，是探索部的职员，员工ID是……是EX27561</t>
+      <t>啊，有人回应了。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我是麦麦，是探索部的职员，员工ID是……</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是EX27561</t>
     </r>
   </si>
   <si>
@@ -169,7 +202,27 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>抱歉，我也不确定具体的经纬度，迫降的时候保护泡沫就把飞船舷窗封住了。现在外面是什么情况我也不太清楚。</t>
+      <t>抱歉，我也不确定具体的经纬度。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>迫降的时候保护泡沫就把飞船舷窗封住了</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>现在外面是什么情况我也不太清楚。</t>
     </r>
   </si>
   <si>
@@ -189,17 +242,47 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>不是，别！是…一定是因为钱的问题吧？是因为觉得救我们不值得吗？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我以后会想办法还钱的，飞船破损的钱，还有救援队的钱，我以后都会想办法还的。</t>
+      <t>不是，别！</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>一定是因为钱的问题吧？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是因为觉得救我们不值得吗？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我以后会想办法还钱的。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>飞船破损的钱，还有救援队的钱，我以后都会想办法还的。</t>
     </r>
   </si>
   <si>
@@ -239,7 +322,17 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>我这边没有信号，唯一能联系得上的只有你。得先救我出来，我才能给你钱吧。</t>
+      <t>我这边没有信号，唯一能联系得上的只有你。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你得先救我出来，我才能给你钱吧。</t>
     </r>
   </si>
   <si>
@@ -279,17 +372,37 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>怎么帮？额，你不是安全联络员吗？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>应急预案，或是救援方案，公司之前应该有过这样的培训的吧？应该有的吧？</t>
+      <t>怎么帮？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你不是安全联络员吗？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>应急预案，或是救援方案？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>公司之前应该有过这样的培训的吧？应该有的吧？</t>
     </r>
   </si>
   <si>
@@ -309,24 +422,68 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>我倒希望我是你们的安全联络员，但很可惜我不是，我只是一个打游戏的。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>说起来，我这边也挺奇怪的。我今天下了一个生存游戏，点开以后电脑直接就关机了。</t>
-    </r>
-  </si>
-  <si>
-    <t>重新开机后，电脑的屏幕还有操作系统全都变样了，连以前下的软件都没了，就剩几个我没见过的软件在桌面，我还因为是中病毒了。</t>
-  </si>
-  <si>
-    <t>再然后，就弹出了一个窗口，里面是你在对我求救。</t>
+      <t>我倒希望我是你们的安全联络员，但很可惜我不是。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我今天下了一个生存游戏，点开以后电脑直接就关机了。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>重新开机后，电脑的屏幕还有操作系统全都变样了。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>连以前下的软件都找不到了。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>就剩几个我没见过的软件在桌面。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我还以为是中病毒了。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>再然后，就弹出了一个窗口，里面是你在对我求救。</t>
+    </r>
   </si>
   <si>
     <r>
@@ -355,7 +512,7 @@
     <t>提示</t>
   </si>
   <si>
-    <t>双击桌面上的软件，打开摄像头窗口。</t>
+    <t>点击底边栏的摄像头图标，打开摄像头窗口。</t>
   </si>
   <si>
     <r>
@@ -374,17 +531,47 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>桌面上有一个叫摄像头的软件。点开后能看见一个像是直播的画面，里面是一个女孩的正脸。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>等等！背景的这个墙壁……好像有点眼熟？你刚才给我发的照片里就是这样的墙。总不会摄像头里的是你吧？</t>
+      <t>桌面上有一个叫摄像头的软件。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点开后能看见一个像是直播的画面，里面是一个女孩的正脸。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>等等！背景的这个墙壁……好像有点眼熟？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你刚才给我发的照片里就是这样的墙。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>总不会摄像头里的是你吧？</t>
     </r>
   </si>
   <si>
@@ -414,7 +601,17 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>啊？！！不会真是我吧。可我眼前没看见摄像头呀。</t>
+      <t>啊？！！不会真是我吧。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>可我眼前没看见摄像头呀。</t>
     </r>
   </si>
   <si>
@@ -434,27 +631,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>她看起来好几天没洗头了，头好油啊。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>……</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>在太空洗头很麻烦的，所以没怎么洗也很正常。</t>
+      <t>我觉得这就是你。</t>
     </r>
   </si>
   <si>
@@ -484,20 +661,37 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>双击点开桌面上的软件，打开背包窗口。</t>
-    </r>
-  </si>
-  <si>
-    <t>打开背包窗口</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>桌面上还有一个叫背包的软件，点开后看见了几个格子，其中一个格子里有一块压缩饼干。</t>
+      <t>点开底边栏的背包图标，打开背包窗口。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>打开背包窗口</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>桌面上还有一个叫背包的软件，点开后看见了几个格子。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>其中一个格子里有一块压缩饼干。</t>
     </r>
   </si>
   <si>
@@ -547,11 +741,18 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>双击背包窗口中的“压缩饼干”。打开详情窗口。</t>
-    </r>
-  </si>
-  <si>
-    <t>打开“压缩饼干”的详情窗口</t>
+      <t>点击背包窗口中的“压缩饼干”。打开详情窗口。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>打开“压缩饼干”的详情窗口</t>
+    </r>
   </si>
   <si>
     <r>
@@ -634,7 +835,14 @@
     </r>
   </si>
   <si>
-    <t>打开“状态窗口”</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>打开“状态窗口”</t>
+    </r>
   </si>
   <si>
     <r>
@@ -663,17 +871,17 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>还有几个我猜是表示水分、氧气、精神或者心情……还有一个是困倦度吗？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>你身上是绑了个生命体征检测仪吗？怎么有这么详细的状态显示？</t>
+      <t>还有几个我猜是表示水分、氧气、精神……还有一个是清醒度吗？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你身上是绑了个生命体征检测仪吗？</t>
     </r>
   </si>
   <si>
@@ -723,7 +931,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>现在最着急的是得像个办法把把渗水的裂缝堵住。</t>
+      <t>现在最着急的是得想个办法把渗水的裂缝堵住。</t>
     </r>
   </si>
   <si>
@@ -787,7 +995,14 @@
     </r>
   </si>
   <si>
-    <t>打开“研究窗口”</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>打开“研究窗口”</t>
+    </r>
   </si>
   <si>
     <r>
@@ -806,7 +1021,17 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>这些论文被人整理归类后像树状图一样排列，后面的一些文章看起来还挺复杂的，如果没看过前面的文章的话估计很难搞懂。</t>
+      <t>这些论文被人整理归类后像树状图一样排列。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>后面的一些文章看起来还挺复杂的，如果没看过前面的文章的话估计很难搞懂。</t>
     </r>
   </si>
   <si>
@@ -826,7 +1051,17 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>如果是眼下的情况是因为某种故障，我的电脑连上了安全联络员的系统，那桌面上的这些东西应该就是用来在救援飞船到达之前帮助受困人员活下去的软件。</t>
+      <t>如果是眼下的情况是因为某种故障，我的电脑连上了安全联络员的系统。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>那桌面上的这些东西应该就是用来在救援飞船到达之前帮助受困人员活下去的软件。</t>
     </r>
   </si>
   <si>
@@ -856,7 +1091,17 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>好像找到了，在比较前面的文章里，有一篇《极端环境下的行星飞船应急维修技术：基于有限资源的多样化修复方案》</t>
+      <t>好像找到了，在比较前面的文章里，有一篇……</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>《极端环境下的行星飞船应急维修技术：基于有限资源的多样化修复方案》</t>
     </r>
   </si>
   <si>
@@ -886,11 +1131,18 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>点击“修理”这项科技，然后点击“研究”。</t>
-    </r>
-  </si>
-  <si>
-    <t>研究“修理”这项科技</t>
+      <t>在“研究”窗口中，打开“装备”子菜单，找到“修理”这些科技，并点击左下角的“开始研究”</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>研究“修理”这项科技</t>
+    </r>
   </si>
   <si>
     <r>
@@ -999,27 +1251,57 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>就是赶快把飞船的裂缝堵起来，然后去维生舱找哈特。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>哈特？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>哦，我还没跟你提过。哈特是我的妹妹，同时也是这所飞船的驾驶员。</t>
+      <t>就是赶快把飞船的裂缝堵起来。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>然后去维生舱找哈特。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>哈特是谁？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>哦，我还没跟你提过。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>哈特是我的妹妹。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>同时她也是这所飞船的驾驶员。</t>
     </r>
   </si>
   <si>
@@ -1063,7 +1345,14 @@
     </r>
   </si>
   <si>
-    <t>打开地点窗口</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>打开地点窗口</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1116,7 +1405,14 @@
     </r>
   </si>
   <si>
-    <t>点击探索按钮</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点击探索按钮</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1145,14 +1441,21 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>教程结束了，记得指挥麦麦工作，不然她只会发呆。</t>
+      <t>教程结束了，记得指挥麦麦工作，不然她只会发呆。（在你没进行操作时，游戏时间是静止的）</t>
     </r>
   </si>
   <si>
     <t>修理研究完毕</t>
   </si>
   <si>
-    <t>“修理”研究完毕</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>“修理”研究完毕</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1258,9 +1561,6 @@
     </r>
   </si>
   <si>
-    <t>身上有“废金属”</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -1301,7 +1601,14 @@
     </r>
   </si>
   <si>
-    <t>制作“裂缝填充物”</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>制作“裂缝填充物”</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1340,7 +1647,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>以前刮大风的时候，家里的屋顶不是被吹走，就是被东西砸破。然后雨就哗啦啦地淋进来。</t>
+      <t>以前刮大风的时候，家里的屋顶不是被吹走就是被东西砸破。然后雨就哗啦啦地淋进来。</t>
     </r>
   </si>
   <si>
@@ -1430,14 +1737,31 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>接下来就看我的把，我保证把裂缝堵得严严实实的。</t>
+      <t>接下来就看我的吧，我保证把裂缝堵得严严实实的。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点击“渗水裂缝”，打开其详情窗口，然后点击堵住，就能堵住裂缝了</t>
     </r>
   </si>
   <si>
     <t>死亡</t>
   </si>
   <si>
-    <t>健康&lt;=0</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>健康&lt;=0</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1526,6 +1850,16 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
+      <t>其他_死亡</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>醒醒，再坚持一下，会有希望的。</t>
     </r>
   </si>
@@ -1540,18 +1874,330 @@
     </r>
   </si>
   <si>
-    <t>其他_死亡</t>
+    <t>第一次点开气密舱门</t>
+  </si>
+  <si>
+    <t>首次点开“气密舱门”</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我找到出舱的门了</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>外面应该是一片水域环境，不知道水有多深。</t>
+    </r>
+  </si>
+  <si>
+    <t>未装备“氧气面罩”</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最好是戴上氧气面罩再出去探索比较好。</t>
+    </r>
+  </si>
+  <si>
+    <t>已装备“氧气面罩”</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>虽然已经戴上氧气面罩了，但心里还是有些害怕。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>可是飞船里的资源总是会耗尽的，就算再害怕，也还是得出去看看。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>小心一点，不要太勉强。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>说不定开门就捡到一架完整的宇宙飞船，然后你就能直接开船回去了呢。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>嗯，好的。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>那还是有点夸张。不过，借你吉言啦。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>话说，你那边应该能看见我的身体状态吧。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>如果氧气快不够了，你一定要早点提醒我往回走。</t>
+    </r>
+  </si>
+  <si>
+    <t>第一次进珊瑚礁海域</t>
+  </si>
+  <si>
+    <t>第一次进入珊瑚礁海域</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>唔，唔嗯嗯唔唔嗯呢。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>呜呜嗯嗯？呢唔唔呜呜唔唔唔，嗯嗯喔喔额额。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你悠着点，别呛水了。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你在干嘛？你不是能用脑电交流吗？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>哦哦。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我忘记了。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>下意识地就想直接讲话，但是又讲不出来。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>没带氧气面罩就潜水真的太难受了</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这个氧气面罩挺好使的。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我感觉眼睛很痛。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>话说这颗星球的水里会不会有什么有害物质呀？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>要不还是先回飞船，等做出氧气面罩了，再出来探索？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不戴氧气面罩探索水域环境时需要消耗更多时间，且每次探索都会减少健康</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>一滴水都没漏进来。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>接下来我们该探索一下飞船外的这片区域了。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最好能找到些吃的，以及淡水的来源。</t>
+    </r>
+  </si>
+  <si>
+    <t>困了_01</t>
+  </si>
+  <si>
+    <t>每次清醒度&lt;=30</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>呼，感觉眼睛都睁不开了。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>要不考虑先回去休息一下？</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -2174,8 +2820,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2717,11 +3366,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I108"/>
+  <dimension ref="A1:I131"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="4" width="18"/>
-    <col min="5" max="5" width="18.0277777777778" customWidth="1"/>
+    <col min="5" max="5" width="27"/>
     <col min="6" max="6" width="49"/>
     <col min="7" max="7" width="11"/>
     <col min="8" max="8" width="15"/>
@@ -2758,19 +3407,19 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2">
+      <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="G2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
+      <c r="E2" s="3"/>
+      <c r="G2" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
@@ -2782,15 +3431,16 @@
       <c r="D3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
@@ -2802,15 +3452,16 @@
       <c r="D4" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>3</v>
       </c>
+      <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5">
+      <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
@@ -2822,2118 +3473,2676 @@
       <c r="D5" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6">
+      <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D6" t="s">
+      <c r="G6" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G7" s="1">
+        <v>6</v>
+      </c>
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
         <v>17</v>
       </c>
-      <c r="G6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="1">
+        <v>8</v>
+      </c>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="1">
+        <v>8</v>
+      </c>
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="1">
+        <v>9</v>
+      </c>
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="1">
+        <v>10</v>
+      </c>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="1">
+        <v>12</v>
+      </c>
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" s="1">
+        <v>13</v>
+      </c>
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="1">
+        <v>14</v>
+      </c>
+      <c r="H15" s="1"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="1">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G16" s="1">
         <v>15</v>
       </c>
-      <c r="D7" t="s">
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="1">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" s="1">
         <v>16</v>
       </c>
-      <c r="F7" s="2" t="s">
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="1">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" t="s">
         <v>18</v>
       </c>
-      <c r="G7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="F18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G18" s="1">
+        <v>17</v>
+      </c>
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="1">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G19" s="1">
+        <v>18</v>
+      </c>
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="1">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G20" s="1">
         <v>19</v>
       </c>
-      <c r="G8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="1">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="1">
         <v>20</v>
       </c>
-      <c r="G9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="2" t="s">
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="1">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G22" s="1">
         <v>21</v>
       </c>
-      <c r="G10">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="1">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G23" s="1">
         <v>22</v>
       </c>
-      <c r="G11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="2" t="s">
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="1">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G24" s="1">
         <v>23</v>
       </c>
-      <c r="G12">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="2" t="s">
+      <c r="H24" s="1"/>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="1">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G25" s="1">
+        <v>27</v>
+      </c>
+      <c r="H25" s="1"/>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="G13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="B26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G26" s="1">
         <v>25</v>
       </c>
-      <c r="G14">
-        <v>13</v>
-      </c>
-      <c r="I14" s="1"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="H26" s="1"/>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="1">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G27" s="1">
         <v>26</v>
       </c>
-      <c r="G15">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="H27" s="1"/>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="1">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G28" s="1">
         <v>27</v>
       </c>
-      <c r="G16">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" t="s">
-        <v>16</v>
-      </c>
-      <c r="F17" s="2" t="s">
+      <c r="H28" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="1">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G29" s="1">
         <v>28</v>
       </c>
-      <c r="G17">
+      <c r="H29" s="1"/>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="1">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G30" s="1">
+        <v>29</v>
+      </c>
+      <c r="H30" s="1"/>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="1">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>16</v>
-      </c>
-      <c r="B18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" t="s">
-        <v>16</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G18">
+      <c r="D31" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G31" s="1">
+        <v>30</v>
+      </c>
+      <c r="H31" s="1"/>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="1">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G32" s="1">
+        <v>31</v>
+      </c>
+      <c r="H32" s="1"/>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="1">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G33" s="1">
+        <v>32</v>
+      </c>
+      <c r="H33" s="1"/>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="1">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G34" s="1">
+        <v>33</v>
+      </c>
+      <c r="H34" s="1"/>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="1">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G35" s="1">
+        <v>34</v>
+      </c>
+      <c r="H35" s="1"/>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="1">
+        <v>34</v>
+      </c>
+      <c r="B36" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G36" s="1">
+        <v>35</v>
+      </c>
+      <c r="H36" s="1"/>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="1">
+        <v>35</v>
+      </c>
+      <c r="B37" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
+      <c r="D37" t="s">
+        <v>18</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G37" s="1">
+        <v>36</v>
+      </c>
+      <c r="H37" s="1"/>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="1">
+        <v>36</v>
+      </c>
+      <c r="B38" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" t="s">
         <v>17</v>
       </c>
-      <c r="B19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G19">
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G38" s="1">
+        <v>39</v>
+      </c>
+      <c r="H38" s="1"/>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="1">
+        <v>37</v>
+      </c>
+      <c r="B39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G39" s="1">
+        <v>38</v>
+      </c>
+      <c r="H39" s="1"/>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="1">
+        <v>38</v>
+      </c>
+      <c r="B40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G40" s="1">
+        <v>39</v>
+      </c>
+      <c r="H40" s="1"/>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="1">
+        <v>39</v>
+      </c>
+      <c r="B41" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" t="s">
+        <v>17</v>
+      </c>
+      <c r="D41" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G41" s="1">
+        <v>40</v>
+      </c>
+      <c r="H41" s="1"/>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="1">
+        <v>40</v>
+      </c>
+      <c r="B42" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" t="s">
+        <v>17</v>
+      </c>
+      <c r="D42" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G42" s="1">
+        <v>41</v>
+      </c>
+      <c r="H42" s="1"/>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="1">
+        <v>41</v>
+      </c>
+      <c r="B43" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" t="s">
+        <v>17</v>
+      </c>
+      <c r="D43" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G43" s="1">
+        <v>42</v>
+      </c>
+      <c r="H43" s="1"/>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="1">
+        <v>42</v>
+      </c>
+      <c r="B44" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G44" s="1">
+        <v>43</v>
+      </c>
+      <c r="H44" s="1"/>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="1">
+        <v>43</v>
+      </c>
+      <c r="B45" t="s">
+        <v>9</v>
+      </c>
+      <c r="C45" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G45" s="1">
+        <v>44</v>
+      </c>
+      <c r="H45" s="1"/>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="1">
+        <v>44</v>
+      </c>
+      <c r="B46" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" t="s">
+        <v>57</v>
+      </c>
+      <c r="D46" t="s">
+        <v>58</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G46" s="1">
+        <v>45</v>
+      </c>
+      <c r="H46" s="1"/>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="1">
+        <v>45</v>
+      </c>
+      <c r="B47" t="s">
+        <v>9</v>
+      </c>
+      <c r="C47" t="s">
+        <v>17</v>
+      </c>
+      <c r="D47" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G47" s="1">
+        <v>46</v>
+      </c>
+      <c r="H47" s="1"/>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="1">
+        <v>46</v>
+      </c>
+      <c r="B48" t="s">
+        <v>9</v>
+      </c>
+      <c r="C48" t="s">
+        <v>17</v>
+      </c>
+      <c r="D48" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G48" s="1">
+        <v>47</v>
+      </c>
+      <c r="H48" s="1"/>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="1">
+        <v>47</v>
+      </c>
+      <c r="B49" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49" t="s">
+        <v>17</v>
+      </c>
+      <c r="D49" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G49" s="1">
+        <v>48</v>
+      </c>
+      <c r="H49" s="1"/>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="1">
+        <v>48</v>
+      </c>
+      <c r="B50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50" t="s">
+        <v>17</v>
+      </c>
+      <c r="D50" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G50" s="1">
+        <v>49</v>
+      </c>
+      <c r="H50" s="1"/>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="1">
+        <v>49</v>
+      </c>
+      <c r="B51" t="s">
+        <v>9</v>
+      </c>
+      <c r="C51" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G51" s="1">
+        <v>50</v>
+      </c>
+      <c r="H51" s="1"/>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="1">
+        <v>50</v>
+      </c>
+      <c r="B52" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" t="s">
+        <v>11</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G52" s="1">
+        <v>51</v>
+      </c>
+      <c r="H52" s="1"/>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="1">
+        <v>51</v>
+      </c>
+      <c r="B53" t="s">
+        <v>9</v>
+      </c>
+      <c r="C53" t="s">
+        <v>17</v>
+      </c>
+      <c r="D53" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20">
+      <c r="F53" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G53" s="1">
+        <v>52</v>
+      </c>
+      <c r="H53" s="1"/>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="1">
+        <v>52</v>
+      </c>
+      <c r="B54" t="s">
+        <v>9</v>
+      </c>
+      <c r="C54" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" t="s">
+        <v>11</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G54" s="1">
+        <v>53</v>
+      </c>
+      <c r="H54" s="1"/>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="1">
+        <v>53</v>
+      </c>
+      <c r="B55" t="s">
+        <v>9</v>
+      </c>
+      <c r="C55" t="s">
+        <v>10</v>
+      </c>
+      <c r="D55" t="s">
+        <v>11</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G55" s="1">
+        <v>54</v>
+      </c>
+      <c r="H55" s="1"/>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="1">
+        <v>54</v>
+      </c>
+      <c r="B56" t="s">
+        <v>9</v>
+      </c>
+      <c r="C56" t="s">
+        <v>17</v>
+      </c>
+      <c r="D56" t="s">
         <v>18</v>
       </c>
-      <c r="B20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G20">
-        <v>19</v>
-      </c>
-      <c r="H20">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21">
-        <v>19</v>
-      </c>
-      <c r="B21" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G21">
-        <v>20</v>
-      </c>
-      <c r="I21" s="2"/>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20</v>
-      </c>
-      <c r="B22" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" t="s">
-        <v>16</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G22">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21</v>
-      </c>
-      <c r="B23" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G23">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>22</v>
-      </c>
-      <c r="B24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G24">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>23</v>
-      </c>
-      <c r="B25" t="s">
-        <v>9</v>
-      </c>
-      <c r="C25" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G25">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>24</v>
-      </c>
-      <c r="B26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" t="s">
-        <v>15</v>
-      </c>
-      <c r="D26" t="s">
-        <v>16</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G26">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>25</v>
-      </c>
-      <c r="B27" t="s">
-        <v>9</v>
-      </c>
-      <c r="C27" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G27">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>26</v>
-      </c>
-      <c r="B28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C28" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G28">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>27</v>
-      </c>
-      <c r="B29" t="s">
-        <v>9</v>
-      </c>
-      <c r="C29" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G29">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>28</v>
-      </c>
-      <c r="B30" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G30">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>29</v>
-      </c>
-      <c r="B31" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G31">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32">
-        <v>30</v>
-      </c>
-      <c r="B32" t="s">
-        <v>9</v>
-      </c>
-      <c r="C32" t="s">
-        <v>43</v>
-      </c>
-      <c r="D32" t="s">
-        <v>44</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G32">
-        <v>31</v>
-      </c>
-      <c r="I32" s="2"/>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>31</v>
-      </c>
-      <c r="B33" t="s">
-        <v>9</v>
-      </c>
-      <c r="C33" t="s">
-        <v>15</v>
-      </c>
-      <c r="D33" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G33">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>32</v>
-      </c>
-      <c r="B34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" t="s">
-        <v>15</v>
-      </c>
-      <c r="D34" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G34">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>33</v>
-      </c>
-      <c r="B35" t="s">
-        <v>9</v>
-      </c>
-      <c r="C35" t="s">
-        <v>10</v>
-      </c>
-      <c r="D35" t="s">
-        <v>11</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G35">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>34</v>
-      </c>
-      <c r="B36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" t="s">
-        <v>15</v>
-      </c>
-      <c r="D36" t="s">
-        <v>16</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G36">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>35</v>
-      </c>
-      <c r="B37" t="s">
-        <v>9</v>
-      </c>
-      <c r="C37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G37">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>36</v>
-      </c>
-      <c r="B38" t="s">
-        <v>9</v>
-      </c>
-      <c r="C38" t="s">
-        <v>15</v>
-      </c>
-      <c r="D38" t="s">
-        <v>16</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G38">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>37</v>
-      </c>
-      <c r="B39" t="s">
-        <v>9</v>
-      </c>
-      <c r="C39" t="s">
-        <v>15</v>
-      </c>
-      <c r="D39" t="s">
-        <v>16</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G39">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>38</v>
-      </c>
-      <c r="B40" t="s">
-        <v>9</v>
-      </c>
-      <c r="C40" t="s">
-        <v>10</v>
-      </c>
-      <c r="D40" t="s">
-        <v>11</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G40">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>39</v>
-      </c>
-      <c r="B41" t="s">
-        <v>9</v>
-      </c>
-      <c r="C41" t="s">
-        <v>10</v>
-      </c>
-      <c r="D41" t="s">
-        <v>11</v>
-      </c>
-      <c r="F41" s="2" t="s">
+      <c r="F56" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G56" s="1">
+        <v>56</v>
+      </c>
+      <c r="H56" s="1"/>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="1">
         <v>55</v>
       </c>
-      <c r="G41">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>40</v>
-      </c>
-      <c r="B42" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" t="s">
-        <v>10</v>
-      </c>
-      <c r="D42" t="s">
-        <v>11</v>
-      </c>
-      <c r="F42" s="2" t="s">
+      <c r="B57" t="s">
+        <v>9</v>
+      </c>
+      <c r="C57" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57" t="s">
+        <v>18</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G57" s="1">
         <v>56</v>
       </c>
-      <c r="G42">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>41</v>
-      </c>
-      <c r="B43" t="s">
-        <v>9</v>
-      </c>
-      <c r="C43" t="s">
-        <v>10</v>
-      </c>
-      <c r="D43" t="s">
-        <v>11</v>
-      </c>
-      <c r="F43" s="2" t="s">
+      <c r="H57" s="1"/>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="1">
+        <v>56</v>
+      </c>
+      <c r="B58" t="s">
+        <v>9</v>
+      </c>
+      <c r="C58" t="s">
+        <v>10</v>
+      </c>
+      <c r="D58" t="s">
+        <v>11</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G58" s="1">
         <v>57</v>
       </c>
-      <c r="G43">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44">
-        <v>42</v>
-      </c>
-      <c r="B44" t="s">
-        <v>9</v>
-      </c>
-      <c r="C44" t="s">
-        <v>43</v>
-      </c>
-      <c r="D44" t="s">
-        <v>44</v>
-      </c>
-      <c r="F44" s="2" t="s">
+      <c r="H58" s="1"/>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="1">
+        <v>57</v>
+      </c>
+      <c r="B59" t="s">
+        <v>9</v>
+      </c>
+      <c r="C59" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59" t="s">
+        <v>11</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G59" s="1">
         <v>58</v>
       </c>
-      <c r="G44">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45">
-        <v>43</v>
-      </c>
-      <c r="B45" t="s">
-        <v>9</v>
-      </c>
-      <c r="C45" t="s">
-        <v>15</v>
-      </c>
-      <c r="D45" t="s">
-        <v>16</v>
-      </c>
-      <c r="E45" s="1" t="s">
+      <c r="H59" s="1"/>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="1">
+        <v>58</v>
+      </c>
+      <c r="B60" t="s">
+        <v>9</v>
+      </c>
+      <c r="C60" t="s">
+        <v>57</v>
+      </c>
+      <c r="D60" t="s">
+        <v>58</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G60" s="1">
         <v>59</v>
       </c>
-      <c r="F45" s="2" t="s">
+      <c r="H60" s="1"/>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="1">
+        <v>59</v>
+      </c>
+      <c r="B61" t="s">
+        <v>9</v>
+      </c>
+      <c r="C61" t="s">
+        <v>17</v>
+      </c>
+      <c r="D61" t="s">
+        <v>18</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G61" s="1">
         <v>60</v>
       </c>
-      <c r="G45">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9">
-      <c r="A46">
-        <v>44</v>
-      </c>
-      <c r="B46" t="s">
-        <v>9</v>
-      </c>
-      <c r="C46" t="s">
-        <v>10</v>
-      </c>
-      <c r="D46" t="s">
-        <v>11</v>
-      </c>
-      <c r="F46" s="2" t="s">
+      <c r="H61" s="1"/>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="1">
+        <v>60</v>
+      </c>
+      <c r="B62" t="s">
+        <v>9</v>
+      </c>
+      <c r="C62" t="s">
+        <v>10</v>
+      </c>
+      <c r="D62" t="s">
+        <v>11</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G62" s="1">
         <v>61</v>
       </c>
-      <c r="G46">
-        <v>45</v>
-      </c>
-      <c r="H46">
-        <v>3000</v>
-      </c>
-      <c r="I46" s="2"/>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47">
-        <v>45</v>
-      </c>
-      <c r="B47" t="s">
-        <v>9</v>
-      </c>
-      <c r="C47" t="s">
-        <v>10</v>
-      </c>
-      <c r="D47" t="s">
-        <v>11</v>
-      </c>
-      <c r="F47" s="2" t="s">
+      <c r="H62" s="1"/>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="1">
+        <v>61</v>
+      </c>
+      <c r="B63" t="s">
+        <v>9</v>
+      </c>
+      <c r="C63" t="s">
+        <v>10</v>
+      </c>
+      <c r="D63" t="s">
+        <v>11</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G63" s="1">
         <v>62</v>
       </c>
-      <c r="G47">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48">
-        <v>46</v>
-      </c>
-      <c r="B48" t="s">
-        <v>9</v>
-      </c>
-      <c r="C48" t="s">
-        <v>10</v>
-      </c>
-      <c r="D48" t="s">
-        <v>11</v>
-      </c>
-      <c r="F48" s="2" t="s">
+      <c r="H63" s="1"/>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="1">
+        <v>62</v>
+      </c>
+      <c r="B64" t="s">
+        <v>9</v>
+      </c>
+      <c r="C64" t="s">
+        <v>10</v>
+      </c>
+      <c r="D64" t="s">
+        <v>11</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G64" s="1">
         <v>63</v>
       </c>
-      <c r="G48">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49">
-        <v>47</v>
-      </c>
-      <c r="B49" t="s">
-        <v>9</v>
-      </c>
-      <c r="C49" t="s">
-        <v>10</v>
-      </c>
-      <c r="D49" t="s">
-        <v>11</v>
-      </c>
-      <c r="F49" s="2" t="s">
+      <c r="H64" s="1"/>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="1">
+        <v>63</v>
+      </c>
+      <c r="B65" t="s">
+        <v>9</v>
+      </c>
+      <c r="C65" t="s">
+        <v>10</v>
+      </c>
+      <c r="D65" t="s">
+        <v>11</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G65" s="1">
         <v>64</v>
       </c>
-      <c r="G49">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50">
-        <v>48</v>
-      </c>
-      <c r="B50" t="s">
-        <v>9</v>
-      </c>
-      <c r="C50" t="s">
-        <v>43</v>
-      </c>
-      <c r="D50" t="s">
-        <v>44</v>
-      </c>
-      <c r="F50" s="2" t="s">
+      <c r="H65" s="1"/>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="1">
+        <v>64</v>
+      </c>
+      <c r="B66" t="s">
+        <v>9</v>
+      </c>
+      <c r="C66" t="s">
+        <v>10</v>
+      </c>
+      <c r="D66" t="s">
+        <v>11</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G66" s="1">
         <v>65</v>
       </c>
-      <c r="G50">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51">
-        <v>49</v>
-      </c>
-      <c r="B51" t="s">
-        <v>9</v>
-      </c>
-      <c r="C51" t="s">
-        <v>15</v>
-      </c>
-      <c r="D51" t="s">
-        <v>16</v>
-      </c>
-      <c r="E51" s="1" t="s">
+      <c r="H66" s="1"/>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="1">
+        <v>65</v>
+      </c>
+      <c r="B67" t="s">
+        <v>9</v>
+      </c>
+      <c r="C67" t="s">
+        <v>57</v>
+      </c>
+      <c r="D67" t="s">
+        <v>58</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G67" s="1">
         <v>66</v>
       </c>
-      <c r="F51" s="2" t="s">
+      <c r="H67" s="1"/>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="1">
+        <v>66</v>
+      </c>
+      <c r="B68" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68" t="s">
+        <v>17</v>
+      </c>
+      <c r="D68" t="s">
+        <v>18</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G68" s="1">
         <v>67</v>
       </c>
-      <c r="G51">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52">
-        <v>50</v>
-      </c>
-      <c r="B52" t="s">
-        <v>9</v>
-      </c>
-      <c r="C52" t="s">
-        <v>15</v>
-      </c>
-      <c r="D52" t="s">
-        <v>11</v>
-      </c>
-      <c r="F52" s="2" t="s">
+      <c r="H68" s="1"/>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="1">
+        <v>67</v>
+      </c>
+      <c r="B69" t="s">
+        <v>9</v>
+      </c>
+      <c r="C69" t="s">
+        <v>17</v>
+      </c>
+      <c r="D69" t="s">
+        <v>11</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G69" s="1">
         <v>68</v>
       </c>
-      <c r="G52">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53">
-        <v>51</v>
-      </c>
-      <c r="B53" t="s">
-        <v>9</v>
-      </c>
-      <c r="C53" t="s">
-        <v>15</v>
-      </c>
-      <c r="D53" t="s">
-        <v>11</v>
-      </c>
-      <c r="F53" s="2" t="s">
+      <c r="H69" s="1"/>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="1">
+        <v>68</v>
+      </c>
+      <c r="B70" t="s">
+        <v>9</v>
+      </c>
+      <c r="C70" t="s">
+        <v>17</v>
+      </c>
+      <c r="D70" t="s">
+        <v>11</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G70" s="1">
         <v>69</v>
       </c>
-      <c r="G53">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54">
-        <v>52</v>
-      </c>
-      <c r="B54" t="s">
-        <v>9</v>
-      </c>
-      <c r="C54" t="s">
-        <v>15</v>
-      </c>
-      <c r="D54" t="s">
-        <v>11</v>
-      </c>
-      <c r="F54" s="2" t="s">
+      <c r="H70" s="1"/>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="1">
+        <v>69</v>
+      </c>
+      <c r="B71" t="s">
+        <v>9</v>
+      </c>
+      <c r="C71" t="s">
+        <v>17</v>
+      </c>
+      <c r="D71" t="s">
+        <v>11</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G71" s="1">
         <v>70</v>
       </c>
-      <c r="G54">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55">
-        <v>53</v>
-      </c>
-      <c r="B55" t="s">
-        <v>9</v>
-      </c>
-      <c r="C55" t="s">
-        <v>15</v>
-      </c>
-      <c r="D55" t="s">
-        <v>11</v>
-      </c>
-      <c r="F55" s="2" t="s">
+      <c r="H71" s="1"/>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="1">
+        <v>70</v>
+      </c>
+      <c r="B72" t="s">
+        <v>9</v>
+      </c>
+      <c r="C72" t="s">
+        <v>17</v>
+      </c>
+      <c r="D72" t="s">
+        <v>11</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G72" s="1">
         <v>71</v>
       </c>
-      <c r="G55">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56">
-        <v>54</v>
-      </c>
-      <c r="B56" t="s">
-        <v>9</v>
-      </c>
-      <c r="C56" t="s">
-        <v>10</v>
-      </c>
-      <c r="D56" t="s">
-        <v>11</v>
-      </c>
-      <c r="F56" s="2" t="s">
+      <c r="H72" s="1"/>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="1">
+        <v>71</v>
+      </c>
+      <c r="B73" t="s">
+        <v>9</v>
+      </c>
+      <c r="C73" t="s">
+        <v>10</v>
+      </c>
+      <c r="D73" t="s">
+        <v>11</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G73" s="1">
         <v>72</v>
       </c>
-      <c r="G56">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57">
-        <v>55</v>
-      </c>
-      <c r="B57" t="s">
-        <v>9</v>
-      </c>
-      <c r="C57" t="s">
-        <v>10</v>
-      </c>
-      <c r="D57" t="s">
-        <v>11</v>
-      </c>
-      <c r="F57" s="2" t="s">
+      <c r="H73" s="1"/>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="1">
+        <v>72</v>
+      </c>
+      <c r="B74" t="s">
+        <v>9</v>
+      </c>
+      <c r="C74" t="s">
+        <v>10</v>
+      </c>
+      <c r="D74" t="s">
+        <v>11</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G74" s="1">
         <v>73</v>
       </c>
-      <c r="G57">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58">
-        <v>56</v>
-      </c>
-      <c r="B58" t="s">
-        <v>9</v>
-      </c>
-      <c r="C58" t="s">
-        <v>43</v>
-      </c>
-      <c r="D58" t="s">
-        <v>44</v>
-      </c>
-      <c r="F58" s="2" t="s">
+      <c r="H74" s="1"/>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="1">
+        <v>73</v>
+      </c>
+      <c r="B75" t="s">
+        <v>9</v>
+      </c>
+      <c r="C75" t="s">
+        <v>57</v>
+      </c>
+      <c r="D75" t="s">
+        <v>58</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G75" s="1">
         <v>74</v>
       </c>
-      <c r="G58">
+      <c r="H75" s="1"/>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="1">
+        <v>74</v>
+      </c>
+      <c r="B76" t="s">
+        <v>9</v>
+      </c>
+      <c r="C76" t="s">
+        <v>17</v>
+      </c>
+      <c r="D76" t="s">
+        <v>18</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G76" s="1">
+        <v>75</v>
+      </c>
+      <c r="H76" s="1"/>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="1">
+        <v>75</v>
+      </c>
+      <c r="B77" t="s">
+        <v>9</v>
+      </c>
+      <c r="C77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D77" t="s">
+        <v>11</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G77" s="1">
+        <v>76</v>
+      </c>
+      <c r="H77" s="1"/>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="1">
+        <v>76</v>
+      </c>
+      <c r="B78" t="s">
+        <v>9</v>
+      </c>
+      <c r="C78" t="s">
+        <v>17</v>
+      </c>
+      <c r="D78" t="s">
+        <v>11</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G78" s="1">
+        <v>77</v>
+      </c>
+      <c r="H78" s="1"/>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" s="1">
+        <v>77</v>
+      </c>
+      <c r="B79" t="s">
+        <v>9</v>
+      </c>
+      <c r="C79" t="s">
+        <v>17</v>
+      </c>
+      <c r="D79" t="s">
+        <v>11</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G79" s="1">
+        <v>78</v>
+      </c>
+      <c r="H79" s="1"/>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" s="1">
+        <v>78</v>
+      </c>
+      <c r="B80" t="s">
+        <v>9</v>
+      </c>
+      <c r="C80" t="s">
+        <v>10</v>
+      </c>
+      <c r="D80" t="s">
+        <v>11</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G80" s="1">
+        <v>79</v>
+      </c>
+      <c r="H80" s="1"/>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" s="1">
+        <v>79</v>
+      </c>
+      <c r="B81" t="s">
+        <v>9</v>
+      </c>
+      <c r="C81" t="s">
+        <v>10</v>
+      </c>
+      <c r="D81" t="s">
+        <v>11</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G81" s="1">
+        <v>80</v>
+      </c>
+      <c r="H81" s="1"/>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" s="1">
+        <v>80</v>
+      </c>
+      <c r="B82" t="s">
+        <v>9</v>
+      </c>
+      <c r="C82" t="s">
+        <v>10</v>
+      </c>
+      <c r="D82" t="s">
+        <v>11</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G82" s="1">
+        <v>81</v>
+      </c>
+      <c r="H82" s="1"/>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" s="1">
+        <v>81</v>
+      </c>
+      <c r="B83" t="s">
+        <v>9</v>
+      </c>
+      <c r="C83" t="s">
+        <v>10</v>
+      </c>
+      <c r="D83" t="s">
+        <v>11</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G83" s="1">
+        <v>82</v>
+      </c>
+      <c r="H83" s="1"/>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" s="1">
+        <v>82</v>
+      </c>
+      <c r="B84" t="s">
+        <v>9</v>
+      </c>
+      <c r="C84" t="s">
+        <v>10</v>
+      </c>
+      <c r="D84" t="s">
+        <v>11</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G84" s="1">
+        <v>83</v>
+      </c>
+      <c r="H84" s="1"/>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" s="1">
+        <v>83</v>
+      </c>
+      <c r="B85" t="s">
+        <v>9</v>
+      </c>
+      <c r="C85" t="s">
+        <v>10</v>
+      </c>
+      <c r="D85" t="s">
+        <v>11</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G85" s="1">
+        <v>84</v>
+      </c>
+      <c r="H85" s="1"/>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" s="1">
+        <v>84</v>
+      </c>
+      <c r="B86" t="s">
+        <v>9</v>
+      </c>
+      <c r="C86" t="s">
+        <v>10</v>
+      </c>
+      <c r="D86" t="s">
+        <v>11</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G86" s="1">
+        <v>85</v>
+      </c>
+      <c r="H86" s="1"/>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" s="1">
+        <v>85</v>
+      </c>
+      <c r="B87" t="s">
+        <v>9</v>
+      </c>
+      <c r="C87" t="s">
+        <v>10</v>
+      </c>
+      <c r="D87" t="s">
+        <v>11</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G87" s="1">
+        <v>86</v>
+      </c>
+      <c r="H87" s="1"/>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" s="1">
+        <v>86</v>
+      </c>
+      <c r="B88" t="s">
+        <v>9</v>
+      </c>
+      <c r="C88" t="s">
+        <v>10</v>
+      </c>
+      <c r="D88" t="s">
+        <v>11</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G88" s="1">
+        <v>87</v>
+      </c>
+      <c r="H88" s="1"/>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" s="1">
+        <v>87</v>
+      </c>
+      <c r="B89" t="s">
+        <v>9</v>
+      </c>
+      <c r="C89" t="s">
+        <v>10</v>
+      </c>
+      <c r="D89" t="s">
+        <v>11</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G89" s="1">
+        <v>88</v>
+      </c>
+      <c r="H89" s="1"/>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" s="1">
+        <v>88</v>
+      </c>
+      <c r="B90" t="s">
+        <v>9</v>
+      </c>
+      <c r="C90" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59">
+      <c r="D90" t="s">
+        <v>58</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G90" s="1">
+        <v>90</v>
+      </c>
+      <c r="H90" s="1"/>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" s="1">
+        <v>89</v>
+      </c>
+      <c r="B91" t="s">
+        <v>9</v>
+      </c>
+      <c r="C91" t="s">
+        <v>17</v>
+      </c>
+      <c r="D91" t="s">
+        <v>18</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G91" s="1">
+        <v>90</v>
+      </c>
+      <c r="H91" s="1"/>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" s="1">
+        <v>90</v>
+      </c>
+      <c r="B92" t="s">
+        <v>9</v>
+      </c>
+      <c r="C92" t="s">
+        <v>17</v>
+      </c>
+      <c r="D92" t="s">
+        <v>11</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G92" s="1">
+        <v>91</v>
+      </c>
+      <c r="H92" s="1"/>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" s="1">
+        <v>91</v>
+      </c>
+      <c r="B93" t="s">
+        <v>9</v>
+      </c>
+      <c r="C93" t="s">
+        <v>17</v>
+      </c>
+      <c r="D93" t="s">
+        <v>11</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G93" s="1">
+        <v>92</v>
+      </c>
+      <c r="H93" s="1"/>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" s="1">
+        <v>92</v>
+      </c>
+      <c r="B94" t="s">
+        <v>9</v>
+      </c>
+      <c r="C94" t="s">
+        <v>17</v>
+      </c>
+      <c r="D94" t="s">
+        <v>11</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G94" s="1">
+        <v>93</v>
+      </c>
+      <c r="H94" s="1"/>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" s="1">
+        <v>93</v>
+      </c>
+      <c r="B95" t="s">
+        <v>9</v>
+      </c>
+      <c r="C95" t="s">
+        <v>17</v>
+      </c>
+      <c r="D95" t="s">
+        <v>11</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G95" s="1">
+        <v>94</v>
+      </c>
+      <c r="H95" s="1"/>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" s="1">
+        <v>94</v>
+      </c>
+      <c r="B96" t="s">
+        <v>9</v>
+      </c>
+      <c r="C96" t="s">
+        <v>17</v>
+      </c>
+      <c r="D96" t="s">
+        <v>11</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G96" s="1">
+        <v>95</v>
+      </c>
+      <c r="H96" s="1"/>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" s="1">
+        <v>95</v>
+      </c>
+      <c r="B97" t="s">
+        <v>9</v>
+      </c>
+      <c r="C97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D97" t="s">
+        <v>11</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G97" s="1">
+        <v>96</v>
+      </c>
+      <c r="H97" s="1"/>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" s="1">
+        <v>96</v>
+      </c>
+      <c r="B98" t="s">
+        <v>9</v>
+      </c>
+      <c r="C98" t="s">
+        <v>17</v>
+      </c>
+      <c r="D98" t="s">
+        <v>18</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G98" s="1">
+        <v>97</v>
+      </c>
+      <c r="H98" s="1"/>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" s="1">
+        <v>97</v>
+      </c>
+      <c r="B99" t="s">
+        <v>9</v>
+      </c>
+      <c r="C99" t="s">
+        <v>17</v>
+      </c>
+      <c r="D99" t="s">
+        <v>11</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G99" s="1">
+        <v>98</v>
+      </c>
+      <c r="H99" s="1"/>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" s="1">
+        <v>98</v>
+      </c>
+      <c r="B100" t="s">
+        <v>9</v>
+      </c>
+      <c r="C100" t="s">
+        <v>17</v>
+      </c>
+      <c r="D100" t="s">
+        <v>11</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G100" s="1">
+        <v>99</v>
+      </c>
+      <c r="H100" s="1"/>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" s="1">
+        <v>99</v>
+      </c>
+      <c r="B101" t="s">
+        <v>9</v>
+      </c>
+      <c r="C101" t="s">
+        <v>10</v>
+      </c>
+      <c r="D101" t="s">
+        <v>11</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G101" s="1">
+        <v>100</v>
+      </c>
+      <c r="H101" s="1"/>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" s="1">
+        <v>100</v>
+      </c>
+      <c r="B102" t="s">
+        <v>9</v>
+      </c>
+      <c r="C102" t="s">
+        <v>10</v>
+      </c>
+      <c r="D102" t="s">
+        <v>11</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G102" s="1">
+        <v>101</v>
+      </c>
+      <c r="H102" s="1"/>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" s="1">
+        <v>101</v>
+      </c>
+      <c r="B103" t="s">
+        <v>9</v>
+      </c>
+      <c r="C103" t="s">
         <v>57</v>
       </c>
-      <c r="B59" t="s">
-        <v>9</v>
-      </c>
-      <c r="C59" t="s">
-        <v>15</v>
-      </c>
-      <c r="D59" t="s">
-        <v>16</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G59">
+      <c r="D103" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60">
+      <c r="F103" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G103" s="1">
+        <v>102</v>
+      </c>
+      <c r="H103" s="1"/>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" s="1">
+        <v>102</v>
+      </c>
+      <c r="B104" t="s">
+        <v>9</v>
+      </c>
+      <c r="C104" t="s">
+        <v>17</v>
+      </c>
+      <c r="D104" t="s">
+        <v>18</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G104" s="1">
+        <v>103</v>
+      </c>
+      <c r="H104" s="1"/>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" s="1">
+        <v>103</v>
+      </c>
+      <c r="B105" t="s">
+        <v>9</v>
+      </c>
+      <c r="C105" t="s">
+        <v>17</v>
+      </c>
+      <c r="D105" t="s">
+        <v>11</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G105" s="1">
+        <v>104</v>
+      </c>
+      <c r="H105" s="1"/>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" s="1">
+        <v>104</v>
+      </c>
+      <c r="B106" t="s">
+        <v>9</v>
+      </c>
+      <c r="C106" t="s">
+        <v>17</v>
+      </c>
+      <c r="D106" t="s">
+        <v>11</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G106" s="1">
+        <v>105</v>
+      </c>
+      <c r="H106" s="1"/>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" s="1">
+        <v>105</v>
+      </c>
+      <c r="B107" t="s">
+        <v>9</v>
+      </c>
+      <c r="C107" t="s">
+        <v>17</v>
+      </c>
+      <c r="D107" t="s">
+        <v>11</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G107" s="1">
+        <v>106</v>
+      </c>
+      <c r="H107" s="1"/>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" s="1">
+        <v>106</v>
+      </c>
+      <c r="B108" t="s">
+        <v>9</v>
+      </c>
+      <c r="C108" t="s">
+        <v>17</v>
+      </c>
+      <c r="D108" t="s">
+        <v>11</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G108" s="1">
+        <v>107</v>
+      </c>
+      <c r="H108" s="1"/>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109" s="1">
+        <v>107</v>
+      </c>
+      <c r="B109" t="s">
+        <v>9</v>
+      </c>
+      <c r="C109" t="s">
+        <v>10</v>
+      </c>
+      <c r="D109" t="s">
+        <v>11</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G109" s="1">
+        <v>108</v>
+      </c>
+      <c r="H109" s="1"/>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110" s="1">
+        <v>108</v>
+      </c>
+      <c r="B110" t="s">
+        <v>9</v>
+      </c>
+      <c r="C110" t="s">
+        <v>17</v>
+      </c>
+      <c r="D110" t="s">
+        <v>18</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G110" s="1">
+        <v>110</v>
+      </c>
+      <c r="H110" s="1"/>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111" s="1">
+        <v>109</v>
+      </c>
+      <c r="B111" t="s">
+        <v>9</v>
+      </c>
+      <c r="C111" t="s">
+        <v>17</v>
+      </c>
+      <c r="D111" t="s">
+        <v>18</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G111" s="1">
+        <v>110</v>
+      </c>
+      <c r="H111" s="1"/>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112" s="1">
+        <v>110</v>
+      </c>
+      <c r="B112" t="s">
+        <v>9</v>
+      </c>
+      <c r="C112" t="s">
+        <v>10</v>
+      </c>
+      <c r="D112" t="s">
+        <v>11</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G112" s="1">
+        <v>111</v>
+      </c>
+      <c r="H112" s="1"/>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113" s="1">
+        <v>111</v>
+      </c>
+      <c r="B113" t="s">
+        <v>9</v>
+      </c>
+      <c r="C113" t="s">
+        <v>10</v>
+      </c>
+      <c r="D113" t="s">
+        <v>11</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G113" s="1">
+        <v>112</v>
+      </c>
+      <c r="H113" s="1"/>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114" s="1">
+        <v>112</v>
+      </c>
+      <c r="B114" t="s">
+        <v>9</v>
+      </c>
+      <c r="C114" t="s">
+        <v>10</v>
+      </c>
+      <c r="D114" t="s">
+        <v>11</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G114" s="1">
+        <v>113</v>
+      </c>
+      <c r="H114" s="1"/>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" s="1">
+        <v>113</v>
+      </c>
+      <c r="B115" t="s">
+        <v>9</v>
+      </c>
+      <c r="C115" t="s">
+        <v>10</v>
+      </c>
+      <c r="D115" t="s">
+        <v>11</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="G115" s="1">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116" s="1">
+        <v>114</v>
+      </c>
+      <c r="B116" t="s">
+        <v>9</v>
+      </c>
+      <c r="C116" t="s">
+        <v>17</v>
+      </c>
+      <c r="D116" t="s">
+        <v>18</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G116" s="1">
+        <v>115</v>
+      </c>
+      <c r="H116" s="1"/>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117" s="1">
+        <v>115</v>
+      </c>
+      <c r="B117" t="s">
+        <v>9</v>
+      </c>
+      <c r="C117" t="s">
+        <v>10</v>
+      </c>
+      <c r="D117" t="s">
+        <v>11</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G117" s="1">
+        <v>116</v>
+      </c>
+      <c r="H117" s="1"/>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118" s="1">
+        <v>116</v>
+      </c>
+      <c r="B118" t="s">
+        <v>9</v>
+      </c>
+      <c r="C118" t="s">
+        <v>10</v>
+      </c>
+      <c r="D118" t="s">
+        <v>11</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G118" s="1">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119" s="1">
+        <v>117</v>
+      </c>
+      <c r="B119" t="s">
+        <v>9</v>
+      </c>
+      <c r="C119" t="s">
+        <v>10</v>
+      </c>
+      <c r="D119" t="s">
+        <v>11</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G119" s="1">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120" s="1">
+        <v>118</v>
+      </c>
+      <c r="B120" t="s">
+        <v>9</v>
+      </c>
+      <c r="C120" t="s">
+        <v>10</v>
+      </c>
+      <c r="D120" t="s">
+        <v>11</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G120" s="1">
+        <v>119</v>
+      </c>
+      <c r="H120" s="1"/>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121" s="1">
+        <v>119</v>
+      </c>
+      <c r="B121" t="s">
+        <v>9</v>
+      </c>
+      <c r="C121" t="s">
+        <v>10</v>
+      </c>
+      <c r="D121" t="s">
+        <v>11</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G121" s="1">
+        <v>120</v>
+      </c>
+      <c r="H121" s="1"/>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122" s="1">
+        <v>120</v>
+      </c>
+      <c r="B122" t="s">
+        <v>9</v>
+      </c>
+      <c r="C122" t="s">
+        <v>10</v>
+      </c>
+      <c r="D122" t="s">
+        <v>11</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G122" s="1">
+        <v>121</v>
+      </c>
+      <c r="H122" s="1"/>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123" s="1">
+        <v>121</v>
+      </c>
+      <c r="B123" t="s">
+        <v>9</v>
+      </c>
+      <c r="C123" t="s">
+        <v>57</v>
+      </c>
+      <c r="D123" t="s">
         <v>58</v>
       </c>
-      <c r="B60" t="s">
-        <v>9</v>
-      </c>
-      <c r="C60" t="s">
-        <v>15</v>
-      </c>
-      <c r="D60" t="s">
-        <v>11</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G60">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
-      <c r="A61">
-        <v>59</v>
-      </c>
-      <c r="B61" t="s">
-        <v>9</v>
-      </c>
-      <c r="C61" t="s">
-        <v>15</v>
-      </c>
-      <c r="D61" t="s">
-        <v>11</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G61">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
-      <c r="A62">
-        <v>60</v>
-      </c>
-      <c r="B62" t="s">
-        <v>9</v>
-      </c>
-      <c r="C62" t="s">
-        <v>15</v>
-      </c>
-      <c r="D62" t="s">
-        <v>11</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G62">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
-      <c r="A63">
-        <v>61</v>
-      </c>
-      <c r="B63" t="s">
-        <v>9</v>
-      </c>
-      <c r="C63" t="s">
-        <v>10</v>
-      </c>
-      <c r="D63" t="s">
-        <v>11</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="G63">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
-      <c r="A64">
-        <v>62</v>
-      </c>
-      <c r="B64" t="s">
-        <v>9</v>
-      </c>
-      <c r="C64" t="s">
-        <v>10</v>
-      </c>
-      <c r="D64" t="s">
-        <v>11</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G64">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
-      <c r="A65">
-        <v>63</v>
-      </c>
-      <c r="B65" t="s">
-        <v>9</v>
-      </c>
-      <c r="C65" t="s">
-        <v>10</v>
-      </c>
-      <c r="D65" t="s">
-        <v>11</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G65">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
-      <c r="A66">
-        <v>64</v>
-      </c>
-      <c r="B66" t="s">
-        <v>9</v>
-      </c>
-      <c r="C66" t="s">
-        <v>10</v>
-      </c>
-      <c r="D66" t="s">
-        <v>11</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G66">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7">
-      <c r="A67">
-        <v>65</v>
-      </c>
-      <c r="B67" t="s">
-        <v>9</v>
-      </c>
-      <c r="C67" t="s">
-        <v>10</v>
-      </c>
-      <c r="D67" t="s">
-        <v>11</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G67">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
-      <c r="A68">
-        <v>66</v>
-      </c>
-      <c r="B68" t="s">
-        <v>9</v>
-      </c>
-      <c r="C68" t="s">
-        <v>10</v>
-      </c>
-      <c r="D68" t="s">
-        <v>11</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="G68">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9">
-      <c r="A69">
-        <v>67</v>
-      </c>
-      <c r="B69" t="s">
-        <v>9</v>
-      </c>
-      <c r="C69" t="s">
-        <v>10</v>
-      </c>
-      <c r="D69" t="s">
-        <v>11</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G69">
-        <v>68</v>
-      </c>
-      <c r="H69">
-        <v>3000</v>
-      </c>
-      <c r="I69" s="2"/>
-    </row>
-    <row r="70" spans="1:7">
-      <c r="A70">
-        <v>68</v>
-      </c>
-      <c r="B70" t="s">
-        <v>9</v>
-      </c>
-      <c r="C70" t="s">
-        <v>10</v>
-      </c>
-      <c r="D70" t="s">
-        <v>11</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G70">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7">
-      <c r="A71">
-        <v>69</v>
-      </c>
-      <c r="B71" t="s">
-        <v>9</v>
-      </c>
-      <c r="C71" t="s">
-        <v>10</v>
-      </c>
-      <c r="D71" t="s">
-        <v>11</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G71">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7">
-      <c r="A72">
-        <v>70</v>
-      </c>
-      <c r="B72" t="s">
-        <v>9</v>
-      </c>
-      <c r="C72" t="s">
-        <v>10</v>
-      </c>
-      <c r="D72" t="s">
-        <v>11</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G72">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7">
-      <c r="A73">
-        <v>71</v>
-      </c>
-      <c r="B73" t="s">
-        <v>9</v>
-      </c>
-      <c r="C73" t="s">
-        <v>43</v>
-      </c>
-      <c r="D73" t="s">
-        <v>44</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G73">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7">
-      <c r="A74">
-        <v>72</v>
-      </c>
-      <c r="B74" t="s">
-        <v>9</v>
-      </c>
-      <c r="C74" t="s">
-        <v>15</v>
-      </c>
-      <c r="D74" t="s">
-        <v>16</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G74">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7">
-      <c r="A75">
-        <v>73</v>
-      </c>
-      <c r="B75" t="s">
-        <v>9</v>
-      </c>
-      <c r="C75" t="s">
-        <v>15</v>
-      </c>
-      <c r="D75" t="s">
-        <v>11</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G75">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7">
-      <c r="A76">
-        <v>74</v>
-      </c>
-      <c r="B76" t="s">
-        <v>9</v>
-      </c>
-      <c r="C76" t="s">
-        <v>15</v>
-      </c>
-      <c r="D76" t="s">
-        <v>11</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="G76">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7">
-      <c r="A77">
-        <v>75</v>
-      </c>
-      <c r="B77" t="s">
-        <v>9</v>
-      </c>
-      <c r="C77" t="s">
-        <v>15</v>
-      </c>
-      <c r="D77" t="s">
-        <v>11</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G77">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7">
-      <c r="A78">
-        <v>76</v>
-      </c>
-      <c r="B78" t="s">
-        <v>9</v>
-      </c>
-      <c r="C78" t="s">
-        <v>10</v>
-      </c>
-      <c r="D78" t="s">
-        <v>11</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="G78">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9">
-      <c r="A79">
-        <v>77</v>
-      </c>
-      <c r="B79" t="s">
-        <v>9</v>
-      </c>
-      <c r="C79" t="s">
-        <v>15</v>
-      </c>
-      <c r="D79" t="s">
-        <v>16</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="G79">
-        <v>78</v>
-      </c>
-      <c r="H79">
-        <v>3000</v>
-      </c>
-      <c r="I79" s="2"/>
-    </row>
-    <row r="80" spans="1:7">
-      <c r="A80">
-        <v>78</v>
-      </c>
-      <c r="B80" t="s">
-        <v>9</v>
-      </c>
-      <c r="C80" t="s">
-        <v>15</v>
-      </c>
-      <c r="D80" t="s">
-        <v>11</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="G80">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7">
-      <c r="A81">
-        <v>79</v>
-      </c>
-      <c r="B81" t="s">
-        <v>9</v>
-      </c>
-      <c r="C81" t="s">
-        <v>10</v>
-      </c>
-      <c r="D81" t="s">
-        <v>11</v>
-      </c>
-      <c r="F81" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="G81">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7">
-      <c r="A82">
-        <v>80</v>
-      </c>
-      <c r="B82" t="s">
-        <v>9</v>
-      </c>
-      <c r="C82" t="s">
-        <v>10</v>
-      </c>
-      <c r="D82" t="s">
-        <v>11</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G82">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7">
-      <c r="A83">
-        <v>81</v>
-      </c>
-      <c r="B83" t="s">
-        <v>9</v>
-      </c>
-      <c r="C83" t="s">
-        <v>43</v>
-      </c>
-      <c r="D83" t="s">
-        <v>44</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="G83">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9">
-      <c r="A84">
-        <v>82</v>
-      </c>
-      <c r="B84" t="s">
-        <v>9</v>
-      </c>
-      <c r="C84" t="s">
-        <v>15</v>
-      </c>
-      <c r="D84" t="s">
-        <v>16</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="G84">
-        <v>83</v>
-      </c>
-      <c r="H84">
-        <v>3000</v>
-      </c>
-      <c r="I84" s="2"/>
-    </row>
-    <row r="85" spans="1:7">
-      <c r="A85">
-        <v>83</v>
-      </c>
-      <c r="B85" t="s">
-        <v>9</v>
-      </c>
-      <c r="C85" t="s">
-        <v>15</v>
-      </c>
-      <c r="D85" t="s">
-        <v>11</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="G85">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7">
-      <c r="A86">
-        <v>84</v>
-      </c>
-      <c r="B86" t="s">
-        <v>9</v>
-      </c>
-      <c r="C86" t="s">
-        <v>15</v>
-      </c>
-      <c r="D86" t="s">
-        <v>11</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="G86">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7">
-      <c r="A87">
-        <v>85</v>
-      </c>
-      <c r="B87" t="s">
-        <v>9</v>
-      </c>
-      <c r="C87" t="s">
-        <v>15</v>
-      </c>
-      <c r="D87" t="s">
-        <v>11</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="G87">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7">
-      <c r="A88">
-        <v>86</v>
-      </c>
-      <c r="B88" t="s">
-        <v>9</v>
-      </c>
-      <c r="C88" t="s">
-        <v>15</v>
-      </c>
-      <c r="D88" t="s">
-        <v>11</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G88">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7">
-      <c r="A89">
-        <v>87</v>
-      </c>
-      <c r="B89" t="s">
-        <v>9</v>
-      </c>
-      <c r="C89" t="s">
-        <v>10</v>
-      </c>
-      <c r="D89" t="s">
-        <v>11</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G89">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7">
-      <c r="A90">
-        <v>88</v>
-      </c>
-      <c r="B90" t="s">
-        <v>9</v>
-      </c>
-      <c r="C90" t="s">
-        <v>15</v>
-      </c>
-      <c r="D90" t="s">
-        <v>16</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="G90">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7">
-      <c r="A91">
-        <v>89</v>
-      </c>
-      <c r="B91" t="s">
-        <v>9</v>
-      </c>
-      <c r="C91" t="s">
-        <v>15</v>
-      </c>
-      <c r="D91" t="s">
-        <v>16</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="G91">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7">
-      <c r="A92">
-        <v>90</v>
-      </c>
-      <c r="B92" t="s">
-        <v>9</v>
-      </c>
-      <c r="C92" t="s">
-        <v>10</v>
-      </c>
-      <c r="D92" t="s">
-        <v>11</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="G92">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7">
-      <c r="A93">
-        <v>91</v>
-      </c>
-      <c r="B93" t="s">
-        <v>9</v>
-      </c>
-      <c r="C93" t="s">
-        <v>10</v>
-      </c>
-      <c r="D93" t="s">
-        <v>11</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="G93">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7">
-      <c r="A94">
-        <v>92</v>
-      </c>
-      <c r="B94" t="s">
-        <v>9</v>
-      </c>
-      <c r="C94" t="s">
-        <v>10</v>
-      </c>
-      <c r="D94" t="s">
-        <v>11</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="G94">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7">
-      <c r="A95">
-        <v>93</v>
-      </c>
-      <c r="B95" t="s">
-        <v>9</v>
-      </c>
-      <c r="C95" t="s">
-        <v>15</v>
-      </c>
-      <c r="D95" t="s">
-        <v>16</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G95">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7">
-      <c r="A96">
-        <v>94</v>
-      </c>
-      <c r="B96" t="s">
-        <v>9</v>
-      </c>
-      <c r="C96" t="s">
-        <v>10</v>
-      </c>
-      <c r="D96" t="s">
-        <v>11</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="G96">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7">
-      <c r="A97">
-        <v>95</v>
-      </c>
-      <c r="B97" t="s">
-        <v>9</v>
-      </c>
-      <c r="C97" t="s">
-        <v>10</v>
-      </c>
-      <c r="D97" t="s">
-        <v>11</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="G97">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7">
-      <c r="A98">
-        <v>96</v>
-      </c>
-      <c r="B98" t="s">
-        <v>9</v>
-      </c>
-      <c r="C98" t="s">
-        <v>10</v>
-      </c>
-      <c r="D98" t="s">
-        <v>11</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="G98">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7">
-      <c r="A99">
-        <v>97</v>
-      </c>
-      <c r="B99" t="s">
-        <v>9</v>
-      </c>
-      <c r="C99" t="s">
-        <v>10</v>
-      </c>
-      <c r="D99" t="s">
-        <v>11</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G99">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7">
-      <c r="A100">
-        <v>98</v>
-      </c>
-      <c r="B100" t="s">
-        <v>9</v>
-      </c>
-      <c r="C100" t="s">
-        <v>43</v>
-      </c>
-      <c r="D100" t="s">
-        <v>44</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="G100">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7">
-      <c r="A101">
-        <v>99</v>
-      </c>
-      <c r="B101" t="s">
-        <v>9</v>
-      </c>
-      <c r="C101" t="s">
-        <v>15</v>
-      </c>
-      <c r="D101" t="s">
-        <v>16</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="G101">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7">
-      <c r="A102">
-        <v>100</v>
-      </c>
-      <c r="B102" t="s">
-        <v>9</v>
-      </c>
-      <c r="C102" t="s">
-        <v>15</v>
-      </c>
-      <c r="D102" t="s">
-        <v>11</v>
-      </c>
-      <c r="F102" s="2" t="s">
+      <c r="F123" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G123" s="1">
         <v>122</v>
       </c>
-      <c r="G102">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7">
-      <c r="A103">
-        <v>101</v>
-      </c>
-      <c r="B103" t="s">
-        <v>9</v>
-      </c>
-      <c r="C103" t="s">
-        <v>15</v>
-      </c>
-      <c r="D103" t="s">
-        <v>11</v>
-      </c>
-      <c r="F103" s="2" t="s">
+      <c r="H123" s="1"/>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124" s="1">
+        <v>122</v>
+      </c>
+      <c r="B124" t="s">
+        <v>9</v>
+      </c>
+      <c r="C124" t="s">
+        <v>17</v>
+      </c>
+      <c r="D124" t="s">
+        <v>18</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G124" s="1">
         <v>123</v>
       </c>
-      <c r="G103">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7">
-      <c r="A104">
-        <v>102</v>
-      </c>
-      <c r="B104" t="s">
-        <v>9</v>
-      </c>
-      <c r="C104" t="s">
-        <v>10</v>
-      </c>
-      <c r="D104" t="s">
-        <v>11</v>
-      </c>
-      <c r="F104" s="2" t="s">
+      <c r="H124" s="1"/>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" s="1">
+        <v>123</v>
+      </c>
+      <c r="B125" t="s">
+        <v>9</v>
+      </c>
+      <c r="C125" t="s">
+        <v>17</v>
+      </c>
+      <c r="D125" t="s">
+        <v>11</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="G125" s="1">
         <v>124</v>
       </c>
-      <c r="G104">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7">
-      <c r="A105">
-        <v>103</v>
-      </c>
-      <c r="B105" t="s">
-        <v>9</v>
-      </c>
-      <c r="C105" t="s">
-        <v>43</v>
-      </c>
-      <c r="D105" t="s">
-        <v>44</v>
-      </c>
-      <c r="F105" s="2" t="s">
+      <c r="H125" s="1"/>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126" s="1">
+        <v>124</v>
+      </c>
+      <c r="B126" t="s">
+        <v>9</v>
+      </c>
+      <c r="C126" t="s">
+        <v>17</v>
+      </c>
+      <c r="D126" t="s">
+        <v>11</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G126" s="1">
         <v>125</v>
       </c>
-      <c r="G105">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7">
-      <c r="A106">
-        <v>104</v>
-      </c>
-      <c r="B106" t="s">
-        <v>9</v>
-      </c>
-      <c r="C106" t="s">
-        <v>10</v>
-      </c>
-      <c r="D106" t="s">
-        <v>11</v>
-      </c>
-      <c r="E106" s="1" t="s">
+      <c r="H126" s="1"/>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127" s="1">
+        <v>125</v>
+      </c>
+      <c r="B127" t="s">
+        <v>9</v>
+      </c>
+      <c r="C127" t="s">
+        <v>10</v>
+      </c>
+      <c r="D127" t="s">
+        <v>11</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G127" s="1">
         <v>126</v>
       </c>
-      <c r="F106" s="2" t="s">
+      <c r="H127" s="1"/>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128" s="1">
+        <v>126</v>
+      </c>
+      <c r="B128" t="s">
+        <v>9</v>
+      </c>
+      <c r="C128" t="s">
+        <v>57</v>
+      </c>
+      <c r="D128" t="s">
+        <v>58</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G128" s="1">
         <v>127</v>
       </c>
-      <c r="G106">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7">
-      <c r="A107">
-        <v>105</v>
-      </c>
-      <c r="B107" t="s">
-        <v>9</v>
-      </c>
-      <c r="C107" t="s">
-        <v>10</v>
-      </c>
-      <c r="D107" t="s">
-        <v>11</v>
-      </c>
-      <c r="F107" s="2" t="s">
+      <c r="H128" s="1"/>
+    </row>
+    <row r="129" spans="1:8">
+      <c r="A129" s="1">
+        <v>127</v>
+      </c>
+      <c r="B129" t="s">
+        <v>9</v>
+      </c>
+      <c r="C129" t="s">
+        <v>10</v>
+      </c>
+      <c r="D129" t="s">
+        <v>11</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G129" s="1">
         <v>128</v>
       </c>
-      <c r="G107">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7">
-      <c r="A108">
-        <v>106</v>
-      </c>
-      <c r="B108" t="s">
-        <v>9</v>
-      </c>
-      <c r="C108" t="s">
-        <v>43</v>
-      </c>
-      <c r="D108" t="s">
-        <v>44</v>
-      </c>
-      <c r="F108" s="2" t="s">
+      <c r="H129" s="1"/>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130" s="1">
+        <v>128</v>
+      </c>
+      <c r="B130" t="s">
+        <v>9</v>
+      </c>
+      <c r="C130" t="s">
+        <v>10</v>
+      </c>
+      <c r="D130" t="s">
+        <v>11</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G130" s="1">
         <v>129</v>
       </c>
-      <c r="G108">
+      <c r="H130" s="1"/>
+    </row>
+    <row r="131" spans="1:8">
+      <c r="A131" s="1">
+        <v>129</v>
+      </c>
+      <c r="B131" t="s">
+        <v>9</v>
+      </c>
+      <c r="C131" t="s">
+        <v>57</v>
+      </c>
+      <c r="D131" t="s">
+        <v>58</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G131" s="1">
         <v>-1</v>
       </c>
+      <c r="H131" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4944,11 +6153,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="4" width="18"/>
-    <col min="5" max="5" width="24.9166666666667" customWidth="1"/>
+    <col min="5" max="5" width="24"/>
     <col min="6" max="6" width="42"/>
     <col min="9" max="9" width="18"/>
   </cols>
@@ -4983,337 +6192,337 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2">
+      <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G2">
+        <v>153</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="G2" s="1">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3">
+      <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="G3" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="G4" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G5" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G6" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>153</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G7" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G8" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>153</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>160</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="G9" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="G10" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>153</v>
+      </c>
+      <c r="C11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="G11" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>153</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G12" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>153</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G13" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>153</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="G14" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>153</v>
+      </c>
+      <c r="C15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="G15" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="1">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>153</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="G16" s="1">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="1">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>153</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="G17" s="1">
         <v>16</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>130</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>130</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>130</v>
-      </c>
-      <c r="C8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" t="s">
-        <v>137</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="G9">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>130</v>
-      </c>
-      <c r="C10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" t="s">
-        <v>137</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="G10">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>130</v>
-      </c>
-      <c r="C11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>130</v>
-      </c>
-      <c r="C12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="G12">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s">
-        <v>130</v>
-      </c>
-      <c r="C13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="G13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
-        <v>130</v>
-      </c>
-      <c r="C14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G14">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s">
-        <v>130</v>
-      </c>
-      <c r="C15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="G15">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>130</v>
-      </c>
-      <c r="C16" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="G16">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>130</v>
-      </c>
-      <c r="C17" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G17">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>16</v>
-      </c>
       <c r="B18" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -5321,19 +6530,19 @@
       <c r="D18" t="s">
         <v>11</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="G18">
+      <c r="F18" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="G18" s="1">
         <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19">
+      <c r="A19" s="1">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="C19" t="s">
         <v>10</v>
@@ -5341,19 +6550,19 @@
       <c r="D19" t="s">
         <v>11</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="G19">
+      <c r="F19" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G19" s="1">
         <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20">
+      <c r="A20" s="1">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
@@ -5361,39 +6570,39 @@
       <c r="D20" t="s">
         <v>11</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G20" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="1">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
         <v>153</v>
       </c>
-      <c r="G20">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>19</v>
-      </c>
-      <c r="B21" t="s">
-        <v>130</v>
-      </c>
       <c r="C21" t="s">
         <v>10</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="G21">
+      <c r="F21" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G21" s="1">
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22">
+      <c r="A22" s="1">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="C22" t="s">
         <v>10</v>
@@ -5401,79 +6610,79 @@
       <c r="D22" t="s">
         <v>11</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G22">
+      <c r="F22" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="G22" s="1">
         <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23">
+      <c r="A23" s="1">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="C23" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="G23">
+        <v>18</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G23" s="1">
         <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24">
+      <c r="A24" s="1">
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="C24" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="G24">
+        <v>18</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G24" s="1">
         <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25">
+      <c r="A25" s="1">
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="G25">
+        <v>18</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G25" s="1">
         <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26">
+      <c r="A26" s="1">
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="C26" t="s">
         <v>10</v>
@@ -5481,19 +6690,19 @@
       <c r="D26" t="s">
         <v>11</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="G26">
+      <c r="F26" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G26" s="1">
         <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27">
+      <c r="A27" s="1">
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="C27" t="s">
         <v>10</v>
@@ -5501,19 +6710,19 @@
       <c r="D27" t="s">
         <v>11</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="G27">
+      <c r="F27" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G27" s="1">
         <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28">
+      <c r="A28" s="1">
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="C28" t="s">
         <v>10</v>
@@ -5521,10 +6730,30 @@
       <c r="D28" t="s">
         <v>11</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="G28">
+      <c r="F28" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G28" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="1">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>153</v>
+      </c>
+      <c r="C29" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" t="s">
+        <v>58</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G29" s="1">
         <v>-1</v>
       </c>
     </row>
@@ -5575,25 +6804,25 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2">
+      <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="G2">
+        <v>185</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G2" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3">
+      <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -5601,19 +6830,19 @@
       <c r="D3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="G3">
+      <c r="F3" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4">
+      <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -5621,19 +6850,19 @@
       <c r="D4" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="G4">
+      <c r="F4" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5">
+      <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -5641,19 +6870,19 @@
       <c r="D5" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="G5">
+      <c r="F5" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G5" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6">
+      <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -5661,19 +6890,19 @@
       <c r="D6" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="G6">
+      <c r="F6" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="G6" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7">
+      <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -5681,19 +6910,19 @@
       <c r="D7" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="G7">
+      <c r="F7" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8">
+      <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -5701,19 +6930,19 @@
       <c r="D8" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="G8">
+      <c r="F8" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="G8" s="1">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9">
+      <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -5721,74 +6950,852 @@
       <c r="D9" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="G9">
+      <c r="F9" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="G9" s="1">
         <v>8</v>
       </c>
     </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="G10" s="1">
+        <v>-1</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>185</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="G11" s="1">
+        <v>-1</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>185</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="G12" s="1">
+        <v>-1</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.2"/>
+  <cols>
+    <col min="1" max="4" width="18"/>
+    <col min="6" max="6" width="42"/>
+    <col min="9" max="9" width="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="G2" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="G4" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>198</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G5" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>198</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>160</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G6" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>198</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G7" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="G8" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>198</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="G9" s="1">
+        <v>9</v>
+      </c>
+    </row>
     <row r="10" spans="1:7">
-      <c r="A10">
+      <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>162</v>
+        <v>198</v>
       </c>
       <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>198</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="G11" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>198</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="G12" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>198</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G13" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.2"/>
+  <cols>
+    <col min="1" max="4" width="18"/>
+    <col min="6" max="6" width="42"/>
+    <col min="9" max="9" width="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="G2" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G4" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>213</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G5" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="G6" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="G7" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>213</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G8" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G9" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>213</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>213</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>160</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="G11" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G12" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>213</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="G13" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>213</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G14" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>213</v>
+      </c>
+      <c r="C15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G15" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="1">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>213</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="G16" s="1">
         <v>15</v>
       </c>
-      <c r="D10" t="s">
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="1">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>213</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="G17" s="1">
         <v>16</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G10">
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="1">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>213</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="G18" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.2" outlineLevelRow="3"/>
+  <cols>
+    <col min="1" max="4" width="18"/>
+    <col min="6" max="6" width="42"/>
+    <col min="9" max="9" width="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>162</v>
-      </c>
-      <c r="C11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G11">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>162</v>
-      </c>
-      <c r="C12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="G12">
+    <row r="2" spans="1:7">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G2" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>231</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="G4" s="1">
         <v>-1</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Excel/ChatData.xlsx
+++ b/Assets/StreamingAssets/Excel/ChatData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="7"/>
+    <workbookView windowWidth="22188" windowHeight="9060" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="一切的开始" sheetId="1" r:id="rId1"/>
@@ -1882,14 +1882,7 @@
     <t>第一次点开气密舱门</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>首次点开“气密舱门”</t>
-    </r>
+    <t>首次点开气密舱门</t>
   </si>
   <si>
     <r>
@@ -3502,7 +3495,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I138"/>
-  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="10.287037037037" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="27"/>
@@ -6450,7 +6443,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I29"/>
-  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="10.287037037037" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="24"/>
@@ -7070,7 +7063,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="10.287037037037" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -7341,7 +7334,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="10.287037037037" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -7386,7 +7379,7 @@
       <c r="B2" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>204</v>
       </c>
       <c r="G2" s="2">
@@ -7649,7 +7642,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="10.287037037037" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -8037,7 +8030,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="12.75" outlineLevelRow="3"/>
+  <sheetFormatPr defaultColWidth="10.287037037037" defaultRowHeight="13.2" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -8139,7 +8132,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="12.75" outlineLevelRow="3"/>
+  <sheetFormatPr defaultColWidth="10.287037037037" defaultRowHeight="13.2" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -8241,7 +8234,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="10.287037037037" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>

--- a/Assets/StreamingAssets/Excel/ChatData.xlsx
+++ b/Assets/StreamingAssets/Excel/ChatData.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B35AD78D-1FBD-4FE2-91AA-E8E411B13D12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="22188" windowHeight="9060" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="一切的开始" sheetId="1" r:id="rId1"/>
@@ -23,6 +17,19 @@
     <sheet name="困了_03" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -520,6 +527,9 @@
     <t>点击底边栏的摄像头图标,打开摄像头窗口</t>
   </si>
   <si>
+    <t>解锁_摄像头</t>
+  </si>
+  <si>
     <t>打开摄像头窗口</t>
   </si>
   <si>
@@ -663,6 +673,9 @@
     </r>
   </si>
   <si>
+    <t>解锁_背包</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -743,6 +756,9 @@
     </r>
   </si>
   <si>
+    <t>添加_玩家_压缩饼干</t>
+  </si>
+  <si>
     <t>打开压缩饼干的详情窗口</t>
   </si>
   <si>
@@ -826,6 +842,9 @@
     </r>
   </si>
   <si>
+    <t>解锁_状态</t>
+  </si>
+  <si>
     <t>打开状态窗口</t>
   </si>
   <si>
@@ -1029,6 +1048,9 @@
     </r>
   </si>
   <si>
+    <t>解锁_研究</t>
+  </si>
+  <si>
     <t>打开研究窗口</t>
   </si>
   <si>
@@ -1152,6 +1174,9 @@
     </r>
   </si>
   <si>
+    <t>在"研究"窗口中,打开"建筑"子菜单，点击"修理"这项科技,并点击左下角的“开始研究”</t>
+  </si>
+  <si>
     <t>研究修理这项科技</t>
   </si>
   <si>
@@ -1353,6 +1378,9 @@
       </rPr>
       <t>双击点开桌面上的软件,打开地点窗口</t>
     </r>
+  </si>
+  <si>
+    <t>解锁_地点</t>
   </si>
   <si>
     <r>
@@ -1464,6 +1492,9 @@
     </r>
   </si>
   <si>
+    <t>解锁_休息;解锁_装备</t>
+  </si>
+  <si>
     <t>修理研究完毕</t>
   </si>
   <si>
@@ -1865,14 +1896,7 @@
     <t>第一次点开气密舱门</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>首次点开“气密舱门”</t>
-    </r>
+    <t>首次点开气密舱门</t>
   </si>
   <si>
     <r>
@@ -2301,48 +2325,20 @@
       </rPr>
       <t>嗯</t>
     </r>
-  </si>
-  <si>
-    <t>添加_玩家_压缩饼干</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>解锁_背包</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>解锁_休息;解锁_装备</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>解锁_研究</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>解锁_摄像头</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>解锁_状态</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>在"研究"窗口中,打开"建筑"子菜单，点击"修理"这项科技,并点击左下角的“开始研究”</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>解锁_地点</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="25">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -2362,36 +2358,364 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -2399,9 +2723,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2418,165 +2984,96 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -2587,7 +3084,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -2615,40 +3112,154 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2906,14 +3517,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I138"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="27"/>
@@ -2923,7 +3534,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2952,7 +3563,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -2964,7 +3575,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -2985,7 +3596,7 @@
       </c>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -3006,7 +3617,7 @@
       </c>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -3026,7 +3637,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -3046,7 +3657,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -3067,7 +3678,7 @@
       </c>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -3088,7 +3699,7 @@
       </c>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -3109,7 +3720,7 @@
       </c>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -3130,7 +3741,7 @@
       </c>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -3151,7 +3762,7 @@
       </c>
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -3171,7 +3782,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -3192,7 +3803,7 @@
       </c>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -3212,7 +3823,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -3233,7 +3844,7 @@
       </c>
       <c r="H15" s="1"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -3254,7 +3865,7 @@
       </c>
       <c r="H16" s="1"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -3274,7 +3885,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -3294,7 +3905,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -3315,7 +3926,7 @@
       </c>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -3336,7 +3947,7 @@
       </c>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -3357,7 +3968,7 @@
       </c>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -3378,7 +3989,7 @@
       </c>
       <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -3399,7 +4010,7 @@
       </c>
       <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -3419,7 +4030,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -3440,7 +4051,7 @@
       </c>
       <c r="H25" s="1"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -3461,7 +4072,7 @@
       </c>
       <c r="H26" s="1"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -3482,7 +4093,7 @@
       </c>
       <c r="H27" s="1"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -3503,7 +4114,7 @@
       </c>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -3526,7 +4137,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -3547,7 +4158,7 @@
       </c>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -3568,7 +4179,7 @@
       </c>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -3589,7 +4200,7 @@
       </c>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -3610,7 +4221,7 @@
       </c>
       <c r="H33" s="1"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -3631,7 +4242,7 @@
       </c>
       <c r="H34" s="1"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -3652,7 +4263,7 @@
       </c>
       <c r="H35" s="1"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -3673,7 +4284,7 @@
       </c>
       <c r="H36" s="1"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -3694,7 +4305,7 @@
       </c>
       <c r="H37" s="1"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -3715,7 +4326,7 @@
       </c>
       <c r="H38" s="1"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -3736,7 +4347,7 @@
       </c>
       <c r="H39" s="1"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -3757,7 +4368,7 @@
       </c>
       <c r="H40" s="1"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -3778,7 +4389,7 @@
       </c>
       <c r="H41" s="1"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -3799,7 +4410,7 @@
       </c>
       <c r="H42" s="1"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -3820,7 +4431,7 @@
       </c>
       <c r="H43" s="1"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -3841,7 +4452,7 @@
       </c>
       <c r="H44" s="1"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -3862,7 +4473,7 @@
       </c>
       <c r="H45" s="1"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -3883,7 +4494,7 @@
       </c>
       <c r="H46" s="1"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -3904,10 +4515,10 @@
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="4" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -3921,10 +4532,10 @@
         <v>11</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G48" s="1">
         <v>47</v>
@@ -3932,7 +4543,7 @@
       <c r="H48" s="1"/>
       <c r="I48" s="4"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -3946,14 +4557,14 @@
         <v>11</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G49" s="1">
         <v>48</v>
       </c>
       <c r="H49" s="1"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -3967,14 +4578,14 @@
         <v>11</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G50" s="1">
         <v>49</v>
       </c>
       <c r="H50" s="1"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -3988,14 +4599,14 @@
         <v>11</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G51" s="1">
         <v>50</v>
       </c>
       <c r="H51" s="1"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -4009,14 +4620,14 @@
         <v>11</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G52" s="1">
         <v>51</v>
       </c>
       <c r="H52" s="1"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -4030,14 +4641,14 @@
         <v>11</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G53" s="1">
         <v>52</v>
       </c>
       <c r="H53" s="1"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -4051,14 +4662,14 @@
         <v>18</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G54" s="1">
         <v>53</v>
       </c>
       <c r="H54" s="1"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -4072,14 +4683,14 @@
         <v>11</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G55" s="1">
         <v>54</v>
       </c>
       <c r="H55" s="1"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -4093,14 +4704,14 @@
         <v>11</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G56" s="1">
         <v>55</v>
       </c>
       <c r="H56" s="1"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -4114,14 +4725,14 @@
         <v>18</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G57" s="1">
         <v>57</v>
       </c>
       <c r="H57" s="1"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -4135,14 +4746,14 @@
         <v>18</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G58" s="1">
         <v>57</v>
       </c>
       <c r="H58" s="1"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -4156,14 +4767,14 @@
         <v>11</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G59" s="1">
         <v>58</v>
       </c>
       <c r="H59" s="1"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -4177,14 +4788,14 @@
         <v>11</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G60" s="1">
         <v>59</v>
       </c>
       <c r="H60" s="1"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -4198,17 +4809,17 @@
         <v>59</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G61" s="1">
         <v>60</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="4" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -4222,17 +4833,17 @@
         <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G62" s="1">
         <v>61</v>
       </c>
       <c r="H62" s="1"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -4246,14 +4857,14 @@
         <v>11</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G63" s="1">
         <v>62</v>
       </c>
       <c r="H63" s="1"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -4267,14 +4878,14 @@
         <v>11</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G64" s="1">
         <v>63</v>
       </c>
       <c r="H64" s="1"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -4288,14 +4899,14 @@
         <v>11</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G65" s="1">
         <v>64</v>
       </c>
       <c r="H65" s="1"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -4309,14 +4920,14 @@
         <v>11</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G66" s="1">
         <v>65</v>
       </c>
       <c r="H66" s="1"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -4330,14 +4941,14 @@
         <v>11</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G67" s="1">
         <v>66</v>
       </c>
       <c r="H67" s="1"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -4351,17 +4962,17 @@
         <v>59</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G68" s="1">
         <v>67</v>
       </c>
       <c r="H68" s="1"/>
       <c r="I68" s="4" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -4375,17 +4986,17 @@
         <v>18</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G69" s="1">
         <v>68</v>
       </c>
       <c r="H69" s="1"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -4399,7 +5010,7 @@
         <v>11</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G70" s="1">
         <v>69</v>
@@ -4408,7 +5019,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -4422,14 +5033,14 @@
         <v>11</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G71" s="1">
         <v>70</v>
       </c>
       <c r="H71" s="1"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -4443,14 +5054,14 @@
         <v>11</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G72" s="1">
         <v>71</v>
       </c>
       <c r="H72" s="1"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -4464,7 +5075,7 @@
         <v>11</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G73" s="1">
         <v>72</v>
@@ -4473,7 +5084,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -4487,7 +5098,7 @@
         <v>11</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G74" s="1">
         <v>73</v>
@@ -4496,7 +5107,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -4510,7 +5121,7 @@
         <v>11</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G75" s="1">
         <v>74</v>
@@ -4518,7 +5129,7 @@
       <c r="H75" s="1"/>
       <c r="I75" s="4"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -4532,17 +5143,17 @@
         <v>59</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G76" s="1">
         <v>75</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="4" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -4556,17 +5167,17 @@
         <v>18</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G77" s="1">
         <v>76</v>
       </c>
       <c r="H77" s="1"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -4580,14 +5191,14 @@
         <v>11</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G78" s="1">
         <v>77</v>
       </c>
       <c r="H78" s="1"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -4601,7 +5212,7 @@
         <v>11</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G79" s="1">
         <v>78</v>
@@ -4610,7 +5221,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -4624,14 +5235,14 @@
         <v>11</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G80" s="1">
         <v>79</v>
       </c>
       <c r="H80" s="1"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -4645,14 +5256,14 @@
         <v>11</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G81" s="1">
         <v>80</v>
       </c>
       <c r="H81" s="1"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -4666,14 +5277,14 @@
         <v>11</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G82" s="1">
         <v>81</v>
       </c>
       <c r="H82" s="1"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -4687,7 +5298,7 @@
         <v>11</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G83" s="1">
         <v>82</v>
@@ -4696,7 +5307,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -4710,13 +5321,13 @@
         <v>11</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G84" s="1">
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -4730,13 +5341,13 @@
         <v>11</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G85" s="1">
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -4750,14 +5361,14 @@
         <v>11</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G86" s="1">
         <v>85</v>
       </c>
       <c r="H86" s="1"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -4771,13 +5382,13 @@
         <v>11</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G87" s="1">
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -4791,14 +5402,14 @@
         <v>11</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G88" s="1">
         <v>87</v>
       </c>
       <c r="H88" s="1"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -4812,7 +5423,7 @@
         <v>11</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G89" s="1">
         <v>88</v>
@@ -4821,7 +5432,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8">
       <c r="A90" s="1">
         <v>88</v>
       </c>
@@ -4835,14 +5446,14 @@
         <v>11</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G90" s="1">
         <v>89</v>
       </c>
       <c r="H90" s="1"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7">
       <c r="A91" s="1">
         <v>89</v>
       </c>
@@ -4856,13 +5467,13 @@
         <v>11</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G91" s="1">
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8">
       <c r="A92" s="1">
         <v>90</v>
       </c>
@@ -4876,7 +5487,7 @@
         <v>11</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G92" s="1">
         <v>91</v>
@@ -4885,7 +5496,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8">
       <c r="A93" s="1">
         <v>91</v>
       </c>
@@ -4899,14 +5510,14 @@
         <v>11</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G93" s="1">
         <v>92</v>
       </c>
       <c r="H93" s="1"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7">
       <c r="A94" s="1">
         <v>92</v>
       </c>
@@ -4920,13 +5531,13 @@
         <v>11</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G94" s="1">
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8">
       <c r="A95" s="1">
         <v>93</v>
       </c>
@@ -4940,14 +5551,14 @@
         <v>11</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G95" s="1">
         <v>94</v>
       </c>
       <c r="H95" s="1"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8">
       <c r="A96" s="1">
         <v>94</v>
       </c>
@@ -4961,14 +5572,14 @@
         <v>11</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G96" s="1">
         <v>95</v>
       </c>
       <c r="H96" s="1"/>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9">
       <c r="A97" s="1">
         <v>95</v>
       </c>
@@ -4982,17 +5593,17 @@
         <v>59</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G97" s="1">
         <v>96</v>
       </c>
       <c r="H97" s="1"/>
       <c r="I97" s="4" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
       <c r="A98" s="1">
         <v>96</v>
       </c>
@@ -5006,17 +5617,17 @@
         <v>18</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G98" s="1">
         <v>97</v>
       </c>
       <c r="H98" s="1"/>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8">
       <c r="A99" s="1">
         <v>97</v>
       </c>
@@ -5030,14 +5641,14 @@
         <v>11</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="G99" s="1">
         <v>98</v>
       </c>
       <c r="H99" s="1"/>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8">
       <c r="A100" s="1">
         <v>98</v>
       </c>
@@ -5051,14 +5662,14 @@
         <v>11</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G100" s="1">
         <v>99</v>
       </c>
       <c r="H100" s="1"/>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8">
       <c r="A101" s="1">
         <v>99</v>
       </c>
@@ -5072,14 +5683,14 @@
         <v>11</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="G101" s="1">
         <v>100</v>
       </c>
       <c r="H101" s="1"/>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8">
       <c r="A102" s="1">
         <v>100</v>
       </c>
@@ -5093,14 +5704,14 @@
         <v>11</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="G102" s="1">
         <v>101</v>
       </c>
       <c r="H102" s="1"/>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8">
       <c r="A103" s="1">
         <v>101</v>
       </c>
@@ -5114,14 +5725,14 @@
         <v>11</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G103" s="1">
         <v>102</v>
       </c>
       <c r="H103" s="1"/>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8">
       <c r="A104" s="1">
         <v>102</v>
       </c>
@@ -5135,14 +5746,14 @@
         <v>11</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G104" s="1">
         <v>103</v>
       </c>
       <c r="H104" s="1"/>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8">
       <c r="A105" s="1">
         <v>103</v>
       </c>
@@ -5156,14 +5767,14 @@
         <v>18</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G105" s="1">
         <v>104</v>
       </c>
       <c r="H105" s="1"/>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8">
       <c r="A106" s="1">
         <v>104</v>
       </c>
@@ -5177,14 +5788,14 @@
         <v>11</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="G106" s="1">
         <v>105</v>
       </c>
       <c r="H106" s="1"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8">
       <c r="A107" s="1">
         <v>105</v>
       </c>
@@ -5198,14 +5809,14 @@
         <v>11</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G107" s="1">
         <v>106</v>
       </c>
       <c r="H107" s="1"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8">
       <c r="A108" s="1">
         <v>106</v>
       </c>
@@ -5219,14 +5830,14 @@
         <v>11</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G108" s="1">
         <v>107</v>
       </c>
       <c r="H108" s="1"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8">
       <c r="A109" s="1">
         <v>107</v>
       </c>
@@ -5240,14 +5851,14 @@
         <v>11</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G109" s="1">
         <v>108</v>
       </c>
       <c r="H109" s="1"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8">
       <c r="A110" s="1">
         <v>108</v>
       </c>
@@ -5261,14 +5872,14 @@
         <v>59</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>257</v>
+        <v>132</v>
       </c>
       <c r="G110" s="1">
         <v>109</v>
       </c>
       <c r="H110" s="1"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8">
       <c r="A111" s="1">
         <v>109</v>
       </c>
@@ -5282,10 +5893,10 @@
         <v>18</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="G111" s="1">
         <v>110</v>
@@ -5294,7 +5905,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8">
       <c r="A112" s="1">
         <v>110</v>
       </c>
@@ -5308,7 +5919,7 @@
         <v>11</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="G112" s="1">
         <v>111</v>
@@ -5317,7 +5928,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8">
       <c r="A113" s="1">
         <v>111</v>
       </c>
@@ -5331,7 +5942,7 @@
         <v>11</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="G113" s="1">
         <v>112</v>
@@ -5340,7 +5951,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8">
       <c r="A114" s="1">
         <v>112</v>
       </c>
@@ -5354,14 +5965,14 @@
         <v>11</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="G114" s="1">
         <v>113</v>
       </c>
       <c r="H114" s="1"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8">
       <c r="A115" s="1">
         <v>113</v>
       </c>
@@ -5375,14 +5986,14 @@
         <v>11</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="G115" s="1">
         <v>114</v>
       </c>
       <c r="H115" s="1"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8">
       <c r="A116" s="1">
         <v>114</v>
       </c>
@@ -5396,14 +6007,14 @@
         <v>11</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G116" s="1">
         <v>115</v>
       </c>
       <c r="H116" s="1"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8">
       <c r="A117" s="1">
         <v>115</v>
       </c>
@@ -5417,14 +6028,14 @@
         <v>18</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="G117" s="1">
         <v>116</v>
       </c>
       <c r="H117" s="1"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8">
       <c r="A118" s="1">
         <v>116</v>
       </c>
@@ -5438,14 +6049,14 @@
         <v>18</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="G118" s="1">
         <v>117</v>
       </c>
       <c r="H118" s="1"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8">
       <c r="A119" s="1">
         <v>117</v>
       </c>
@@ -5459,14 +6070,14 @@
         <v>11</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="G119" s="1">
         <v>118</v>
       </c>
       <c r="H119" s="1"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8">
       <c r="A120" s="1">
         <v>118</v>
       </c>
@@ -5480,14 +6091,14 @@
         <v>11</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G120" s="1">
         <v>119</v>
       </c>
       <c r="H120" s="1"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8">
       <c r="A121" s="1">
         <v>119</v>
       </c>
@@ -5501,14 +6112,14 @@
         <v>11</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="G121" s="1">
         <v>120</v>
       </c>
       <c r="H121" s="1"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7">
       <c r="A122" s="1">
         <v>120</v>
       </c>
@@ -5522,13 +6133,13 @@
         <v>11</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G122" s="1">
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8">
       <c r="A123" s="1">
         <v>121</v>
       </c>
@@ -5542,14 +6153,14 @@
         <v>18</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="G123" s="1">
         <v>122</v>
       </c>
       <c r="H123" s="1"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8">
       <c r="A124" s="1">
         <v>122</v>
       </c>
@@ -5563,14 +6174,14 @@
         <v>11</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G124" s="1">
         <v>123</v>
       </c>
       <c r="H124" s="1"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7">
       <c r="A125" s="1">
         <v>123</v>
       </c>
@@ -5584,13 +6195,13 @@
         <v>11</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="G125" s="1">
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7">
       <c r="A126" s="1">
         <v>124</v>
       </c>
@@ -5604,13 +6215,13 @@
         <v>11</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="G126" s="1">
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8">
       <c r="A127" s="1">
         <v>125</v>
       </c>
@@ -5624,14 +6235,14 @@
         <v>11</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="G127" s="1">
         <v>126</v>
       </c>
       <c r="H127" s="1"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8">
       <c r="A128" s="1">
         <v>126</v>
       </c>
@@ -5645,14 +6256,14 @@
         <v>11</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="G128" s="1">
         <v>127</v>
       </c>
       <c r="H128" s="1"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8">
       <c r="A129" s="1">
         <v>127</v>
       </c>
@@ -5666,14 +6277,14 @@
         <v>11</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="G129" s="1">
         <v>128</v>
       </c>
       <c r="H129" s="1"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9">
       <c r="A130" s="1">
         <v>128</v>
       </c>
@@ -5687,17 +6298,17 @@
         <v>59</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="G130" s="1">
         <v>129</v>
       </c>
       <c r="H130" s="1"/>
       <c r="I130" s="4" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9">
       <c r="A131" s="1">
         <v>129</v>
       </c>
@@ -5711,10 +6322,10 @@
         <v>18</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="G131" s="1">
         <v>130</v>
@@ -5722,7 +6333,7 @@
       <c r="H131" s="1"/>
       <c r="I131" s="4"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8">
       <c r="A132" s="1">
         <v>130</v>
       </c>
@@ -5736,14 +6347,14 @@
         <v>11</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="G132" s="1">
         <v>131</v>
       </c>
       <c r="H132" s="1"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8">
       <c r="A133" s="1">
         <v>131</v>
       </c>
@@ -5757,14 +6368,14 @@
         <v>11</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="G133" s="1">
         <v>132</v>
       </c>
       <c r="H133" s="1"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8">
       <c r="A134" s="1">
         <v>132</v>
       </c>
@@ -5778,14 +6389,14 @@
         <v>11</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="G134" s="1">
         <v>133</v>
       </c>
       <c r="H134" s="1"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8">
       <c r="A135" s="1">
         <v>133</v>
       </c>
@@ -5799,14 +6410,14 @@
         <v>59</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G135" s="1">
         <v>134</v>
       </c>
       <c r="H135" s="1"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8">
       <c r="A136" s="1">
         <v>134</v>
       </c>
@@ -5820,17 +6431,17 @@
         <v>11</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="G136" s="1">
         <v>135</v>
       </c>
       <c r="H136" s="1"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8">
       <c r="A137" s="1">
         <v>135</v>
       </c>
@@ -5844,14 +6455,14 @@
         <v>11</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="G137" s="1">
         <v>136</v>
       </c>
       <c r="H137" s="1"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9">
       <c r="A138" s="1">
         <v>136</v>
       </c>
@@ -5865,26 +6476,27 @@
         <v>59</v>
       </c>
       <c r="F138" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="G138" s="1">
         <v>-1</v>
       </c>
       <c r="H138" s="1"/>
       <c r="I138" s="4" t="s">
-        <v>253</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I29"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="24"/>
@@ -5893,7 +6505,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5922,26 +6534,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="G2" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C3" t="s">
         <v>17</v>
@@ -5950,18 +6562,18 @@
         <v>18</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="G3" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
@@ -5970,18 +6582,18 @@
         <v>18</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -5990,18 +6602,18 @@
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="G5" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -6010,18 +6622,18 @@
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C7" t="s">
         <v>17</v>
@@ -6030,18 +6642,18 @@
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -6050,64 +6662,64 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="G9" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="G10" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C11" t="s">
         <v>58</v>
@@ -6116,18 +6728,18 @@
         <v>59</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="G11" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
@@ -6136,21 +6748,21 @@
         <v>11</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C13" t="s">
         <v>17</v>
@@ -6159,18 +6771,18 @@
         <v>18</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -6179,18 +6791,18 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="G14" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C15" t="s">
         <v>58</v>
@@ -6199,18 +6811,18 @@
         <v>59</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="G15" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C16" t="s">
         <v>10</v>
@@ -6219,21 +6831,21 @@
         <v>11</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="G16" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
@@ -6242,18 +6854,18 @@
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="G17" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -6262,18 +6874,18 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="G18" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8">
       <c r="A19" s="1">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C19" t="s">
         <v>10</v>
@@ -6282,7 +6894,7 @@
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="G19" s="1">
         <v>18</v>
@@ -6291,12 +6903,12 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8">
       <c r="A20" s="1">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
@@ -6305,7 +6917,7 @@
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="G20" s="1">
         <v>19</v>
@@ -6314,12 +6926,12 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7">
       <c r="A21" s="1">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C21" t="s">
         <v>10</v>
@@ -6328,18 +6940,18 @@
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="G21" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7">
       <c r="A22" s="1">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C22" t="s">
         <v>10</v>
@@ -6348,18 +6960,18 @@
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="G22" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7">
       <c r="A23" s="1">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C23" t="s">
         <v>17</v>
@@ -6368,18 +6980,18 @@
         <v>18</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="G23" s="1">
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7">
       <c r="A24" s="1">
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C24" t="s">
         <v>17</v>
@@ -6388,18 +7000,18 @@
         <v>18</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="G24" s="1">
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7">
       <c r="A25" s="1">
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C25" t="s">
         <v>17</v>
@@ -6408,18 +7020,18 @@
         <v>18</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="G25" s="1">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7">
       <c r="A26" s="1">
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C26" t="s">
         <v>10</v>
@@ -6428,18 +7040,18 @@
         <v>11</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="G26" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7">
       <c r="A27" s="1">
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C27" t="s">
         <v>10</v>
@@ -6448,18 +7060,18 @@
         <v>11</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="G27" s="1">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7">
       <c r="A28" s="1">
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C28" t="s">
         <v>10</v>
@@ -6468,18 +7080,18 @@
         <v>11</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="G28" s="1">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7">
       <c r="A29" s="1">
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C29" t="s">
         <v>58</v>
@@ -6488,22 +7100,23 @@
         <v>59</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="G29" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -6512,7 +7125,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6541,26 +7154,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="G2" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -6569,18 +7182,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -6589,18 +7202,18 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -6609,18 +7222,18 @@
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="G5" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -6629,18 +7242,18 @@
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -6649,18 +7262,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -6669,18 +7282,18 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -6689,18 +7302,18 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C10" t="s">
         <v>17</v>
@@ -6709,21 +7322,21 @@
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="G10" s="1">
         <v>-1</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C11" t="s">
         <v>17</v>
@@ -6732,21 +7345,21 @@
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="G11" s="1">
         <v>-1</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -6755,25 +7368,26 @@
         <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="G12" s="1">
         <v>-1</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -6782,7 +7396,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6811,26 +7425,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>203</v>
+        <v>210</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>211</v>
       </c>
       <c r="G2" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -6839,18 +7453,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -6859,64 +7473,64 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="G5" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -6925,18 +7539,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -6945,18 +7559,18 @@
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="G8" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -6965,18 +7579,18 @@
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="G9" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
@@ -6985,18 +7599,18 @@
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="G10" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
@@ -7005,18 +7619,18 @@
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="G11" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
@@ -7025,18 +7639,18 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -7045,18 +7659,18 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -7065,22 +7679,23 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="G14" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -7089,7 +7704,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7118,26 +7733,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="G2" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7146,18 +7761,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7166,18 +7781,18 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -7186,18 +7801,18 @@
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="G5" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -7206,18 +7821,18 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -7226,18 +7841,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -7246,18 +7861,18 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -7266,64 +7881,64 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="G10" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="G11" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
@@ -7332,18 +7947,18 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -7352,18 +7967,18 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -7372,18 +7987,18 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="G14" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C15" t="s">
         <v>58</v>
@@ -7392,18 +8007,18 @@
         <v>59</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="G15" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C16" t="s">
         <v>10</v>
@@ -7412,18 +8027,18 @@
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="G16" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
@@ -7432,18 +8047,18 @@
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="G17" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -7452,22 +8067,23 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="G18" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -7476,7 +8092,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7505,26 +8121,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7533,18 +8149,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7553,22 +8169,23 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="G4" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -7577,7 +8194,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7606,26 +8223,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7634,18 +8251,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7654,22 +8271,23 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="G4" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -7678,7 +8296,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7707,26 +8325,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7735,18 +8353,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7755,18 +8373,18 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -7775,18 +8393,18 @@
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="G5" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -7795,18 +8413,18 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="G6" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -7815,18 +8433,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -7835,18 +8453,18 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="G8" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -7855,14 +8473,14 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="G9" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Excel/ChatData.xlsx
+++ b/Assets/StreamingAssets/Excel/ChatData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060" activeTab="3"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="一切的开始" sheetId="1" r:id="rId1"/>
@@ -686,24 +686,10 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>桌面上还有一个叫背包的软件,点开后看见了几个格子</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>其中一个格子里有一块压缩饼干</t>
-    </r>
+    <t>桌面上还有一个叫背包的软件,点开后看见了几个格子</t>
+  </si>
+  <si>
+    <t>其中一个格子里有一块压缩饼干</t>
   </si>
   <si>
     <r>
@@ -1370,27 +1356,13 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>双击点开桌面上的软件,打开地点窗口</t>
-    </r>
+    <t>双击点开桌面上的软件,打开地点窗口</t>
   </si>
   <si>
     <t>解锁_地点</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>打开地点窗口</t>
-    </r>
+    <t>打开地点窗口</t>
   </si>
   <si>
     <r>
@@ -1433,24 +1405,10 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>点击地点窗口中的"探索"按钮</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>点击探索按钮</t>
-    </r>
+    <t>点击地点窗口中的"开始探索"按钮</t>
+  </si>
+  <si>
+    <t>点击探索按钮</t>
   </si>
   <si>
     <r>
@@ -2338,7 +2296,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="23">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -2348,18 +2306,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2826,19 +2772,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2847,131 +2802,122 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2984,10 +2930,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4835,7 +4778,7 @@
       <c r="E62" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F62" s="2" t="s">
+      <c r="F62" s="3" t="s">
         <v>79</v>
       </c>
       <c r="G62" s="1">
@@ -4851,12 +4794,12 @@
         <v>9</v>
       </c>
       <c r="C63" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D63" t="s">
         <v>11</v>
       </c>
-      <c r="F63" s="2" t="s">
+      <c r="F63" s="3" t="s">
         <v>80</v>
       </c>
       <c r="G63" s="1">
@@ -5871,7 +5814,7 @@
       <c r="D110" t="s">
         <v>59</v>
       </c>
-      <c r="F110" s="5" t="s">
+      <c r="F110" s="3" t="s">
         <v>132</v>
       </c>
       <c r="G110" s="1">
@@ -6297,7 +6240,7 @@
       <c r="D130" t="s">
         <v>59</v>
       </c>
-      <c r="F130" s="2" t="s">
+      <c r="F130" s="3" t="s">
         <v>153</v>
       </c>
       <c r="G130" s="1">
@@ -6321,7 +6264,7 @@
       <c r="D131" t="s">
         <v>18</v>
       </c>
-      <c r="E131" s="2" t="s">
+      <c r="E131" s="3" t="s">
         <v>155</v>
       </c>
       <c r="F131" s="2" t="s">
@@ -6409,7 +6352,7 @@
       <c r="D135" t="s">
         <v>59</v>
       </c>
-      <c r="F135" s="2" t="s">
+      <c r="F135" s="3" t="s">
         <v>160</v>
       </c>
       <c r="G135" s="1">
@@ -6430,7 +6373,7 @@
       <c r="D136" t="s">
         <v>11</v>
       </c>
-      <c r="E136" s="2" t="s">
+      <c r="E136" s="3" t="s">
         <v>161</v>
       </c>
       <c r="F136" s="2" t="s">

--- a/Assets/StreamingAssets/Excel/ChatData.xlsx
+++ b/Assets/StreamingAssets/Excel/ChatData.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480F2C5B-E497-4F68-B1C8-A045D1C68F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="一切的开始" sheetId="1" r:id="rId1"/>
@@ -17,24 +23,11 @@
     <sheet name="困了_03" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="262">
   <si>
     <t>小段</t>
   </si>
@@ -818,16 +811,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>双击点开桌面上的软件，打开"状态"窗口。</t>
-    </r>
-  </si>
-  <si>
     <t>解锁_状态</t>
   </si>
   <si>
@@ -840,16 +823,6 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>这还有一个软件，我点开以后看见了很多数据。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>这个标志有点像餐具,是表示饥饿吗？</t>
     </r>
   </si>
@@ -960,16 +933,6 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>这才几分钟时间,水就漫到我脚腕了。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>现在飞船整个斜过来了</t>
     </r>
   </si>
@@ -991,16 +954,6 @@
         <charset val="134"/>
       </rPr>
       <t>等我一下</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我现在爬到了一个稍微高一点的地方。</t>
     </r>
   </si>
   <si>
@@ -1462,50 +1415,10 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>我已经看完《极端环境下的行星飞船应急维修技术：基于有限资源的多样化修复方案》了</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我已经看完那篇名字长得要死的文章了</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>怎么样？你找到修补裂缝的办法了吗？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>飞船里的水位越来越高了</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>你那边能找到一些废金属吗？</t>
-    </r>
-  </si>
-  <si>
     <t>分支对话</t>
   </si>
   <si>
@@ -1541,16 +1454,6 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>找到一块“废金属”,并拖入麦麦的背包</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>我找到废金属了！</t>
     </r>
   </si>
@@ -1634,16 +1537,6 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>那个雨又脏又臭，淋到头上还会掉头发。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>这时候我爸就会做一个差不多的东西把屋顶补上。</t>
     </r>
   </si>
@@ -2283,20 +2176,68 @@
       </rPr>
       <t>嗯</t>
     </r>
+  </si>
+  <si>
+    <t>麦麦</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>对话</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你看完那篇什么什么修理指南了吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>是《极端环境下的行星飞船应急维修技术：基于有限资源的多样化修复方案》</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>看完了</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>怎么样？你找到修补裂缝的办法了吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你那边能找到一些废金属吗？修裂缝需要用</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>找到一块"废金属",并拖入麦麦的背包</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>那个雨又脏又臭,淋到头上还会掉头发</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这还有一个软件,我点开以后看见了很多数据</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>双击点开桌面上的软件，打开"状态"窗口</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这才几分钟时间,水就漫到我脚腕了</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我现在爬到了一个稍微高一点的地方</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.00_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="1">
+    <numFmt numFmtId="178" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -2316,352 +2257,43 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="10"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -2669,259 +2301,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2930,93 +2320,168 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -3027,7 +2492,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -3055,154 +2520,40 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -3460,14 +2811,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I138"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="27"/>
@@ -3477,7 +2828,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3506,7 +2857,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -3518,7 +2869,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3539,7 +2890,7 @@
       </c>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -3560,7 +2911,7 @@
       </c>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -3580,7 +2931,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -3600,7 +2951,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -3621,7 +2972,7 @@
       </c>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -3642,7 +2993,7 @@
       </c>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -3663,7 +3014,7 @@
       </c>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -3684,7 +3035,7 @@
       </c>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -3705,7 +3056,7 @@
       </c>
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -3725,7 +3076,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -3746,7 +3097,7 @@
       </c>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -3766,7 +3117,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -3787,7 +3138,7 @@
       </c>
       <c r="H15" s="1"/>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -3808,7 +3159,7 @@
       </c>
       <c r="H16" s="1"/>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -3828,7 +3179,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -3848,7 +3199,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -3869,7 +3220,7 @@
       </c>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -3890,7 +3241,7 @@
       </c>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -3911,7 +3262,7 @@
       </c>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -3932,7 +3283,7 @@
       </c>
       <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -3953,7 +3304,7 @@
       </c>
       <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -3973,7 +3324,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -3994,7 +3345,7 @@
       </c>
       <c r="H25" s="1"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -4015,7 +3366,7 @@
       </c>
       <c r="H26" s="1"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -4036,7 +3387,7 @@
       </c>
       <c r="H27" s="1"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -4057,7 +3408,7 @@
       </c>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -4080,7 +3431,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -4101,7 +3452,7 @@
       </c>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -4122,7 +3473,7 @@
       </c>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -4143,7 +3494,7 @@
       </c>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -4164,7 +3515,7 @@
       </c>
       <c r="H33" s="1"/>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -4185,7 +3536,7 @@
       </c>
       <c r="H34" s="1"/>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -4206,7 +3557,7 @@
       </c>
       <c r="H35" s="1"/>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -4227,7 +3578,7 @@
       </c>
       <c r="H36" s="1"/>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -4248,7 +3599,7 @@
       </c>
       <c r="H37" s="1"/>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -4269,7 +3620,7 @@
       </c>
       <c r="H38" s="1"/>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -4290,7 +3641,7 @@
       </c>
       <c r="H39" s="1"/>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -4311,7 +3662,7 @@
       </c>
       <c r="H40" s="1"/>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -4332,7 +3683,7 @@
       </c>
       <c r="H41" s="1"/>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -4353,7 +3704,7 @@
       </c>
       <c r="H42" s="1"/>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -4374,7 +3725,7 @@
       </c>
       <c r="H43" s="1"/>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -4395,7 +3746,7 @@
       </c>
       <c r="H44" s="1"/>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -4416,7 +3767,7 @@
       </c>
       <c r="H45" s="1"/>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -4437,7 +3788,7 @@
       </c>
       <c r="H46" s="1"/>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -4457,11 +3808,11 @@
         <v>46</v>
       </c>
       <c r="H47" s="1"/>
-      <c r="I47" s="4" t="s">
+      <c r="I47" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -4484,9 +3835,8 @@
         <v>47</v>
       </c>
       <c r="H48" s="1"/>
-      <c r="I48" s="4"/>
-    </row>
-    <row r="49" spans="1:8">
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -4507,7 +3857,7 @@
       </c>
       <c r="H49" s="1"/>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -4528,7 +3878,7 @@
       </c>
       <c r="H50" s="1"/>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -4549,7 +3899,7 @@
       </c>
       <c r="H51" s="1"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -4570,7 +3920,7 @@
       </c>
       <c r="H52" s="1"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -4591,7 +3941,7 @@
       </c>
       <c r="H53" s="1"/>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -4612,7 +3962,7 @@
       </c>
       <c r="H54" s="1"/>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -4633,7 +3983,7 @@
       </c>
       <c r="H55" s="1"/>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -4654,7 +4004,7 @@
       </c>
       <c r="H56" s="1"/>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -4675,7 +4025,7 @@
       </c>
       <c r="H57" s="1"/>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -4696,7 +4046,7 @@
       </c>
       <c r="H58" s="1"/>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -4717,7 +4067,7 @@
       </c>
       <c r="H59" s="1"/>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -4738,7 +4088,7 @@
       </c>
       <c r="H60" s="1"/>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -4758,11 +4108,11 @@
         <v>60</v>
       </c>
       <c r="H61" s="1"/>
-      <c r="I61" s="4" t="s">
+      <c r="I61" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -4786,7 +4136,7 @@
       </c>
       <c r="H62" s="1"/>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -4807,7 +4157,7 @@
       </c>
       <c r="H63" s="1"/>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -4828,7 +4178,7 @@
       </c>
       <c r="H64" s="1"/>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -4849,7 +4199,7 @@
       </c>
       <c r="H65" s="1"/>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -4870,7 +4220,7 @@
       </c>
       <c r="H66" s="1"/>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -4891,7 +4241,7 @@
       </c>
       <c r="H67" s="1"/>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -4911,11 +4261,11 @@
         <v>67</v>
       </c>
       <c r="H68" s="1"/>
-      <c r="I68" s="4" t="s">
+      <c r="I68" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -4939,7 +4289,7 @@
       </c>
       <c r="H69" s="1"/>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -4962,7 +4312,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -4983,7 +4333,7 @@
       </c>
       <c r="H71" s="1"/>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -5004,7 +4354,7 @@
       </c>
       <c r="H72" s="1"/>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -5027,7 +4377,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -5050,7 +4400,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -5070,9 +4420,8 @@
         <v>74</v>
       </c>
       <c r="H75" s="1"/>
-      <c r="I75" s="4"/>
-    </row>
-    <row r="76" spans="1:9">
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -5085,18 +4434,18 @@
       <c r="D76" t="s">
         <v>59</v>
       </c>
-      <c r="F76" s="2" t="s">
-        <v>95</v>
+      <c r="F76" s="5" t="s">
+        <v>259</v>
       </c>
       <c r="G76" s="1">
         <v>75</v>
       </c>
       <c r="H76" s="1"/>
-      <c r="I76" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8">
+      <c r="I76" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -5110,17 +4459,17 @@
         <v>18</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>258</v>
       </c>
       <c r="G77" s="1">
         <v>76</v>
       </c>
       <c r="H77" s="1"/>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -5134,14 +4483,14 @@
         <v>11</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G78" s="1">
         <v>77</v>
       </c>
       <c r="H78" s="1"/>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -5155,7 +4504,7 @@
         <v>11</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G79" s="1">
         <v>78</v>
@@ -5164,7 +4513,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -5178,14 +4527,14 @@
         <v>11</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G80" s="1">
         <v>79</v>
       </c>
       <c r="H80" s="1"/>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -5199,14 +4548,14 @@
         <v>11</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G81" s="1">
         <v>80</v>
       </c>
       <c r="H81" s="1"/>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -5220,14 +4569,14 @@
         <v>11</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G82" s="1">
         <v>81</v>
       </c>
       <c r="H82" s="1"/>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -5241,7 +4590,7 @@
         <v>11</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G83" s="1">
         <v>82</v>
@@ -5250,7 +4599,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -5264,13 +4613,13 @@
         <v>11</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G84" s="1">
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -5284,13 +4633,13 @@
         <v>11</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G85" s="1">
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -5304,14 +4653,14 @@
         <v>11</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G86" s="1">
         <v>85</v>
       </c>
       <c r="H86" s="1"/>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -5325,13 +4674,13 @@
         <v>11</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G87" s="1">
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -5345,14 +4694,14 @@
         <v>11</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G88" s="1">
         <v>87</v>
       </c>
       <c r="H88" s="1"/>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -5365,8 +4714,8 @@
       <c r="D89" t="s">
         <v>11</v>
       </c>
-      <c r="F89" s="2" t="s">
-        <v>110</v>
+      <c r="F89" s="5" t="s">
+        <v>260</v>
       </c>
       <c r="G89" s="1">
         <v>88</v>
@@ -5375,7 +4724,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>88</v>
       </c>
@@ -5389,14 +4738,14 @@
         <v>11</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G90" s="1">
         <v>89</v>
       </c>
       <c r="H90" s="1"/>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>89</v>
       </c>
@@ -5410,13 +4759,13 @@
         <v>11</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G91" s="1">
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>90</v>
       </c>
@@ -5430,7 +4779,7 @@
         <v>11</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G92" s="1">
         <v>91</v>
@@ -5439,7 +4788,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>91</v>
       </c>
@@ -5460,7 +4809,7 @@
       </c>
       <c r="H93" s="1"/>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>92</v>
       </c>
@@ -5473,14 +4822,14 @@
       <c r="D94" t="s">
         <v>11</v>
       </c>
-      <c r="F94" s="2" t="s">
-        <v>114</v>
+      <c r="F94" s="5" t="s">
+        <v>261</v>
       </c>
       <c r="G94" s="1">
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>93</v>
       </c>
@@ -5494,14 +4843,14 @@
         <v>11</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G95" s="1">
         <v>94</v>
       </c>
       <c r="H95" s="1"/>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>94</v>
       </c>
@@ -5515,14 +4864,14 @@
         <v>11</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G96" s="1">
         <v>95</v>
       </c>
       <c r="H96" s="1"/>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>95</v>
       </c>
@@ -5536,17 +4885,17 @@
         <v>59</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G97" s="1">
         <v>96</v>
       </c>
       <c r="H97" s="1"/>
-      <c r="I97" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8">
+      <c r="I97" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>96</v>
       </c>
@@ -5560,17 +4909,17 @@
         <v>18</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G98" s="1">
         <v>97</v>
       </c>
       <c r="H98" s="1"/>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>97</v>
       </c>
@@ -5584,14 +4933,14 @@
         <v>11</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G99" s="1">
         <v>98</v>
       </c>
       <c r="H99" s="1"/>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>98</v>
       </c>
@@ -5605,14 +4954,14 @@
         <v>11</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="G100" s="1">
         <v>99</v>
       </c>
       <c r="H100" s="1"/>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>99</v>
       </c>
@@ -5626,14 +4975,14 @@
         <v>11</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G101" s="1">
         <v>100</v>
       </c>
       <c r="H101" s="1"/>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>100</v>
       </c>
@@ -5647,14 +4996,14 @@
         <v>11</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G102" s="1">
         <v>101</v>
       </c>
       <c r="H102" s="1"/>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>101</v>
       </c>
@@ -5668,14 +5017,14 @@
         <v>11</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G103" s="1">
         <v>102</v>
       </c>
       <c r="H103" s="1"/>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>102</v>
       </c>
@@ -5689,14 +5038,14 @@
         <v>11</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G104" s="1">
         <v>103</v>
       </c>
       <c r="H104" s="1"/>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>103</v>
       </c>
@@ -5710,14 +5059,14 @@
         <v>18</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G105" s="1">
         <v>104</v>
       </c>
       <c r="H105" s="1"/>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>104</v>
       </c>
@@ -5731,14 +5080,14 @@
         <v>11</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G106" s="1">
         <v>105</v>
       </c>
       <c r="H106" s="1"/>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>105</v>
       </c>
@@ -5752,14 +5101,14 @@
         <v>11</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G107" s="1">
         <v>106</v>
       </c>
       <c r="H107" s="1"/>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>106</v>
       </c>
@@ -5773,14 +5122,14 @@
         <v>11</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G108" s="1">
         <v>107</v>
       </c>
       <c r="H108" s="1"/>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>107</v>
       </c>
@@ -5794,14 +5143,14 @@
         <v>11</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G109" s="1">
         <v>108</v>
       </c>
       <c r="H109" s="1"/>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>108</v>
       </c>
@@ -5815,14 +5164,14 @@
         <v>59</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G110" s="1">
         <v>109</v>
       </c>
       <c r="H110" s="1"/>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>109</v>
       </c>
@@ -5836,10 +5185,10 @@
         <v>18</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G111" s="1">
         <v>110</v>
@@ -5848,7 +5197,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>110</v>
       </c>
@@ -5862,7 +5211,7 @@
         <v>11</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="G112" s="1">
         <v>111</v>
@@ -5871,7 +5220,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>111</v>
       </c>
@@ -5885,7 +5234,7 @@
         <v>11</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="G113" s="1">
         <v>112</v>
@@ -5894,7 +5243,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>112</v>
       </c>
@@ -5908,14 +5257,14 @@
         <v>11</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G114" s="1">
         <v>113</v>
       </c>
       <c r="H114" s="1"/>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>113</v>
       </c>
@@ -5929,14 +5278,14 @@
         <v>11</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G115" s="1">
         <v>114</v>
       </c>
       <c r="H115" s="1"/>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>114</v>
       </c>
@@ -5950,14 +5299,14 @@
         <v>11</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G116" s="1">
         <v>115</v>
       </c>
       <c r="H116" s="1"/>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>115</v>
       </c>
@@ -5971,14 +5320,14 @@
         <v>18</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G117" s="1">
         <v>116</v>
       </c>
       <c r="H117" s="1"/>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>116</v>
       </c>
@@ -5992,14 +5341,14 @@
         <v>18</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G118" s="1">
         <v>117</v>
       </c>
       <c r="H118" s="1"/>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>117</v>
       </c>
@@ -6013,14 +5362,14 @@
         <v>11</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G119" s="1">
         <v>118</v>
       </c>
       <c r="H119" s="1"/>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>118</v>
       </c>
@@ -6034,14 +5383,14 @@
         <v>11</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G120" s="1">
         <v>119</v>
       </c>
       <c r="H120" s="1"/>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>119</v>
       </c>
@@ -6055,14 +5404,14 @@
         <v>11</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="G121" s="1">
         <v>120</v>
       </c>
       <c r="H121" s="1"/>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>120</v>
       </c>
@@ -6076,13 +5425,13 @@
         <v>11</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="G122" s="1">
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>121</v>
       </c>
@@ -6096,14 +5445,14 @@
         <v>18</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="G123" s="1">
         <v>122</v>
       </c>
       <c r="H123" s="1"/>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>122</v>
       </c>
@@ -6117,14 +5466,14 @@
         <v>11</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G124" s="1">
         <v>123</v>
       </c>
       <c r="H124" s="1"/>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>123</v>
       </c>
@@ -6138,13 +5487,13 @@
         <v>11</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G125" s="1">
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>124</v>
       </c>
@@ -6158,13 +5507,13 @@
         <v>11</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="G126" s="1">
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>125</v>
       </c>
@@ -6178,14 +5527,14 @@
         <v>11</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G127" s="1">
         <v>126</v>
       </c>
       <c r="H127" s="1"/>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>126</v>
       </c>
@@ -6199,14 +5548,14 @@
         <v>11</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G128" s="1">
         <v>127</v>
       </c>
       <c r="H128" s="1"/>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>127</v>
       </c>
@@ -6220,14 +5569,14 @@
         <v>11</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="G129" s="1">
         <v>128</v>
       </c>
       <c r="H129" s="1"/>
     </row>
-    <row r="130" spans="1:9">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>128</v>
       </c>
@@ -6241,17 +5590,17 @@
         <v>59</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="G130" s="1">
         <v>129</v>
       </c>
       <c r="H130" s="1"/>
-      <c r="I130" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9">
+      <c r="I130" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>129</v>
       </c>
@@ -6265,18 +5614,17 @@
         <v>18</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="G131" s="1">
         <v>130</v>
       </c>
       <c r="H131" s="1"/>
-      <c r="I131" s="4"/>
-    </row>
-    <row r="132" spans="1:8">
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>130</v>
       </c>
@@ -6290,14 +5638,14 @@
         <v>11</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G132" s="1">
         <v>131</v>
       </c>
       <c r="H132" s="1"/>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>131</v>
       </c>
@@ -6311,14 +5659,14 @@
         <v>11</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="G133" s="1">
         <v>132</v>
       </c>
       <c r="H133" s="1"/>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>132</v>
       </c>
@@ -6332,14 +5680,14 @@
         <v>11</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G134" s="1">
         <v>133</v>
       </c>
       <c r="H134" s="1"/>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>133</v>
       </c>
@@ -6353,14 +5701,14 @@
         <v>59</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="G135" s="1">
         <v>134</v>
       </c>
       <c r="H135" s="1"/>
     </row>
-    <row r="136" spans="1:8">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>134</v>
       </c>
@@ -6374,17 +5722,17 @@
         <v>11</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G136" s="1">
         <v>135</v>
       </c>
       <c r="H136" s="1"/>
     </row>
-    <row r="137" spans="1:8">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>135</v>
       </c>
@@ -6398,14 +5746,14 @@
         <v>11</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G137" s="1">
         <v>136</v>
       </c>
       <c r="H137" s="1"/>
     </row>
-    <row r="138" spans="1:9">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>136</v>
       </c>
@@ -6419,27 +5767,26 @@
         <v>59</v>
       </c>
       <c r="F138" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G138" s="1">
         <v>-1</v>
       </c>
       <c r="H138" s="1"/>
-      <c r="I138" s="4" t="s">
-        <v>165</v>
+      <c r="I138" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:I29"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:I30"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="24"/>
@@ -6448,7 +5795,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6477,46 +5824,46 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G2" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>167</v>
+        <v>162</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>251</v>
       </c>
       <c r="G3" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
@@ -6524,39 +5871,39 @@
       <c r="D4" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>168</v>
+      <c r="F4" s="5" t="s">
+        <v>252</v>
       </c>
       <c r="G4" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>169</v>
+        <v>18</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>253</v>
       </c>
       <c r="G5" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -6564,231 +5911,228 @@
       <c r="D6" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>170</v>
+      <c r="F6" s="5" t="s">
+        <v>254</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>83</v>
+        <v>163</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>171</v>
+        <v>83</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>174</v>
+        <v>11</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>255</v>
       </c>
       <c r="G9" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>162</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>164</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" t="s">
-        <v>172</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>176</v>
-      </c>
       <c r="G10" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>164</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="G11" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>162</v>
+      </c>
+      <c r="C12" t="s">
         <v>58</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D12" t="s">
         <v>59</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="G11" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>166</v>
-      </c>
-      <c r="C12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>178</v>
+      <c r="F12" s="5" t="s">
+        <v>256</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>11</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>167</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C14" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="G14" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="G15" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C16" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>182</v>
+        <v>59</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="G16" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
@@ -6796,19 +6140,22 @@
       <c r="D17" t="s">
         <v>11</v>
       </c>
+      <c r="E17" s="3" t="s">
+        <v>173</v>
+      </c>
       <c r="F17" s="2" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="G17" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -6817,18 +6164,18 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="G18" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C19" t="s">
         <v>10</v>
@@ -6837,21 +6184,18 @@
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="G19" s="1">
         <v>18</v>
       </c>
-      <c r="H19" s="1">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
@@ -6860,21 +6204,21 @@
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="G20" s="1">
         <v>19</v>
       </c>
       <c r="H20" s="1">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C21" t="s">
         <v>10</v>
@@ -6882,19 +6226,22 @@
       <c r="D21" t="s">
         <v>11</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>188</v>
+      <c r="F21" s="5" t="s">
+        <v>257</v>
       </c>
       <c r="G21" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="H21" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C22" t="s">
         <v>10</v>
@@ -6903,38 +6250,38 @@
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="G22" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C23" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D23" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="G23" s="1">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C24" t="s">
         <v>17</v>
@@ -6943,18 +6290,18 @@
         <v>18</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="G24" s="1">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C25" t="s">
         <v>17</v>
@@ -6963,38 +6310,38 @@
         <v>18</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="G25" s="1">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C26" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D26" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="G26" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C27" t="s">
         <v>10</v>
@@ -7003,18 +6350,18 @@
         <v>11</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="G27" s="1">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C28" t="s">
         <v>10</v>
@@ -7023,43 +6370,62 @@
         <v>11</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="G28" s="1">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C29" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="G29" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>162</v>
+      </c>
+      <c r="C30" t="s">
         <v>58</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D30" t="s">
         <v>59</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="G29" s="1">
+      <c r="F30" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="G30" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -7068,7 +6434,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7097,26 +6463,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="G2" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7125,18 +6491,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7145,18 +6511,18 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -7165,18 +6531,18 @@
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G5" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -7185,18 +6551,18 @@
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -7205,18 +6571,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -7225,18 +6591,18 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -7245,18 +6611,18 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="C10" t="s">
         <v>17</v>
@@ -7265,21 +6631,21 @@
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="G10" s="1">
         <v>-1</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="C11" t="s">
         <v>17</v>
@@ -7288,21 +6654,21 @@
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="G11" s="1">
         <v>-1</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -7311,26 +6677,25 @@
         <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="G12" s="1">
         <v>-1</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -7339,7 +6704,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7368,26 +6733,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="G2" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7396,18 +6761,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7416,64 +6781,64 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="G5" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -7482,18 +6847,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -7502,18 +6867,18 @@
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="G8" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -7522,18 +6887,18 @@
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="G9" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
@@ -7542,18 +6907,18 @@
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="G10" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
@@ -7562,18 +6927,18 @@
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="G11" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
@@ -7582,18 +6947,18 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -7602,18 +6967,18 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -7622,23 +6987,22 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="G14" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -7647,7 +7011,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7676,26 +7040,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="G2" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7704,18 +7068,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7724,18 +7088,18 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -7744,18 +7108,18 @@
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="G5" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -7764,18 +7128,18 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -7784,18 +7148,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -7804,18 +7168,18 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -7824,64 +7188,64 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>216</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>164</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>164</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>226</v>
-      </c>
-      <c r="C10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" t="s">
-        <v>172</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="G10" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>226</v>
-      </c>
-      <c r="C11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" t="s">
-        <v>172</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>236</v>
       </c>
       <c r="G11" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
@@ -7890,18 +7254,18 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -7910,18 +7274,18 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -7930,18 +7294,18 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="G14" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C15" t="s">
         <v>58</v>
@@ -7950,18 +7314,18 @@
         <v>59</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="G15" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C16" t="s">
         <v>10</v>
@@ -7970,18 +7334,18 @@
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="G16" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
@@ -7990,18 +7354,18 @@
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="G17" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -8010,23 +7374,22 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="G18" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2" outlineLevelRow="3"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -8035,7 +7398,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8064,26 +7427,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -8092,18 +7455,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -8112,23 +7475,22 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="G4" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2" outlineLevelRow="3"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -8137,7 +7499,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8166,26 +7528,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -8194,18 +7556,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -8214,23 +7576,22 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="G4" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -8239,7 +7600,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8268,26 +7629,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -8296,18 +7657,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -8316,18 +7677,18 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -8336,18 +7697,18 @@
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="G5" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -8356,18 +7717,18 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="G6" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -8376,18 +7737,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -8396,18 +7757,18 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="G8" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -8416,14 +7777,14 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="G9" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Excel/ChatData.xlsx
+++ b/Assets/StreamingAssets/Excel/ChatData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060"/>
+    <workbookView windowWidth="22188" windowHeight="9060" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="一切的开始" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="260">
   <si>
     <t>小段</t>
   </si>
@@ -1583,6 +1583,9 @@
       </rPr>
       <t>打开“制作窗口”,指挥麦麦制作一个“裂缝填充物”</t>
     </r>
+  </si>
+  <si>
+    <t>解锁_制作</t>
   </si>
   <si>
     <t>制作裂缝填充物</t>
@@ -6740,7 +6743,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:9">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -6758,6 +6761,9 @@
       </c>
       <c r="G15" s="1">
         <v>14</v>
+      </c>
+      <c r="I15" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -6774,10 +6780,10 @@
         <v>11</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G16" s="1">
         <v>15</v>
@@ -6797,7 +6803,7 @@
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G17" s="1">
         <v>16</v>
@@ -6817,7 +6823,7 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G18" s="1">
         <v>17</v>
@@ -6837,7 +6843,7 @@
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G19" s="1">
         <v>18</v>
@@ -6860,7 +6866,7 @@
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G20" s="1">
         <v>19</v>
@@ -6883,7 +6889,7 @@
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G21" s="1">
         <v>20</v>
@@ -6903,7 +6909,7 @@
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G22" s="1">
         <v>21</v>
@@ -6923,7 +6929,7 @@
         <v>18</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G23" s="1">
         <v>26</v>
@@ -6943,7 +6949,7 @@
         <v>18</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G24" s="1">
         <v>26</v>
@@ -6963,7 +6969,7 @@
         <v>18</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G25" s="1">
         <v>24</v>
@@ -6983,7 +6989,7 @@
         <v>11</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G26" s="1">
         <v>25</v>
@@ -7003,7 +7009,7 @@
         <v>11</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G27" s="1">
         <v>26</v>
@@ -7023,7 +7029,7 @@
         <v>11</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G28" s="1">
         <v>27</v>
@@ -7043,7 +7049,7 @@
         <v>59</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G29" s="1">
         <v>-1</v>
@@ -7102,10 +7108,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G2" s="1">
         <v>10</v>
@@ -7116,7 +7122,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7125,7 +7131,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
@@ -7136,7 +7142,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7145,7 +7151,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
@@ -7156,7 +7162,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -7165,7 +7171,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G5" s="1">
         <v>4</v>
@@ -7176,7 +7182,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -7185,7 +7191,7 @@
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
@@ -7196,7 +7202,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -7205,7 +7211,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
@@ -7216,7 +7222,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -7225,7 +7231,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
@@ -7236,7 +7242,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -7245,7 +7251,7 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
@@ -7256,7 +7262,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C10" t="s">
         <v>17</v>
@@ -7265,13 +7271,13 @@
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G10" s="1">
         <v>-1</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -7279,7 +7285,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C11" t="s">
         <v>17</v>
@@ -7288,13 +7294,13 @@
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G11" s="1">
         <v>-1</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -7302,7 +7308,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -7311,13 +7317,13 @@
         <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G12" s="1">
         <v>-1</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -7373,10 +7379,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G2" s="1">
         <v>4</v>
@@ -7387,7 +7393,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7396,7 +7402,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
@@ -7407,7 +7413,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7416,7 +7422,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
@@ -7427,7 +7433,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -7436,10 +7442,10 @@
         <v>172</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G5" s="1">
         <v>-1</v>
@@ -7450,7 +7456,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -7459,10 +7465,10 @@
         <v>172</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
@@ -7473,7 +7479,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -7482,7 +7488,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
@@ -7493,7 +7499,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -7502,7 +7508,7 @@
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G8" s="1">
         <v>8</v>
@@ -7513,7 +7519,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -7522,7 +7528,7 @@
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G9" s="1">
         <v>9</v>
@@ -7533,7 +7539,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
@@ -7542,7 +7548,7 @@
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G10" s="1">
         <v>11</v>
@@ -7553,7 +7559,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
@@ -7562,7 +7568,7 @@
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G11" s="1">
         <v>10</v>
@@ -7573,7 +7579,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
@@ -7582,7 +7588,7 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
@@ -7593,7 +7599,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -7602,7 +7608,7 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
@@ -7613,7 +7619,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -7622,7 +7628,7 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G14" s="1">
         <v>-1</v>
@@ -7681,10 +7687,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G2" s="1">
         <v>4</v>
@@ -7695,7 +7701,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7704,7 +7710,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
@@ -7715,7 +7721,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7724,7 +7730,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
@@ -7735,7 +7741,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -7744,7 +7750,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G5" s="1">
         <v>5</v>
@@ -7755,7 +7761,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -7764,7 +7770,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
@@ -7775,7 +7781,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -7784,7 +7790,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
@@ -7795,7 +7801,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -7804,7 +7810,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
@@ -7815,7 +7821,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -7824,7 +7830,7 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
@@ -7835,7 +7841,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
@@ -7844,10 +7850,10 @@
         <v>172</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G10" s="1">
         <v>10</v>
@@ -7858,7 +7864,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
@@ -7867,10 +7873,10 @@
         <v>172</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G11" s="1">
         <v>14</v>
@@ -7881,7 +7887,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
@@ -7890,7 +7896,7 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
@@ -7901,7 +7907,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -7910,7 +7916,7 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
@@ -7921,7 +7927,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -7930,7 +7936,7 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G14" s="1">
         <v>13</v>
@@ -7941,7 +7947,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C15" t="s">
         <v>58</v>
@@ -7950,7 +7956,7 @@
         <v>59</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G15" s="1">
         <v>-1</v>
@@ -7961,7 +7967,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C16" t="s">
         <v>10</v>
@@ -7970,7 +7976,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G16" s="1">
         <v>15</v>
@@ -7981,7 +7987,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
@@ -7990,7 +7996,7 @@
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G17" s="1">
         <v>16</v>
@@ -8001,7 +8007,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -8010,7 +8016,7 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G18" s="1">
         <v>-1</v>
@@ -8069,10 +8075,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
@@ -8083,7 +8089,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -8092,7 +8098,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
@@ -8103,7 +8109,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -8112,7 +8118,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G4" s="1">
         <v>-1</v>
@@ -8171,10 +8177,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
@@ -8185,7 +8191,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -8194,7 +8200,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
@@ -8205,7 +8211,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -8214,7 +8220,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G4" s="1">
         <v>-1</v>
@@ -8273,10 +8279,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
@@ -8287,7 +8293,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -8296,7 +8302,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
@@ -8307,7 +8313,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -8316,7 +8322,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
@@ -8327,7 +8333,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -8336,7 +8342,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G5" s="1">
         <v>5</v>
@@ -8347,7 +8353,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -8356,7 +8362,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G6" s="1">
         <v>7</v>
@@ -8367,7 +8373,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -8376,7 +8382,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
@@ -8387,7 +8393,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -8396,7 +8402,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G8" s="1">
         <v>-1</v>
@@ -8407,7 +8413,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -8416,7 +8422,7 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G9" s="1">
         <v>-1</v>

--- a/Assets/StreamingAssets/Excel/ChatData.xlsx
+++ b/Assets/StreamingAssets/Excel/ChatData.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480F2C5B-E497-4F68-B1C8-A045D1C68F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="22188" windowHeight="9060" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="一切的开始" sheetId="1" r:id="rId1"/>
@@ -23,11 +17,24 @@
     <sheet name="困了_03" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="261">
   <si>
     <t>小段</t>
   </si>
@@ -811,12 +818,18 @@
     </r>
   </si>
   <si>
+    <t>双击点开桌面上的软件，打开"状态"窗口</t>
+  </si>
+  <si>
     <t>解锁_状态</t>
   </si>
   <si>
     <t>打开状态窗口</t>
   </si>
   <si>
+    <t>这还有一个软件,我点开以后看见了很多数据</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -927,6 +940,9 @@
     </r>
   </si>
   <si>
+    <t>这才几分钟时间,水就漫到我脚腕了</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -955,6 +971,9 @@
       </rPr>
       <t>等我一下</t>
     </r>
+  </si>
+  <si>
+    <t>我现在爬到了一个稍微高一点的地方</t>
   </si>
   <si>
     <r>
@@ -1409,6 +1428,18 @@
     <t>修理研究完毕</t>
   </si>
   <si>
+    <t>你看完那篇什么什么修理指南了吗？</t>
+  </si>
+  <si>
+    <t>是《极端环境下的行星飞船应急维修技术：基于有限资源的多样化修复方案》</t>
+  </si>
+  <si>
+    <t>看完了</t>
+  </si>
+  <si>
+    <t>怎么样？你找到修补裂缝的办法了吗？</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -1419,6 +1450,9 @@
     </r>
   </si>
   <si>
+    <t>你那边能找到一些废金属吗？修裂缝需要用</t>
+  </si>
+  <si>
     <t>分支对话</t>
   </si>
   <si>
@@ -1448,6 +1482,9 @@
     </r>
   </si>
   <si>
+    <t>找到一块"废金属",并拖入麦麦的背包</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -1478,6 +1515,9 @@
     </r>
   </si>
   <si>
+    <t>解锁_制作</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -1531,6 +1571,9 @@
     </r>
   </si>
   <si>
+    <t>那个雨又脏又臭,淋到头上还会掉头发</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -2176,68 +2219,20 @@
       </rPr>
       <t>嗯</t>
     </r>
-  </si>
-  <si>
-    <t>麦麦</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>对话</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>你看完那篇什么什么修理指南了吗？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>是《极端环境下的行星飞船应急维修技术：基于有限资源的多样化修复方案》</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>看完了</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>怎么样？你找到修补裂缝的办法了吗？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>你那边能找到一些废金属吗？修裂缝需要用</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>找到一块"废金属",并拖入麦麦的背包</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>那个雨又脏又臭,淋到头上还会掉头发</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>这还有一个软件,我点开以后看见了很多数据</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>双击点开桌面上的软件，打开"状态"窗口</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>这才几分钟时间,水就漫到我脚腕了</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我现在爬到了一个稍微高一点的地方</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="0.00_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="26">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -2257,43 +2252,370 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -2301,9 +2623,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2311,7 +2875,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2320,168 +2884,99 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -2492,7 +2987,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -2520,40 +3015,154 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2811,14 +3420,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I138"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="27"/>
@@ -2828,7 +3437,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2857,7 +3466,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -2869,7 +3478,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -2890,7 +3499,7 @@
       </c>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -2911,7 +3520,7 @@
       </c>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -2931,7 +3540,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -2951,7 +3560,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -2972,7 +3581,7 @@
       </c>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -2993,7 +3602,7 @@
       </c>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -3014,7 +3623,7 @@
       </c>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -3035,7 +3644,7 @@
       </c>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -3056,7 +3665,7 @@
       </c>
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -3076,7 +3685,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -3097,7 +3706,7 @@
       </c>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -3117,7 +3726,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -3138,7 +3747,7 @@
       </c>
       <c r="H15" s="1"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -3159,7 +3768,7 @@
       </c>
       <c r="H16" s="1"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -3179,7 +3788,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -3199,7 +3808,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -3220,7 +3829,7 @@
       </c>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -3241,7 +3850,7 @@
       </c>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -3262,7 +3871,7 @@
       </c>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -3283,7 +3892,7 @@
       </c>
       <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -3304,7 +3913,7 @@
       </c>
       <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -3324,7 +3933,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -3345,7 +3954,7 @@
       </c>
       <c r="H25" s="1"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -3366,7 +3975,7 @@
       </c>
       <c r="H26" s="1"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -3387,7 +3996,7 @@
       </c>
       <c r="H27" s="1"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -3408,7 +4017,7 @@
       </c>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -3431,7 +4040,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -3452,7 +4061,7 @@
       </c>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -3473,7 +4082,7 @@
       </c>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -3494,7 +4103,7 @@
       </c>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -3515,7 +4124,7 @@
       </c>
       <c r="H33" s="1"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -3536,7 +4145,7 @@
       </c>
       <c r="H34" s="1"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -3557,7 +4166,7 @@
       </c>
       <c r="H35" s="1"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -3578,7 +4187,7 @@
       </c>
       <c r="H36" s="1"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -3599,7 +4208,7 @@
       </c>
       <c r="H37" s="1"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -3620,7 +4229,7 @@
       </c>
       <c r="H38" s="1"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -3641,7 +4250,7 @@
       </c>
       <c r="H39" s="1"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -3662,7 +4271,7 @@
       </c>
       <c r="H40" s="1"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -3683,7 +4292,7 @@
       </c>
       <c r="H41" s="1"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -3704,7 +4313,7 @@
       </c>
       <c r="H42" s="1"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -3725,7 +4334,7 @@
       </c>
       <c r="H43" s="1"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -3746,7 +4355,7 @@
       </c>
       <c r="H44" s="1"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -3767,7 +4376,7 @@
       </c>
       <c r="H45" s="1"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -3788,7 +4397,7 @@
       </c>
       <c r="H46" s="1"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -3812,7 +4421,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -3836,7 +4445,7 @@
       </c>
       <c r="H48" s="1"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -3857,7 +4466,7 @@
       </c>
       <c r="H49" s="1"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -3878,7 +4487,7 @@
       </c>
       <c r="H50" s="1"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -3899,7 +4508,7 @@
       </c>
       <c r="H51" s="1"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -3920,7 +4529,7 @@
       </c>
       <c r="H52" s="1"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -3941,7 +4550,7 @@
       </c>
       <c r="H53" s="1"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -3962,7 +4571,7 @@
       </c>
       <c r="H54" s="1"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -3983,7 +4592,7 @@
       </c>
       <c r="H55" s="1"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -4004,7 +4613,7 @@
       </c>
       <c r="H56" s="1"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -4025,7 +4634,7 @@
       </c>
       <c r="H57" s="1"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -4046,7 +4655,7 @@
       </c>
       <c r="H58" s="1"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -4067,7 +4676,7 @@
       </c>
       <c r="H59" s="1"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -4088,7 +4697,7 @@
       </c>
       <c r="H60" s="1"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -4112,7 +4721,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -4136,7 +4745,7 @@
       </c>
       <c r="H62" s="1"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -4157,7 +4766,7 @@
       </c>
       <c r="H63" s="1"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -4178,7 +4787,7 @@
       </c>
       <c r="H64" s="1"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -4199,7 +4808,7 @@
       </c>
       <c r="H65" s="1"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -4220,7 +4829,7 @@
       </c>
       <c r="H66" s="1"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -4241,7 +4850,7 @@
       </c>
       <c r="H67" s="1"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -4265,7 +4874,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -4289,7 +4898,7 @@
       </c>
       <c r="H69" s="1"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -4312,7 +4921,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -4333,7 +4942,7 @@
       </c>
       <c r="H71" s="1"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -4354,7 +4963,7 @@
       </c>
       <c r="H72" s="1"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -4377,7 +4986,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -4400,7 +5009,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -4421,7 +5030,7 @@
       </c>
       <c r="H75" s="1"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -4434,18 +5043,18 @@
       <c r="D76" t="s">
         <v>59</v>
       </c>
-      <c r="F76" s="5" t="s">
-        <v>259</v>
+      <c r="F76" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="G76" s="1">
         <v>75</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -4459,17 +5068,17 @@
         <v>18</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F77" s="5" t="s">
-        <v>258</v>
+        <v>97</v>
+      </c>
+      <c r="F77" s="6" t="s">
+        <v>98</v>
       </c>
       <c r="G77" s="1">
         <v>76</v>
       </c>
       <c r="H77" s="1"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -4483,14 +5092,14 @@
         <v>11</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G78" s="1">
         <v>77</v>
       </c>
       <c r="H78" s="1"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -4504,7 +5113,7 @@
         <v>11</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G79" s="1">
         <v>78</v>
@@ -4513,7 +5122,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -4527,14 +5136,14 @@
         <v>11</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G80" s="1">
         <v>79</v>
       </c>
       <c r="H80" s="1"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -4548,14 +5157,14 @@
         <v>11</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G81" s="1">
         <v>80</v>
       </c>
       <c r="H81" s="1"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -4569,14 +5178,14 @@
         <v>11</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G82" s="1">
         <v>81</v>
       </c>
       <c r="H82" s="1"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -4590,7 +5199,7 @@
         <v>11</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G83" s="1">
         <v>82</v>
@@ -4599,7 +5208,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -4613,13 +5222,13 @@
         <v>11</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G84" s="1">
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -4633,13 +5242,13 @@
         <v>11</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G85" s="1">
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -4653,14 +5262,14 @@
         <v>11</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G86" s="1">
         <v>85</v>
       </c>
       <c r="H86" s="1"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -4674,13 +5283,13 @@
         <v>11</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G87" s="1">
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -4694,14 +5303,14 @@
         <v>11</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G88" s="1">
         <v>87</v>
       </c>
       <c r="H88" s="1"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -4714,8 +5323,8 @@
       <c r="D89" t="s">
         <v>11</v>
       </c>
-      <c r="F89" s="5" t="s">
-        <v>260</v>
+      <c r="F89" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="G89" s="1">
         <v>88</v>
@@ -4724,7 +5333,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8">
       <c r="A90" s="1">
         <v>88</v>
       </c>
@@ -4738,14 +5347,14 @@
         <v>11</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G90" s="1">
         <v>89</v>
       </c>
       <c r="H90" s="1"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7">
       <c r="A91" s="1">
         <v>89</v>
       </c>
@@ -4759,13 +5368,13 @@
         <v>11</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G91" s="1">
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8">
       <c r="A92" s="1">
         <v>90</v>
       </c>
@@ -4779,7 +5388,7 @@
         <v>11</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G92" s="1">
         <v>91</v>
@@ -4788,7 +5397,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8">
       <c r="A93" s="1">
         <v>91</v>
       </c>
@@ -4809,7 +5418,7 @@
       </c>
       <c r="H93" s="1"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7">
       <c r="A94" s="1">
         <v>92</v>
       </c>
@@ -4822,14 +5431,14 @@
       <c r="D94" t="s">
         <v>11</v>
       </c>
-      <c r="F94" s="5" t="s">
-        <v>261</v>
+      <c r="F94" s="6" t="s">
+        <v>114</v>
       </c>
       <c r="G94" s="1">
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8">
       <c r="A95" s="1">
         <v>93</v>
       </c>
@@ -4843,14 +5452,14 @@
         <v>11</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G95" s="1">
         <v>94</v>
       </c>
       <c r="H95" s="1"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8">
       <c r="A96" s="1">
         <v>94</v>
       </c>
@@ -4864,14 +5473,14 @@
         <v>11</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G96" s="1">
         <v>95</v>
       </c>
       <c r="H96" s="1"/>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9">
       <c r="A97" s="1">
         <v>95</v>
       </c>
@@ -4885,17 +5494,17 @@
         <v>59</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G97" s="1">
         <v>96</v>
       </c>
       <c r="H97" s="1"/>
       <c r="I97" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
       <c r="A98" s="1">
         <v>96</v>
       </c>
@@ -4909,17 +5518,17 @@
         <v>18</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G98" s="1">
         <v>97</v>
       </c>
       <c r="H98" s="1"/>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8">
       <c r="A99" s="1">
         <v>97</v>
       </c>
@@ -4933,14 +5542,14 @@
         <v>11</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G99" s="1">
         <v>98</v>
       </c>
       <c r="H99" s="1"/>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8">
       <c r="A100" s="1">
         <v>98</v>
       </c>
@@ -4954,14 +5563,14 @@
         <v>11</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G100" s="1">
         <v>99</v>
       </c>
       <c r="H100" s="1"/>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8">
       <c r="A101" s="1">
         <v>99</v>
       </c>
@@ -4975,14 +5584,14 @@
         <v>11</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G101" s="1">
         <v>100</v>
       </c>
       <c r="H101" s="1"/>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8">
       <c r="A102" s="1">
         <v>100</v>
       </c>
@@ -4996,14 +5605,14 @@
         <v>11</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G102" s="1">
         <v>101</v>
       </c>
       <c r="H102" s="1"/>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8">
       <c r="A103" s="1">
         <v>101</v>
       </c>
@@ -5017,14 +5626,14 @@
         <v>11</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G103" s="1">
         <v>102</v>
       </c>
       <c r="H103" s="1"/>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8">
       <c r="A104" s="1">
         <v>102</v>
       </c>
@@ -5038,14 +5647,14 @@
         <v>11</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G104" s="1">
         <v>103</v>
       </c>
       <c r="H104" s="1"/>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8">
       <c r="A105" s="1">
         <v>103</v>
       </c>
@@ -5059,14 +5668,14 @@
         <v>18</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G105" s="1">
         <v>104</v>
       </c>
       <c r="H105" s="1"/>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8">
       <c r="A106" s="1">
         <v>104</v>
       </c>
@@ -5080,14 +5689,14 @@
         <v>11</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G106" s="1">
         <v>105</v>
       </c>
       <c r="H106" s="1"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8">
       <c r="A107" s="1">
         <v>105</v>
       </c>
@@ -5101,14 +5710,14 @@
         <v>11</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G107" s="1">
         <v>106</v>
       </c>
       <c r="H107" s="1"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8">
       <c r="A108" s="1">
         <v>106</v>
       </c>
@@ -5122,14 +5731,14 @@
         <v>11</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G108" s="1">
         <v>107</v>
       </c>
       <c r="H108" s="1"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8">
       <c r="A109" s="1">
         <v>107</v>
       </c>
@@ -5143,14 +5752,14 @@
         <v>11</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G109" s="1">
         <v>108</v>
       </c>
       <c r="H109" s="1"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8">
       <c r="A110" s="1">
         <v>108</v>
       </c>
@@ -5164,14 +5773,14 @@
         <v>59</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="G110" s="1">
         <v>109</v>
       </c>
       <c r="H110" s="1"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8">
       <c r="A111" s="1">
         <v>109</v>
       </c>
@@ -5185,10 +5794,10 @@
         <v>18</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G111" s="1">
         <v>110</v>
@@ -5197,7 +5806,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8">
       <c r="A112" s="1">
         <v>110</v>
       </c>
@@ -5211,7 +5820,7 @@
         <v>11</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G112" s="1">
         <v>111</v>
@@ -5220,7 +5829,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8">
       <c r="A113" s="1">
         <v>111</v>
       </c>
@@ -5234,7 +5843,7 @@
         <v>11</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G113" s="1">
         <v>112</v>
@@ -5243,7 +5852,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8">
       <c r="A114" s="1">
         <v>112</v>
       </c>
@@ -5257,14 +5866,14 @@
         <v>11</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G114" s="1">
         <v>113</v>
       </c>
       <c r="H114" s="1"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8">
       <c r="A115" s="1">
         <v>113</v>
       </c>
@@ -5278,14 +5887,14 @@
         <v>11</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="G115" s="1">
         <v>114</v>
       </c>
       <c r="H115" s="1"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8">
       <c r="A116" s="1">
         <v>114</v>
       </c>
@@ -5299,14 +5908,14 @@
         <v>11</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G116" s="1">
         <v>115</v>
       </c>
       <c r="H116" s="1"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8">
       <c r="A117" s="1">
         <v>115</v>
       </c>
@@ -5320,14 +5929,14 @@
         <v>18</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G117" s="1">
         <v>116</v>
       </c>
       <c r="H117" s="1"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8">
       <c r="A118" s="1">
         <v>116</v>
       </c>
@@ -5341,14 +5950,14 @@
         <v>18</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G118" s="1">
         <v>117</v>
       </c>
       <c r="H118" s="1"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8">
       <c r="A119" s="1">
         <v>117</v>
       </c>
@@ -5362,14 +5971,14 @@
         <v>11</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G119" s="1">
         <v>118</v>
       </c>
       <c r="H119" s="1"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8">
       <c r="A120" s="1">
         <v>118</v>
       </c>
@@ -5383,14 +5992,14 @@
         <v>11</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G120" s="1">
         <v>119</v>
       </c>
       <c r="H120" s="1"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8">
       <c r="A121" s="1">
         <v>119</v>
       </c>
@@ -5404,14 +6013,14 @@
         <v>11</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G121" s="1">
         <v>120</v>
       </c>
       <c r="H121" s="1"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7">
       <c r="A122" s="1">
         <v>120</v>
       </c>
@@ -5425,13 +6034,13 @@
         <v>11</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G122" s="1">
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8">
       <c r="A123" s="1">
         <v>121</v>
       </c>
@@ -5445,14 +6054,14 @@
         <v>18</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G123" s="1">
         <v>122</v>
       </c>
       <c r="H123" s="1"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8">
       <c r="A124" s="1">
         <v>122</v>
       </c>
@@ -5466,14 +6075,14 @@
         <v>11</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G124" s="1">
         <v>123</v>
       </c>
       <c r="H124" s="1"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7">
       <c r="A125" s="1">
         <v>123</v>
       </c>
@@ -5487,13 +6096,13 @@
         <v>11</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="G125" s="1">
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7">
       <c r="A126" s="1">
         <v>124</v>
       </c>
@@ -5507,13 +6116,13 @@
         <v>11</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G126" s="1">
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8">
       <c r="A127" s="1">
         <v>125</v>
       </c>
@@ -5527,14 +6136,14 @@
         <v>11</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="G127" s="1">
         <v>126</v>
       </c>
       <c r="H127" s="1"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8">
       <c r="A128" s="1">
         <v>126</v>
       </c>
@@ -5548,14 +6157,14 @@
         <v>11</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G128" s="1">
         <v>127</v>
       </c>
       <c r="H128" s="1"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8">
       <c r="A129" s="1">
         <v>127</v>
       </c>
@@ -5569,14 +6178,14 @@
         <v>11</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G129" s="1">
         <v>128</v>
       </c>
       <c r="H129" s="1"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9">
       <c r="A130" s="1">
         <v>128</v>
       </c>
@@ -5590,17 +6199,17 @@
         <v>59</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="G130" s="1">
         <v>129</v>
       </c>
       <c r="H130" s="1"/>
       <c r="I130" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
       <c r="A131" s="1">
         <v>129</v>
       </c>
@@ -5614,17 +6223,17 @@
         <v>18</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G131" s="1">
         <v>130</v>
       </c>
       <c r="H131" s="1"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8">
       <c r="A132" s="1">
         <v>130</v>
       </c>
@@ -5638,14 +6247,14 @@
         <v>11</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G132" s="1">
         <v>131</v>
       </c>
       <c r="H132" s="1"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8">
       <c r="A133" s="1">
         <v>131</v>
       </c>
@@ -5659,14 +6268,14 @@
         <v>11</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="G133" s="1">
         <v>132</v>
       </c>
       <c r="H133" s="1"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8">
       <c r="A134" s="1">
         <v>132</v>
       </c>
@@ -5680,14 +6289,14 @@
         <v>11</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="G134" s="1">
         <v>133</v>
       </c>
       <c r="H134" s="1"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8">
       <c r="A135" s="1">
         <v>133</v>
       </c>
@@ -5701,14 +6310,14 @@
         <v>59</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="G135" s="1">
         <v>134</v>
       </c>
       <c r="H135" s="1"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8">
       <c r="A136" s="1">
         <v>134</v>
       </c>
@@ -5722,17 +6331,17 @@
         <v>11</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="G136" s="1">
         <v>135</v>
       </c>
       <c r="H136" s="1"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8">
       <c r="A137" s="1">
         <v>135</v>
       </c>
@@ -5746,14 +6355,14 @@
         <v>11</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="G137" s="1">
         <v>136</v>
       </c>
       <c r="H137" s="1"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9">
       <c r="A138" s="1">
         <v>136</v>
       </c>
@@ -5767,26 +6376,27 @@
         <v>59</v>
       </c>
       <c r="F138" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="G138" s="1">
         <v>-1</v>
       </c>
       <c r="H138" s="1"/>
       <c r="I138" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="24"/>
@@ -5795,7 +6405,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5824,46 +6434,46 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G2" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>249</v>
+        <v>10</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>251</v>
+        <v>11</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>167</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
@@ -5871,19 +6481,19 @@
       <c r="D4" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>252</v>
+      <c r="F4" s="6" t="s">
+        <v>168</v>
       </c>
       <c r="G4" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -5891,19 +6501,19 @@
       <c r="D5" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>253</v>
+      <c r="F5" s="6" t="s">
+        <v>169</v>
       </c>
       <c r="G5" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -5911,19 +6521,19 @@
       <c r="D6" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>254</v>
+      <c r="F6" s="6" t="s">
+        <v>170</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -5932,18 +6542,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -5958,12 +6568,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -5971,65 +6581,65 @@
       <c r="D9" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>255</v>
+      <c r="F9" s="6" t="s">
+        <v>172</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="F10" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
         <v>166</v>
       </c>
-      <c r="G10" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>162</v>
-      </c>
       <c r="C11" t="s">
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="G11" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C12" t="s">
         <v>58</v>
@@ -6037,19 +6647,19 @@
       <c r="D12" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>256</v>
+      <c r="F12" s="6" t="s">
+        <v>178</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -6058,21 +6668,21 @@
         <v>11</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C14" t="s">
         <v>17</v>
@@ -6081,18 +6691,18 @@
         <v>18</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="G14" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C15" t="s">
         <v>10</v>
@@ -6101,18 +6711,21 @@
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="G15" s="1">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H15" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C16" t="s">
         <v>58</v>
@@ -6121,18 +6734,18 @@
         <v>59</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="G16" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
@@ -6141,21 +6754,21 @@
         <v>11</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="G17" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -6164,18 +6777,18 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="G18" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7">
       <c r="A19" s="1">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C19" t="s">
         <v>10</v>
@@ -6184,18 +6797,18 @@
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="G19" s="1">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8">
       <c r="A20" s="1">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
@@ -6204,7 +6817,7 @@
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="G20" s="1">
         <v>19</v>
@@ -6213,12 +6826,12 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8">
       <c r="A21" s="1">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C21" t="s">
         <v>10</v>
@@ -6226,8 +6839,8 @@
       <c r="D21" t="s">
         <v>11</v>
       </c>
-      <c r="F21" s="5" t="s">
-        <v>257</v>
+      <c r="F21" s="6" t="s">
+        <v>189</v>
       </c>
       <c r="G21" s="1">
         <v>20</v>
@@ -6236,12 +6849,12 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7">
       <c r="A22" s="1">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C22" t="s">
         <v>10</v>
@@ -6250,18 +6863,18 @@
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="G22" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7">
       <c r="A23" s="1">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C23" t="s">
         <v>10</v>
@@ -6270,18 +6883,18 @@
         <v>11</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G23" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7">
       <c r="A24" s="1">
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C24" t="s">
         <v>17</v>
@@ -6290,18 +6903,18 @@
         <v>18</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="G24" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7">
       <c r="A25" s="1">
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C25" t="s">
         <v>17</v>
@@ -6310,18 +6923,18 @@
         <v>18</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="G25" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7">
       <c r="A26" s="1">
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C26" t="s">
         <v>17</v>
@@ -6330,18 +6943,18 @@
         <v>18</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="G26" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7">
       <c r="A27" s="1">
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C27" t="s">
         <v>10</v>
@@ -6350,18 +6963,18 @@
         <v>11</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="G27" s="1">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7">
       <c r="A28" s="1">
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C28" t="s">
         <v>10</v>
@@ -6370,18 +6983,18 @@
         <v>11</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="G28" s="1">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7">
       <c r="A29" s="1">
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C29" t="s">
         <v>10</v>
@@ -6390,18 +7003,18 @@
         <v>11</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="G29" s="1">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7">
       <c r="A30" s="1">
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C30" t="s">
         <v>58</v>
@@ -6410,22 +7023,23 @@
         <v>59</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="G30" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -6434,7 +7048,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6463,26 +7077,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="G2" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -6491,18 +7105,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -6511,18 +7125,18 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -6531,18 +7145,18 @@
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="G5" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -6551,18 +7165,18 @@
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -6571,18 +7185,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -6591,18 +7205,18 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -6611,18 +7225,18 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="C10" t="s">
         <v>17</v>
@@ -6631,21 +7245,21 @@
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="G10" s="1">
         <v>-1</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="C11" t="s">
         <v>17</v>
@@ -6654,21 +7268,21 @@
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="G11" s="1">
         <v>-1</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -6677,25 +7291,26 @@
         <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="G12" s="1">
         <v>-1</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -6704,7 +7319,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6733,26 +7348,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="G2" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -6761,18 +7376,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -6781,64 +7396,64 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="G5" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -6847,18 +7462,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -6867,18 +7482,18 @@
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="G8" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -6887,18 +7502,18 @@
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="G9" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
@@ -6907,18 +7522,18 @@
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="G10" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
@@ -6927,19 +7542,19 @@
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="G11" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
         <v>212</v>
       </c>
-      <c r="G11" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>200</v>
-      </c>
       <c r="C12" t="s">
         <v>10</v>
       </c>
@@ -6947,18 +7562,18 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -6967,18 +7582,18 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -6987,22 +7602,23 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="G14" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -7011,7 +7627,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7040,26 +7656,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="G2" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7068,18 +7684,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7088,18 +7704,18 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -7108,18 +7724,18 @@
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="G5" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -7128,18 +7744,18 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -7148,18 +7764,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -7168,18 +7784,18 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -7188,64 +7804,64 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>228</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>173</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" t="s">
-        <v>164</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>204</v>
-      </c>
       <c r="F10" s="2" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="G10" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="G11" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
@@ -7254,18 +7870,18 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -7274,18 +7890,18 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -7294,18 +7910,18 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="G14" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C15" t="s">
         <v>58</v>
@@ -7314,18 +7930,18 @@
         <v>59</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="G15" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C16" t="s">
         <v>10</v>
@@ -7334,18 +7950,18 @@
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="G16" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
@@ -7354,18 +7970,18 @@
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="G17" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -7374,22 +7990,23 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="G18" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -7398,7 +8015,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7427,26 +8044,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7455,18 +8072,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7475,22 +8092,23 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="G4" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -7499,7 +8117,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7528,26 +8146,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7556,18 +8174,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7576,22 +8194,23 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="G4" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -7600,7 +8219,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7629,26 +8248,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7657,18 +8276,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7677,18 +8296,18 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -7697,18 +8316,18 @@
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="G5" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -7717,18 +8336,18 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="G6" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -7737,18 +8356,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -7757,18 +8376,18 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="G8" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -7777,14 +8396,14 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="G9" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Excel/ChatData.xlsx
+++ b/Assets/StreamingAssets/Excel/ChatData.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D69A4ED8-B662-4EC0-9C6C-DA1565BA7348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="一切的开始" sheetId="1" r:id="rId1"/>
@@ -17,19 +23,6 @@
     <sheet name="困了_03" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -1515,724 +1508,721 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>打开“制作窗口”,指挥麦麦制作一个“裂缝填充物”</t>
+    </r>
+  </si>
+  <si>
+    <t>制作裂缝填充物</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>做好啦！</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>原来那论文捣鼓了半天就是做这个东西呀？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这个我熟啊</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>以前刮大风的时候,家里的屋顶不是被吹走就是被东西砸破。然后雨就哗啦啦地淋进来</t>
+    </r>
+  </si>
+  <si>
+    <t>那个雨又脏又臭,淋到头上还会掉头发</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这时候我爸就会做一个差不多的东西把屋顶补上。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我没自己做过,可也经常在旁边看</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>那你很有生活经验了</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>原来你以前还有这样的经历呀</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>完全不一样好吧，论文里其实写了很多方案，只是根据你目前的情况选了个最原始的方案</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>原来是这样吗？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不过能解决问题就好</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>接下来就看我的吧,我保证把裂缝堵得严严实实的</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点击"渗水裂缝",打开其详情窗口,然后点击"堵住"，就能堵住裂缝了</t>
+    </r>
+  </si>
+  <si>
+    <t>死亡</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>健康&lt;=0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我真的支撑不住了</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我对不起哈特,对不起爸爸妈妈……</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>当初为什么要去做那些不切实际的梦呢……</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不知道爸爸妈妈现在怎么样了……</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>如果有一天,你能联系到他们</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>请告诉他们</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>“麦麦爱你们”</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不……</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>其他_死亡</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>醒醒,再坚持一下,会有希望的</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>[忘记这一切]</t>
+    </r>
+  </si>
+  <si>
+    <t>第一次点开气密舱门</t>
+  </si>
+  <si>
+    <t>首次点开气密舱门</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我找到出舱的门了</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>外面应该是一片水域环境,不知道水有多深</t>
+    </r>
+  </si>
+  <si>
+    <t>未装备氧气面罩</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最好是戴上氧气面罩再出去探索比较好</t>
+    </r>
+  </si>
+  <si>
+    <t>已装备氧气面罩</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>虽然已经戴上氧气面罩了,但心里还是有些害怕</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>可是飞船里的资源总是会耗尽的,就算再害怕，也还是得出去看看</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>小心一点,不要太勉强</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>说不定开门就捡到一架完整的宇宙飞船,然后你就能直接开船回去了呢</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>嗯,好的</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>那还是有点夸张</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不过,借你吉言啦</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>话说，你那边应该能看见我的身体状态吧。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>如果氧气快不够了，你一定要早点提醒我往回走。</t>
+    </r>
+  </si>
+  <si>
+    <t>第一次进珊瑚礁海域</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>第一次进入珊瑚礁海域</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>唔,唔嗯嗯唔唔嗯呢</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>呜呜嗯嗯？呢唔唔呜呜唔唔唔,嗯嗯喔喔额额</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你悠着点,别呛水了</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你在干嘛？你不是能用脑电交流吗？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>哦哦</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我忘记了</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>下意识地就想直接讲话,但是又讲不出来</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>没戴氧气面罩就潜水真的太难受了</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这个氧气面罩挺好使的</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我感觉眼睛很痛</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>话说这颗星球的水里会不会有什么有害物质呀？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>要不还是先回飞船,等做出氧气面罩了,再出来探索？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不戴氧气面罩探索水域环境时需要消耗更多时间,且每次探索都会减少健康</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>一滴水都没漏进来</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>接下来我们该探索一下飞船外的这片区域了</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最好能找到些吃的,以及淡水的来源</t>
+    </r>
+  </si>
+  <si>
+    <t>困了_01</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>每次清醒度&lt;=30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>呼,感觉眼睛都睁不开了</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>要不考虑先回去休息一下？</t>
+    </r>
+  </si>
+  <si>
+    <t>困了_02</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是不是该休息了？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>感觉已经好久没睡觉了</t>
+    </r>
+  </si>
+  <si>
+    <t>困了_03</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>感觉眼睛有点干干的</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是不是该休息一下了？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不是的,你还能加班,别这么早休息</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>那还是回去睡一觉吧</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>……</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>好吧</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>嗯</t>
+    </r>
+  </si>
+  <si>
     <t>解锁_制作</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>打开“制作窗口”,指挥麦麦制作一个“裂缝填充物”</t>
-    </r>
-  </si>
-  <si>
-    <t>制作裂缝填充物</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>做好啦！</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>原来那论文捣鼓了半天就是做这个东西呀？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这个我熟啊</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>以前刮大风的时候,家里的屋顶不是被吹走就是被东西砸破。然后雨就哗啦啦地淋进来</t>
-    </r>
-  </si>
-  <si>
-    <t>那个雨又脏又臭,淋到头上还会掉头发</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这时候我爸就会做一个差不多的东西把屋顶补上。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我没自己做过,可也经常在旁边看</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>那你很有生活经验了</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>原来你以前还有这样的经历呀</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>完全不一样好吧，论文里其实写了很多方案，只是根据你目前的情况选了个最原始的方案</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>原来是这样吗？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>不过能解决问题就好</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>接下来就看我的吧,我保证把裂缝堵得严严实实的</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>点击"渗水裂缝",打开其详情窗口,然后点击"堵住"，就能堵住裂缝了</t>
-    </r>
-  </si>
-  <si>
-    <t>死亡</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>健康&lt;=0</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我真的支撑不住了</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我对不起哈特,对不起爸爸妈妈……</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>当初为什么要去做那些不切实际的梦呢……</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>不知道爸爸妈妈现在怎么样了……</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>如果有一天,你能联系到他们</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>请告诉他们</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>“麦麦爱你们”</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>不……</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>其他_死亡</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>醒醒,再坚持一下,会有希望的</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>[忘记这一切]</t>
-    </r>
-  </si>
-  <si>
-    <t>第一次点开气密舱门</t>
-  </si>
-  <si>
-    <t>首次点开气密舱门</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我找到出舱的门了</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>外面应该是一片水域环境,不知道水有多深</t>
-    </r>
-  </si>
-  <si>
-    <t>未装备氧气面罩</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>最好是戴上氧气面罩再出去探索比较好</t>
-    </r>
-  </si>
-  <si>
-    <t>已装备氧气面罩</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>虽然已经戴上氧气面罩了,但心里还是有些害怕</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>可是飞船里的资源总是会耗尽的,就算再害怕，也还是得出去看看</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>小心一点,不要太勉强</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>说不定开门就捡到一架完整的宇宙飞船,然后你就能直接开船回去了呢</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>嗯,好的</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>那还是有点夸张</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>不过,借你吉言啦</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>话说，你那边应该能看见我的身体状态吧。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>如果氧气快不够了，你一定要早点提醒我往回走。</t>
-    </r>
-  </si>
-  <si>
-    <t>第一次进珊瑚礁海域</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>第一次进入珊瑚礁海域</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>唔,唔嗯嗯唔唔嗯呢</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>呜呜嗯嗯？呢唔唔呜呜唔唔唔,嗯嗯喔喔额额</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>你悠着点,别呛水了</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>你在干嘛？你不是能用脑电交流吗？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>哦哦</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我忘记了</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>下意识地就想直接讲话,但是又讲不出来</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>没戴氧气面罩就潜水真的太难受了</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这个氧气面罩挺好使的</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我感觉眼睛很痛</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>话说这颗星球的水里会不会有什么有害物质呀？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>要不还是先回飞船,等做出氧气面罩了,再出来探索？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>不戴氧气面罩探索水域环境时需要消耗更多时间,且每次探索都会减少健康</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>一滴水都没漏进来</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>接下来我们该探索一下飞船外的这片区域了</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>最好能找到些吃的,以及淡水的来源</t>
-    </r>
-  </si>
-  <si>
-    <t>困了_01</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>每次清醒度&lt;=30</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>呼,感觉眼睛都睁不开了</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>要不考虑先回去休息一下？</t>
-    </r>
-  </si>
-  <si>
-    <t>困了_02</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>是不是该休息了？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>感觉已经好久没睡觉了</t>
-    </r>
-  </si>
-  <si>
-    <t>困了_03</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>感觉眼睛有点干干的</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>是不是该休息一下了？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>不是的,你还能加班,别这么早休息</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>那还是回去睡一觉吧</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>……</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>好吧</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>嗯</t>
-    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.00_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="1">
+    <numFmt numFmtId="178" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -2270,352 +2260,30 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -2623,259 +2291,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2893,90 +2319,162 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -2987,7 +2485,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -3015,154 +2513,40 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -3420,14 +2804,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I138"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="27"/>
@@ -3437,7 +2821,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3466,7 +2850,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -3478,7 +2862,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3499,7 +2883,7 @@
       </c>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -3520,7 +2904,7 @@
       </c>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -3540,7 +2924,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -3560,7 +2944,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -3581,7 +2965,7 @@
       </c>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -3602,7 +2986,7 @@
       </c>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -3623,7 +3007,7 @@
       </c>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -3644,7 +3028,7 @@
       </c>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -3665,7 +3049,7 @@
       </c>
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -3685,7 +3069,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -3706,7 +3090,7 @@
       </c>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -3726,7 +3110,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -3747,7 +3131,7 @@
       </c>
       <c r="H15" s="1"/>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -3768,7 +3152,7 @@
       </c>
       <c r="H16" s="1"/>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -3788,7 +3172,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -3808,7 +3192,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -3829,7 +3213,7 @@
       </c>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -3850,7 +3234,7 @@
       </c>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -3871,7 +3255,7 @@
       </c>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -3892,7 +3276,7 @@
       </c>
       <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -3913,7 +3297,7 @@
       </c>
       <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -3933,7 +3317,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -3954,7 +3338,7 @@
       </c>
       <c r="H25" s="1"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -3975,7 +3359,7 @@
       </c>
       <c r="H26" s="1"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -3996,7 +3380,7 @@
       </c>
       <c r="H27" s="1"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -4017,7 +3401,7 @@
       </c>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -4040,7 +3424,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -4061,7 +3445,7 @@
       </c>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -4082,7 +3466,7 @@
       </c>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -4103,7 +3487,7 @@
       </c>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -4124,7 +3508,7 @@
       </c>
       <c r="H33" s="1"/>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -4145,7 +3529,7 @@
       </c>
       <c r="H34" s="1"/>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -4166,7 +3550,7 @@
       </c>
       <c r="H35" s="1"/>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -4187,7 +3571,7 @@
       </c>
       <c r="H36" s="1"/>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -4208,7 +3592,7 @@
       </c>
       <c r="H37" s="1"/>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -4229,7 +3613,7 @@
       </c>
       <c r="H38" s="1"/>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -4250,7 +3634,7 @@
       </c>
       <c r="H39" s="1"/>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -4271,7 +3655,7 @@
       </c>
       <c r="H40" s="1"/>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -4292,7 +3676,7 @@
       </c>
       <c r="H41" s="1"/>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -4313,7 +3697,7 @@
       </c>
       <c r="H42" s="1"/>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -4334,7 +3718,7 @@
       </c>
       <c r="H43" s="1"/>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -4355,7 +3739,7 @@
       </c>
       <c r="H44" s="1"/>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -4376,7 +3760,7 @@
       </c>
       <c r="H45" s="1"/>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -4397,7 +3781,7 @@
       </c>
       <c r="H46" s="1"/>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -4421,7 +3805,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -4445,7 +3829,7 @@
       </c>
       <c r="H48" s="1"/>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -4466,7 +3850,7 @@
       </c>
       <c r="H49" s="1"/>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -4487,7 +3871,7 @@
       </c>
       <c r="H50" s="1"/>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -4508,7 +3892,7 @@
       </c>
       <c r="H51" s="1"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -4529,7 +3913,7 @@
       </c>
       <c r="H52" s="1"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -4550,7 +3934,7 @@
       </c>
       <c r="H53" s="1"/>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -4571,7 +3955,7 @@
       </c>
       <c r="H54" s="1"/>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -4592,7 +3976,7 @@
       </c>
       <c r="H55" s="1"/>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -4613,7 +3997,7 @@
       </c>
       <c r="H56" s="1"/>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -4634,7 +4018,7 @@
       </c>
       <c r="H57" s="1"/>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -4655,7 +4039,7 @@
       </c>
       <c r="H58" s="1"/>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -4676,7 +4060,7 @@
       </c>
       <c r="H59" s="1"/>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -4697,7 +4081,7 @@
       </c>
       <c r="H60" s="1"/>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -4721,7 +4105,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -4745,7 +4129,7 @@
       </c>
       <c r="H62" s="1"/>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -4766,7 +4150,7 @@
       </c>
       <c r="H63" s="1"/>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -4787,7 +4171,7 @@
       </c>
       <c r="H64" s="1"/>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -4808,7 +4192,7 @@
       </c>
       <c r="H65" s="1"/>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -4829,7 +4213,7 @@
       </c>
       <c r="H66" s="1"/>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -4850,7 +4234,7 @@
       </c>
       <c r="H67" s="1"/>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -4874,7 +4258,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -4898,7 +4282,7 @@
       </c>
       <c r="H69" s="1"/>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -4921,7 +4305,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -4942,7 +4326,7 @@
       </c>
       <c r="H71" s="1"/>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -4963,7 +4347,7 @@
       </c>
       <c r="H72" s="1"/>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -4986,7 +4370,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -5009,7 +4393,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -5030,7 +4414,7 @@
       </c>
       <c r="H75" s="1"/>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -5054,7 +4438,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -5078,7 +4462,7 @@
       </c>
       <c r="H77" s="1"/>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -5099,7 +4483,7 @@
       </c>
       <c r="H78" s="1"/>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -5122,7 +4506,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -5143,7 +4527,7 @@
       </c>
       <c r="H80" s="1"/>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -5164,7 +4548,7 @@
       </c>
       <c r="H81" s="1"/>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -5185,7 +4569,7 @@
       </c>
       <c r="H82" s="1"/>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -5208,7 +4592,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -5228,7 +4612,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -5248,7 +4632,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -5269,7 +4653,7 @@
       </c>
       <c r="H86" s="1"/>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -5289,7 +4673,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -5310,7 +4694,7 @@
       </c>
       <c r="H88" s="1"/>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -5333,7 +4717,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>88</v>
       </c>
@@ -5354,7 +4738,7 @@
       </c>
       <c r="H90" s="1"/>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>89</v>
       </c>
@@ -5374,7 +4758,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>90</v>
       </c>
@@ -5397,7 +4781,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>91</v>
       </c>
@@ -5418,7 +4802,7 @@
       </c>
       <c r="H93" s="1"/>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>92</v>
       </c>
@@ -5438,7 +4822,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>93</v>
       </c>
@@ -5459,7 +4843,7 @@
       </c>
       <c r="H95" s="1"/>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>94</v>
       </c>
@@ -5480,7 +4864,7 @@
       </c>
       <c r="H96" s="1"/>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>95</v>
       </c>
@@ -5504,7 +4888,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>96</v>
       </c>
@@ -5528,7 +4912,7 @@
       </c>
       <c r="H98" s="1"/>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>97</v>
       </c>
@@ -5549,7 +4933,7 @@
       </c>
       <c r="H99" s="1"/>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>98</v>
       </c>
@@ -5570,7 +4954,7 @@
       </c>
       <c r="H100" s="1"/>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>99</v>
       </c>
@@ -5591,7 +4975,7 @@
       </c>
       <c r="H101" s="1"/>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>100</v>
       </c>
@@ -5612,7 +4996,7 @@
       </c>
       <c r="H102" s="1"/>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>101</v>
       </c>
@@ -5633,7 +5017,7 @@
       </c>
       <c r="H103" s="1"/>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>102</v>
       </c>
@@ -5654,7 +5038,7 @@
       </c>
       <c r="H104" s="1"/>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>103</v>
       </c>
@@ -5675,7 +5059,7 @@
       </c>
       <c r="H105" s="1"/>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>104</v>
       </c>
@@ -5696,7 +5080,7 @@
       </c>
       <c r="H106" s="1"/>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>105</v>
       </c>
@@ -5717,7 +5101,7 @@
       </c>
       <c r="H107" s="1"/>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>106</v>
       </c>
@@ -5738,7 +5122,7 @@
       </c>
       <c r="H108" s="1"/>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>107</v>
       </c>
@@ -5759,7 +5143,7 @@
       </c>
       <c r="H109" s="1"/>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>108</v>
       </c>
@@ -5780,7 +5164,7 @@
       </c>
       <c r="H110" s="1"/>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>109</v>
       </c>
@@ -5806,7 +5190,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>110</v>
       </c>
@@ -5829,7 +5213,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>111</v>
       </c>
@@ -5852,7 +5236,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>112</v>
       </c>
@@ -5873,7 +5257,7 @@
       </c>
       <c r="H114" s="1"/>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>113</v>
       </c>
@@ -5894,7 +5278,7 @@
       </c>
       <c r="H115" s="1"/>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>114</v>
       </c>
@@ -5915,7 +5299,7 @@
       </c>
       <c r="H116" s="1"/>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>115</v>
       </c>
@@ -5936,7 +5320,7 @@
       </c>
       <c r="H117" s="1"/>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>116</v>
       </c>
@@ -5957,7 +5341,7 @@
       </c>
       <c r="H118" s="1"/>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>117</v>
       </c>
@@ -5978,7 +5362,7 @@
       </c>
       <c r="H119" s="1"/>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>118</v>
       </c>
@@ -5999,7 +5383,7 @@
       </c>
       <c r="H120" s="1"/>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>119</v>
       </c>
@@ -6020,7 +5404,7 @@
       </c>
       <c r="H121" s="1"/>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>120</v>
       </c>
@@ -6040,7 +5424,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>121</v>
       </c>
@@ -6061,7 +5445,7 @@
       </c>
       <c r="H123" s="1"/>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>122</v>
       </c>
@@ -6082,7 +5466,7 @@
       </c>
       <c r="H124" s="1"/>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>123</v>
       </c>
@@ -6102,7 +5486,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>124</v>
       </c>
@@ -6122,7 +5506,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>125</v>
       </c>
@@ -6143,7 +5527,7 @@
       </c>
       <c r="H127" s="1"/>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>126</v>
       </c>
@@ -6164,7 +5548,7 @@
       </c>
       <c r="H128" s="1"/>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>127</v>
       </c>
@@ -6185,7 +5569,7 @@
       </c>
       <c r="H129" s="1"/>
     </row>
-    <row r="130" spans="1:9">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>128</v>
       </c>
@@ -6209,7 +5593,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>129</v>
       </c>
@@ -6233,7 +5617,7 @@
       </c>
       <c r="H131" s="1"/>
     </row>
-    <row r="132" spans="1:8">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>130</v>
       </c>
@@ -6254,7 +5638,7 @@
       </c>
       <c r="H132" s="1"/>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>131</v>
       </c>
@@ -6275,7 +5659,7 @@
       </c>
       <c r="H133" s="1"/>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>132</v>
       </c>
@@ -6296,7 +5680,7 @@
       </c>
       <c r="H134" s="1"/>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>133</v>
       </c>
@@ -6317,7 +5701,7 @@
       </c>
       <c r="H135" s="1"/>
     </row>
-    <row r="136" spans="1:8">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>134</v>
       </c>
@@ -6341,7 +5725,7 @@
       </c>
       <c r="H136" s="1"/>
     </row>
-    <row r="137" spans="1:8">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>135</v>
       </c>
@@ -6362,7 +5746,7 @@
       </c>
       <c r="H137" s="1"/>
     </row>
-    <row r="138" spans="1:9">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>136</v>
       </c>
@@ -6387,16 +5771,15 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="24"/>
@@ -6405,7 +5788,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6434,7 +5817,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -6448,7 +5831,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -6468,7 +5851,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -6488,7 +5871,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -6508,7 +5891,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -6528,7 +5911,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -6548,7 +5931,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -6568,7 +5951,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -6588,7 +5971,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -6611,7 +5994,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -6634,7 +6017,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -6654,7 +6037,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -6677,7 +6060,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -6697,7 +6080,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -6716,11 +6099,11 @@
       <c r="G15" s="1">
         <v>14</v>
       </c>
-      <c r="H15" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="I15" s="7" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -6734,13 +6117,13 @@
         <v>59</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G16" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -6754,16 +6137,16 @@
         <v>11</v>
       </c>
       <c r="E17" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>185</v>
       </c>
       <c r="G17" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -6777,13 +6160,13 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G18" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -6797,13 +6180,13 @@
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G19" s="1">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -6817,7 +6200,7 @@
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G20" s="1">
         <v>19</v>
@@ -6826,7 +6209,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -6840,7 +6223,7 @@
         <v>11</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G21" s="1">
         <v>20</v>
@@ -6849,7 +6232,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -6863,13 +6246,13 @@
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G22" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -6883,13 +6266,13 @@
         <v>11</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G23" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -6903,13 +6286,13 @@
         <v>18</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G24" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -6923,13 +6306,13 @@
         <v>18</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G25" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -6943,13 +6326,13 @@
         <v>18</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G26" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -6963,13 +6346,13 @@
         <v>11</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G27" s="1">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -6983,13 +6366,13 @@
         <v>11</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G28" s="1">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -7003,13 +6386,13 @@
         <v>11</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G29" s="1">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -7023,23 +6406,22 @@
         <v>59</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G30" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -7048,7 +6430,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7077,26 +6459,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>200</v>
-      </c>
       <c r="G2" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7105,18 +6487,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7125,18 +6507,18 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -7145,18 +6527,18 @@
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G5" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -7165,18 +6547,18 @@
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -7185,18 +6567,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -7205,18 +6587,18 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -7225,18 +6607,18 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C10" t="s">
         <v>17</v>
@@ -7245,21 +6627,21 @@
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G10" s="1">
         <v>-1</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C11" t="s">
         <v>17</v>
@@ -7268,21 +6650,21 @@
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G11" s="1">
         <v>-1</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -7291,26 +6673,25 @@
         <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G12" s="1">
         <v>-1</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -7319,7 +6700,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7348,26 +6729,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>213</v>
       </c>
       <c r="G2" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7376,18 +6757,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7396,18 +6777,18 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -7416,21 +6797,21 @@
         <v>173</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="G5" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -7439,21 +6820,21 @@
         <v>173</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>218</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>219</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -7462,18 +6843,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -7482,18 +6863,18 @@
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G8" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -7502,18 +6883,18 @@
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G9" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
@@ -7522,78 +6903,78 @@
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G10" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>211</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="G10" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>212</v>
-      </c>
-      <c r="C11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="G11" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>211</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="G11" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>212</v>
-      </c>
-      <c r="C12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="G12" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>211</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="G12" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s">
-        <v>212</v>
-      </c>
-      <c r="C13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -7602,23 +6983,22 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G14" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -7627,7 +7007,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7656,26 +7036,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>228</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>229</v>
       </c>
       <c r="G2" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7684,18 +7064,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7704,18 +7084,18 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -7724,18 +7104,18 @@
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G5" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -7744,18 +7124,18 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -7764,18 +7144,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -7784,18 +7164,18 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -7804,18 +7184,18 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
@@ -7824,21 +7204,21 @@
         <v>173</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G10" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
@@ -7847,21 +7227,21 @@
         <v>173</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G11" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
@@ -7870,38 +7250,38 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G12" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>227</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="G12" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s">
-        <v>228</v>
-      </c>
-      <c r="C13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>240</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -7910,18 +7290,18 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G14" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C15" t="s">
         <v>58</v>
@@ -7930,18 +7310,18 @@
         <v>59</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G15" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C16" t="s">
         <v>10</v>
@@ -7950,18 +7330,18 @@
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G16" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
@@ -7970,18 +7350,18 @@
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G17" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -7990,23 +7370,22 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G18" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2" outlineLevelRow="3"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -8015,7 +7394,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8044,26 +7423,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -8072,18 +7451,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -8092,23 +7471,22 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G4" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2" outlineLevelRow="3"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -8117,7 +7495,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8146,46 +7524,46 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>250</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>251</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -8194,23 +7572,22 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G4" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -8219,7 +7596,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8248,46 +7625,46 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>254</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -8296,18 +7673,18 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -8316,18 +7693,18 @@
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G5" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -8336,18 +7713,18 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G6" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -8356,18 +7733,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -8376,18 +7753,18 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G8" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -8396,14 +7773,14 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G9" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Excel/ChatData.xlsx
+++ b/Assets/StreamingAssets/Excel/ChatData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D69A4ED8-B662-4EC0-9C6C-DA1565BA7348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{433652E6-26A3-4365-9C88-0AEE104E6FB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -517,9 +517,6 @@
     <t>提示</t>
   </si>
   <si>
-    <t>点击底边栏的摄像头图标,打开摄像头窗口</t>
-  </si>
-  <si>
     <t>解锁_摄像头</t>
   </si>
   <si>
@@ -656,16 +653,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>点开底边栏的背包图标,打开背包窗口</t>
-    </r>
-  </si>
-  <si>
     <t>解锁_背包</t>
   </si>
   <si>
@@ -811,9 +798,6 @@
     </r>
   </si>
   <si>
-    <t>双击点开桌面上的软件，打开"状态"窗口</t>
-  </si>
-  <si>
     <t>解锁_状态</t>
   </si>
   <si>
@@ -989,16 +973,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>点击底边栏的研究图标,打开"研究"窗口</t>
-    </r>
-  </si>
-  <si>
     <t>解锁_研究</t>
   </si>
   <si>
@@ -1125,1093 +1099,1092 @@
     </r>
   </si>
   <si>
+    <t>研究修理这项科技</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>稍等一下,我还在看</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>嗯……摘要、研究背景、创新性、问题定义、研究目的……</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>虽然是比较靠前的文章,但对我来说还是有些深奥。研究完这些东西估计需要些时间</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>论文是2395年发表在《星际工程学报》上的,很多名词我都没听过</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>顺带一提,我这边现在是*XXXX*年</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>哦</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>哦？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你为什么不震惊啊？我对你来说是古代人诶</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>没有没有,只是今天发生的事太多了,我都有些麻木了</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我现在就只想着一件事</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>就是赶快把飞船的裂缝堵起来</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>然后去维生舱找哈特</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>哈特是谁？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>哦,我还没跟你提过</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>哈特是我的妹妹</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>同时她也是这艘飞船的驾驶员</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>之前在轨道飞行时,她感到有些恶心,就先到休眠仓里休息了</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不知道她现在怎么样了,我得赶快找到她才行</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>可是我现在现在飞船里一团乱,我连去其他舱室的路都找不到了</t>
+    </r>
+  </si>
+  <si>
+    <t>解锁_地点</t>
+  </si>
+  <si>
+    <t>打开地点窗口</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我这边有一个能监测地点环境的软件,能看到你所在地点的信息</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>虽然图上看起来有些乱,但是我大概知道去其他舱室的门在哪个方向</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不过我毕竟不在现场,我把位置告诉你,你来清理一条路出来</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>没问题！我会按照你说的做的</t>
+    </r>
+  </si>
+  <si>
+    <t>点击地点窗口中的"开始探索"按钮</t>
+  </si>
+  <si>
+    <t>点击探索按钮</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我按照你说的清理了一下道路,还找到了一些东西</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>说起来修补裂缝也还需要材料,正好可以趁你研究的这段时间收集一下</t>
+    </r>
+  </si>
+  <si>
+    <t>修理研究完毕</t>
+  </si>
+  <si>
+    <t>你看完那篇什么什么修理指南了吗？</t>
+  </si>
+  <si>
+    <t>是《极端环境下的行星飞船应急维修技术：基于有限资源的多样化修复方案》</t>
+  </si>
+  <si>
+    <t>看完了</t>
+  </si>
+  <si>
+    <t>怎么样？你找到修补裂缝的办法了吗？</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>飞船里的水位越来越高了</t>
+    </r>
+  </si>
+  <si>
+    <t>你那边能找到一些废金属吗？修裂缝需要用</t>
+  </si>
+  <si>
+    <t>分支对话</t>
+  </si>
+  <si>
+    <t>身上没有废金属</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>还没,我去找一下</t>
+    </r>
+  </si>
+  <si>
+    <t>身上有废金属</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>能找到,我现在身上就有</t>
+    </r>
+  </si>
+  <si>
+    <t>找到一块"废金属",并拖入麦麦的背包</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我找到废金属了！</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>好的,接下来我会一步步教你修补裂缝,你按照我说的做。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>好的好的！</t>
+    </r>
+  </si>
+  <si>
+    <t>制作裂缝填充物</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>做好啦！</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>原来那论文捣鼓了半天就是做这个东西呀？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这个我熟啊</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>以前刮大风的时候,家里的屋顶不是被吹走就是被东西砸破。然后雨就哗啦啦地淋进来</t>
+    </r>
+  </si>
+  <si>
+    <t>那个雨又脏又臭,淋到头上还会掉头发</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这时候我爸就会做一个差不多的东西把屋顶补上。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我没自己做过,可也经常在旁边看</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>那你很有生活经验了</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>原来你以前还有这样的经历呀</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>完全不一样好吧，论文里其实写了很多方案，只是根据你目前的情况选了个最原始的方案</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>原来是这样吗？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不过能解决问题就好</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>接下来就看我的吧,我保证把裂缝堵得严严实实的</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点击"渗水裂缝",打开其详情窗口,然后点击"堵住"，就能堵住裂缝了</t>
+    </r>
+  </si>
+  <si>
+    <t>死亡</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>健康&lt;=0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我真的支撑不住了</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我对不起哈特,对不起爸爸妈妈……</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>当初为什么要去做那些不切实际的梦呢……</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不知道爸爸妈妈现在怎么样了……</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>如果有一天,你能联系到他们</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>请告诉他们</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>“麦麦爱你们”</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不……</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>其他_死亡</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>醒醒,再坚持一下,会有希望的</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>[忘记这一切]</t>
+    </r>
+  </si>
+  <si>
+    <t>第一次点开气密舱门</t>
+  </si>
+  <si>
+    <t>首次点开气密舱门</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我找到出舱的门了</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>外面应该是一片水域环境,不知道水有多深</t>
+    </r>
+  </si>
+  <si>
+    <t>未装备氧气面罩</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最好是戴上氧气面罩再出去探索比较好</t>
+    </r>
+  </si>
+  <si>
+    <t>已装备氧气面罩</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>虽然已经戴上氧气面罩了,但心里还是有些害怕</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>可是飞船里的资源总是会耗尽的,就算再害怕，也还是得出去看看</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>小心一点,不要太勉强</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>说不定开门就捡到一架完整的宇宙飞船,然后你就能直接开船回去了呢</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>嗯,好的</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>那还是有点夸张</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不过,借你吉言啦</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>话说，你那边应该能看见我的身体状态吧。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>如果氧气快不够了，你一定要早点提醒我往回走。</t>
+    </r>
+  </si>
+  <si>
+    <t>第一次进珊瑚礁海域</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>第一次进入珊瑚礁海域</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>唔,唔嗯嗯唔唔嗯呢</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>呜呜嗯嗯？呢唔唔呜呜唔唔唔,嗯嗯喔喔额额</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你悠着点,别呛水了</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你在干嘛？你不是能用脑电交流吗？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>哦哦</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我忘记了</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>下意识地就想直接讲话,但是又讲不出来</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>没戴氧气面罩就潜水真的太难受了</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这个氧气面罩挺好使的</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我感觉眼睛很痛</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>话说这颗星球的水里会不会有什么有害物质呀？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>要不还是先回飞船,等做出氧气面罩了,再出来探索？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不戴氧气面罩探索水域环境时需要消耗更多时间,且每次探索都会减少健康</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>一滴水都没漏进来</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>接下来我们该探索一下飞船外的这片区域了</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最好能找到些吃的,以及淡水的来源</t>
+    </r>
+  </si>
+  <si>
+    <t>困了_01</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>每次清醒度&lt;=30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>呼,感觉眼睛都睁不开了</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>要不考虑先回去休息一下？</t>
+    </r>
+  </si>
+  <si>
+    <t>困了_02</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是不是该休息了？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>感觉已经好久没睡觉了</t>
+    </r>
+  </si>
+  <si>
+    <t>困了_03</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>感觉眼睛有点干干的</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是不是该休息一下了？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不是的,你还能加班,别这么早休息</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>那还是回去睡一觉吧</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>……</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>好吧</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>嗯</t>
+    </r>
+  </si>
+  <si>
+    <t>解锁_制作</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁_休息;解锁_装备;解锁_详情</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击底边栏的研究图标,打开"研究"窗口</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击底边栏的地点图标,打开"地点"窗口</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击底边栏的状态图标,打开"状态"窗口</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击底边栏的背包图标,打开"背包"窗口</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击底边栏的摄像头图标,打开"摄像头"窗口</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>教程结束了，记得指挥麦麦工作，不然她只会发呆
+在你没进行操作时，游戏时间是静止的</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>在"研究"窗口中,打开"建筑"子菜单，点击"修理"这项科技,并点击左下角的“开始研究”</t>
-  </si>
-  <si>
-    <t>研究修理这项科技</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>稍等一下,我还在看</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>嗯……摘要、研究背景、创新性、问题定义、研究目的……</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>虽然是比较靠前的文章,但对我来说还是有些深奥。研究完这些东西估计需要些时间</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>论文是2395年发表在《星际工程学报》上的,很多名词我都没听过</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>顺带一提,我这边现在是*XXXX*年</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>哦</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>哦？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>你为什么不震惊啊？我对你来说是古代人诶</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>没有没有,只是今天发生的事太多了,我都有些麻木了</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我现在就只想着一件事</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>就是赶快把飞船的裂缝堵起来</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>然后去维生舱找哈特</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>哈特是谁？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>哦,我还没跟你提过</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>哈特是我的妹妹</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>同时她也是这艘飞船的驾驶员</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>之前在轨道飞行时,她感到有些恶心,就先到休眠仓里休息了</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>不知道她现在怎么样了,我得赶快找到她才行</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>可是我现在现在飞船里一团乱,我连去其他舱室的路都找不到了</t>
-    </r>
-  </si>
-  <si>
-    <t>双击点开桌面上的软件,打开地点窗口</t>
-  </si>
-  <si>
-    <t>解锁_地点</t>
-  </si>
-  <si>
-    <t>打开地点窗口</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我这边有一个能监测地点环境的软件,能看到你所在地点的信息</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>虽然图上看起来有些乱,但是我大概知道去其他舱室的门在哪个方向</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>不过我毕竟不在现场,我把位置告诉你,你来清理一条路出来</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>没问题！我会按照你说的做的</t>
-    </r>
-  </si>
-  <si>
-    <t>点击地点窗口中的"开始探索"按钮</t>
-  </si>
-  <si>
-    <t>点击探索按钮</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我按照你说的清理了一下道路,还找到了一些东西</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>说起来修补裂缝也还需要材料,正好可以趁你研究的这段时间收集一下</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">教程结束了，记得指挥麦麦工作，不然她只会发呆
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（在你没进行操作时，游戏时间是静止的）</t>
-    </r>
-  </si>
-  <si>
-    <t>解锁_休息;解锁_装备</t>
-  </si>
-  <si>
-    <t>修理研究完毕</t>
-  </si>
-  <si>
-    <t>你看完那篇什么什么修理指南了吗？</t>
-  </si>
-  <si>
-    <t>是《极端环境下的行星飞船应急维修技术：基于有限资源的多样化修复方案》</t>
-  </si>
-  <si>
-    <t>看完了</t>
-  </si>
-  <si>
-    <t>怎么样？你找到修补裂缝的办法了吗？</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>飞船里的水位越来越高了</t>
-    </r>
-  </si>
-  <si>
-    <t>你那边能找到一些废金属吗？修裂缝需要用</t>
-  </si>
-  <si>
-    <t>分支对话</t>
-  </si>
-  <si>
-    <t>身上没有废金属</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>还没,我去找一下</t>
-    </r>
-  </si>
-  <si>
-    <t>身上有废金属</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>能找到,我现在身上就有</t>
-    </r>
-  </si>
-  <si>
-    <t>找到一块"废金属",并拖入麦麦的背包</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我找到废金属了！</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>好的,接下来我会一步步教你修补裂缝,你按照我说的做。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>好的好的！</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>打开“制作窗口”,指挥麦麦制作一个“裂缝填充物”</t>
-    </r>
-  </si>
-  <si>
-    <t>制作裂缝填充物</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>做好啦！</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>原来那论文捣鼓了半天就是做这个东西呀？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这个我熟啊</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>以前刮大风的时候,家里的屋顶不是被吹走就是被东西砸破。然后雨就哗啦啦地淋进来</t>
-    </r>
-  </si>
-  <si>
-    <t>那个雨又脏又臭,淋到头上还会掉头发</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这时候我爸就会做一个差不多的东西把屋顶补上。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我没自己做过,可也经常在旁边看</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>那你很有生活经验了</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>原来你以前还有这样的经历呀</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>完全不一样好吧，论文里其实写了很多方案，只是根据你目前的情况选了个最原始的方案</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>原来是这样吗？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>不过能解决问题就好</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>接下来就看我的吧,我保证把裂缝堵得严严实实的</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>点击"渗水裂缝",打开其详情窗口,然后点击"堵住"，就能堵住裂缝了</t>
-    </r>
-  </si>
-  <si>
-    <t>死亡</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>健康&lt;=0</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我真的支撑不住了</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我对不起哈特,对不起爸爸妈妈……</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>当初为什么要去做那些不切实际的梦呢……</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>不知道爸爸妈妈现在怎么样了……</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>如果有一天,你能联系到他们</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>请告诉他们</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>“麦麦爱你们”</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>不……</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>其他_死亡</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>醒醒,再坚持一下,会有希望的</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>[忘记这一切]</t>
-    </r>
-  </si>
-  <si>
-    <t>第一次点开气密舱门</t>
-  </si>
-  <si>
-    <t>首次点开气密舱门</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我找到出舱的门了</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>外面应该是一片水域环境,不知道水有多深</t>
-    </r>
-  </si>
-  <si>
-    <t>未装备氧气面罩</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>最好是戴上氧气面罩再出去探索比较好</t>
-    </r>
-  </si>
-  <si>
-    <t>已装备氧气面罩</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>虽然已经戴上氧气面罩了,但心里还是有些害怕</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>可是飞船里的资源总是会耗尽的,就算再害怕，也还是得出去看看</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>小心一点,不要太勉强</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>说不定开门就捡到一架完整的宇宙飞船,然后你就能直接开船回去了呢</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>嗯,好的</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>那还是有点夸张</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>不过,借你吉言啦</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>话说，你那边应该能看见我的身体状态吧。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>如果氧气快不够了，你一定要早点提醒我往回走。</t>
-    </r>
-  </si>
-  <si>
-    <t>第一次进珊瑚礁海域</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>第一次进入珊瑚礁海域</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>唔,唔嗯嗯唔唔嗯呢</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>呜呜嗯嗯？呢唔唔呜呜唔唔唔,嗯嗯喔喔额额</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>你悠着点,别呛水了</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>你在干嘛？你不是能用脑电交流吗？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>哦哦</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我忘记了</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>下意识地就想直接讲话,但是又讲不出来</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>没戴氧气面罩就潜水真的太难受了</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这个氧气面罩挺好使的</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我感觉眼睛很痛</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>话说这颗星球的水里会不会有什么有害物质呀？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>要不还是先回飞船,等做出氧气面罩了,再出来探索？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>不戴氧气面罩探索水域环境时需要消耗更多时间,且每次探索都会减少健康</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>一滴水都没漏进来</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>接下来我们该探索一下飞船外的这片区域了</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>最好能找到些吃的,以及淡水的来源</t>
-    </r>
-  </si>
-  <si>
-    <t>困了_01</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>每次清醒度&lt;=30</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>呼,感觉眼睛都睁不开了</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>要不考虑先回去休息一下？</t>
-    </r>
-  </si>
-  <si>
-    <t>困了_02</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>是不是该休息了？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>感觉已经好久没睡觉了</t>
-    </r>
-  </si>
-  <si>
-    <t>困了_03</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>感觉眼睛有点干干的</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>是不是该休息一下了？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>不是的,你还能加班,别这么早休息</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>那还是回去睡一觉吧</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>……</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>好吧</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>嗯</t>
-    </r>
-  </si>
-  <si>
-    <t>解锁_制作</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>打开"制作窗口",指挥麦麦制作一个"裂缝填充物"</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -2220,9 +2193,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -2274,6 +2247,12 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2297,11 +2276,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2321,6 +2300,15 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3794,15 +3782,15 @@
       <c r="D47" t="s">
         <v>59</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>60</v>
+      <c r="F47" s="8" t="s">
+        <v>257</v>
       </c>
       <c r="G47" s="1">
         <v>46</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -3819,10 +3807,10 @@
         <v>11</v>
       </c>
       <c r="E48" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F48" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="G48" s="1">
         <v>47</v>
@@ -3843,7 +3831,7 @@
         <v>11</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G49" s="1">
         <v>48</v>
@@ -3864,7 +3852,7 @@
         <v>11</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G50" s="1">
         <v>49</v>
@@ -3885,7 +3873,7 @@
         <v>11</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G51" s="1">
         <v>50</v>
@@ -3906,7 +3894,7 @@
         <v>11</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G52" s="1">
         <v>51</v>
@@ -3927,7 +3915,7 @@
         <v>11</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G53" s="1">
         <v>52</v>
@@ -3948,7 +3936,7 @@
         <v>18</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G54" s="1">
         <v>53</v>
@@ -3969,7 +3957,7 @@
         <v>11</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G55" s="1">
         <v>54</v>
@@ -3990,7 +3978,7 @@
         <v>11</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G56" s="1">
         <v>55</v>
@@ -4011,7 +3999,7 @@
         <v>18</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G57" s="1">
         <v>57</v>
@@ -4032,7 +4020,7 @@
         <v>18</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G58" s="1">
         <v>57</v>
@@ -4053,7 +4041,7 @@
         <v>11</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G59" s="1">
         <v>58</v>
@@ -4074,7 +4062,7 @@
         <v>11</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G60" s="1">
         <v>59</v>
@@ -4094,15 +4082,15 @@
       <c r="D61" t="s">
         <v>59</v>
       </c>
-      <c r="F61" s="2" t="s">
-        <v>76</v>
+      <c r="F61" s="8" t="s">
+        <v>256</v>
       </c>
       <c r="G61" s="1">
         <v>60</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -4119,10 +4107,10 @@
         <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G62" s="1">
         <v>61</v>
@@ -4143,7 +4131,7 @@
         <v>11</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G63" s="1">
         <v>62</v>
@@ -4164,7 +4152,7 @@
         <v>11</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G64" s="1">
         <v>63</v>
@@ -4185,7 +4173,7 @@
         <v>11</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G65" s="1">
         <v>64</v>
@@ -4206,7 +4194,7 @@
         <v>11</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G66" s="1">
         <v>65</v>
@@ -4227,7 +4215,7 @@
         <v>11</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G67" s="1">
         <v>66</v>
@@ -4248,14 +4236,14 @@
         <v>59</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G68" s="1">
         <v>67</v>
       </c>
       <c r="H68" s="1"/>
       <c r="I68" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
@@ -4272,10 +4260,10 @@
         <v>18</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G69" s="1">
         <v>68</v>
@@ -4296,7 +4284,7 @@
         <v>11</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G70" s="1">
         <v>69</v>
@@ -4319,7 +4307,7 @@
         <v>11</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G71" s="1">
         <v>70</v>
@@ -4340,7 +4328,7 @@
         <v>11</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G72" s="1">
         <v>71</v>
@@ -4361,7 +4349,7 @@
         <v>11</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G73" s="1">
         <v>72</v>
@@ -4384,7 +4372,7 @@
         <v>11</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G74" s="1">
         <v>73</v>
@@ -4407,7 +4395,7 @@
         <v>11</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G75" s="1">
         <v>74</v>
@@ -4427,15 +4415,15 @@
       <c r="D76" t="s">
         <v>59</v>
       </c>
-      <c r="F76" s="6" t="s">
-        <v>95</v>
+      <c r="F76" s="8" t="s">
+        <v>255</v>
       </c>
       <c r="G76" s="1">
         <v>75</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
@@ -4452,10 +4440,10 @@
         <v>18</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G77" s="1">
         <v>76</v>
@@ -4476,7 +4464,7 @@
         <v>11</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G78" s="1">
         <v>77</v>
@@ -4497,7 +4485,7 @@
         <v>11</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G79" s="1">
         <v>78</v>
@@ -4520,7 +4508,7 @@
         <v>11</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G80" s="1">
         <v>79</v>
@@ -4541,7 +4529,7 @@
         <v>11</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G81" s="1">
         <v>80</v>
@@ -4562,7 +4550,7 @@
         <v>11</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G82" s="1">
         <v>81</v>
@@ -4583,7 +4571,7 @@
         <v>11</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G83" s="1">
         <v>82</v>
@@ -4606,7 +4594,7 @@
         <v>11</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G84" s="1">
         <v>83</v>
@@ -4626,7 +4614,7 @@
         <v>11</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G85" s="1">
         <v>84</v>
@@ -4646,7 +4634,7 @@
         <v>11</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G86" s="1">
         <v>85</v>
@@ -4667,7 +4655,7 @@
         <v>11</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G87" s="1">
         <v>86</v>
@@ -4687,7 +4675,7 @@
         <v>11</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G88" s="1">
         <v>87</v>
@@ -4708,7 +4696,7 @@
         <v>11</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G89" s="1">
         <v>88</v>
@@ -4731,7 +4719,7 @@
         <v>11</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G90" s="1">
         <v>89</v>
@@ -4752,7 +4740,7 @@
         <v>11</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G91" s="1">
         <v>90</v>
@@ -4772,7 +4760,7 @@
         <v>11</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G92" s="1">
         <v>91</v>
@@ -4795,7 +4783,7 @@
         <v>11</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G93" s="1">
         <v>92</v>
@@ -4816,7 +4804,7 @@
         <v>11</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G94" s="1">
         <v>93</v>
@@ -4836,7 +4824,7 @@
         <v>11</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G95" s="1">
         <v>94</v>
@@ -4857,7 +4845,7 @@
         <v>11</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="G96" s="1">
         <v>95</v>
@@ -4877,15 +4865,15 @@
       <c r="D97" t="s">
         <v>59</v>
       </c>
-      <c r="F97" s="2" t="s">
-        <v>117</v>
+      <c r="F97" s="8" t="s">
+        <v>253</v>
       </c>
       <c r="G97" s="1">
         <v>96</v>
       </c>
       <c r="H97" s="1"/>
       <c r="I97" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
@@ -4902,10 +4890,10 @@
         <v>18</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G98" s="1">
         <v>97</v>
@@ -4926,7 +4914,7 @@
         <v>11</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G99" s="1">
         <v>98</v>
@@ -4947,7 +4935,7 @@
         <v>11</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="G100" s="1">
         <v>99</v>
@@ -4968,7 +4956,7 @@
         <v>11</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G101" s="1">
         <v>100</v>
@@ -4989,7 +4977,7 @@
         <v>11</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G102" s="1">
         <v>101</v>
@@ -5010,7 +4998,7 @@
         <v>11</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G103" s="1">
         <v>102</v>
@@ -5031,7 +5019,7 @@
         <v>11</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G104" s="1">
         <v>103</v>
@@ -5052,7 +5040,7 @@
         <v>18</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G105" s="1">
         <v>104</v>
@@ -5073,7 +5061,7 @@
         <v>11</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G106" s="1">
         <v>105</v>
@@ -5094,7 +5082,7 @@
         <v>11</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G107" s="1">
         <v>106</v>
@@ -5115,7 +5103,7 @@
         <v>11</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G108" s="1">
         <v>107</v>
@@ -5136,7 +5124,7 @@
         <v>11</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G109" s="1">
         <v>108</v>
@@ -5156,8 +5144,8 @@
       <c r="D110" t="s">
         <v>59</v>
       </c>
-      <c r="F110" s="3" t="s">
-        <v>132</v>
+      <c r="F110" s="10" t="s">
+        <v>259</v>
       </c>
       <c r="G110" s="1">
         <v>109</v>
@@ -5178,10 +5166,10 @@
         <v>18</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="G111" s="1">
         <v>110</v>
@@ -5204,7 +5192,7 @@
         <v>11</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G112" s="1">
         <v>111</v>
@@ -5227,7 +5215,7 @@
         <v>11</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="G113" s="1">
         <v>112</v>
@@ -5250,7 +5238,7 @@
         <v>11</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="G114" s="1">
         <v>113</v>
@@ -5271,7 +5259,7 @@
         <v>11</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="G115" s="1">
         <v>114</v>
@@ -5292,7 +5280,7 @@
         <v>11</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="G116" s="1">
         <v>115</v>
@@ -5313,7 +5301,7 @@
         <v>18</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G117" s="1">
         <v>116</v>
@@ -5334,7 +5322,7 @@
         <v>18</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="G118" s="1">
         <v>117</v>
@@ -5355,7 +5343,7 @@
         <v>11</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="G119" s="1">
         <v>118</v>
@@ -5376,7 +5364,7 @@
         <v>11</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="G120" s="1">
         <v>119</v>
@@ -5397,7 +5385,7 @@
         <v>11</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G121" s="1">
         <v>120</v>
@@ -5418,7 +5406,7 @@
         <v>11</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G122" s="1">
         <v>121</v>
@@ -5438,7 +5426,7 @@
         <v>18</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="G123" s="1">
         <v>122</v>
@@ -5459,7 +5447,7 @@
         <v>11</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="G124" s="1">
         <v>123</v>
@@ -5480,7 +5468,7 @@
         <v>11</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="G125" s="1">
         <v>124</v>
@@ -5500,7 +5488,7 @@
         <v>11</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="G126" s="1">
         <v>125</v>
@@ -5520,7 +5508,7 @@
         <v>11</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G127" s="1">
         <v>126</v>
@@ -5541,7 +5529,7 @@
         <v>11</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G128" s="1">
         <v>127</v>
@@ -5562,7 +5550,7 @@
         <v>11</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G129" s="1">
         <v>128</v>
@@ -5582,15 +5570,15 @@
       <c r="D130" t="s">
         <v>59</v>
       </c>
-      <c r="F130" s="3" t="s">
-        <v>153</v>
+      <c r="F130" s="8" t="s">
+        <v>254</v>
       </c>
       <c r="G130" s="1">
         <v>129</v>
       </c>
       <c r="H130" s="1"/>
       <c r="I130" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
@@ -5607,10 +5595,10 @@
         <v>18</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="G131" s="1">
         <v>130</v>
@@ -5631,7 +5619,7 @@
         <v>11</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="G132" s="1">
         <v>131</v>
@@ -5652,7 +5640,7 @@
         <v>11</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G133" s="1">
         <v>132</v>
@@ -5673,7 +5661,7 @@
         <v>11</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G134" s="1">
         <v>133</v>
@@ -5694,7 +5682,7 @@
         <v>59</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="G135" s="1">
         <v>134</v>
@@ -5715,10 +5703,10 @@
         <v>11</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="G136" s="1">
         <v>135</v>
@@ -5739,14 +5727,14 @@
         <v>11</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="G137" s="1">
         <v>136</v>
       </c>
       <c r="H137" s="1"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" ht="24" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>136</v>
       </c>
@@ -5759,15 +5747,15 @@
       <c r="D138" t="s">
         <v>59</v>
       </c>
-      <c r="F138" t="s">
-        <v>164</v>
+      <c r="F138" s="9" t="s">
+        <v>258</v>
       </c>
       <c r="G138" s="1">
         <v>-1</v>
       </c>
       <c r="H138" s="1"/>
-      <c r="I138" t="s">
-        <v>165</v>
+      <c r="I138" s="7" t="s">
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -5822,10 +5810,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="G2" s="1">
         <v>8</v>
@@ -5836,7 +5824,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>10</v>
@@ -5845,7 +5833,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
@@ -5856,7 +5844,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
@@ -5865,7 +5853,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="G4" s="1">
         <v>4</v>
@@ -5876,7 +5864,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -5885,7 +5873,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="G5" s="1">
         <v>4</v>
@@ -5896,7 +5884,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -5905,7 +5893,7 @@
         <v>11</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
@@ -5916,7 +5904,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -5925,7 +5913,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
@@ -5936,7 +5924,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -5945,7 +5933,7 @@
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
@@ -5956,7 +5944,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -5965,7 +5953,7 @@
         <v>11</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
@@ -5976,19 +5964,19 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" t="s">
-        <v>173</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="F10" s="2" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="G10" s="1">
         <v>10</v>
@@ -5999,19 +5987,19 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="G11" s="1">
         <v>12</v>
@@ -6022,7 +6010,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C12" t="s">
         <v>58</v>
@@ -6031,7 +6019,7 @@
         <v>59</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
@@ -6042,7 +6030,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -6051,10 +6039,10 @@
         <v>11</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
@@ -6065,7 +6053,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C14" t="s">
         <v>17</v>
@@ -6074,7 +6062,7 @@
         <v>18</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="G14" s="1">
         <v>13</v>
@@ -6085,7 +6073,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C15" t="s">
         <v>10</v>
@@ -6094,13 +6082,13 @@
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="G15" s="1">
         <v>14</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -6108,7 +6096,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C16" t="s">
         <v>58</v>
@@ -6116,8 +6104,8 @@
       <c r="D16" t="s">
         <v>59</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>182</v>
+      <c r="F16" s="8" t="s">
+        <v>260</v>
       </c>
       <c r="G16" s="1">
         <v>15</v>
@@ -6128,7 +6116,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
@@ -6137,10 +6125,10 @@
         <v>11</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="G17" s="1">
         <v>16</v>
@@ -6151,7 +6139,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -6160,7 +6148,7 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G18" s="1">
         <v>17</v>
@@ -6171,7 +6159,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C19" t="s">
         <v>10</v>
@@ -6180,7 +6168,7 @@
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="G19" s="1">
         <v>18</v>
@@ -6191,7 +6179,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
@@ -6200,7 +6188,7 @@
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="G20" s="1">
         <v>19</v>
@@ -6214,7 +6202,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C21" t="s">
         <v>10</v>
@@ -6223,7 +6211,7 @@
         <v>11</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="G21" s="1">
         <v>20</v>
@@ -6237,7 +6225,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C22" t="s">
         <v>10</v>
@@ -6246,7 +6234,7 @@
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="G22" s="1">
         <v>21</v>
@@ -6257,7 +6245,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C23" t="s">
         <v>10</v>
@@ -6266,7 +6254,7 @@
         <v>11</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="G23" s="1">
         <v>22</v>
@@ -6277,7 +6265,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C24" t="s">
         <v>17</v>
@@ -6286,7 +6274,7 @@
         <v>18</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="G24" s="1">
         <v>25</v>
@@ -6297,7 +6285,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C25" t="s">
         <v>17</v>
@@ -6306,7 +6294,7 @@
         <v>18</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="G25" s="1">
         <v>25</v>
@@ -6317,7 +6305,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C26" t="s">
         <v>17</v>
@@ -6326,7 +6314,7 @@
         <v>18</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G26" s="1">
         <v>25</v>
@@ -6337,7 +6325,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C27" t="s">
         <v>10</v>
@@ -6346,7 +6334,7 @@
         <v>11</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="G27" s="1">
         <v>26</v>
@@ -6357,7 +6345,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C28" t="s">
         <v>10</v>
@@ -6366,7 +6354,7 @@
         <v>11</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="G28" s="1">
         <v>27</v>
@@ -6377,7 +6365,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C29" t="s">
         <v>10</v>
@@ -6386,7 +6374,7 @@
         <v>11</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="G29" s="1">
         <v>28</v>
@@ -6397,7 +6385,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C30" t="s">
         <v>58</v>
@@ -6406,7 +6394,7 @@
         <v>59</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="G30" s="1">
         <v>-1</v>
@@ -6464,10 +6452,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="G2" s="1">
         <v>10</v>
@@ -6478,7 +6466,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -6487,7 +6475,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
@@ -6498,7 +6486,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -6507,7 +6495,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
@@ -6518,7 +6506,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -6527,7 +6515,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="G5" s="1">
         <v>4</v>
@@ -6538,7 +6526,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -6547,7 +6535,7 @@
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
@@ -6558,7 +6546,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -6567,7 +6555,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
@@ -6578,7 +6566,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -6587,7 +6575,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
@@ -6598,7 +6586,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -6607,7 +6595,7 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
@@ -6618,7 +6606,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C10" t="s">
         <v>17</v>
@@ -6627,13 +6615,13 @@
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="G10" s="1">
         <v>-1</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -6641,7 +6629,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C11" t="s">
         <v>17</v>
@@ -6650,13 +6638,13 @@
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="G11" s="1">
         <v>-1</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -6664,7 +6652,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -6673,13 +6661,13 @@
         <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="G12" s="1">
         <v>-1</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -6734,10 +6722,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="G2" s="1">
         <v>4</v>
@@ -6748,7 +6736,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -6757,7 +6745,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
@@ -6768,7 +6756,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -6777,7 +6765,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
@@ -6788,19 +6776,19 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="G5" s="1">
         <v>-1</v>
@@ -6811,19 +6799,19 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
@@ -6834,7 +6822,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -6843,7 +6831,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
@@ -6854,7 +6842,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -6863,7 +6851,7 @@
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="G8" s="1">
         <v>8</v>
@@ -6874,7 +6862,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -6883,7 +6871,7 @@
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="G9" s="1">
         <v>9</v>
@@ -6894,7 +6882,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
@@ -6903,7 +6891,7 @@
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="G10" s="1">
         <v>11</v>
@@ -6914,7 +6902,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
@@ -6923,7 +6911,7 @@
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="G11" s="1">
         <v>10</v>
@@ -6934,7 +6922,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
@@ -6943,7 +6931,7 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
@@ -6954,7 +6942,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -6963,7 +6951,7 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
@@ -6974,7 +6962,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -6983,7 +6971,7 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="G14" s="1">
         <v>-1</v>
@@ -7041,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="G2" s="1">
         <v>4</v>
@@ -7055,7 +7043,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7064,7 +7052,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
@@ -7075,7 +7063,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7084,7 +7072,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
@@ -7095,7 +7083,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -7104,7 +7092,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="G5" s="1">
         <v>5</v>
@@ -7115,7 +7103,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -7124,7 +7112,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
@@ -7135,7 +7123,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -7144,7 +7132,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
@@ -7155,7 +7143,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -7164,7 +7152,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
@@ -7175,7 +7163,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -7184,7 +7172,7 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
@@ -7195,19 +7183,19 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>218</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>227</v>
-      </c>
-      <c r="C10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" t="s">
-        <v>173</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>236</v>
       </c>
       <c r="G10" s="1">
         <v>10</v>
@@ -7218,19 +7206,19 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="G11" s="1">
         <v>14</v>
@@ -7241,7 +7229,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
@@ -7250,7 +7238,7 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
@@ -7261,7 +7249,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -7270,7 +7258,7 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
@@ -7281,7 +7269,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -7290,7 +7278,7 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="G14" s="1">
         <v>13</v>
@@ -7301,7 +7289,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C15" t="s">
         <v>58</v>
@@ -7310,7 +7298,7 @@
         <v>59</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="G15" s="1">
         <v>-1</v>
@@ -7321,7 +7309,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C16" t="s">
         <v>10</v>
@@ -7330,7 +7318,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="G16" s="1">
         <v>15</v>
@@ -7341,7 +7329,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
@@ -7350,7 +7338,7 @@
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="G17" s="1">
         <v>16</v>
@@ -7361,7 +7349,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -7370,7 +7358,7 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="G18" s="1">
         <v>-1</v>
@@ -7428,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
@@ -7442,7 +7430,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7451,7 +7439,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
@@ -7462,7 +7450,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7471,7 +7459,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="G4" s="1">
         <v>-1</v>
@@ -7529,10 +7517,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
@@ -7543,7 +7531,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7552,7 +7540,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
@@ -7563,7 +7551,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7572,7 +7560,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="G4" s="1">
         <v>-1</v>
@@ -7630,10 +7618,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
@@ -7644,7 +7632,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7653,7 +7641,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
@@ -7664,7 +7652,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7673,7 +7661,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
@@ -7684,7 +7672,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -7693,7 +7681,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="G5" s="1">
         <v>5</v>
@@ -7704,7 +7692,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -7713,7 +7701,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="G6" s="1">
         <v>7</v>
@@ -7724,7 +7712,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -7733,7 +7721,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
@@ -7744,7 +7732,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -7753,7 +7741,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="G8" s="1">
         <v>-1</v>
@@ -7764,7 +7752,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -7773,7 +7761,7 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="G9" s="1">
         <v>-1</v>

--- a/Assets/StreamingAssets/Excel/ChatData.xlsx
+++ b/Assets/StreamingAssets/Excel/ChatData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{433652E6-26A3-4365-9C88-0AEE104E6FB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F2D30FC-2E53-4B95-B30A-4116CA910FF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="一切的开始" sheetId="1" r:id="rId1"/>
@@ -227,16 +227,6 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>现在外面是什么情况我也不太清楚。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>你找错人了,我不是什么"总台"</t>
     </r>
   </si>
@@ -277,16 +267,6 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>我以后会想办法还钱的。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>飞船破损的钱,还有救援队的钱,我以后都会想办法还的</t>
     </r>
   </si>
@@ -1791,16 +1771,6 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>说不定开门就捡到一架完整的宇宙飞船,然后你就能直接开船回去了呢</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>嗯,好的</t>
     </r>
   </si>
@@ -1905,26 +1875,6 @@
         <charset val="134"/>
       </rPr>
       <t>哦哦</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我忘记了</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>下意识地就想直接讲话,但是又讲不出来</t>
     </r>
   </si>
   <si>
@@ -2185,6 +2135,26 @@
   </si>
   <si>
     <t>打开"制作窗口",指挥麦麦制作一个"裂缝填充物"</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在外面是什么情况我也不太清楚</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>我以后会想办法还钱的</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>说不定开门就捡到一架完整的宇宙飞船,然后你就能直接开船回去了呢</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>下意识地就想直接讲话,但是又讲不出来</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>我忘记能用脑电了</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -3173,8 +3143,8 @@
       <c r="D18" t="s">
         <v>11</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>29</v>
+      <c r="F18" s="8" t="s">
+        <v>256</v>
       </c>
       <c r="G18" s="1">
         <v>17</v>
@@ -3194,7 +3164,7 @@
         <v>18</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G19" s="1">
         <v>18</v>
@@ -3215,7 +3185,7 @@
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G20" s="1">
         <v>19</v>
@@ -3236,7 +3206,7 @@
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G21" s="1">
         <v>20</v>
@@ -3257,7 +3227,7 @@
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G22" s="1">
         <v>21</v>
@@ -3277,8 +3247,8 @@
       <c r="D23" t="s">
         <v>11</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>34</v>
+      <c r="F23" s="8" t="s">
+        <v>257</v>
       </c>
       <c r="G23" s="1">
         <v>22</v>
@@ -3299,7 +3269,7 @@
         <v>11</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G24" s="1">
         <v>23</v>
@@ -3319,7 +3289,7 @@
         <v>11</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G25" s="1">
         <v>24</v>
@@ -3340,7 +3310,7 @@
         <v>18</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G26" s="1">
         <v>28</v>
@@ -3361,7 +3331,7 @@
         <v>18</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G27" s="1">
         <v>26</v>
@@ -3382,7 +3352,7 @@
         <v>11</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G28" s="1">
         <v>27</v>
@@ -3403,7 +3373,7 @@
         <v>11</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G29" s="1">
         <v>28</v>
@@ -3426,7 +3396,7 @@
         <v>11</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G30" s="1">
         <v>29</v>
@@ -3447,7 +3417,7 @@
         <v>11</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G31" s="1">
         <v>30</v>
@@ -3468,7 +3438,7 @@
         <v>18</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G32" s="1">
         <v>31</v>
@@ -3489,7 +3459,7 @@
         <v>11</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G33" s="1">
         <v>32</v>
@@ -3510,7 +3480,7 @@
         <v>11</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G34" s="1">
         <v>33</v>
@@ -3531,7 +3501,7 @@
         <v>11</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G35" s="1">
         <v>34</v>
@@ -3552,7 +3522,7 @@
         <v>11</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G36" s="1">
         <v>35</v>
@@ -3573,7 +3543,7 @@
         <v>11</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G37" s="1">
         <v>36</v>
@@ -3594,7 +3564,7 @@
         <v>18</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G38" s="1">
         <v>37</v>
@@ -3615,7 +3585,7 @@
         <v>11</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G39" s="1">
         <v>38</v>
@@ -3636,7 +3606,7 @@
         <v>11</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G40" s="1">
         <v>39</v>
@@ -3657,7 +3627,7 @@
         <v>11</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G41" s="1">
         <v>40</v>
@@ -3678,7 +3648,7 @@
         <v>11</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G42" s="1">
         <v>41</v>
@@ -3699,7 +3669,7 @@
         <v>11</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G43" s="1">
         <v>42</v>
@@ -3720,7 +3690,7 @@
         <v>11</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G44" s="1">
         <v>43</v>
@@ -3741,7 +3711,7 @@
         <v>11</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G45" s="1">
         <v>44</v>
@@ -3762,7 +3732,7 @@
         <v>11</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G46" s="1">
         <v>45</v>
@@ -3777,20 +3747,20 @@
         <v>9</v>
       </c>
       <c r="C47" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D47" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G47" s="1">
         <v>46</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -3807,10 +3777,10 @@
         <v>11</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G48" s="1">
         <v>47</v>
@@ -3831,7 +3801,7 @@
         <v>11</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G49" s="1">
         <v>48</v>
@@ -3852,7 +3822,7 @@
         <v>11</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G50" s="1">
         <v>49</v>
@@ -3873,7 +3843,7 @@
         <v>11</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G51" s="1">
         <v>50</v>
@@ -3894,7 +3864,7 @@
         <v>11</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G52" s="1">
         <v>51</v>
@@ -3915,7 +3885,7 @@
         <v>11</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G53" s="1">
         <v>52</v>
@@ -3936,7 +3906,7 @@
         <v>18</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G54" s="1">
         <v>53</v>
@@ -3957,7 +3927,7 @@
         <v>11</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G55" s="1">
         <v>54</v>
@@ -3978,7 +3948,7 @@
         <v>11</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G56" s="1">
         <v>55</v>
@@ -3999,7 +3969,7 @@
         <v>18</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G57" s="1">
         <v>57</v>
@@ -4020,7 +3990,7 @@
         <v>18</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G58" s="1">
         <v>57</v>
@@ -4041,7 +4011,7 @@
         <v>11</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G59" s="1">
         <v>58</v>
@@ -4062,7 +4032,7 @@
         <v>11</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G60" s="1">
         <v>59</v>
@@ -4077,20 +4047,20 @@
         <v>9</v>
       </c>
       <c r="C61" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D61" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="G61" s="1">
         <v>60</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -4107,10 +4077,10 @@
         <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G62" s="1">
         <v>61</v>
@@ -4131,7 +4101,7 @@
         <v>11</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G63" s="1">
         <v>62</v>
@@ -4152,7 +4122,7 @@
         <v>11</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G64" s="1">
         <v>63</v>
@@ -4173,7 +4143,7 @@
         <v>11</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G65" s="1">
         <v>64</v>
@@ -4194,7 +4164,7 @@
         <v>11</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G66" s="1">
         <v>65</v>
@@ -4215,7 +4185,7 @@
         <v>11</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G67" s="1">
         <v>66</v>
@@ -4230,20 +4200,20 @@
         <v>9</v>
       </c>
       <c r="C68" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D68" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G68" s="1">
         <v>67</v>
       </c>
       <c r="H68" s="1"/>
       <c r="I68" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
@@ -4260,10 +4230,10 @@
         <v>18</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G69" s="1">
         <v>68</v>
@@ -4284,7 +4254,7 @@
         <v>11</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G70" s="1">
         <v>69</v>
@@ -4307,7 +4277,7 @@
         <v>11</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G71" s="1">
         <v>70</v>
@@ -4328,7 +4298,7 @@
         <v>11</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G72" s="1">
         <v>71</v>
@@ -4349,7 +4319,7 @@
         <v>11</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G73" s="1">
         <v>72</v>
@@ -4372,7 +4342,7 @@
         <v>11</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G74" s="1">
         <v>73</v>
@@ -4395,7 +4365,7 @@
         <v>11</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G75" s="1">
         <v>74</v>
@@ -4410,20 +4380,20 @@
         <v>9</v>
       </c>
       <c r="C76" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D76" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="G76" s="1">
         <v>75</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
@@ -4440,10 +4410,10 @@
         <v>18</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G77" s="1">
         <v>76</v>
@@ -4464,7 +4434,7 @@
         <v>11</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G78" s="1">
         <v>77</v>
@@ -4485,7 +4455,7 @@
         <v>11</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G79" s="1">
         <v>78</v>
@@ -4508,7 +4478,7 @@
         <v>11</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G80" s="1">
         <v>79</v>
@@ -4529,7 +4499,7 @@
         <v>11</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G81" s="1">
         <v>80</v>
@@ -4550,7 +4520,7 @@
         <v>11</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G82" s="1">
         <v>81</v>
@@ -4571,7 +4541,7 @@
         <v>11</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G83" s="1">
         <v>82</v>
@@ -4594,7 +4564,7 @@
         <v>11</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G84" s="1">
         <v>83</v>
@@ -4614,7 +4584,7 @@
         <v>11</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G85" s="1">
         <v>84</v>
@@ -4634,7 +4604,7 @@
         <v>11</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G86" s="1">
         <v>85</v>
@@ -4655,7 +4625,7 @@
         <v>11</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G87" s="1">
         <v>86</v>
@@ -4675,7 +4645,7 @@
         <v>11</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G88" s="1">
         <v>87</v>
@@ -4696,7 +4666,7 @@
         <v>11</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G89" s="1">
         <v>88</v>
@@ -4719,7 +4689,7 @@
         <v>11</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G90" s="1">
         <v>89</v>
@@ -4740,7 +4710,7 @@
         <v>11</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G91" s="1">
         <v>90</v>
@@ -4760,7 +4730,7 @@
         <v>11</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G92" s="1">
         <v>91</v>
@@ -4783,7 +4753,7 @@
         <v>11</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G93" s="1">
         <v>92</v>
@@ -4804,7 +4774,7 @@
         <v>11</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G94" s="1">
         <v>93</v>
@@ -4824,7 +4794,7 @@
         <v>11</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G95" s="1">
         <v>94</v>
@@ -4845,7 +4815,7 @@
         <v>11</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G96" s="1">
         <v>95</v>
@@ -4860,20 +4830,20 @@
         <v>9</v>
       </c>
       <c r="C97" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D97" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="G97" s="1">
         <v>96</v>
       </c>
       <c r="H97" s="1"/>
       <c r="I97" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
@@ -4890,15 +4860,17 @@
         <v>18</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G98" s="1">
         <v>97</v>
       </c>
-      <c r="H98" s="1"/>
+      <c r="H98" s="1">
+        <v>4000</v>
+      </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
@@ -4914,12 +4886,14 @@
         <v>11</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G99" s="1">
         <v>98</v>
       </c>
-      <c r="H99" s="1"/>
+      <c r="H99" s="1">
+        <v>4000</v>
+      </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
@@ -4935,12 +4909,14 @@
         <v>11</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G100" s="1">
         <v>99</v>
       </c>
-      <c r="H100" s="1"/>
+      <c r="H100" s="1">
+        <v>5000</v>
+      </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
@@ -4956,12 +4932,14 @@
         <v>11</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G101" s="1">
         <v>100</v>
       </c>
-      <c r="H101" s="1"/>
+      <c r="H101" s="1">
+        <v>5000</v>
+      </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
@@ -4977,12 +4955,14 @@
         <v>11</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G102" s="1">
         <v>101</v>
       </c>
-      <c r="H102" s="1"/>
+      <c r="H102" s="1">
+        <v>5500</v>
+      </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
@@ -4998,12 +4978,14 @@
         <v>11</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G103" s="1">
         <v>102</v>
       </c>
-      <c r="H103" s="1"/>
+      <c r="H103" s="1">
+        <v>5500</v>
+      </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
@@ -5019,12 +5001,14 @@
         <v>11</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G104" s="1">
         <v>103</v>
       </c>
-      <c r="H104" s="1"/>
+      <c r="H104" s="1">
+        <v>3400</v>
+      </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
@@ -5040,7 +5024,7 @@
         <v>18</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G105" s="1">
         <v>104</v>
@@ -5061,7 +5045,7 @@
         <v>11</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G106" s="1">
         <v>105</v>
@@ -5082,12 +5066,14 @@
         <v>11</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G107" s="1">
         <v>106</v>
       </c>
-      <c r="H107" s="1"/>
+      <c r="H107" s="1">
+        <v>4000</v>
+      </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
@@ -5103,7 +5089,7 @@
         <v>11</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G108" s="1">
         <v>107</v>
@@ -5124,7 +5110,7 @@
         <v>11</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G109" s="1">
         <v>108</v>
@@ -5139,13 +5125,13 @@
         <v>9</v>
       </c>
       <c r="C110" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D110" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F110" s="10" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="G110" s="1">
         <v>109</v>
@@ -5166,10 +5152,10 @@
         <v>18</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G111" s="1">
         <v>110</v>
@@ -5192,7 +5178,7 @@
         <v>11</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G112" s="1">
         <v>111</v>
@@ -5215,7 +5201,7 @@
         <v>11</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G113" s="1">
         <v>112</v>
@@ -5238,12 +5224,14 @@
         <v>11</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G114" s="1">
         <v>113</v>
       </c>
-      <c r="H114" s="1"/>
+      <c r="H114" s="1">
+        <v>4000</v>
+      </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
@@ -5259,7 +5247,7 @@
         <v>11</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G115" s="1">
         <v>114</v>
@@ -5280,7 +5268,7 @@
         <v>11</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G116" s="1">
         <v>115</v>
@@ -5301,7 +5289,7 @@
         <v>18</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G117" s="1">
         <v>116</v>
@@ -5322,7 +5310,7 @@
         <v>18</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G118" s="1">
         <v>117</v>
@@ -5343,7 +5331,7 @@
         <v>11</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G119" s="1">
         <v>118</v>
@@ -5364,7 +5352,7 @@
         <v>11</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G120" s="1">
         <v>119</v>
@@ -5385,7 +5373,7 @@
         <v>11</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G121" s="1">
         <v>120</v>
@@ -5406,7 +5394,7 @@
         <v>11</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G122" s="1">
         <v>121</v>
@@ -5426,7 +5414,7 @@
         <v>18</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G123" s="1">
         <v>122</v>
@@ -5447,7 +5435,7 @@
         <v>11</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G124" s="1">
         <v>123</v>
@@ -5468,7 +5456,7 @@
         <v>11</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G125" s="1">
         <v>124</v>
@@ -5488,7 +5476,7 @@
         <v>11</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G126" s="1">
         <v>125</v>
@@ -5508,7 +5496,7 @@
         <v>11</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G127" s="1">
         <v>126</v>
@@ -5529,7 +5517,7 @@
         <v>11</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G128" s="1">
         <v>127</v>
@@ -5550,7 +5538,7 @@
         <v>11</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G129" s="1">
         <v>128</v>
@@ -5565,20 +5553,20 @@
         <v>9</v>
       </c>
       <c r="C130" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D130" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="G130" s="1">
         <v>129</v>
       </c>
       <c r="H130" s="1"/>
       <c r="I130" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
@@ -5595,15 +5583,17 @@
         <v>18</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G131" s="1">
         <v>130</v>
       </c>
-      <c r="H131" s="1"/>
+      <c r="H131" s="1">
+        <v>3500</v>
+      </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
@@ -5619,12 +5609,14 @@
         <v>11</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G132" s="1">
         <v>131</v>
       </c>
-      <c r="H132" s="1"/>
+      <c r="H132" s="1">
+        <v>4500</v>
+      </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
@@ -5640,7 +5632,7 @@
         <v>11</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G133" s="1">
         <v>132</v>
@@ -5661,7 +5653,7 @@
         <v>11</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G134" s="1">
         <v>133</v>
@@ -5676,13 +5668,13 @@
         <v>9</v>
       </c>
       <c r="C135" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D135" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G135" s="1">
         <v>134</v>
@@ -5703,10 +5695,10 @@
         <v>11</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G136" s="1">
         <v>135</v>
@@ -5727,7 +5719,7 @@
         <v>11</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G137" s="1">
         <v>136</v>
@@ -5742,20 +5734,20 @@
         <v>9</v>
       </c>
       <c r="C138" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D138" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F138" s="9" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="G138" s="1">
         <v>-1</v>
       </c>
       <c r="H138" s="1"/>
       <c r="I138" s="7" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -5810,10 +5802,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G2" s="1">
         <v>8</v>
@@ -5824,7 +5816,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>10</v>
@@ -5833,7 +5825,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
@@ -5844,7 +5836,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
@@ -5853,7 +5845,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G4" s="1">
         <v>4</v>
@@ -5864,7 +5856,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -5873,7 +5865,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G5" s="1">
         <v>4</v>
@@ -5884,7 +5876,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -5893,7 +5885,7 @@
         <v>11</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
@@ -5904,7 +5896,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -5913,7 +5905,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
@@ -5924,7 +5916,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -5933,7 +5925,7 @@
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
@@ -5944,7 +5936,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -5953,7 +5945,7 @@
         <v>11</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
@@ -5964,19 +5956,19 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
       </c>
       <c r="D10" t="s">
+        <v>163</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="G10" s="1">
         <v>10</v>
@@ -5987,19 +5979,19 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G11" s="1">
         <v>12</v>
@@ -6010,16 +6002,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
@@ -6030,7 +6022,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -6039,10 +6031,10 @@
         <v>11</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
@@ -6053,7 +6045,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C14" t="s">
         <v>17</v>
@@ -6062,7 +6054,7 @@
         <v>18</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G14" s="1">
         <v>13</v>
@@ -6073,7 +6065,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C15" t="s">
         <v>10</v>
@@ -6082,13 +6074,13 @@
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G15" s="1">
         <v>14</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -6096,16 +6088,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="G16" s="1">
         <v>15</v>
@@ -6116,7 +6108,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
@@ -6125,10 +6117,10 @@
         <v>11</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G17" s="1">
         <v>16</v>
@@ -6139,7 +6131,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -6148,7 +6140,7 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G18" s="1">
         <v>17</v>
@@ -6159,7 +6151,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C19" t="s">
         <v>10</v>
@@ -6168,7 +6160,7 @@
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G19" s="1">
         <v>18</v>
@@ -6179,7 +6171,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
@@ -6188,7 +6180,7 @@
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G20" s="1">
         <v>19</v>
@@ -6202,7 +6194,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C21" t="s">
         <v>10</v>
@@ -6211,7 +6203,7 @@
         <v>11</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G21" s="1">
         <v>20</v>
@@ -6225,7 +6217,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C22" t="s">
         <v>10</v>
@@ -6234,7 +6226,7 @@
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G22" s="1">
         <v>21</v>
@@ -6245,7 +6237,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C23" t="s">
         <v>10</v>
@@ -6254,7 +6246,7 @@
         <v>11</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G23" s="1">
         <v>22</v>
@@ -6265,7 +6257,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C24" t="s">
         <v>17</v>
@@ -6274,7 +6266,7 @@
         <v>18</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G24" s="1">
         <v>25</v>
@@ -6285,7 +6277,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C25" t="s">
         <v>17</v>
@@ -6294,7 +6286,7 @@
         <v>18</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G25" s="1">
         <v>25</v>
@@ -6305,7 +6297,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C26" t="s">
         <v>17</v>
@@ -6314,7 +6306,7 @@
         <v>18</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G26" s="1">
         <v>25</v>
@@ -6325,7 +6317,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C27" t="s">
         <v>10</v>
@@ -6334,7 +6326,7 @@
         <v>11</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G27" s="1">
         <v>26</v>
@@ -6345,7 +6337,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C28" t="s">
         <v>10</v>
@@ -6354,7 +6346,7 @@
         <v>11</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G28" s="1">
         <v>27</v>
@@ -6365,7 +6357,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C29" t="s">
         <v>10</v>
@@ -6374,7 +6366,7 @@
         <v>11</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G29" s="1">
         <v>28</v>
@@ -6385,16 +6377,16 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C30" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D30" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G30" s="1">
         <v>-1</v>
@@ -6452,10 +6444,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G2" s="1">
         <v>10</v>
@@ -6466,16 +6458,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>191</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
@@ -6486,7 +6478,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -6495,7 +6487,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
@@ -6506,7 +6498,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -6515,7 +6507,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G5" s="1">
         <v>4</v>
@@ -6526,7 +6518,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -6535,7 +6527,7 @@
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
@@ -6546,7 +6538,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -6555,7 +6547,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
@@ -6566,7 +6558,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -6575,7 +6567,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
@@ -6586,7 +6578,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -6595,7 +6587,7 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
@@ -6606,7 +6598,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C10" t="s">
         <v>17</v>
@@ -6615,13 +6607,13 @@
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G10" s="1">
         <v>-1</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -6629,7 +6621,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C11" t="s">
         <v>17</v>
@@ -6638,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G11" s="1">
         <v>-1</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -6652,7 +6644,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -6661,13 +6653,13 @@
         <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G12" s="1">
         <v>-1</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -6722,10 +6714,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G2" s="1">
         <v>4</v>
@@ -6736,16 +6728,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
@@ -6756,7 +6748,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -6765,7 +6757,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
@@ -6776,19 +6768,19 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G5" s="1">
         <v>-1</v>
@@ -6799,19 +6791,19 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
@@ -6822,7 +6814,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -6831,7 +6823,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
@@ -6842,7 +6834,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -6851,7 +6843,7 @@
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G8" s="1">
         <v>8</v>
@@ -6862,7 +6854,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -6870,8 +6862,8 @@
       <c r="D9" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>212</v>
+      <c r="F9" s="8" t="s">
+        <v>258</v>
       </c>
       <c r="G9" s="1">
         <v>9</v>
@@ -6882,7 +6874,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
@@ -6891,7 +6883,7 @@
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="G10" s="1">
         <v>11</v>
@@ -6902,7 +6894,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
@@ -6911,7 +6903,7 @@
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="G11" s="1">
         <v>10</v>
@@ -6922,7 +6914,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
@@ -6931,7 +6923,7 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
@@ -6942,7 +6934,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -6951,7 +6943,7 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
@@ -6962,7 +6954,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -6971,7 +6963,7 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G14" s="1">
         <v>-1</v>
@@ -7029,10 +7021,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="G2" s="1">
         <v>4</v>
@@ -7043,7 +7035,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7052,7 +7044,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
@@ -7063,16 +7055,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>218</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>221</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
@@ -7083,7 +7075,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -7092,7 +7084,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="G5" s="1">
         <v>5</v>
@@ -7103,7 +7095,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -7112,7 +7104,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
@@ -7123,7 +7115,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -7132,7 +7124,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
@@ -7143,7 +7135,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -7151,8 +7143,8 @@
       <c r="D8" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>225</v>
+      <c r="F8" s="8" t="s">
+        <v>260</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
@@ -7163,7 +7155,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -7171,8 +7163,8 @@
       <c r="D9" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>226</v>
+      <c r="F9" s="8" t="s">
+        <v>259</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
@@ -7183,19 +7175,19 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="G10" s="1">
         <v>10</v>
@@ -7206,19 +7198,19 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="G11" s="1">
         <v>14</v>
@@ -7229,7 +7221,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
@@ -7238,7 +7230,7 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
@@ -7249,7 +7241,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -7258,7 +7250,7 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
@@ -7269,7 +7261,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -7278,7 +7270,7 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="G14" s="1">
         <v>13</v>
@@ -7289,16 +7281,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="G15" s="1">
         <v>-1</v>
@@ -7309,7 +7301,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C16" t="s">
         <v>10</v>
@@ -7318,7 +7310,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="G16" s="1">
         <v>15</v>
@@ -7329,7 +7321,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
@@ -7338,7 +7330,7 @@
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="G17" s="1">
         <v>16</v>
@@ -7349,7 +7341,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -7358,7 +7350,7 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="G18" s="1">
         <v>-1</v>
@@ -7416,10 +7408,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
@@ -7430,7 +7422,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7439,7 +7431,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
@@ -7450,7 +7442,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7459,7 +7451,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="G4" s="1">
         <v>-1</v>
@@ -7517,10 +7509,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
@@ -7531,7 +7523,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7540,7 +7532,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
@@ -7551,7 +7543,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7560,7 +7552,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="G4" s="1">
         <v>-1</v>
@@ -7618,10 +7610,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
@@ -7632,7 +7624,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7641,7 +7633,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
@@ -7652,7 +7644,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7661,7 +7653,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
@@ -7672,7 +7664,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -7681,7 +7673,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G5" s="1">
         <v>5</v>
@@ -7692,7 +7684,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -7701,7 +7693,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="G6" s="1">
         <v>7</v>
@@ -7712,16 +7704,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>238</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="C7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>248</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
@@ -7732,7 +7724,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -7741,7 +7733,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="G8" s="1">
         <v>-1</v>
@@ -7752,7 +7744,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -7761,7 +7753,7 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="G9" s="1">
         <v>-1</v>

--- a/Assets/StreamingAssets/Excel/ChatData.xlsx
+++ b/Assets/StreamingAssets/Excel/ChatData.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{433652E6-26A3-4365-9C88-0AEE104E6FB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="22188" windowHeight="9060" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="一切的开始" sheetId="1" r:id="rId1"/>
@@ -23,6 +17,19 @@
     <sheet name="困了_03" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -517,6 +524,9 @@
     <t>提示</t>
   </si>
   <si>
+    <t>点击底边栏的摄像头图标,打开"摄像头"窗口</t>
+  </si>
+  <si>
     <t>解锁_摄像头</t>
   </si>
   <si>
@@ -653,6 +663,9 @@
     </r>
   </si>
   <si>
+    <t>点击底边栏的背包图标,打开"背包"窗口</t>
+  </si>
+  <si>
     <t>解锁_背包</t>
   </si>
   <si>
@@ -798,6 +811,9 @@
     </r>
   </si>
   <si>
+    <t>点击底边栏的状态图标,打开"状态"窗口</t>
+  </si>
+  <si>
     <t>解锁_状态</t>
   </si>
   <si>
@@ -973,6 +989,9 @@
     </r>
   </si>
   <si>
+    <t>点击底边栏的研究图标,打开"研究"窗口</t>
+  </si>
+  <si>
     <t>解锁_研究</t>
   </si>
   <si>
@@ -1099,6 +1118,9 @@
     </r>
   </si>
   <si>
+    <t>在"研究"窗口中,打开"建筑"子菜单，点击"修理"这项科技,并点击左下角的“开始研究”</t>
+  </si>
+  <si>
     <t>研究修理这项科技</t>
   </si>
   <si>
@@ -1292,6 +1314,9 @@
     </r>
   </si>
   <si>
+    <t>点击底边栏的地点图标,打开"地点"窗口</t>
+  </si>
+  <si>
     <t>解锁_地点</t>
   </si>
   <si>
@@ -1362,840 +1387,816 @@
       </rPr>
       <t>说起来修补裂缝也还需要材料,正好可以趁你研究的这段时间收集一下</t>
     </r>
-  </si>
-  <si>
-    <t>修理研究完毕</t>
-  </si>
-  <si>
-    <t>你看完那篇什么什么修理指南了吗？</t>
-  </si>
-  <si>
-    <t>是《极端环境下的行星飞船应急维修技术：基于有限资源的多样化修复方案》</t>
-  </si>
-  <si>
-    <t>看完了</t>
-  </si>
-  <si>
-    <t>怎么样？你找到修补裂缝的办法了吗？</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>飞船里的水位越来越高了</t>
-    </r>
-  </si>
-  <si>
-    <t>你那边能找到一些废金属吗？修裂缝需要用</t>
-  </si>
-  <si>
-    <t>分支对话</t>
-  </si>
-  <si>
-    <t>身上没有废金属</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>还没,我去找一下</t>
-    </r>
-  </si>
-  <si>
-    <t>身上有废金属</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>能找到,我现在身上就有</t>
-    </r>
-  </si>
-  <si>
-    <t>找到一块"废金属",并拖入麦麦的背包</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我找到废金属了！</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>好的,接下来我会一步步教你修补裂缝,你按照我说的做。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>好的好的！</t>
-    </r>
-  </si>
-  <si>
-    <t>制作裂缝填充物</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>做好啦！</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>原来那论文捣鼓了半天就是做这个东西呀？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这个我熟啊</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>以前刮大风的时候,家里的屋顶不是被吹走就是被东西砸破。然后雨就哗啦啦地淋进来</t>
-    </r>
-  </si>
-  <si>
-    <t>那个雨又脏又臭,淋到头上还会掉头发</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这时候我爸就会做一个差不多的东西把屋顶补上。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我没自己做过,可也经常在旁边看</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>那你很有生活经验了</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>原来你以前还有这样的经历呀</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>完全不一样好吧，论文里其实写了很多方案，只是根据你目前的情况选了个最原始的方案</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>原来是这样吗？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>不过能解决问题就好</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>接下来就看我的吧,我保证把裂缝堵得严严实实的</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>点击"渗水裂缝",打开其详情窗口,然后点击"堵住"，就能堵住裂缝了</t>
-    </r>
-  </si>
-  <si>
-    <t>死亡</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>健康&lt;=0</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我真的支撑不住了</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我对不起哈特,对不起爸爸妈妈……</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>当初为什么要去做那些不切实际的梦呢……</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>不知道爸爸妈妈现在怎么样了……</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>如果有一天,你能联系到他们</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>请告诉他们</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>“麦麦爱你们”</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>不……</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>其他_死亡</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>醒醒,再坚持一下,会有希望的</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>[忘记这一切]</t>
-    </r>
-  </si>
-  <si>
-    <t>第一次点开气密舱门</t>
-  </si>
-  <si>
-    <t>首次点开气密舱门</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我找到出舱的门了</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>外面应该是一片水域环境,不知道水有多深</t>
-    </r>
-  </si>
-  <si>
-    <t>未装备氧气面罩</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>最好是戴上氧气面罩再出去探索比较好</t>
-    </r>
-  </si>
-  <si>
-    <t>已装备氧气面罩</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>虽然已经戴上氧气面罩了,但心里还是有些害怕</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>可是飞船里的资源总是会耗尽的,就算再害怕，也还是得出去看看</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>小心一点,不要太勉强</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>说不定开门就捡到一架完整的宇宙飞船,然后你就能直接开船回去了呢</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>嗯,好的</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>那还是有点夸张</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>不过,借你吉言啦</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>话说，你那边应该能看见我的身体状态吧。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>如果氧气快不够了，你一定要早点提醒我往回走。</t>
-    </r>
-  </si>
-  <si>
-    <t>第一次进珊瑚礁海域</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>第一次进入珊瑚礁海域</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>唔,唔嗯嗯唔唔嗯呢</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>呜呜嗯嗯？呢唔唔呜呜唔唔唔,嗯嗯喔喔额额</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>你悠着点,别呛水了</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>你在干嘛？你不是能用脑电交流吗？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>哦哦</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我忘记了</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>下意识地就想直接讲话,但是又讲不出来</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>没戴氧气面罩就潜水真的太难受了</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这个氧气面罩挺好使的</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我感觉眼睛很痛</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>话说这颗星球的水里会不会有什么有害物质呀？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>要不还是先回飞船,等做出氧气面罩了,再出来探索？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>不戴氧气面罩探索水域环境时需要消耗更多时间,且每次探索都会减少健康</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>一滴水都没漏进来</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>接下来我们该探索一下飞船外的这片区域了</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>最好能找到些吃的,以及淡水的来源</t>
-    </r>
-  </si>
-  <si>
-    <t>困了_01</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>每次清醒度&lt;=30</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>呼,感觉眼睛都睁不开了</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>要不考虑先回去休息一下？</t>
-    </r>
-  </si>
-  <si>
-    <t>困了_02</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>是不是该休息了？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>感觉已经好久没睡觉了</t>
-    </r>
-  </si>
-  <si>
-    <t>困了_03</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>感觉眼睛有点干干的</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>是不是该休息一下了？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>不是的,你还能加班,别这么早休息</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>那还是回去睡一觉吧</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>……</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>好吧</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>嗯</t>
-    </r>
-  </si>
-  <si>
-    <t>解锁_制作</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>解锁_休息;解锁_装备;解锁_详情</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>点击底边栏的研究图标,打开"研究"窗口</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>点击底边栏的地点图标,打开"地点"窗口</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>点击底边栏的状态图标,打开"状态"窗口</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>点击底边栏的背包图标,打开"背包"窗口</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>点击底边栏的摄像头图标,打开"摄像头"窗口</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>教程结束了，记得指挥麦麦工作，不然她只会发呆
 在你没进行操作时，游戏时间是静止的</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>在"研究"窗口中,打开"建筑"子菜单，点击"修理"这项科技,并点击左下角的“开始研究”</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁_休息;解锁_装备;解锁_详情</t>
+  </si>
+  <si>
+    <t>修理研究完毕</t>
+  </si>
+  <si>
+    <t>你看完那篇什么什么修理指南了吗？</t>
+  </si>
+  <si>
+    <t>是《极端环境下的行星飞船应急维修技术：基于有限资源的多样化修复方案》</t>
+  </si>
+  <si>
+    <t>看完了</t>
+  </si>
+  <si>
+    <t>怎么样？你找到修补裂缝的办法了吗？</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>飞船里的水位越来越高了</t>
+    </r>
+  </si>
+  <si>
+    <t>你那边能找到一些废金属吗？修裂缝需要用</t>
+  </si>
+  <si>
+    <t>分支对话</t>
+  </si>
+  <si>
+    <t>身上没有废金属</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>还没,我去找一下</t>
+    </r>
+  </si>
+  <si>
+    <t>身上有废金属</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>能找到,我现在身上就有</t>
+    </r>
+  </si>
+  <si>
+    <t>找到一块"废金属",并拖入麦麦的背包</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我找到废金属了！</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>好的,接下来我会一步步教你修补裂缝,你按照我说的做。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>好的好的！</t>
+    </r>
+  </si>
+  <si>
+    <t>解锁_制作</t>
   </si>
   <si>
     <t>打开"制作窗口",指挥麦麦制作一个"裂缝填充物"</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>制作裂缝填充物</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>做好啦！</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>原来那论文捣鼓了半天就是做这个东西呀？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这个我熟啊</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>以前刮大风的时候,家里的屋顶不是被吹走就是被东西砸破。然后雨就哗啦啦地淋进来</t>
+    </r>
+  </si>
+  <si>
+    <t>那个雨又脏又臭,淋到头上还会掉头发</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这时候我爸就会做一个差不多的东西把屋顶补上。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我没自己做过,可也经常在旁边看</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>那你很有生活经验了</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>原来你以前还有这样的经历呀</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>完全不一样好吧，论文里其实写了很多方案，只是根据你目前的情况选了个最原始的方案</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>原来是这样吗？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不过能解决问题就好</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>接下来就看我的吧,我保证把裂缝堵得严严实实的</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点击"渗水裂缝",打开其详情窗口,然后点击"堵住"，就能堵住裂缝了</t>
+    </r>
+  </si>
+  <si>
+    <t>死亡</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>健康&lt;=0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我真的支撑不住了</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我对不起哈特,对不起爸爸妈妈……</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>当初为什么要去做那些不切实际的梦呢……</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不知道爸爸妈妈现在怎么样了……</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>如果有一天,你能联系到他们</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>请告诉他们</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>“麦麦爱你们”</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不……</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>其他_死亡</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>醒醒,再坚持一下,会有希望的</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>[忘记这一切]</t>
+    </r>
+  </si>
+  <si>
+    <t>第一次点开气密舱门</t>
+  </si>
+  <si>
+    <t>首次点开气密舱门</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我找到出舱的门了</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>外面应该是一片水域环境,不知道水有多深</t>
+    </r>
+  </si>
+  <si>
+    <t>未装备氧气面罩</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最好是戴上氧气面罩再出去探索比较好</t>
+    </r>
+  </si>
+  <si>
+    <t>已装备氧气面罩</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>虽然已经戴上氧气面罩了,但心里还是有些害怕</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>可是飞船里的资源总是会耗尽的,就算再害怕，也还是得出去看看</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>小心一点,不要太勉强</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>说不定开门就捡到一架完整的宇宙飞船,然后你就能直接开船回去了呢</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>嗯,好的</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>那还是有点夸张</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不过,借你吉言啦</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>话说，你那边应该能看见我的身体状态吧。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>如果氧气快不够了，你一定要早点提醒我往回走。</t>
+    </r>
+  </si>
+  <si>
+    <t>第一次进珊瑚礁海域</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>第一次进入珊瑚礁海域</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>唔,唔嗯嗯唔唔嗯呢</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>呜呜嗯嗯？呢唔唔呜呜唔唔唔,嗯嗯喔喔额额</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你悠着点,别呛水了</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你在干嘛？你不是能用脑电交流吗？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>哦哦</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我忘记了</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>下意识地就想直接讲话,但是又讲不出来</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>没戴氧气面罩就潜水真的太难受了</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这个氧气面罩挺好使的</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我感觉眼睛很痛</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>话说这颗星球的水里会不会有什么有害物质呀？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>要不还是先回飞船,等做出氧气面罩了,再出来探索？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不戴氧气面罩探索水域环境时需要消耗更多时间,且每次探索都会减少健康</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>一滴水都没漏进来</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>接下来我们该探索一下飞船外的这片区域了</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最好能找到些吃的,以及淡水的来源</t>
+    </r>
+  </si>
+  <si>
+    <t>困了_01</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>每次清醒度&lt;=30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>呼,感觉眼睛都睁不开了</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>要不考虑先回去休息一下？</t>
+    </r>
+  </si>
+  <si>
+    <t>困了_02</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是不是该休息了？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>感觉已经好久没睡觉了</t>
+    </r>
+  </si>
+  <si>
+    <t>困了_03</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>感觉眼睛有点干干的</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是不是该休息一下了？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不是的,你还能加班,别这么早休息</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>那还是回去睡一觉吧</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>……</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>好吧</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>嗯</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="25">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -2216,53 +2217,363 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="等线"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="等线"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -2270,13 +2581,255 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2289,180 +2842,105 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -2473,7 +2951,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -2501,40 +2979,154 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2792,14 +3384,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I138"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="27"/>
@@ -2809,7 +3401,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2838,7 +3430,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -2850,7 +3442,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -2871,7 +3463,7 @@
       </c>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -2892,7 +3484,7 @@
       </c>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -2912,7 +3504,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -2932,7 +3524,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -2953,7 +3545,7 @@
       </c>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -2974,7 +3566,7 @@
       </c>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -2995,7 +3587,7 @@
       </c>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -3016,7 +3608,7 @@
       </c>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -3037,7 +3629,7 @@
       </c>
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -3057,7 +3649,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -3078,7 +3670,7 @@
       </c>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -3098,7 +3690,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -3119,7 +3711,7 @@
       </c>
       <c r="H15" s="1"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -3140,7 +3732,7 @@
       </c>
       <c r="H16" s="1"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -3160,7 +3752,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -3180,7 +3772,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -3201,7 +3793,7 @@
       </c>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -3222,7 +3814,7 @@
       </c>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -3243,7 +3835,7 @@
       </c>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -3264,7 +3856,7 @@
       </c>
       <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -3285,7 +3877,7 @@
       </c>
       <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -3305,7 +3897,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -3326,7 +3918,7 @@
       </c>
       <c r="H25" s="1"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -3347,7 +3939,7 @@
       </c>
       <c r="H26" s="1"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -3368,7 +3960,7 @@
       </c>
       <c r="H27" s="1"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -3389,7 +3981,7 @@
       </c>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -3412,7 +4004,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -3433,7 +4025,7 @@
       </c>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -3454,7 +4046,7 @@
       </c>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -3475,7 +4067,7 @@
       </c>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -3496,7 +4088,7 @@
       </c>
       <c r="H33" s="1"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -3517,7 +4109,7 @@
       </c>
       <c r="H34" s="1"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -3538,7 +4130,7 @@
       </c>
       <c r="H35" s="1"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -3559,7 +4151,7 @@
       </c>
       <c r="H36" s="1"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -3580,7 +4172,7 @@
       </c>
       <c r="H37" s="1"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -3601,7 +4193,7 @@
       </c>
       <c r="H38" s="1"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -3622,7 +4214,7 @@
       </c>
       <c r="H39" s="1"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -3643,7 +4235,7 @@
       </c>
       <c r="H40" s="1"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -3664,7 +4256,7 @@
       </c>
       <c r="H41" s="1"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -3685,7 +4277,7 @@
       </c>
       <c r="H42" s="1"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -3706,7 +4298,7 @@
       </c>
       <c r="H43" s="1"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -3727,7 +4319,7 @@
       </c>
       <c r="H44" s="1"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -3748,7 +4340,7 @@
       </c>
       <c r="H45" s="1"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -3769,7 +4361,7 @@
       </c>
       <c r="H46" s="1"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -3782,18 +4374,18 @@
       <c r="D47" t="s">
         <v>59</v>
       </c>
-      <c r="F47" s="8" t="s">
-        <v>257</v>
+      <c r="F47" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="G47" s="1">
         <v>46</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -3807,17 +4399,17 @@
         <v>11</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G48" s="1">
         <v>47</v>
       </c>
       <c r="H48" s="1"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -3831,14 +4423,14 @@
         <v>11</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G49" s="1">
         <v>48</v>
       </c>
       <c r="H49" s="1"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -3852,14 +4444,14 @@
         <v>11</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G50" s="1">
         <v>49</v>
       </c>
       <c r="H50" s="1"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -3873,14 +4465,14 @@
         <v>11</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G51" s="1">
         <v>50</v>
       </c>
       <c r="H51" s="1"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -3894,14 +4486,14 @@
         <v>11</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G52" s="1">
         <v>51</v>
       </c>
       <c r="H52" s="1"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -3915,14 +4507,14 @@
         <v>11</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G53" s="1">
         <v>52</v>
       </c>
       <c r="H53" s="1"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -3936,14 +4528,14 @@
         <v>18</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G54" s="1">
         <v>53</v>
       </c>
       <c r="H54" s="1"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -3957,14 +4549,14 @@
         <v>11</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G55" s="1">
         <v>54</v>
       </c>
       <c r="H55" s="1"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -3978,14 +4570,14 @@
         <v>11</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G56" s="1">
         <v>55</v>
       </c>
       <c r="H56" s="1"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -3999,14 +4591,14 @@
         <v>18</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G57" s="1">
         <v>57</v>
       </c>
       <c r="H57" s="1"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -4020,14 +4612,14 @@
         <v>18</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G58" s="1">
         <v>57</v>
       </c>
       <c r="H58" s="1"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -4041,14 +4633,14 @@
         <v>11</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G59" s="1">
         <v>58</v>
       </c>
       <c r="H59" s="1"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -4062,14 +4654,14 @@
         <v>11</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G60" s="1">
         <v>59</v>
       </c>
       <c r="H60" s="1"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -4082,18 +4674,18 @@
       <c r="D61" t="s">
         <v>59</v>
       </c>
-      <c r="F61" s="8" t="s">
-        <v>256</v>
+      <c r="F61" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="G61" s="1">
         <v>60</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -4107,17 +4699,17 @@
         <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G62" s="1">
         <v>61</v>
       </c>
       <c r="H62" s="1"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -4131,14 +4723,14 @@
         <v>11</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G63" s="1">
         <v>62</v>
       </c>
       <c r="H63" s="1"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -4152,14 +4744,14 @@
         <v>11</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G64" s="1">
         <v>63</v>
       </c>
       <c r="H64" s="1"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -4173,14 +4765,14 @@
         <v>11</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G65" s="1">
         <v>64</v>
       </c>
       <c r="H65" s="1"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -4194,14 +4786,14 @@
         <v>11</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G66" s="1">
         <v>65</v>
       </c>
       <c r="H66" s="1"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -4215,14 +4807,14 @@
         <v>11</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G67" s="1">
         <v>66</v>
       </c>
       <c r="H67" s="1"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -4236,17 +4828,17 @@
         <v>59</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G68" s="1">
         <v>67</v>
       </c>
       <c r="H68" s="1"/>
       <c r="I68" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -4260,17 +4852,17 @@
         <v>18</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G69" s="1">
         <v>68</v>
       </c>
       <c r="H69" s="1"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -4284,7 +4876,7 @@
         <v>11</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G70" s="1">
         <v>69</v>
@@ -4293,7 +4885,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -4307,14 +4899,14 @@
         <v>11</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G71" s="1">
         <v>70</v>
       </c>
       <c r="H71" s="1"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -4328,14 +4920,14 @@
         <v>11</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G72" s="1">
         <v>71</v>
       </c>
       <c r="H72" s="1"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -4349,7 +4941,7 @@
         <v>11</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G73" s="1">
         <v>72</v>
@@ -4358,7 +4950,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -4372,7 +4964,7 @@
         <v>11</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G74" s="1">
         <v>73</v>
@@ -4381,7 +4973,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -4395,14 +4987,14 @@
         <v>11</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G75" s="1">
         <v>74</v>
       </c>
       <c r="H75" s="1"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -4415,18 +5007,18 @@
       <c r="D76" t="s">
         <v>59</v>
       </c>
-      <c r="F76" s="8" t="s">
-        <v>255</v>
+      <c r="F76" s="5" t="s">
+        <v>95</v>
       </c>
       <c r="G76" s="1">
         <v>75</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -4440,17 +5032,17 @@
         <v>18</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F77" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="G77" s="1">
         <v>76</v>
       </c>
       <c r="H77" s="1"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -4464,14 +5056,14 @@
         <v>11</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G78" s="1">
         <v>77</v>
       </c>
       <c r="H78" s="1"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -4485,7 +5077,7 @@
         <v>11</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G79" s="1">
         <v>78</v>
@@ -4494,7 +5086,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -4508,14 +5100,14 @@
         <v>11</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G80" s="1">
         <v>79</v>
       </c>
       <c r="H80" s="1"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -4529,14 +5121,14 @@
         <v>11</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G81" s="1">
         <v>80</v>
       </c>
       <c r="H81" s="1"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -4550,14 +5142,14 @@
         <v>11</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G82" s="1">
         <v>81</v>
       </c>
       <c r="H82" s="1"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -4571,7 +5163,7 @@
         <v>11</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G83" s="1">
         <v>82</v>
@@ -4580,7 +5172,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -4594,13 +5186,13 @@
         <v>11</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G84" s="1">
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -4614,13 +5206,13 @@
         <v>11</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G85" s="1">
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -4634,14 +5226,14 @@
         <v>11</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G86" s="1">
         <v>85</v>
       </c>
       <c r="H86" s="1"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -4655,13 +5247,13 @@
         <v>11</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G87" s="1">
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -4675,14 +5267,14 @@
         <v>11</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G88" s="1">
         <v>87</v>
       </c>
       <c r="H88" s="1"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -4695,8 +5287,8 @@
       <c r="D89" t="s">
         <v>11</v>
       </c>
-      <c r="F89" s="6" t="s">
-        <v>107</v>
+      <c r="F89" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="G89" s="1">
         <v>88</v>
@@ -4705,7 +5297,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8">
       <c r="A90" s="1">
         <v>88</v>
       </c>
@@ -4719,14 +5311,14 @@
         <v>11</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G90" s="1">
         <v>89</v>
       </c>
       <c r="H90" s="1"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7">
       <c r="A91" s="1">
         <v>89</v>
       </c>
@@ -4740,13 +5332,13 @@
         <v>11</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G91" s="1">
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8">
       <c r="A92" s="1">
         <v>90</v>
       </c>
@@ -4760,7 +5352,7 @@
         <v>11</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G92" s="1">
         <v>91</v>
@@ -4769,7 +5361,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8">
       <c r="A93" s="1">
         <v>91</v>
       </c>
@@ -4783,14 +5375,14 @@
         <v>11</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G93" s="1">
         <v>92</v>
       </c>
       <c r="H93" s="1"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7">
       <c r="A94" s="1">
         <v>92</v>
       </c>
@@ -4803,14 +5395,14 @@
       <c r="D94" t="s">
         <v>11</v>
       </c>
-      <c r="F94" s="6" t="s">
-        <v>111</v>
+      <c r="F94" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="G94" s="1">
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8">
       <c r="A95" s="1">
         <v>93</v>
       </c>
@@ -4824,14 +5416,14 @@
         <v>11</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G95" s="1">
         <v>94</v>
       </c>
       <c r="H95" s="1"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8">
       <c r="A96" s="1">
         <v>94</v>
       </c>
@@ -4845,14 +5437,14 @@
         <v>11</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G96" s="1">
         <v>95</v>
       </c>
       <c r="H96" s="1"/>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9">
       <c r="A97" s="1">
         <v>95</v>
       </c>
@@ -4865,18 +5457,18 @@
       <c r="D97" t="s">
         <v>59</v>
       </c>
-      <c r="F97" s="8" t="s">
-        <v>253</v>
+      <c r="F97" s="5" t="s">
+        <v>117</v>
       </c>
       <c r="G97" s="1">
         <v>96</v>
       </c>
       <c r="H97" s="1"/>
       <c r="I97" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
       <c r="A98" s="1">
         <v>96</v>
       </c>
@@ -4890,17 +5482,17 @@
         <v>18</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G98" s="1">
         <v>97</v>
       </c>
       <c r="H98" s="1"/>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8">
       <c r="A99" s="1">
         <v>97</v>
       </c>
@@ -4914,14 +5506,14 @@
         <v>11</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G99" s="1">
         <v>98</v>
       </c>
       <c r="H99" s="1"/>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8">
       <c r="A100" s="1">
         <v>98</v>
       </c>
@@ -4935,14 +5527,14 @@
         <v>11</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G100" s="1">
         <v>99</v>
       </c>
       <c r="H100" s="1"/>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8">
       <c r="A101" s="1">
         <v>99</v>
       </c>
@@ -4956,14 +5548,14 @@
         <v>11</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G101" s="1">
         <v>100</v>
       </c>
       <c r="H101" s="1"/>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8">
       <c r="A102" s="1">
         <v>100</v>
       </c>
@@ -4977,14 +5569,14 @@
         <v>11</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G102" s="1">
         <v>101</v>
       </c>
       <c r="H102" s="1"/>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8">
       <c r="A103" s="1">
         <v>101</v>
       </c>
@@ -4998,14 +5590,14 @@
         <v>11</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G103" s="1">
         <v>102</v>
       </c>
       <c r="H103" s="1"/>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8">
       <c r="A104" s="1">
         <v>102</v>
       </c>
@@ -5019,14 +5611,14 @@
         <v>11</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G104" s="1">
         <v>103</v>
       </c>
       <c r="H104" s="1"/>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8">
       <c r="A105" s="1">
         <v>103</v>
       </c>
@@ -5040,14 +5632,14 @@
         <v>18</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G105" s="1">
         <v>104</v>
       </c>
       <c r="H105" s="1"/>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8">
       <c r="A106" s="1">
         <v>104</v>
       </c>
@@ -5061,14 +5653,14 @@
         <v>11</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G106" s="1">
         <v>105</v>
       </c>
       <c r="H106" s="1"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8">
       <c r="A107" s="1">
         <v>105</v>
       </c>
@@ -5082,14 +5674,14 @@
         <v>11</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G107" s="1">
         <v>106</v>
       </c>
       <c r="H107" s="1"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8">
       <c r="A108" s="1">
         <v>106</v>
       </c>
@@ -5103,14 +5695,14 @@
         <v>11</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G108" s="1">
         <v>107</v>
       </c>
       <c r="H108" s="1"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8">
       <c r="A109" s="1">
         <v>107</v>
       </c>
@@ -5124,14 +5716,14 @@
         <v>11</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G109" s="1">
         <v>108</v>
       </c>
       <c r="H109" s="1"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8">
       <c r="A110" s="1">
         <v>108</v>
       </c>
@@ -5144,15 +5736,15 @@
       <c r="D110" t="s">
         <v>59</v>
       </c>
-      <c r="F110" s="10" t="s">
-        <v>259</v>
+      <c r="F110" s="7" t="s">
+        <v>132</v>
       </c>
       <c r="G110" s="1">
         <v>109</v>
       </c>
       <c r="H110" s="1"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8">
       <c r="A111" s="1">
         <v>109</v>
       </c>
@@ -5166,10 +5758,10 @@
         <v>18</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="G111" s="1">
         <v>110</v>
@@ -5178,7 +5770,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8">
       <c r="A112" s="1">
         <v>110</v>
       </c>
@@ -5192,7 +5784,7 @@
         <v>11</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G112" s="1">
         <v>111</v>
@@ -5201,7 +5793,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8">
       <c r="A113" s="1">
         <v>111</v>
       </c>
@@ -5215,7 +5807,7 @@
         <v>11</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="G113" s="1">
         <v>112</v>
@@ -5224,7 +5816,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8">
       <c r="A114" s="1">
         <v>112</v>
       </c>
@@ -5238,14 +5830,14 @@
         <v>11</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G114" s="1">
         <v>113</v>
       </c>
       <c r="H114" s="1"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8">
       <c r="A115" s="1">
         <v>113</v>
       </c>
@@ -5259,14 +5851,14 @@
         <v>11</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="G115" s="1">
         <v>114</v>
       </c>
       <c r="H115" s="1"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8">
       <c r="A116" s="1">
         <v>114</v>
       </c>
@@ -5280,14 +5872,14 @@
         <v>11</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G116" s="1">
         <v>115</v>
       </c>
       <c r="H116" s="1"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8">
       <c r="A117" s="1">
         <v>115</v>
       </c>
@@ -5301,14 +5893,14 @@
         <v>18</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="G117" s="1">
         <v>116</v>
       </c>
       <c r="H117" s="1"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8">
       <c r="A118" s="1">
         <v>116</v>
       </c>
@@ -5322,14 +5914,14 @@
         <v>18</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G118" s="1">
         <v>117</v>
       </c>
       <c r="H118" s="1"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8">
       <c r="A119" s="1">
         <v>117</v>
       </c>
@@ -5343,14 +5935,14 @@
         <v>11</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G119" s="1">
         <v>118</v>
       </c>
       <c r="H119" s="1"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8">
       <c r="A120" s="1">
         <v>118</v>
       </c>
@@ -5364,14 +5956,14 @@
         <v>11</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="G120" s="1">
         <v>119</v>
       </c>
       <c r="H120" s="1"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8">
       <c r="A121" s="1">
         <v>119</v>
       </c>
@@ -5385,14 +5977,14 @@
         <v>11</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G121" s="1">
         <v>120</v>
       </c>
       <c r="H121" s="1"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7">
       <c r="A122" s="1">
         <v>120</v>
       </c>
@@ -5406,13 +5998,13 @@
         <v>11</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G122" s="1">
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8">
       <c r="A123" s="1">
         <v>121</v>
       </c>
@@ -5426,14 +6018,14 @@
         <v>18</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="G123" s="1">
         <v>122</v>
       </c>
       <c r="H123" s="1"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8">
       <c r="A124" s="1">
         <v>122</v>
       </c>
@@ -5447,14 +6039,14 @@
         <v>11</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="G124" s="1">
         <v>123</v>
       </c>
       <c r="H124" s="1"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7">
       <c r="A125" s="1">
         <v>123</v>
       </c>
@@ -5468,13 +6060,13 @@
         <v>11</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="G125" s="1">
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7">
       <c r="A126" s="1">
         <v>124</v>
       </c>
@@ -5488,13 +6080,13 @@
         <v>11</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G126" s="1">
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8">
       <c r="A127" s="1">
         <v>125</v>
       </c>
@@ -5508,14 +6100,14 @@
         <v>11</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G127" s="1">
         <v>126</v>
       </c>
       <c r="H127" s="1"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8">
       <c r="A128" s="1">
         <v>126</v>
       </c>
@@ -5529,14 +6121,14 @@
         <v>11</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G128" s="1">
         <v>127</v>
       </c>
       <c r="H128" s="1"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8">
       <c r="A129" s="1">
         <v>127</v>
       </c>
@@ -5550,14 +6142,14 @@
         <v>11</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="G129" s="1">
         <v>128</v>
       </c>
       <c r="H129" s="1"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9">
       <c r="A130" s="1">
         <v>128</v>
       </c>
@@ -5570,18 +6162,18 @@
       <c r="D130" t="s">
         <v>59</v>
       </c>
-      <c r="F130" s="8" t="s">
-        <v>254</v>
+      <c r="F130" s="5" t="s">
+        <v>153</v>
       </c>
       <c r="G130" s="1">
         <v>129</v>
       </c>
       <c r="H130" s="1"/>
       <c r="I130" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
       <c r="A131" s="1">
         <v>129</v>
       </c>
@@ -5595,17 +6187,17 @@
         <v>18</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="G131" s="1">
         <v>130</v>
       </c>
       <c r="H131" s="1"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8">
       <c r="A132" s="1">
         <v>130</v>
       </c>
@@ -5619,14 +6211,14 @@
         <v>11</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="G132" s="1">
         <v>131</v>
       </c>
       <c r="H132" s="1"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8">
       <c r="A133" s="1">
         <v>131</v>
       </c>
@@ -5640,14 +6232,14 @@
         <v>11</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="G133" s="1">
         <v>132</v>
       </c>
       <c r="H133" s="1"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8">
       <c r="A134" s="1">
         <v>132</v>
       </c>
@@ -5661,14 +6253,14 @@
         <v>11</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="G134" s="1">
         <v>133</v>
       </c>
       <c r="H134" s="1"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8">
       <c r="A135" s="1">
         <v>133</v>
       </c>
@@ -5682,14 +6274,14 @@
         <v>59</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="G135" s="1">
         <v>134</v>
       </c>
       <c r="H135" s="1"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8">
       <c r="A136" s="1">
         <v>134</v>
       </c>
@@ -5703,17 +6295,17 @@
         <v>11</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="G136" s="1">
         <v>135</v>
       </c>
       <c r="H136" s="1"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8">
       <c r="A137" s="1">
         <v>135</v>
       </c>
@@ -5727,14 +6319,14 @@
         <v>11</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="G137" s="1">
         <v>136</v>
       </c>
       <c r="H137" s="1"/>
     </row>
-    <row r="138" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+    <row r="138" ht="24" spans="1:9">
       <c r="A138" s="1">
         <v>136</v>
       </c>
@@ -5747,27 +6339,28 @@
       <c r="D138" t="s">
         <v>59</v>
       </c>
-      <c r="F138" s="9" t="s">
-        <v>258</v>
+      <c r="F138" s="8" t="s">
+        <v>164</v>
       </c>
       <c r="G138" s="1">
         <v>-1</v>
       </c>
       <c r="H138" s="1"/>
-      <c r="I138" s="7" t="s">
-        <v>252</v>
+      <c r="I138" s="6" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="24"/>
@@ -5776,7 +6369,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5805,26 +6398,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="G2" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>10</v>
@@ -5832,19 +6425,19 @@
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>159</v>
+      <c r="F3" s="2" t="s">
+        <v>167</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
@@ -5852,19 +6445,19 @@
       <c r="D4" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>160</v>
+      <c r="F4" s="3" t="s">
+        <v>168</v>
       </c>
       <c r="G4" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -5872,19 +6465,19 @@
       <c r="D5" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>161</v>
+      <c r="F5" s="3" t="s">
+        <v>169</v>
       </c>
       <c r="G5" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -5892,19 +6485,19 @@
       <c r="D6" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>162</v>
+      <c r="F6" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -5913,18 +6506,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -5933,18 +6526,18 @@
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -5952,65 +6545,65 @@
       <c r="D9" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>164</v>
+      <c r="F9" s="3" t="s">
+        <v>172</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
         <v>166</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="G10" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>158</v>
-      </c>
       <c r="C11" t="s">
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="G11" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C12" t="s">
         <v>58</v>
@@ -6018,19 +6611,19 @@
       <c r="D12" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>170</v>
+      <c r="F12" s="3" t="s">
+        <v>178</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -6039,21 +6632,21 @@
         <v>11</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C14" t="s">
         <v>17</v>
@@ -6062,18 +6655,18 @@
         <v>18</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="G14" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C15" t="s">
         <v>10</v>
@@ -6082,21 +6675,21 @@
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="G15" s="1">
         <v>14</v>
       </c>
-      <c r="I15" s="7" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I15" s="6" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C16" t="s">
         <v>58</v>
@@ -6104,19 +6697,19 @@
       <c r="D16" t="s">
         <v>59</v>
       </c>
-      <c r="F16" s="8" t="s">
-        <v>260</v>
+      <c r="F16" s="5" t="s">
+        <v>183</v>
       </c>
       <c r="G16" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
@@ -6125,21 +6718,21 @@
         <v>11</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="G17" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -6148,18 +6741,18 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="G18" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7">
       <c r="A19" s="1">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C19" t="s">
         <v>10</v>
@@ -6168,18 +6761,18 @@
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="G19" s="1">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8">
       <c r="A20" s="1">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
@@ -6188,7 +6781,7 @@
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="G20" s="1">
         <v>19</v>
@@ -6197,12 +6790,12 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8">
       <c r="A21" s="1">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C21" t="s">
         <v>10</v>
@@ -6210,8 +6803,8 @@
       <c r="D21" t="s">
         <v>11</v>
       </c>
-      <c r="F21" s="6" t="s">
-        <v>179</v>
+      <c r="F21" s="3" t="s">
+        <v>189</v>
       </c>
       <c r="G21" s="1">
         <v>20</v>
@@ -6220,12 +6813,12 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7">
       <c r="A22" s="1">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C22" t="s">
         <v>10</v>
@@ -6234,18 +6827,18 @@
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="G22" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7">
       <c r="A23" s="1">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C23" t="s">
         <v>10</v>
@@ -6254,18 +6847,18 @@
         <v>11</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="G23" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7">
       <c r="A24" s="1">
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C24" t="s">
         <v>17</v>
@@ -6274,18 +6867,18 @@
         <v>18</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="G24" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7">
       <c r="A25" s="1">
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C25" t="s">
         <v>17</v>
@@ -6294,18 +6887,18 @@
         <v>18</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="G25" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7">
       <c r="A26" s="1">
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C26" t="s">
         <v>17</v>
@@ -6314,18 +6907,18 @@
         <v>18</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="G26" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7">
       <c r="A27" s="1">
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C27" t="s">
         <v>10</v>
@@ -6334,18 +6927,18 @@
         <v>11</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="G27" s="1">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7">
       <c r="A28" s="1">
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C28" t="s">
         <v>10</v>
@@ -6354,18 +6947,18 @@
         <v>11</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="G28" s="1">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7">
       <c r="A29" s="1">
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C29" t="s">
         <v>10</v>
@@ -6374,18 +6967,18 @@
         <v>11</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="G29" s="1">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7">
       <c r="A30" s="1">
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C30" t="s">
         <v>58</v>
@@ -6394,22 +6987,23 @@
         <v>59</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="G30" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -6418,7 +7012,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6447,26 +7041,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="G2" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -6475,18 +7069,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -6495,18 +7089,18 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -6515,18 +7109,18 @@
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="G5" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -6535,18 +7129,18 @@
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -6555,18 +7149,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -6575,18 +7169,18 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -6595,18 +7189,18 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="C10" t="s">
         <v>17</v>
@@ -6615,21 +7209,21 @@
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="G10" s="1">
         <v>-1</v>
       </c>
       <c r="I10" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
         <v>199</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>189</v>
       </c>
       <c r="C11" t="s">
         <v>17</v>
@@ -6638,21 +7232,21 @@
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G11" s="1">
         <v>-1</v>
       </c>
       <c r="I11" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
         <v>199</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>189</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -6661,25 +7255,26 @@
         <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="G12" s="1">
         <v>-1</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -6688,7 +7283,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6717,26 +7312,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="G2" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -6745,18 +7340,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -6765,64 +7360,64 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="G5" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -6831,18 +7426,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -6851,18 +7446,18 @@
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="G8" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -6871,18 +7466,18 @@
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="G9" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
@@ -6891,18 +7486,18 @@
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="G10" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
@@ -6911,18 +7506,18 @@
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="G11" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
@@ -6931,18 +7526,18 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -6951,18 +7546,18 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -6971,22 +7566,23 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="G14" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -6995,7 +7591,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7024,26 +7620,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="G2" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7052,18 +7648,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7072,18 +7668,18 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -7092,18 +7688,18 @@
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="G5" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -7112,18 +7708,18 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -7132,18 +7728,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -7152,18 +7748,18 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -7172,64 +7768,64 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>228</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>173</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>228</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>173</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" t="s">
-        <v>165</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="G10" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>218</v>
-      </c>
-      <c r="C11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" t="s">
-        <v>165</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>208</v>
-      </c>
       <c r="F11" s="2" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="G11" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
@@ -7238,18 +7834,18 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -7258,18 +7854,18 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -7278,18 +7874,18 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="G14" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="C15" t="s">
         <v>58</v>
@@ -7298,18 +7894,18 @@
         <v>59</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="G15" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="C16" t="s">
         <v>10</v>
@@ -7318,18 +7914,18 @@
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="G16" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
@@ -7338,18 +7934,18 @@
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="G17" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -7358,22 +7954,23 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="G18" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -7382,7 +7979,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7411,26 +8008,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7439,18 +8036,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7459,22 +8056,23 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="G4" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -7483,7 +8081,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7512,26 +8110,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7540,18 +8138,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7560,22 +8158,23 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="G4" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -7584,7 +8183,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7613,26 +8212,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7641,18 +8240,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7661,18 +8260,18 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -7681,18 +8280,18 @@
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="G5" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -7701,18 +8300,18 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="G6" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -7721,18 +8320,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -7741,18 +8340,18 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="G8" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -7761,14 +8360,14 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="G9" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Excel/ChatData.xlsx
+++ b/Assets/StreamingAssets/Excel/ChatData.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Unity\Projects\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E04329F-0910-4BF3-8263-6C148184DCDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060" activeTab="1"/>
+    <workbookView xWindow="2830" yWindow="3940" windowWidth="19200" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="一切的开始" sheetId="1" r:id="rId1"/>
@@ -25,8 +31,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -2188,15 +2192,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.00_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="1">
+    <numFmt numFmtId="178" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -2228,352 +2228,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -2581,251 +2251,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2833,7 +2261,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2858,89 +2286,158 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -2951,7 +2448,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -2979,154 +2476,40 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -3384,14 +2767,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I138"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="10.36328125" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="27"/>
@@ -3401,7 +2784,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3430,7 +2813,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -3442,7 +2825,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3463,7 +2846,7 @@
       </c>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -3484,7 +2867,7 @@
       </c>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -3504,7 +2887,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -3524,7 +2907,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -3545,7 +2928,7 @@
       </c>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -3566,7 +2949,7 @@
       </c>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -3587,7 +2970,7 @@
       </c>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -3608,7 +2991,7 @@
       </c>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -3629,7 +3012,7 @@
       </c>
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -3649,7 +3032,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -3670,7 +3053,7 @@
       </c>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -3690,7 +3073,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -3711,7 +3094,7 @@
       </c>
       <c r="H15" s="1"/>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -3732,7 +3115,7 @@
       </c>
       <c r="H16" s="1"/>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -3752,7 +3135,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -3772,7 +3155,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -3793,7 +3176,7 @@
       </c>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -3814,7 +3197,7 @@
       </c>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -3835,7 +3218,7 @@
       </c>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -3856,7 +3239,7 @@
       </c>
       <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -3877,7 +3260,7 @@
       </c>
       <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -3897,7 +3280,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -3918,7 +3301,7 @@
       </c>
       <c r="H25" s="1"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -3939,7 +3322,7 @@
       </c>
       <c r="H26" s="1"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -3960,7 +3343,7 @@
       </c>
       <c r="H27" s="1"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -3981,7 +3364,7 @@
       </c>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -4004,7 +3387,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -4025,7 +3408,7 @@
       </c>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -4046,7 +3429,7 @@
       </c>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -4067,7 +3450,7 @@
       </c>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -4088,7 +3471,7 @@
       </c>
       <c r="H33" s="1"/>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -4109,7 +3492,7 @@
       </c>
       <c r="H34" s="1"/>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -4130,7 +3513,7 @@
       </c>
       <c r="H35" s="1"/>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -4151,7 +3534,7 @@
       </c>
       <c r="H36" s="1"/>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -4172,7 +3555,7 @@
       </c>
       <c r="H37" s="1"/>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -4193,7 +3576,7 @@
       </c>
       <c r="H38" s="1"/>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -4214,7 +3597,7 @@
       </c>
       <c r="H39" s="1"/>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -4235,7 +3618,7 @@
       </c>
       <c r="H40" s="1"/>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -4256,7 +3639,7 @@
       </c>
       <c r="H41" s="1"/>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -4277,7 +3660,7 @@
       </c>
       <c r="H42" s="1"/>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -4298,7 +3681,7 @@
       </c>
       <c r="H43" s="1"/>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -4319,7 +3702,7 @@
       </c>
       <c r="H44" s="1"/>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -4340,7 +3723,7 @@
       </c>
       <c r="H45" s="1"/>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -4361,7 +3744,7 @@
       </c>
       <c r="H46" s="1"/>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -4385,7 +3768,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -4409,7 +3792,7 @@
       </c>
       <c r="H48" s="1"/>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -4430,7 +3813,7 @@
       </c>
       <c r="H49" s="1"/>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -4451,7 +3834,7 @@
       </c>
       <c r="H50" s="1"/>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -4472,7 +3855,7 @@
       </c>
       <c r="H51" s="1"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -4493,7 +3876,7 @@
       </c>
       <c r="H52" s="1"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -4514,7 +3897,7 @@
       </c>
       <c r="H53" s="1"/>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -4535,7 +3918,7 @@
       </c>
       <c r="H54" s="1"/>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -4556,7 +3939,7 @@
       </c>
       <c r="H55" s="1"/>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -4577,7 +3960,7 @@
       </c>
       <c r="H56" s="1"/>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -4598,7 +3981,7 @@
       </c>
       <c r="H57" s="1"/>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -4619,7 +4002,7 @@
       </c>
       <c r="H58" s="1"/>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -4640,7 +4023,7 @@
       </c>
       <c r="H59" s="1"/>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -4661,7 +4044,7 @@
       </c>
       <c r="H60" s="1"/>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -4685,7 +4068,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -4709,7 +4092,7 @@
       </c>
       <c r="H62" s="1"/>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -4730,7 +4113,7 @@
       </c>
       <c r="H63" s="1"/>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -4751,7 +4134,7 @@
       </c>
       <c r="H64" s="1"/>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -4772,7 +4155,7 @@
       </c>
       <c r="H65" s="1"/>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -4793,7 +4176,7 @@
       </c>
       <c r="H66" s="1"/>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -4814,7 +4197,7 @@
       </c>
       <c r="H67" s="1"/>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -4838,7 +4221,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -4862,7 +4245,7 @@
       </c>
       <c r="H69" s="1"/>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -4885,7 +4268,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -4906,7 +4289,7 @@
       </c>
       <c r="H71" s="1"/>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -4927,7 +4310,7 @@
       </c>
       <c r="H72" s="1"/>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -4950,7 +4333,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -4973,7 +4356,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -4994,7 +4377,7 @@
       </c>
       <c r="H75" s="1"/>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -5018,7 +4401,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -5042,7 +4425,7 @@
       </c>
       <c r="H77" s="1"/>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -5063,7 +4446,7 @@
       </c>
       <c r="H78" s="1"/>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -5086,7 +4469,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -5107,7 +4490,7 @@
       </c>
       <c r="H80" s="1"/>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -5128,7 +4511,7 @@
       </c>
       <c r="H81" s="1"/>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -5149,7 +4532,7 @@
       </c>
       <c r="H82" s="1"/>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -5172,7 +4555,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -5192,7 +4575,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -5212,7 +4595,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -5233,7 +4616,7 @@
       </c>
       <c r="H86" s="1"/>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -5253,7 +4636,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -5274,7 +4657,7 @@
       </c>
       <c r="H88" s="1"/>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -5297,7 +4680,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>88</v>
       </c>
@@ -5318,7 +4701,7 @@
       </c>
       <c r="H90" s="1"/>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>89</v>
       </c>
@@ -5338,7 +4721,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>90</v>
       </c>
@@ -5361,7 +4744,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>91</v>
       </c>
@@ -5382,7 +4765,7 @@
       </c>
       <c r="H93" s="1"/>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>92</v>
       </c>
@@ -5402,7 +4785,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>93</v>
       </c>
@@ -5423,7 +4806,7 @@
       </c>
       <c r="H95" s="1"/>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>94</v>
       </c>
@@ -5444,7 +4827,7 @@
       </c>
       <c r="H96" s="1"/>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>95</v>
       </c>
@@ -5468,7 +4851,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>96</v>
       </c>
@@ -5492,7 +4875,7 @@
       </c>
       <c r="H98" s="1"/>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>97</v>
       </c>
@@ -5513,7 +4896,7 @@
       </c>
       <c r="H99" s="1"/>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>98</v>
       </c>
@@ -5534,7 +4917,7 @@
       </c>
       <c r="H100" s="1"/>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>99</v>
       </c>
@@ -5555,7 +4938,7 @@
       </c>
       <c r="H101" s="1"/>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>100</v>
       </c>
@@ -5576,7 +4959,7 @@
       </c>
       <c r="H102" s="1"/>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>101</v>
       </c>
@@ -5597,7 +4980,7 @@
       </c>
       <c r="H103" s="1"/>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>102</v>
       </c>
@@ -5618,7 +5001,7 @@
       </c>
       <c r="H104" s="1"/>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>103</v>
       </c>
@@ -5639,7 +5022,7 @@
       </c>
       <c r="H105" s="1"/>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>104</v>
       </c>
@@ -5660,7 +5043,7 @@
       </c>
       <c r="H106" s="1"/>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>105</v>
       </c>
@@ -5681,7 +5064,7 @@
       </c>
       <c r="H107" s="1"/>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>106</v>
       </c>
@@ -5702,7 +5085,7 @@
       </c>
       <c r="H108" s="1"/>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>107</v>
       </c>
@@ -5723,7 +5106,7 @@
       </c>
       <c r="H109" s="1"/>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>108</v>
       </c>
@@ -5744,7 +5127,7 @@
       </c>
       <c r="H110" s="1"/>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>109</v>
       </c>
@@ -5770,7 +5153,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>110</v>
       </c>
@@ -5793,7 +5176,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>111</v>
       </c>
@@ -5816,7 +5199,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>112</v>
       </c>
@@ -5837,7 +5220,7 @@
       </c>
       <c r="H114" s="1"/>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>113</v>
       </c>
@@ -5858,7 +5241,7 @@
       </c>
       <c r="H115" s="1"/>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>114</v>
       </c>
@@ -5879,7 +5262,7 @@
       </c>
       <c r="H116" s="1"/>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>115</v>
       </c>
@@ -5900,7 +5283,7 @@
       </c>
       <c r="H117" s="1"/>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>116</v>
       </c>
@@ -5921,7 +5304,7 @@
       </c>
       <c r="H118" s="1"/>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>117</v>
       </c>
@@ -5942,7 +5325,7 @@
       </c>
       <c r="H119" s="1"/>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>118</v>
       </c>
@@ -5963,7 +5346,7 @@
       </c>
       <c r="H120" s="1"/>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>119</v>
       </c>
@@ -5984,7 +5367,7 @@
       </c>
       <c r="H121" s="1"/>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>120</v>
       </c>
@@ -6004,7 +5387,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>121</v>
       </c>
@@ -6025,7 +5408,7 @@
       </c>
       <c r="H123" s="1"/>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>122</v>
       </c>
@@ -6046,7 +5429,7 @@
       </c>
       <c r="H124" s="1"/>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>123</v>
       </c>
@@ -6066,7 +5449,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>124</v>
       </c>
@@ -6086,7 +5469,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>125</v>
       </c>
@@ -6107,7 +5490,7 @@
       </c>
       <c r="H127" s="1"/>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>126</v>
       </c>
@@ -6128,7 +5511,7 @@
       </c>
       <c r="H128" s="1"/>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>127</v>
       </c>
@@ -6149,7 +5532,7 @@
       </c>
       <c r="H129" s="1"/>
     </row>
-    <row r="130" spans="1:9">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>128</v>
       </c>
@@ -6173,7 +5556,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>129</v>
       </c>
@@ -6197,7 +5580,7 @@
       </c>
       <c r="H131" s="1"/>
     </row>
-    <row r="132" spans="1:8">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>130</v>
       </c>
@@ -6218,7 +5601,7 @@
       </c>
       <c r="H132" s="1"/>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>131</v>
       </c>
@@ -6239,7 +5622,7 @@
       </c>
       <c r="H133" s="1"/>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>132</v>
       </c>
@@ -6260,7 +5643,7 @@
       </c>
       <c r="H134" s="1"/>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>133</v>
       </c>
@@ -6281,7 +5664,7 @@
       </c>
       <c r="H135" s="1"/>
     </row>
-    <row r="136" spans="1:8">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>134</v>
       </c>
@@ -6305,7 +5688,7 @@
       </c>
       <c r="H136" s="1"/>
     </row>
-    <row r="137" spans="1:8">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>135</v>
       </c>
@@ -6326,7 +5709,7 @@
       </c>
       <c r="H137" s="1"/>
     </row>
-    <row r="138" ht="24" spans="1:9">
+    <row r="138" spans="1:9" ht="26" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>136</v>
       </c>
@@ -6351,16 +5734,15 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="10.36328125" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="24"/>
@@ -6369,7 +5751,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6398,7 +5780,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -6412,7 +5794,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -6432,7 +5814,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -6452,7 +5834,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -6472,7 +5854,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -6492,7 +5874,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -6512,7 +5894,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -6532,7 +5914,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -6552,7 +5934,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -6575,7 +5957,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -6598,7 +5980,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -6618,7 +6000,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -6641,7 +6023,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -6661,7 +6043,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -6684,7 +6066,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -6704,7 +6086,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -6727,7 +6109,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -6747,7 +6129,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -6767,7 +6149,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -6790,7 +6172,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -6813,7 +6195,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -6833,7 +6215,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -6853,7 +6235,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -6870,10 +6252,10 @@
         <v>192</v>
       </c>
       <c r="G24" s="1">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -6890,10 +6272,10 @@
         <v>193</v>
       </c>
       <c r="G25" s="1">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -6913,7 +6295,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -6933,7 +6315,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -6953,7 +6335,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -6973,7 +6355,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -6994,16 +6376,16 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="10.36328125" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -7012,7 +6394,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7041,7 +6423,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -7055,7 +6437,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -7075,7 +6457,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -7095,7 +6477,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -7115,7 +6497,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -7135,7 +6517,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -7155,7 +6537,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -7175,7 +6557,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -7195,7 +6577,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -7218,7 +6600,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -7241,7 +6623,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -7265,16 +6647,15 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="10.36328125" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -7283,7 +6664,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7312,7 +6693,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -7326,7 +6707,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -7346,7 +6727,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -7366,7 +6747,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -7389,7 +6770,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -7412,7 +6793,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -7432,7 +6813,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -7452,7 +6833,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -7472,7 +6853,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -7492,7 +6873,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -7512,7 +6893,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -7532,7 +6913,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -7552,7 +6933,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -7573,16 +6954,15 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="10.36328125" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -7591,7 +6971,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7620,7 +7000,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -7634,7 +7014,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -7654,7 +7034,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -7674,7 +7054,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -7694,7 +7074,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -7714,7 +7094,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -7734,7 +7114,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -7754,7 +7134,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -7774,7 +7154,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -7797,7 +7177,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -7820,7 +7200,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -7840,7 +7220,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -7860,7 +7240,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -7880,7 +7260,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -7900,7 +7280,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -7920,7 +7300,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -7940,7 +7320,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -7961,16 +7341,15 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2" outlineLevelRow="3"/>
+  <sheetFormatPr defaultColWidth="10.36328125" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -7979,7 +7358,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8008,7 +7387,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -8022,7 +7401,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -8042,7 +7421,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -8063,16 +7442,15 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2" outlineLevelRow="3"/>
+  <sheetFormatPr defaultColWidth="10.36328125" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -8081,7 +7459,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8110,7 +7488,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -8124,7 +7502,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -8144,7 +7522,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -8165,16 +7543,15 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="10.36328125" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -8183,7 +7560,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8212,7 +7589,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -8226,7 +7603,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -8246,7 +7623,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -8266,7 +7643,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -8286,7 +7663,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -8306,7 +7683,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -8326,7 +7703,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -8346,7 +7723,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -8367,7 +7744,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Excel/ChatData.xlsx
+++ b/Assets/StreamingAssets/Excel/ChatData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Unity\Projects\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E04329F-0910-4BF3-8263-6C148184DCDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF7C3645-9825-46AC-BF74-A25A091A5A83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2830" yWindow="3940" windowWidth="19200" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4370" yWindow="2050" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="一切的开始" sheetId="1" r:id="rId1"/>
@@ -2194,7 +2194,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -2261,7 +2261,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -5279,7 +5279,7 @@
         <v>140</v>
       </c>
       <c r="G117" s="1">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H117" s="1"/>
     </row>
@@ -5736,6 +5736,7 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Assets/StreamingAssets/Excel/ChatData.xlsx
+++ b/Assets/StreamingAssets/Excel/ChatData.xlsx
@@ -1,44 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Unity\Projects\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF7C3645-9825-46AC-BF74-A25A091A5A83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B692283-A335-4E62-BA3C-3637680E8E69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4370" yWindow="2050" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="一切的开始" sheetId="1" r:id="rId1"/>
     <sheet name="修理研究完毕" sheetId="2" r:id="rId2"/>
-    <sheet name="死亡" sheetId="3" r:id="rId3"/>
-    <sheet name="第一次点开气密舱门" sheetId="4" r:id="rId4"/>
-    <sheet name="第一次进珊瑚礁海域" sheetId="5" r:id="rId5"/>
-    <sheet name="困了_01" sheetId="6" r:id="rId6"/>
-    <sheet name="困了_02" sheetId="7" r:id="rId7"/>
-    <sheet name="困了_03" sheetId="8" r:id="rId8"/>
+    <sheet name="堵住裂缝" sheetId="10" r:id="rId3"/>
+    <sheet name="死亡" sheetId="3" r:id="rId4"/>
+    <sheet name="第一次点开气密舱门" sheetId="4" r:id="rId5"/>
+    <sheet name="第一次进珊瑚礁海域" sheetId="5" r:id="rId6"/>
+    <sheet name="困了_01" sheetId="6" r:id="rId7"/>
+    <sheet name="困了_02" sheetId="7" r:id="rId8"/>
+    <sheet name="困了_03" sheetId="8" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="294">
   <si>
     <t>小段</t>
   </si>
@@ -1535,29 +1525,6 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>以前刮大风的时候,家里的屋顶不是被吹走就是被东西砸破。然后雨就哗啦啦地淋进来</t>
-    </r>
-  </si>
-  <si>
-    <t>那个雨又脏又臭,淋到头上还会掉头发</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这时候我爸就会做一个差不多的东西把屋顶补上。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>我没自己做过,可也经常在旁边看</t>
     </r>
   </si>
@@ -1588,16 +1555,6 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>完全不一样好吧，论文里其实写了很多方案，只是根据你目前的情况选了个最原始的方案</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>原来是这样吗？</t>
     </r>
   </si>
@@ -2187,6 +2144,154 @@
       </rPr>
       <t>嗯</t>
     </r>
+  </si>
+  <si>
+    <t>以前家里屋顶漏雨的时候</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>爸爸就会做一个差不多的东西把屋顶补上</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>完全不一样好吧</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>论文里其实写了很多方案</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>只是根据你目前的情况选了个最原始的方案</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>对话</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>堵住裂缝</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>我还是很有手法的嘛</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>用几块钉子和铁板就把裂缝堵住了</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>选项</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>第一次堵住渗水裂缝</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>麦麦</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>对话</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>完全没有任何缝隙</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>至少现在没有</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>你信我</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>我贴在墙上检查过了！</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>可我从摄像头里看，总感觉水平面在上升</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>好像是这样……</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>不能呀…</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个裂缝已经没在漏水了</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>应该是其他舱室里也有裂缝</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>我得去看看</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>一会再联系</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>提示</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>求生系统</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>你最好再检查一下,说不定还有缝隙</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>真的吗?</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>真的!</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>!</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>真做到啦?那确实很厉害</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>啊,终于堵住了</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>通话结束,去继续探索飞船内吧</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>我连锤子都没有,直接用铁管敲的</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>话说,从摄像头里看水平面好像在上升</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>你有感觉水平面在上升吗?</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2196,7 +2301,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -2234,6 +2339,27 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2257,7 +2383,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2268,9 +2394,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2284,6 +2407,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2774,7 +2906,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I138"/>
-  <sheetFormatPr defaultColWidth="10.36328125" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="27"/>
@@ -2784,7 +2916,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2813,7 +2945,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -2825,7 +2957,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -2846,7 +2978,7 @@
       </c>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -2867,7 +2999,7 @@
       </c>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -2887,7 +3019,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -2907,7 +3039,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -2928,7 +3060,7 @@
       </c>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -2949,7 +3081,7 @@
       </c>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -2970,7 +3102,7 @@
       </c>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -2991,7 +3123,7 @@
       </c>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -3012,7 +3144,7 @@
       </c>
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -3032,7 +3164,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -3053,7 +3185,7 @@
       </c>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -3073,7 +3205,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -3094,7 +3226,7 @@
       </c>
       <c r="H15" s="1"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -3115,7 +3247,7 @@
       </c>
       <c r="H16" s="1"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -3135,7 +3267,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -3155,7 +3287,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -3176,7 +3308,7 @@
       </c>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -3197,7 +3329,7 @@
       </c>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -3218,7 +3350,7 @@
       </c>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -3239,7 +3371,7 @@
       </c>
       <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -3260,7 +3392,7 @@
       </c>
       <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -3280,7 +3412,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -3301,7 +3433,7 @@
       </c>
       <c r="H25" s="1"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -3322,7 +3454,7 @@
       </c>
       <c r="H26" s="1"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -3343,7 +3475,7 @@
       </c>
       <c r="H27" s="1"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -3364,7 +3496,7 @@
       </c>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -3387,7 +3519,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -3408,7 +3540,7 @@
       </c>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -3429,7 +3561,7 @@
       </c>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -3450,7 +3582,7 @@
       </c>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -3471,7 +3603,7 @@
       </c>
       <c r="H33" s="1"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -3492,7 +3624,7 @@
       </c>
       <c r="H34" s="1"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -3513,7 +3645,7 @@
       </c>
       <c r="H35" s="1"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -3534,7 +3666,7 @@
       </c>
       <c r="H36" s="1"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -3555,7 +3687,7 @@
       </c>
       <c r="H37" s="1"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -3576,7 +3708,7 @@
       </c>
       <c r="H38" s="1"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -3597,7 +3729,7 @@
       </c>
       <c r="H39" s="1"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -3618,7 +3750,7 @@
       </c>
       <c r="H40" s="1"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -3639,7 +3771,7 @@
       </c>
       <c r="H41" s="1"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -3660,7 +3792,7 @@
       </c>
       <c r="H42" s="1"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -3681,7 +3813,7 @@
       </c>
       <c r="H43" s="1"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -3702,7 +3834,7 @@
       </c>
       <c r="H44" s="1"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -3723,7 +3855,7 @@
       </c>
       <c r="H45" s="1"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -3744,7 +3876,7 @@
       </c>
       <c r="H46" s="1"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -3757,7 +3889,7 @@
       <c r="D47" t="s">
         <v>59</v>
       </c>
-      <c r="F47" s="5" t="s">
+      <c r="F47" s="4" t="s">
         <v>60</v>
       </c>
       <c r="G47" s="1">
@@ -3768,7 +3900,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -3792,7 +3924,7 @@
       </c>
       <c r="H48" s="1"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -3813,7 +3945,7 @@
       </c>
       <c r="H49" s="1"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -3834,7 +3966,7 @@
       </c>
       <c r="H50" s="1"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -3855,7 +3987,7 @@
       </c>
       <c r="H51" s="1"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -3876,7 +4008,7 @@
       </c>
       <c r="H52" s="1"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -3897,7 +4029,7 @@
       </c>
       <c r="H53" s="1"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -3918,7 +4050,7 @@
       </c>
       <c r="H54" s="1"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -3939,7 +4071,7 @@
       </c>
       <c r="H55" s="1"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -3960,7 +4092,7 @@
       </c>
       <c r="H56" s="1"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -3981,7 +4113,7 @@
       </c>
       <c r="H57" s="1"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -4002,7 +4134,7 @@
       </c>
       <c r="H58" s="1"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -4023,7 +4155,7 @@
       </c>
       <c r="H59" s="1"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -4044,7 +4176,7 @@
       </c>
       <c r="H60" s="1"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -4057,7 +4189,7 @@
       <c r="D61" t="s">
         <v>59</v>
       </c>
-      <c r="F61" s="5" t="s">
+      <c r="F61" s="4" t="s">
         <v>76</v>
       </c>
       <c r="G61" s="1">
@@ -4068,7 +4200,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -4092,7 +4224,7 @@
       </c>
       <c r="H62" s="1"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -4113,7 +4245,7 @@
       </c>
       <c r="H63" s="1"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -4134,7 +4266,7 @@
       </c>
       <c r="H64" s="1"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -4155,7 +4287,7 @@
       </c>
       <c r="H65" s="1"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -4176,7 +4308,7 @@
       </c>
       <c r="H66" s="1"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -4197,7 +4329,7 @@
       </c>
       <c r="H67" s="1"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -4221,7 +4353,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -4245,7 +4377,7 @@
       </c>
       <c r="H69" s="1"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -4268,7 +4400,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -4289,7 +4421,7 @@
       </c>
       <c r="H71" s="1"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -4310,7 +4442,7 @@
       </c>
       <c r="H72" s="1"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -4333,7 +4465,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -4356,7 +4488,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -4377,7 +4509,7 @@
       </c>
       <c r="H75" s="1"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -4390,7 +4522,7 @@
       <c r="D76" t="s">
         <v>59</v>
       </c>
-      <c r="F76" s="5" t="s">
+      <c r="F76" s="4" t="s">
         <v>95</v>
       </c>
       <c r="G76" s="1">
@@ -4401,7 +4533,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -4425,7 +4557,7 @@
       </c>
       <c r="H77" s="1"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -4446,7 +4578,7 @@
       </c>
       <c r="H78" s="1"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -4469,7 +4601,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -4490,7 +4622,7 @@
       </c>
       <c r="H80" s="1"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -4511,7 +4643,7 @@
       </c>
       <c r="H81" s="1"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -4532,7 +4664,7 @@
       </c>
       <c r="H82" s="1"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -4555,7 +4687,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -4575,7 +4707,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -4595,7 +4727,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -4616,7 +4748,7 @@
       </c>
       <c r="H86" s="1"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -4636,7 +4768,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -4657,7 +4789,7 @@
       </c>
       <c r="H88" s="1"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -4680,7 +4812,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>88</v>
       </c>
@@ -4701,7 +4833,7 @@
       </c>
       <c r="H90" s="1"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>89</v>
       </c>
@@ -4721,7 +4853,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>90</v>
       </c>
@@ -4744,7 +4876,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>91</v>
       </c>
@@ -4765,7 +4897,7 @@
       </c>
       <c r="H93" s="1"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>92</v>
       </c>
@@ -4785,7 +4917,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>93</v>
       </c>
@@ -4806,7 +4938,7 @@
       </c>
       <c r="H95" s="1"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>94</v>
       </c>
@@ -4827,7 +4959,7 @@
       </c>
       <c r="H96" s="1"/>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>95</v>
       </c>
@@ -4840,7 +4972,7 @@
       <c r="D97" t="s">
         <v>59</v>
       </c>
-      <c r="F97" s="5" t="s">
+      <c r="F97" s="4" t="s">
         <v>117</v>
       </c>
       <c r="G97" s="1">
@@ -4851,7 +4983,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>96</v>
       </c>
@@ -4875,7 +5007,7 @@
       </c>
       <c r="H98" s="1"/>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>97</v>
       </c>
@@ -4896,7 +5028,7 @@
       </c>
       <c r="H99" s="1"/>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>98</v>
       </c>
@@ -4917,7 +5049,7 @@
       </c>
       <c r="H100" s="1"/>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>99</v>
       </c>
@@ -4938,7 +5070,7 @@
       </c>
       <c r="H101" s="1"/>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>100</v>
       </c>
@@ -4959,7 +5091,7 @@
       </c>
       <c r="H102" s="1"/>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>101</v>
       </c>
@@ -4980,7 +5112,7 @@
       </c>
       <c r="H103" s="1"/>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>102</v>
       </c>
@@ -5001,7 +5133,7 @@
       </c>
       <c r="H104" s="1"/>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>103</v>
       </c>
@@ -5022,7 +5154,7 @@
       </c>
       <c r="H105" s="1"/>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>104</v>
       </c>
@@ -5043,7 +5175,7 @@
       </c>
       <c r="H106" s="1"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>105</v>
       </c>
@@ -5064,7 +5196,7 @@
       </c>
       <c r="H107" s="1"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>106</v>
       </c>
@@ -5085,7 +5217,7 @@
       </c>
       <c r="H108" s="1"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>107</v>
       </c>
@@ -5106,7 +5238,7 @@
       </c>
       <c r="H109" s="1"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>108</v>
       </c>
@@ -5119,7 +5251,7 @@
       <c r="D110" t="s">
         <v>59</v>
       </c>
-      <c r="F110" s="7" t="s">
+      <c r="F110" s="6" t="s">
         <v>132</v>
       </c>
       <c r="G110" s="1">
@@ -5127,7 +5259,7 @@
       </c>
       <c r="H110" s="1"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>109</v>
       </c>
@@ -5153,7 +5285,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>110</v>
       </c>
@@ -5176,7 +5308,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>111</v>
       </c>
@@ -5199,7 +5331,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>112</v>
       </c>
@@ -5220,7 +5352,7 @@
       </c>
       <c r="H114" s="1"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>113</v>
       </c>
@@ -5241,7 +5373,7 @@
       </c>
       <c r="H115" s="1"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>114</v>
       </c>
@@ -5262,7 +5394,7 @@
       </c>
       <c r="H116" s="1"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>115</v>
       </c>
@@ -5283,7 +5415,7 @@
       </c>
       <c r="H117" s="1"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>116</v>
       </c>
@@ -5304,7 +5436,7 @@
       </c>
       <c r="H118" s="1"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>117</v>
       </c>
@@ -5325,7 +5457,7 @@
       </c>
       <c r="H119" s="1"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>118</v>
       </c>
@@ -5346,7 +5478,7 @@
       </c>
       <c r="H120" s="1"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>119</v>
       </c>
@@ -5367,7 +5499,7 @@
       </c>
       <c r="H121" s="1"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>120</v>
       </c>
@@ -5387,7 +5519,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>121</v>
       </c>
@@ -5408,7 +5540,7 @@
       </c>
       <c r="H123" s="1"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>122</v>
       </c>
@@ -5429,7 +5561,7 @@
       </c>
       <c r="H124" s="1"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>123</v>
       </c>
@@ -5449,7 +5581,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>124</v>
       </c>
@@ -5469,7 +5601,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>125</v>
       </c>
@@ -5490,7 +5622,7 @@
       </c>
       <c r="H127" s="1"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>126</v>
       </c>
@@ -5511,7 +5643,7 @@
       </c>
       <c r="H128" s="1"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>127</v>
       </c>
@@ -5532,7 +5664,7 @@
       </c>
       <c r="H129" s="1"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>128</v>
       </c>
@@ -5545,7 +5677,7 @@
       <c r="D130" t="s">
         <v>59</v>
       </c>
-      <c r="F130" s="5" t="s">
+      <c r="F130" s="4" t="s">
         <v>153</v>
       </c>
       <c r="G130" s="1">
@@ -5556,7 +5688,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>129</v>
       </c>
@@ -5580,7 +5712,7 @@
       </c>
       <c r="H131" s="1"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>130</v>
       </c>
@@ -5601,7 +5733,7 @@
       </c>
       <c r="H132" s="1"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>131</v>
       </c>
@@ -5622,7 +5754,7 @@
       </c>
       <c r="H133" s="1"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>132</v>
       </c>
@@ -5643,7 +5775,7 @@
       </c>
       <c r="H134" s="1"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>133</v>
       </c>
@@ -5664,7 +5796,7 @@
       </c>
       <c r="H135" s="1"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>134</v>
       </c>
@@ -5688,7 +5820,7 @@
       </c>
       <c r="H136" s="1"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>135</v>
       </c>
@@ -5709,7 +5841,7 @@
       </c>
       <c r="H137" s="1"/>
     </row>
-    <row r="138" spans="1:9" ht="26" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" ht="24" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>136</v>
       </c>
@@ -5722,14 +5854,14 @@
       <c r="D138" t="s">
         <v>59</v>
       </c>
-      <c r="F138" s="8" t="s">
+      <c r="F138" s="7" t="s">
         <v>164</v>
       </c>
       <c r="G138" s="1">
         <v>-1</v>
       </c>
       <c r="H138" s="1"/>
-      <c r="I138" s="6" t="s">
+      <c r="I138" s="5" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5742,8 +5874,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultColWidth="10.36328125" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I32"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="24"/>
@@ -5752,7 +5884,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5781,7 +5913,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -5795,17 +5927,17 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>166</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
@@ -5815,7 +5947,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -5835,7 +5967,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -5855,7 +5987,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -5875,7 +6007,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -5895,7 +6027,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -5915,7 +6047,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -5935,7 +6067,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -5958,7 +6090,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -5981,7 +6113,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -6001,7 +6133,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -6024,7 +6156,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -6044,7 +6176,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -6063,11 +6195,11 @@
       <c r="G15" s="1">
         <v>14</v>
       </c>
-      <c r="I15" s="6" t="s">
+      <c r="I15" s="5" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -6080,14 +6212,14 @@
       <c r="D16" t="s">
         <v>59</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="4" t="s">
         <v>183</v>
       </c>
       <c r="G16" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -6110,7 +6242,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -6130,7 +6262,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -6150,7 +6282,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -6163,17 +6295,15 @@
       <c r="D20" t="s">
         <v>11</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>188</v>
+      <c r="F20" s="8" t="s">
+        <v>257</v>
       </c>
       <c r="G20" s="1">
         <v>19</v>
       </c>
-      <c r="H20" s="1">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -6186,17 +6316,15 @@
       <c r="D21" t="s">
         <v>11</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>189</v>
+      <c r="F21" s="8" t="s">
+        <v>258</v>
       </c>
       <c r="G21" s="1">
         <v>20</v>
       </c>
-      <c r="H21" s="1">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -6210,13 +6338,13 @@
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G22" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -6224,19 +6352,19 @@
         <v>166</v>
       </c>
       <c r="C23" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D23" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G23" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -6250,13 +6378,13 @@
         <v>18</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G24" s="1">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -6269,14 +6397,14 @@
       <c r="D25" t="s">
         <v>18</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>193</v>
+      <c r="F25" s="8" t="s">
+        <v>259</v>
       </c>
       <c r="G25" s="1">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -6286,17 +6414,17 @@
       <c r="C26" t="s">
         <v>17</v>
       </c>
-      <c r="D26" t="s">
-        <v>18</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>194</v>
+      <c r="D26" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>260</v>
       </c>
       <c r="G26" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -6304,19 +6432,19 @@
         <v>166</v>
       </c>
       <c r="C27" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>195</v>
+        <v>17</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>261</v>
       </c>
       <c r="G27" s="1">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -6330,13 +6458,13 @@
         <v>11</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="G28" s="1">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -6350,13 +6478,13 @@
         <v>11</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="G29" s="1">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -6364,17 +6492,41 @@
         <v>166</v>
       </c>
       <c r="C30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G30" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>166</v>
+      </c>
+      <c r="C31" t="s">
         <v>58</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D31" t="s">
         <v>59</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="G30" s="1">
+      <c r="F31" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G31" s="1">
         <v>-1</v>
       </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="G32" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -6384,9 +6536,582 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9720864F-1D73-4315-BBEE-79B914F8E21C}">
+  <dimension ref="A1:I30"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="19.44140625" customWidth="1"/>
+    <col min="6" max="6" width="34.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="G2" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="G4" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="G5" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="G6" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="G7" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="G8" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="G9" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="G10" s="1">
+        <v>9</v>
+      </c>
+      <c r="H10">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="G11" s="1">
+        <v>10</v>
+      </c>
+      <c r="H11">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="G12" s="1">
+        <v>11</v>
+      </c>
+      <c r="H12">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="G13" s="1">
+        <v>12</v>
+      </c>
+      <c r="H13">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="G14" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="G15" s="1">
+        <v>14</v>
+      </c>
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>14</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="G16" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>15</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="G17" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>16</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="G18" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>17</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="G19" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>18</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="G20" s="1">
+        <v>19</v>
+      </c>
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>19</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="G21" s="1">
+        <v>20</v>
+      </c>
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>20</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="G22" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>21</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="G23" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>22</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="G24" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>23</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="G25" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+      <c r="B26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="1"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+      <c r="B27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="1"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="B28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="1"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="B29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="1"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultColWidth="10.36328125" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -6395,7 +7120,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6424,26 +7149,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G2" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -6452,18 +7177,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -6472,38 +7197,38 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>203</v>
       </c>
       <c r="G5" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -6512,18 +7237,18 @@
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -6532,18 +7257,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -6552,18 +7277,18 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -6572,18 +7297,18 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C10" t="s">
         <v>17</v>
@@ -6592,21 +7317,21 @@
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G10" s="1">
         <v>-1</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C11" t="s">
         <v>17</v>
@@ -6615,21 +7340,21 @@
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G11" s="1">
         <v>-1</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -6638,13 +7363,13 @@
         <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="G12" s="1">
         <v>-1</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -6653,10 +7378,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultColWidth="10.36328125" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -6665,7 +7390,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6694,26 +7419,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="G2" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -6722,18 +7447,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -6742,18 +7467,18 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -6762,21 +7487,21 @@
         <v>173</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="G5" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -6785,21 +7510,21 @@
         <v>173</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -6808,18 +7533,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -6828,18 +7553,18 @@
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="G8" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -6848,18 +7573,18 @@
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="G9" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
@@ -6868,18 +7593,18 @@
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="G10" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
@@ -6888,18 +7613,18 @@
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G11" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
@@ -6908,18 +7633,18 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -6928,18 +7653,18 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -6948,7 +7673,7 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="G14" s="1">
         <v>-1</v>
@@ -6960,10 +7685,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultColWidth="10.36328125" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -6972,7 +7697,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7001,26 +7726,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="G2" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7029,18 +7754,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7049,18 +7774,18 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -7069,18 +7794,18 @@
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="G5" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -7089,18 +7814,18 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -7109,18 +7834,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -7129,18 +7854,18 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -7149,18 +7874,18 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
@@ -7169,21 +7894,21 @@
         <v>173</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G10" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
@@ -7192,21 +7917,21 @@
         <v>173</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G11" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
@@ -7215,18 +7940,18 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -7235,18 +7960,18 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -7255,18 +7980,18 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="G14" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C15" t="s">
         <v>58</v>
@@ -7275,18 +8000,18 @@
         <v>59</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="G15" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C16" t="s">
         <v>10</v>
@@ -7295,18 +8020,18 @@
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G16" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
@@ -7315,18 +8040,18 @@
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="G17" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -7335,7 +8060,7 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="G18" s="1">
         <v>-1</v>
@@ -7347,10 +8072,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="10.36328125" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -7359,7 +8084,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7388,26 +8113,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7416,18 +8141,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7436,7 +8161,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="G4" s="1">
         <v>-1</v>
@@ -7448,10 +8173,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="10.36328125" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -7460,7 +8185,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7489,26 +8214,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7517,18 +8242,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7537,7 +8262,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="G4" s="1">
         <v>-1</v>
@@ -7549,10 +8274,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultColWidth="10.36328125" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -7561,7 +8286,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7590,26 +8315,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7618,18 +8343,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7638,18 +8363,18 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -7658,18 +8383,18 @@
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="G5" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -7678,18 +8403,18 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G6" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -7698,18 +8423,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -7718,18 +8443,18 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="G8" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -7738,7 +8463,7 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="G9" s="1">
         <v>-1</v>

--- a/Assets/StreamingAssets/Excel/ChatData.xlsx
+++ b/Assets/StreamingAssets/Excel/ChatData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B692283-A335-4E62-BA3C-3637680E8E69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65200659-DCE1-406E-84C8-A3944F83DE8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="一切的开始" sheetId="1" r:id="rId1"/>
@@ -521,9 +521,6 @@
     <t>点击底边栏的摄像头图标,打开"摄像头"窗口</t>
   </si>
   <si>
-    <t>解锁_摄像头</t>
-  </si>
-  <si>
     <t>打开摄像头窗口</t>
   </si>
   <si>
@@ -660,9 +657,6 @@
     <t>点击底边栏的背包图标,打开"背包"窗口</t>
   </si>
   <si>
-    <t>解锁_背包</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -729,9 +723,6 @@
     </r>
   </si>
   <si>
-    <t>添加_玩家_压缩饼干</t>
-  </si>
-  <si>
     <t>打开压缩饼干的详情窗口</t>
   </si>
   <si>
@@ -808,9 +799,6 @@
     <t>点击底边栏的状态图标,打开"状态"窗口</t>
   </si>
   <si>
-    <t>解锁_状态</t>
-  </si>
-  <si>
     <t>打开状态窗口</t>
   </si>
   <si>
@@ -986,9 +974,6 @@
     <t>点击底边栏的研究图标,打开"研究"窗口</t>
   </si>
   <si>
-    <t>解锁_研究</t>
-  </si>
-  <si>
     <t>打开研究窗口</t>
   </si>
   <si>
@@ -1309,9 +1294,6 @@
   </si>
   <si>
     <t>点击底边栏的地点图标,打开"地点"窗口</t>
-  </si>
-  <si>
-    <t>解锁_地点</t>
   </si>
   <si>
     <t>打开地点窗口</t>
@@ -1387,9 +1369,6 @@
 在你没进行操作时，游戏时间是静止的</t>
   </si>
   <si>
-    <t>解锁_休息;解锁_装备;解锁_详情</t>
-  </si>
-  <si>
     <t>修理研究完毕</t>
   </si>
   <si>
@@ -1478,9 +1457,6 @@
       </rPr>
       <t>好的好的！</t>
     </r>
-  </si>
-  <si>
-    <t>解锁_制作</t>
   </si>
   <si>
     <t>打开"制作窗口",指挥麦麦制作一个"裂缝填充物"</t>
@@ -2291,6 +2267,38 @@
   </si>
   <si>
     <t>你有感觉水平面在上升吗?</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加_玩家_压缩饼干;解锁_详情_false</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁_背包_true</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁_摄像头_true</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁_状态_true</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁_研究_true</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁_地点_true</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁_休息_false;解锁_装备_false</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁_制作_true</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -3896,8 +3904,8 @@
         <v>46</v>
       </c>
       <c r="H47" s="1"/>
-      <c r="I47" t="s">
-        <v>61</v>
+      <c r="I47" s="9" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -3914,10 +3922,10 @@
         <v>11</v>
       </c>
       <c r="E48" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F48" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="G48" s="1">
         <v>47</v>
@@ -3938,7 +3946,7 @@
         <v>11</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G49" s="1">
         <v>48</v>
@@ -3959,7 +3967,7 @@
         <v>11</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G50" s="1">
         <v>49</v>
@@ -3980,7 +3988,7 @@
         <v>11</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G51" s="1">
         <v>50</v>
@@ -4001,7 +4009,7 @@
         <v>11</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G52" s="1">
         <v>51</v>
@@ -4022,7 +4030,7 @@
         <v>11</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G53" s="1">
         <v>52</v>
@@ -4043,7 +4051,7 @@
         <v>18</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G54" s="1">
         <v>53</v>
@@ -4064,7 +4072,7 @@
         <v>11</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G55" s="1">
         <v>54</v>
@@ -4085,7 +4093,7 @@
         <v>11</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G56" s="1">
         <v>55</v>
@@ -4106,7 +4114,7 @@
         <v>18</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G57" s="1">
         <v>57</v>
@@ -4127,7 +4135,7 @@
         <v>18</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G58" s="1">
         <v>57</v>
@@ -4148,7 +4156,7 @@
         <v>11</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G59" s="1">
         <v>58</v>
@@ -4169,7 +4177,7 @@
         <v>11</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G60" s="1">
         <v>59</v>
@@ -4190,14 +4198,14 @@
         <v>59</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G61" s="1">
         <v>60</v>
       </c>
       <c r="H61" s="1"/>
-      <c r="I61" t="s">
-        <v>77</v>
+      <c r="I61" s="9" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -4214,10 +4222,10 @@
         <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G62" s="1">
         <v>61</v>
@@ -4238,7 +4246,7 @@
         <v>11</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G63" s="1">
         <v>62</v>
@@ -4259,7 +4267,7 @@
         <v>11</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G64" s="1">
         <v>63</v>
@@ -4280,7 +4288,7 @@
         <v>11</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G65" s="1">
         <v>64</v>
@@ -4301,7 +4309,7 @@
         <v>11</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G66" s="1">
         <v>65</v>
@@ -4322,7 +4330,7 @@
         <v>11</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G67" s="1">
         <v>66</v>
@@ -4343,14 +4351,14 @@
         <v>59</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G68" s="1">
         <v>67</v>
       </c>
       <c r="H68" s="1"/>
-      <c r="I68" t="s">
-        <v>86</v>
+      <c r="I68" s="9" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
@@ -4367,10 +4375,10 @@
         <v>18</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G69" s="1">
         <v>68</v>
@@ -4391,7 +4399,7 @@
         <v>11</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G70" s="1">
         <v>69</v>
@@ -4414,7 +4422,7 @@
         <v>11</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G71" s="1">
         <v>70</v>
@@ -4435,7 +4443,7 @@
         <v>11</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G72" s="1">
         <v>71</v>
@@ -4456,7 +4464,7 @@
         <v>11</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G73" s="1">
         <v>72</v>
@@ -4479,7 +4487,7 @@
         <v>11</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G74" s="1">
         <v>73</v>
@@ -4502,7 +4510,7 @@
         <v>11</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G75" s="1">
         <v>74</v>
@@ -4523,14 +4531,14 @@
         <v>59</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G76" s="1">
         <v>75</v>
       </c>
       <c r="H76" s="1"/>
-      <c r="I76" t="s">
-        <v>96</v>
+      <c r="I76" s="9" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
@@ -4547,10 +4555,10 @@
         <v>18</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G77" s="1">
         <v>76</v>
@@ -4571,7 +4579,7 @@
         <v>11</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G78" s="1">
         <v>77</v>
@@ -4592,7 +4600,7 @@
         <v>11</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G79" s="1">
         <v>78</v>
@@ -4615,7 +4623,7 @@
         <v>11</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G80" s="1">
         <v>79</v>
@@ -4636,7 +4644,7 @@
         <v>11</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G81" s="1">
         <v>80</v>
@@ -4657,7 +4665,7 @@
         <v>11</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G82" s="1">
         <v>81</v>
@@ -4678,7 +4686,7 @@
         <v>11</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G83" s="1">
         <v>82</v>
@@ -4701,7 +4709,7 @@
         <v>11</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G84" s="1">
         <v>83</v>
@@ -4721,7 +4729,7 @@
         <v>11</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G85" s="1">
         <v>84</v>
@@ -4741,7 +4749,7 @@
         <v>11</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G86" s="1">
         <v>85</v>
@@ -4762,7 +4770,7 @@
         <v>11</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G87" s="1">
         <v>86</v>
@@ -4782,7 +4790,7 @@
         <v>11</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G88" s="1">
         <v>87</v>
@@ -4803,7 +4811,7 @@
         <v>11</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G89" s="1">
         <v>88</v>
@@ -4826,7 +4834,7 @@
         <v>11</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G90" s="1">
         <v>89</v>
@@ -4847,7 +4855,7 @@
         <v>11</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G91" s="1">
         <v>90</v>
@@ -4867,7 +4875,7 @@
         <v>11</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G92" s="1">
         <v>91</v>
@@ -4890,7 +4898,7 @@
         <v>11</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G93" s="1">
         <v>92</v>
@@ -4911,7 +4919,7 @@
         <v>11</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G94" s="1">
         <v>93</v>
@@ -4931,7 +4939,7 @@
         <v>11</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G95" s="1">
         <v>94</v>
@@ -4952,7 +4960,7 @@
         <v>11</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G96" s="1">
         <v>95</v>
@@ -4973,14 +4981,14 @@
         <v>59</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G97" s="1">
         <v>96</v>
       </c>
       <c r="H97" s="1"/>
-      <c r="I97" t="s">
-        <v>118</v>
+      <c r="I97" s="9" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
@@ -4997,10 +5005,10 @@
         <v>18</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G98" s="1">
         <v>97</v>
@@ -5021,7 +5029,7 @@
         <v>11</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G99" s="1">
         <v>98</v>
@@ -5042,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G100" s="1">
         <v>99</v>
@@ -5063,7 +5071,7 @@
         <v>11</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="G101" s="1">
         <v>100</v>
@@ -5084,7 +5092,7 @@
         <v>11</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="G102" s="1">
         <v>101</v>
@@ -5105,7 +5113,7 @@
         <v>11</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G103" s="1">
         <v>102</v>
@@ -5126,7 +5134,7 @@
         <v>11</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G104" s="1">
         <v>103</v>
@@ -5147,7 +5155,7 @@
         <v>18</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G105" s="1">
         <v>104</v>
@@ -5168,7 +5176,7 @@
         <v>11</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G106" s="1">
         <v>105</v>
@@ -5189,7 +5197,7 @@
         <v>11</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G107" s="1">
         <v>106</v>
@@ -5210,7 +5218,7 @@
         <v>11</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G108" s="1">
         <v>107</v>
@@ -5231,7 +5239,7 @@
         <v>11</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="G109" s="1">
         <v>108</v>
@@ -5252,7 +5260,7 @@
         <v>59</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="G110" s="1">
         <v>109</v>
@@ -5273,10 +5281,10 @@
         <v>18</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="G111" s="1">
         <v>110</v>
@@ -5299,7 +5307,7 @@
         <v>11</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G112" s="1">
         <v>111</v>
@@ -5322,7 +5330,7 @@
         <v>11</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="G113" s="1">
         <v>112</v>
@@ -5345,7 +5353,7 @@
         <v>11</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="G114" s="1">
         <v>113</v>
@@ -5366,7 +5374,7 @@
         <v>11</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="G115" s="1">
         <v>114</v>
@@ -5387,7 +5395,7 @@
         <v>11</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="G116" s="1">
         <v>115</v>
@@ -5408,7 +5416,7 @@
         <v>18</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G117" s="1">
         <v>117</v>
@@ -5429,7 +5437,7 @@
         <v>18</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="G118" s="1">
         <v>117</v>
@@ -5450,7 +5458,7 @@
         <v>11</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="G119" s="1">
         <v>118</v>
@@ -5471,7 +5479,7 @@
         <v>11</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="G120" s="1">
         <v>119</v>
@@ -5492,7 +5500,7 @@
         <v>11</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G121" s="1">
         <v>120</v>
@@ -5513,7 +5521,7 @@
         <v>11</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G122" s="1">
         <v>121</v>
@@ -5533,7 +5541,7 @@
         <v>18</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="G123" s="1">
         <v>122</v>
@@ -5554,7 +5562,7 @@
         <v>11</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="G124" s="1">
         <v>123</v>
@@ -5575,7 +5583,7 @@
         <v>11</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="G125" s="1">
         <v>124</v>
@@ -5595,7 +5603,7 @@
         <v>11</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="G126" s="1">
         <v>125</v>
@@ -5615,7 +5623,7 @@
         <v>11</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G127" s="1">
         <v>126</v>
@@ -5636,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G128" s="1">
         <v>127</v>
@@ -5657,7 +5665,7 @@
         <v>11</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G129" s="1">
         <v>128</v>
@@ -5678,14 +5686,14 @@
         <v>59</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="G130" s="1">
         <v>129</v>
       </c>
       <c r="H130" s="1"/>
-      <c r="I130" t="s">
-        <v>154</v>
+      <c r="I130" s="9" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
@@ -5702,10 +5710,10 @@
         <v>18</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="G131" s="1">
         <v>130</v>
@@ -5726,7 +5734,7 @@
         <v>11</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="G132" s="1">
         <v>131</v>
@@ -5747,7 +5755,7 @@
         <v>11</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G133" s="1">
         <v>132</v>
@@ -5768,7 +5776,7 @@
         <v>11</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G134" s="1">
         <v>133</v>
@@ -5789,7 +5797,7 @@
         <v>59</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="G135" s="1">
         <v>134</v>
@@ -5810,10 +5818,10 @@
         <v>11</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="G136" s="1">
         <v>135</v>
@@ -5834,7 +5842,7 @@
         <v>11</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="G137" s="1">
         <v>136</v>
@@ -5855,14 +5863,14 @@
         <v>59</v>
       </c>
       <c r="F138" s="7" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G138" s="1">
         <v>-1</v>
       </c>
       <c r="H138" s="1"/>
-      <c r="I138" s="5" t="s">
-        <v>165</v>
+      <c r="I138" s="9" t="s">
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -5918,10 +5926,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="G2" s="1">
         <v>8</v>
@@ -5932,7 +5940,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -5941,7 +5949,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
@@ -5952,7 +5960,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
@@ -5961,7 +5969,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="G4" s="1">
         <v>4</v>
@@ -5972,7 +5980,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -5981,7 +5989,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="G5" s="1">
         <v>4</v>
@@ -5992,7 +6000,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -6001,7 +6009,7 @@
         <v>11</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
@@ -6012,7 +6020,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -6021,7 +6029,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
@@ -6032,7 +6040,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -6041,7 +6049,7 @@
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
@@ -6052,7 +6060,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -6061,7 +6069,7 @@
         <v>11</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
@@ -6072,19 +6080,19 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>159</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
         <v>166</v>
       </c>
-      <c r="C10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" t="s">
-        <v>173</v>
-      </c>
       <c r="E10" s="3" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="G10" s="1">
         <v>10</v>
@@ -6095,19 +6103,19 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>159</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
         <v>166</v>
       </c>
-      <c r="C11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" t="s">
-        <v>173</v>
-      </c>
       <c r="E11" s="3" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="G11" s="1">
         <v>12</v>
@@ -6118,7 +6126,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C12" t="s">
         <v>58</v>
@@ -6127,7 +6135,7 @@
         <v>59</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
@@ -6138,7 +6146,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -6147,10 +6155,10 @@
         <v>11</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
@@ -6161,7 +6169,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C14" t="s">
         <v>17</v>
@@ -6170,7 +6178,7 @@
         <v>18</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="G14" s="1">
         <v>13</v>
@@ -6181,7 +6189,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C15" t="s">
         <v>10</v>
@@ -6190,13 +6198,13 @@
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="G15" s="1">
         <v>14</v>
       </c>
-      <c r="I15" s="5" t="s">
-        <v>182</v>
+      <c r="I15" s="9" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -6204,7 +6212,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C16" t="s">
         <v>58</v>
@@ -6213,7 +6221,7 @@
         <v>59</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="G16" s="1">
         <v>15</v>
@@ -6224,7 +6232,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
@@ -6233,10 +6241,10 @@
         <v>11</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="G17" s="1">
         <v>16</v>
@@ -6247,7 +6255,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -6256,7 +6264,7 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="G18" s="1">
         <v>17</v>
@@ -6267,7 +6275,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C19" t="s">
         <v>10</v>
@@ -6276,7 +6284,7 @@
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="G19" s="1">
         <v>18</v>
@@ -6287,7 +6295,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
@@ -6296,7 +6304,7 @@
         <v>11</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="G20" s="1">
         <v>19</v>
@@ -6308,7 +6316,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C21" t="s">
         <v>10</v>
@@ -6317,7 +6325,7 @@
         <v>11</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="G21" s="1">
         <v>20</v>
@@ -6329,7 +6337,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C22" t="s">
         <v>10</v>
@@ -6338,7 +6346,7 @@
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="G22" s="1">
         <v>21</v>
@@ -6349,7 +6357,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C23" t="s">
         <v>17</v>
@@ -6358,7 +6366,7 @@
         <v>18</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="G23" s="1">
         <v>28</v>
@@ -6369,7 +6377,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C24" t="s">
         <v>17</v>
@@ -6378,7 +6386,7 @@
         <v>18</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="G24" s="1">
         <v>28</v>
@@ -6389,7 +6397,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C25" t="s">
         <v>17</v>
@@ -6398,7 +6406,7 @@
         <v>18</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="G25" s="1">
         <v>24</v>
@@ -6409,16 +6417,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C26" t="s">
         <v>17</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="G26" s="1">
         <v>25</v>
@@ -6429,16 +6437,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C27" t="s">
         <v>17</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="G27" s="1">
         <v>26</v>
@@ -6449,7 +6457,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C28" t="s">
         <v>10</v>
@@ -6458,7 +6466,7 @@
         <v>11</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="G28" s="1">
         <v>27</v>
@@ -6469,7 +6477,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C29" t="s">
         <v>10</v>
@@ -6478,7 +6486,7 @@
         <v>11</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="G29" s="1">
         <v>28</v>
@@ -6489,7 +6497,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C30" t="s">
         <v>10</v>
@@ -6498,7 +6506,7 @@
         <v>11</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="G30" s="1">
         <v>29</v>
@@ -6509,7 +6517,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C31" t="s">
         <v>58</v>
@@ -6518,7 +6526,7 @@
         <v>59</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="G31" s="1">
         <v>-1</v>
@@ -6578,10 +6586,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="G2" s="1">
         <v>8</v>
@@ -6592,7 +6600,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -6601,7 +6609,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
@@ -6612,7 +6620,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -6621,7 +6629,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
@@ -6632,7 +6640,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -6641,7 +6649,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="G5" s="1">
         <v>4</v>
@@ -6652,16 +6660,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="G6" s="1">
         <v>21</v>
@@ -6672,16 +6680,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
@@ -6692,16 +6700,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>263</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>271</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
@@ -6712,16 +6720,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
@@ -6732,17 +6740,17 @@
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="10" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="G10" s="1">
         <v>9</v>
@@ -6756,17 +6764,17 @@
         <v>9</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="10" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="G11" s="1">
         <v>10</v>
@@ -6780,16 +6788,16 @@
         <v>10</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
@@ -6803,17 +6811,17 @@
         <v>11</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="10" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
@@ -6827,16 +6835,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C14" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="F14" s="10" t="s">
         <v>267</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>275</v>
       </c>
       <c r="G14" s="1">
         <v>13</v>
@@ -6847,16 +6855,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="G15" s="1">
         <v>14</v>
@@ -6868,16 +6876,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="G16" s="1">
         <v>15</v>
@@ -6888,17 +6896,17 @@
         <v>15</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="10" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="G17" s="1">
         <v>16</v>
@@ -6909,16 +6917,16 @@
         <v>16</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D18" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="F18" s="10" t="s">
         <v>270</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>278</v>
       </c>
       <c r="G18" s="1">
         <v>17</v>
@@ -6929,16 +6937,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G19" s="1">
         <v>18</v>
@@ -6949,16 +6957,16 @@
         <v>18</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="G20" s="1">
         <v>19</v>
@@ -6970,16 +6978,16 @@
         <v>19</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="G21" s="1">
         <v>20</v>
@@ -6991,16 +6999,16 @@
         <v>20</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="D22" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="F22" s="10" t="s">
         <v>282</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>290</v>
       </c>
       <c r="G22" s="1">
         <v>-1</v>
@@ -7011,16 +7019,16 @@
         <v>21</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G23" s="1">
         <v>22</v>
@@ -7031,16 +7039,16 @@
         <v>22</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="G24" s="1">
         <v>13</v>
@@ -7051,16 +7059,16 @@
         <v>23</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="G25" s="1">
         <v>13</v>
@@ -7154,10 +7162,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="G2" s="1">
         <v>10</v>
@@ -7168,7 +7176,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7177,7 +7185,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
@@ -7188,7 +7196,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7197,7 +7205,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
@@ -7208,7 +7216,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -7217,7 +7225,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="G5" s="1">
         <v>4</v>
@@ -7228,7 +7236,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -7237,7 +7245,7 @@
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
@@ -7248,7 +7256,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -7257,7 +7265,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
@@ -7268,7 +7276,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -7277,7 +7285,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
@@ -7288,16 +7296,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>187</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="C9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>203</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
@@ -7308,7 +7316,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C10" t="s">
         <v>17</v>
@@ -7317,13 +7325,13 @@
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G10" s="1">
         <v>-1</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -7331,7 +7339,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C11" t="s">
         <v>17</v>
@@ -7340,13 +7348,13 @@
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="G11" s="1">
         <v>-1</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -7354,7 +7362,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -7363,13 +7371,13 @@
         <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G12" s="1">
         <v>-1</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -7424,10 +7432,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="G2" s="1">
         <v>4</v>
@@ -7438,7 +7446,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7447,7 +7455,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
@@ -7458,7 +7466,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7467,7 +7475,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
@@ -7478,19 +7486,19 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="G5" s="1">
         <v>-1</v>
@@ -7501,19 +7509,19 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
@@ -7524,16 +7532,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="C7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>216</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
@@ -7544,7 +7552,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -7553,7 +7561,7 @@
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="G8" s="1">
         <v>8</v>
@@ -7564,7 +7572,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -7573,7 +7581,7 @@
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="G9" s="1">
         <v>9</v>
@@ -7584,7 +7592,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
@@ -7593,7 +7601,7 @@
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="G10" s="1">
         <v>11</v>
@@ -7604,7 +7612,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
@@ -7613,7 +7621,7 @@
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="G11" s="1">
         <v>10</v>
@@ -7624,7 +7632,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
@@ -7633,7 +7641,7 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
@@ -7644,7 +7652,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -7653,7 +7661,7 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
@@ -7664,7 +7672,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -7673,7 +7681,7 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="G14" s="1">
         <v>-1</v>
@@ -7731,10 +7739,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="G2" s="1">
         <v>4</v>
@@ -7745,7 +7753,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7754,7 +7762,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
@@ -7765,7 +7773,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7774,7 +7782,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
@@ -7785,7 +7793,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -7794,7 +7802,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="G5" s="1">
         <v>5</v>
@@ -7805,7 +7813,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -7814,7 +7822,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
@@ -7825,7 +7833,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -7834,7 +7842,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
@@ -7845,7 +7853,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -7854,7 +7862,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
@@ -7865,16 +7873,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>216</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>224</v>
-      </c>
-      <c r="C9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>232</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
@@ -7885,19 +7893,19 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="G10" s="1">
         <v>10</v>
@@ -7908,19 +7916,19 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="G11" s="1">
         <v>14</v>
@@ -7931,7 +7939,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
@@ -7940,7 +7948,7 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
@@ -7951,7 +7959,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -7960,7 +7968,7 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
@@ -7971,7 +7979,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -7980,7 +7988,7 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="G14" s="1">
         <v>13</v>
@@ -7991,7 +7999,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C15" t="s">
         <v>58</v>
@@ -8000,7 +8008,7 @@
         <v>59</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="G15" s="1">
         <v>-1</v>
@@ -8011,7 +8019,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C16" t="s">
         <v>10</v>
@@ -8020,7 +8028,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="G16" s="1">
         <v>15</v>
@@ -8031,7 +8039,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
@@ -8040,7 +8048,7 @@
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="G17" s="1">
         <v>16</v>
@@ -8051,7 +8059,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -8060,7 +8068,7 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="G18" s="1">
         <v>-1</v>
@@ -8118,10 +8126,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
@@ -8132,7 +8140,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -8141,7 +8149,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
@@ -8152,7 +8160,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -8161,7 +8169,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="G4" s="1">
         <v>-1</v>
@@ -8219,10 +8227,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
@@ -8233,7 +8241,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -8242,7 +8250,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
@@ -8253,7 +8261,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -8262,7 +8270,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="G4" s="1">
         <v>-1</v>
@@ -8320,10 +8328,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
@@ -8334,7 +8342,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -8343,7 +8351,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
@@ -8354,7 +8362,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -8363,7 +8371,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
@@ -8374,7 +8382,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -8383,7 +8391,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="G5" s="1">
         <v>5</v>
@@ -8394,7 +8402,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -8403,7 +8411,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="G6" s="1">
         <v>7</v>
@@ -8414,7 +8422,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -8423,7 +8431,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
@@ -8434,7 +8442,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -8443,7 +8451,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="G8" s="1">
         <v>-1</v>
@@ -8454,7 +8462,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -8463,7 +8471,7 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="G9" s="1">
         <v>-1</v>

--- a/Assets/StreamingAssets/Excel/ChatData.xlsx
+++ b/Assets/StreamingAssets/Excel/ChatData.xlsx
@@ -8,27 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65200659-DCE1-406E-84C8-A3944F83DE8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCCC3172-97D9-49A6-B180-038A6708C108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="一切的开始" sheetId="1" r:id="rId1"/>
     <sheet name="修理研究完毕" sheetId="2" r:id="rId2"/>
-    <sheet name="堵住裂缝" sheetId="10" r:id="rId3"/>
-    <sheet name="死亡" sheetId="3" r:id="rId4"/>
-    <sheet name="第一次点开气密舱门" sheetId="4" r:id="rId5"/>
-    <sheet name="第一次进珊瑚礁海域" sheetId="5" r:id="rId6"/>
-    <sheet name="困了_01" sheetId="6" r:id="rId7"/>
-    <sheet name="困了_02" sheetId="7" r:id="rId8"/>
-    <sheet name="困了_03" sheetId="8" r:id="rId9"/>
+    <sheet name="不研究修理_01" sheetId="11" r:id="rId3"/>
+    <sheet name="不研究修理_02" sheetId="12" r:id="rId4"/>
+    <sheet name="堵住裂缝" sheetId="10" r:id="rId5"/>
+    <sheet name="死亡" sheetId="3" r:id="rId6"/>
+    <sheet name="第一次点开气密舱门" sheetId="4" r:id="rId7"/>
+    <sheet name="第一次进珊瑚礁海域" sheetId="5" r:id="rId8"/>
+    <sheet name="困了_01" sheetId="6" r:id="rId9"/>
+    <sheet name="困了_02" sheetId="7" r:id="rId10"/>
+    <sheet name="困了_03" sheetId="8" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1255" uniqueCount="351">
   <si>
     <t>小段</t>
   </si>
@@ -2300,6 +2302,226 @@
   <si>
     <t>解锁_制作_true</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>不研究修理_01</t>
+  </si>
+  <si>
+    <t>不研究修理_01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>不研究修理_01</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>第一天5点时，未完成修理的研究</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>已经好久了</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>那篇文章你看得怎么样了?</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>我正在看呢，你先别急</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>抱歉,我没忍住摸了会儿鱼</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>麻烦你了,麻烦你了</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>可是我真的没法不急</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>水面越来越高了</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>辛苦您尽快了</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>选项</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>一定要先研究"修理"哦,不然麦麦撑不了多久了</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>?!!</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在都什么时候了呀?</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>麦麦</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>对话</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>求求您快一点吧</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>不研究修理_02</t>
+  </si>
+  <si>
+    <t>不研究修理_02</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>不研究修理_03</t>
+  </si>
+  <si>
+    <t>第一天11点时，未完成修理的研究</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>真的还没研究完吗?</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>是的，这很复杂</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>还没研究完，你先别着急</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>很感谢你帮助我研究这些东西</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>但是</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>我或许能找到修补裂缝的办法</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>要不自己试一下吧</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>你好像一直研究不完</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>这大概需要1个小时</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>没事的,我一个人研究就行了</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>不研究修理_04</t>
+  </si>
+  <si>
+    <t>不研究修理_05</t>
+  </si>
+  <si>
+    <t>真的吗？</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>我还是有点担心</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>相信我,我不会害你的</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>那个……</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>没问题,说不定你自己就能搞明白怎么修理裂缝</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>好</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>我相信你</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>不要骗麦麦哦</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果你没在研究的话,赶紧研究"修理"这项科技吧</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>你还要搜集物资</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>水和食物也还不够</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>这些你都要去收集</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>研究的事情就交给我来吧</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>那我就去研究了</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>不过搜索物资的任务还得继续</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>只能边探索边在脑子里思考了</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>接下来继续探索并为生存做准备吧</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>麦麦会一心二用,自己在脑子中思考如何修理裂缝</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>不研究修理_06</t>
+  </si>
+  <si>
+    <t>不研究修理_07</t>
+  </si>
+  <si>
+    <t>不研究修理_08</t>
   </si>
 </sst>
 </file>
@@ -2309,7 +2531,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -2368,6 +2590,12 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2391,7 +2619,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2424,6 +2652,27 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5880,6 +6129,308 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="4" width="18"/>
+    <col min="5" max="5" width="10"/>
+    <col min="6" max="6" width="42"/>
+    <col min="7" max="8" width="10"/>
+    <col min="9" max="9" width="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G2" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G4" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="4" width="18"/>
+    <col min="5" max="5" width="10"/>
+    <col min="6" max="6" width="42"/>
+    <col min="7" max="8" width="10"/>
+    <col min="9" max="9" width="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G2" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="G4" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>241</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G5" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>241</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="G6" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>241</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="G7" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>241</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G8" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>241</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="G9" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I32"/>
@@ -6544,6 +7095,1074 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF26B22E-2097-44D2-A335-C76ACA21E475}">
+  <dimension ref="A1:I30"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="13.109375" customWidth="1"/>
+    <col min="5" max="5" width="30.5546875" customWidth="1"/>
+    <col min="6" max="6" width="34.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="G2" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="G4" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="G5" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="G6" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="G7" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="G8" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="G9" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="G10" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="G11" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="G12" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="G13" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="G14" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="1"/>
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="1"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="1"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="1"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="1"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="1"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="1"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="1"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+      <c r="B26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="1"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+      <c r="B27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="1"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="B28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="1"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="B29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="1"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14D5AC1A-C19B-4034-9713-8C5FDC844D81}">
+  <dimension ref="A1:I30"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.33203125" style="11"/>
+    <col min="2" max="2" width="13.109375" style="11" customWidth="1"/>
+    <col min="3" max="4" width="10.33203125" style="11"/>
+    <col min="5" max="5" width="30.5546875" style="11" customWidth="1"/>
+    <col min="6" max="6" width="57.88671875" style="11" customWidth="1"/>
+    <col min="7" max="16384" width="10.33203125" style="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="12">
+        <v>0</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>317</v>
+      </c>
+      <c r="G2" s="12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="12">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>333</v>
+      </c>
+      <c r="G3" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="12">
+        <v>2</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>318</v>
+      </c>
+      <c r="G4" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="12">
+        <v>3</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>319</v>
+      </c>
+      <c r="G5" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="12">
+        <v>4</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>320</v>
+      </c>
+      <c r="G6" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="12">
+        <v>5</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>321</v>
+      </c>
+      <c r="G7" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="12">
+        <v>6</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>322</v>
+      </c>
+      <c r="G8" s="12">
+        <v>7</v>
+      </c>
+      <c r="H8" s="11">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="12">
+        <v>7</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>325</v>
+      </c>
+      <c r="G9" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="12">
+        <v>8</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="E10" s="16"/>
+      <c r="F10" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="G10" s="12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="12">
+        <v>9</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="E11" s="16"/>
+      <c r="F11" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="G11" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="12">
+        <v>10</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>326</v>
+      </c>
+      <c r="G12" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="12">
+        <v>11</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="E13" s="16"/>
+      <c r="F13" s="15" t="s">
+        <v>327</v>
+      </c>
+      <c r="G13" s="12">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="12">
+        <v>12</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>334</v>
+      </c>
+      <c r="G14" s="12">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="12">
+        <v>13</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="G15" s="12">
+        <v>14</v>
+      </c>
+      <c r="I15" s="17"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="12">
+        <v>14</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="G16" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="12">
+        <v>15</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>332</v>
+      </c>
+      <c r="G17" s="12">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="12">
+        <v>16</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="G18" s="12">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="12">
+        <v>17</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="G19" s="12">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="12">
+        <v>18</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="G20" s="12">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="12">
+        <v>19</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="G21" s="12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="12">
+        <v>20</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>335</v>
+      </c>
+      <c r="G22" s="12">
+        <v>22</v>
+      </c>
+      <c r="H22" s="11">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="12">
+        <v>21</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>336</v>
+      </c>
+      <c r="G23" s="12">
+        <v>22</v>
+      </c>
+      <c r="H23" s="11">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="12">
+        <v>22</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>337</v>
+      </c>
+      <c r="G24" s="12">
+        <v>23</v>
+      </c>
+      <c r="H24" s="12"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="12">
+        <v>23</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="G25" s="12">
+        <v>-1</v>
+      </c>
+      <c r="H25" s="12"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="12">
+        <v>24</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="G26" s="11">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="12">
+        <v>25</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="G27" s="11">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="12">
+        <v>26</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="G28" s="11">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="12">
+        <v>27</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>349</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="G29" s="11">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="12">
+        <v>28</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="G30" s="11">
+        <v>-1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9720864F-1D73-4315-BBEE-79B914F8E21C}">
   <dimension ref="A1:I30"/>
   <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
@@ -7116,7 +8735,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I12"/>
   <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
@@ -7386,7 +9005,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I14"/>
   <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
@@ -7693,7 +9312,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I18"/>
   <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
@@ -8080,7 +9699,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
@@ -8179,306 +9798,4 @@
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="4" width="18"/>
-    <col min="5" max="5" width="10"/>
-    <col min="6" max="6" width="42"/>
-    <col min="7" max="8" width="10"/>
-    <col min="9" max="9" width="18"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>238</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="G2" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>238</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="G3" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>238</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="G4" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="4" width="18"/>
-    <col min="5" max="5" width="10"/>
-    <col min="6" max="6" width="42"/>
-    <col min="7" max="8" width="10"/>
-    <col min="9" max="9" width="18"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>241</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="G2" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>241</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="G3" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>241</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="G4" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>241</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="G5" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>241</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="G6" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>241</v>
-      </c>
-      <c r="C7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="G7" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>241</v>
-      </c>
-      <c r="C8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="G8" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>241</v>
-      </c>
-      <c r="C9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="G9" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/Assets/StreamingAssets/Excel/ChatData.xlsx
+++ b/Assets/StreamingAssets/Excel/ChatData.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCCC3172-97D9-49A6-B180-038A6708C108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17655" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="一切的开始" sheetId="1" r:id="rId1"/>
@@ -26,11 +20,24 @@
     <sheet name="困了_03" sheetId="8" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1255" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1255" uniqueCount="337">
   <si>
     <t>小段</t>
   </si>
@@ -523,6 +530,9 @@
     <t>点击底边栏的摄像头图标,打开"摄像头"窗口</t>
   </si>
   <si>
+    <t>解锁_摄像头_true</t>
+  </si>
+  <si>
     <t>打开摄像头窗口</t>
   </si>
   <si>
@@ -659,6 +669,9 @@
     <t>点击底边栏的背包图标,打开"背包"窗口</t>
   </si>
   <si>
+    <t>解锁_背包_true</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -725,6 +738,9 @@
     </r>
   </si>
   <si>
+    <t>添加_玩家_压缩饼干;解锁_详情_false</t>
+  </si>
+  <si>
     <t>打开压缩饼干的详情窗口</t>
   </si>
   <si>
@@ -801,6 +817,9 @@
     <t>点击底边栏的状态图标,打开"状态"窗口</t>
   </si>
   <si>
+    <t>解锁_状态_true</t>
+  </si>
+  <si>
     <t>打开状态窗口</t>
   </si>
   <si>
@@ -976,6 +995,9 @@
     <t>点击底边栏的研究图标,打开"研究"窗口</t>
   </si>
   <si>
+    <t>解锁_研究_true</t>
+  </si>
+  <si>
     <t>打开研究窗口</t>
   </si>
   <si>
@@ -1296,6 +1318,9 @@
   </si>
   <si>
     <t>点击底边栏的地点图标,打开"地点"窗口</t>
+  </si>
+  <si>
+    <t>解锁_地点_true</t>
   </si>
   <si>
     <t>打开地点窗口</t>
@@ -1371,6 +1396,9 @@
 在你没进行操作时，游戏时间是静止的</t>
   </si>
   <si>
+    <t>解锁_休息_false;解锁_装备_false</t>
+  </si>
+  <si>
     <t>修理研究完毕</t>
   </si>
   <si>
@@ -1461,6 +1489,9 @@
     </r>
   </si>
   <si>
+    <t>解锁_制作_true</t>
+  </si>
+  <si>
     <t>打开"制作窗口",指挥麦麦制作一个"裂缝填充物"</t>
   </si>
   <si>
@@ -1497,6 +1528,12 @@
     </r>
   </si>
   <si>
+    <t>以前家里屋顶漏雨的时候</t>
+  </si>
+  <si>
+    <t>爸爸就会做一个差不多的东西把屋顶补上</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -1527,6 +1564,15 @@
     </r>
   </si>
   <si>
+    <t>完全不一样好吧</t>
+  </si>
+  <si>
+    <t>论文里其实写了很多方案</t>
+  </si>
+  <si>
+    <t>只是根据你目前的情况选了个最原始的方案</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -1567,6 +1613,231 @@
     </r>
   </si>
   <si>
+    <t>不研究修理_01</t>
+  </si>
+  <si>
+    <t>第一天5点时，未完成修理的研究</t>
+  </si>
+  <si>
+    <t>已经好久了</t>
+  </si>
+  <si>
+    <t>那篇文章你看得怎么样了?</t>
+  </si>
+  <si>
+    <t>我正在看呢，你先别急</t>
+  </si>
+  <si>
+    <t>抱歉,我没忍住摸了会儿鱼</t>
+  </si>
+  <si>
+    <t>麻烦你了,麻烦你了</t>
+  </si>
+  <si>
+    <t>可是我真的没法不急</t>
+  </si>
+  <si>
+    <t>水面越来越高了</t>
+  </si>
+  <si>
+    <t>辛苦您尽快了</t>
+  </si>
+  <si>
+    <t>一定要先研究"修理"哦,不然麦麦撑不了多久了</t>
+  </si>
+  <si>
+    <t>?!!</t>
+  </si>
+  <si>
+    <t>现在都什么时候了呀?</t>
+  </si>
+  <si>
+    <t>求求您快一点吧</t>
+  </si>
+  <si>
+    <t>不研究修理_02</t>
+  </si>
+  <si>
+    <t>第一天11点时，未完成修理的研究</t>
+  </si>
+  <si>
+    <t>那个……</t>
+  </si>
+  <si>
+    <t>真的还没研究完吗?</t>
+  </si>
+  <si>
+    <t>是的，这很复杂</t>
+  </si>
+  <si>
+    <t>还没研究完，你先别着急</t>
+  </si>
+  <si>
+    <t>很感谢你帮助我研究这些东西</t>
+  </si>
+  <si>
+    <t>但是</t>
+  </si>
+  <si>
+    <t>你好像一直研究不完</t>
+  </si>
+  <si>
+    <t>要不自己试一下吧</t>
+  </si>
+  <si>
+    <t>我或许能找到修补裂缝的办法</t>
+  </si>
+  <si>
+    <t>这大概需要1个小时</t>
+  </si>
+  <si>
+    <t>没事的,我一个人研究就行了</t>
+  </si>
+  <si>
+    <t>没问题,说不定你自己就能搞明白怎么修理裂缝</t>
+  </si>
+  <si>
+    <t>真的吗？</t>
+  </si>
+  <si>
+    <t>我还是有点担心</t>
+  </si>
+  <si>
+    <t>相信我,我不会害你的</t>
+  </si>
+  <si>
+    <t>你还要搜集物资</t>
+  </si>
+  <si>
+    <t>水和食物也还不够</t>
+  </si>
+  <si>
+    <t>这些你都要去收集</t>
+  </si>
+  <si>
+    <t>研究的事情就交给我来吧</t>
+  </si>
+  <si>
+    <t>好</t>
+  </si>
+  <si>
+    <t>我相信你</t>
+  </si>
+  <si>
+    <t>不要骗麦麦哦</t>
+  </si>
+  <si>
+    <t>不研究修理_03</t>
+  </si>
+  <si>
+    <t>如果你没在研究的话,赶紧研究"修理"这项科技吧</t>
+  </si>
+  <si>
+    <t>不研究修理_04</t>
+  </si>
+  <si>
+    <t>那我就去研究了</t>
+  </si>
+  <si>
+    <t>不研究修理_05</t>
+  </si>
+  <si>
+    <t>不过搜索物资的任务还得继续</t>
+  </si>
+  <si>
+    <t>不研究修理_06</t>
+  </si>
+  <si>
+    <t>只能边探索边在脑子里思考了</t>
+  </si>
+  <si>
+    <t>不研究修理_07</t>
+  </si>
+  <si>
+    <t>麦麦会一心二用,自己在脑子中思考如何修理裂缝</t>
+  </si>
+  <si>
+    <t>不研究修理_08</t>
+  </si>
+  <si>
+    <t>接下来继续探索并为生存做准备吧</t>
+  </si>
+  <si>
+    <t>堵住裂缝</t>
+  </si>
+  <si>
+    <t>第一次堵住渗水裂缝</t>
+  </si>
+  <si>
+    <t>啊,终于堵住了</t>
+  </si>
+  <si>
+    <t>我还是很有手法的嘛</t>
+  </si>
+  <si>
+    <t>用几块钉子和铁板就把裂缝堵住了</t>
+  </si>
+  <si>
+    <t>真做到啦?那确实很厉害</t>
+  </si>
+  <si>
+    <t>你最好再检查一下,说不定还有缝隙</t>
+  </si>
+  <si>
+    <t>完全没有任何缝隙</t>
+  </si>
+  <si>
+    <t>真的吗?</t>
+  </si>
+  <si>
+    <t>真的!</t>
+  </si>
+  <si>
+    <t>至少现在没有</t>
+  </si>
+  <si>
+    <t>你信我</t>
+  </si>
+  <si>
+    <t>我贴在墙上检查过了！</t>
+  </si>
+  <si>
+    <t>可我从摄像头里看，总感觉水平面在上升</t>
+  </si>
+  <si>
+    <t>!</t>
+  </si>
+  <si>
+    <t>好像是这样……</t>
+  </si>
+  <si>
+    <t>不能呀…</t>
+  </si>
+  <si>
+    <t>这个裂缝已经没在漏水了</t>
+  </si>
+  <si>
+    <t>应该是其他舱室里也有裂缝</t>
+  </si>
+  <si>
+    <t>我得去看看</t>
+  </si>
+  <si>
+    <t>一会再联系</t>
+  </si>
+  <si>
+    <t>通话结束,去继续探索飞船内吧</t>
+  </si>
+  <si>
+    <t>我连锤子都没有,直接用铁管敲的</t>
+  </si>
+  <si>
+    <t>话说,从摄像头里看水平面好像在上升</t>
+  </si>
+  <si>
+    <t>你有感觉水平面在上升吗?</t>
+  </si>
+  <si>
     <t>死亡</t>
   </si>
   <si>
@@ -2122,416 +2393,20 @@
       </rPr>
       <t>嗯</t>
     </r>
-  </si>
-  <si>
-    <t>以前家里屋顶漏雨的时候</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>爸爸就会做一个差不多的东西把屋顶补上</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>完全不一样好吧</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>论文里其实写了很多方案</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>只是根据你目前的情况选了个最原始的方案</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>对话</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>堵住裂缝</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>我还是很有手法的嘛</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>用几块钉子和铁板就把裂缝堵住了</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>选项</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>玩家</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>第一次堵住渗水裂缝</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>麦麦</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>对话</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>完全没有任何缝隙</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>至少现在没有</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>你信我</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>我贴在墙上检查过了！</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>可我从摄像头里看，总感觉水平面在上升</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>好像是这样……</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>不能呀…</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>这个裂缝已经没在漏水了</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>应该是其他舱室里也有裂缝</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>我得去看看</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>一会再联系</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>提示</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>求生系统</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>你最好再检查一下,说不定还有缝隙</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>真的吗?</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>真的!</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>真做到啦?那确实很厉害</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>啊,终于堵住了</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>通话结束,去继续探索飞船内吧</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>我连锤子都没有,直接用铁管敲的</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>话说,从摄像头里看水平面好像在上升</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>你有感觉水平面在上升吗?</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>添加_玩家_压缩饼干;解锁_详情_false</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>解锁_背包_true</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>解锁_摄像头_true</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>解锁_状态_true</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>解锁_研究_true</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>解锁_地点_true</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>解锁_休息_false;解锁_装备_false</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>解锁_制作_true</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>不研究修理_01</t>
-  </si>
-  <si>
-    <t>不研究修理_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>不研究修理_01</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>第一天5点时，未完成修理的研究</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>已经好久了</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>那篇文章你看得怎么样了?</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>我正在看呢，你先别急</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>抱歉,我没忍住摸了会儿鱼</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>麻烦你了,麻烦你了</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>可是我真的没法不急</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>水面越来越高了</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>辛苦您尽快了</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>选项</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>玩家</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>一定要先研究"修理"哦,不然麦麦撑不了多久了</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>?!!</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>现在都什么时候了呀?</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>麦麦</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>对话</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>求求您快一点吧</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>不研究修理_02</t>
-  </si>
-  <si>
-    <t>不研究修理_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>不研究修理_03</t>
-  </si>
-  <si>
-    <t>第一天11点时，未完成修理的研究</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>真的还没研究完吗?</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>是的，这很复杂</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>还没研究完，你先别着急</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>很感谢你帮助我研究这些东西</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>但是</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>我或许能找到修补裂缝的办法</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>要不自己试一下吧</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>你好像一直研究不完</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>这大概需要1个小时</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>没事的,我一个人研究就行了</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>不研究修理_04</t>
-  </si>
-  <si>
-    <t>不研究修理_05</t>
-  </si>
-  <si>
-    <t>真的吗？</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>我还是有点担心</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>相信我,我不会害你的</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>那个……</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>没问题,说不定你自己就能搞明白怎么修理裂缝</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>好</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>我相信你</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>不要骗麦麦哦</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>如果你没在研究的话,赶紧研究"修理"这项科技吧</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>你还要搜集物资</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>水和食物也还不够</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>这些你都要去收集</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>研究的事情就交给我来吧</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>那我就去研究了</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>不过搜索物资的任务还得继续</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>只能边探索边在脑子里思考了</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>接下来继续探索并为生存做准备吧</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>麦麦会一心二用,自己在脑子中思考如何修理裂缝</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>不研究修理_06</t>
-  </si>
-  <si>
-    <t>不研究修理_07</t>
-  </si>
-  <si>
-    <t>不研究修理_08</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="23">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -2551,61 +2426,352 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -2613,13 +2779,255 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2632,25 +3040,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2659,174 +3049,105 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -2837,7 +3158,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -2865,40 +3186,154 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -3156,14 +3591,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I138"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="27"/>
@@ -3173,7 +3608,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3202,7 +3637,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -3214,7 +3649,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3235,7 +3670,7 @@
       </c>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -3256,7 +3691,7 @@
       </c>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -3276,7 +3711,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -3296,7 +3731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -3317,7 +3752,7 @@
       </c>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -3338,7 +3773,7 @@
       </c>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -3359,7 +3794,7 @@
       </c>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -3380,7 +3815,7 @@
       </c>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -3401,7 +3836,7 @@
       </c>
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -3421,7 +3856,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -3442,7 +3877,7 @@
       </c>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -3462,7 +3897,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -3483,7 +3918,7 @@
       </c>
       <c r="H15" s="1"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -3504,7 +3939,7 @@
       </c>
       <c r="H16" s="1"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -3524,7 +3959,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -3544,7 +3979,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -3565,7 +4000,7 @@
       </c>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -3586,7 +4021,7 @@
       </c>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -3607,7 +4042,7 @@
       </c>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -3628,7 +4063,7 @@
       </c>
       <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -3649,7 +4084,7 @@
       </c>
       <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -3669,7 +4104,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -3690,7 +4125,7 @@
       </c>
       <c r="H25" s="1"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -3711,7 +4146,7 @@
       </c>
       <c r="H26" s="1"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -3732,7 +4167,7 @@
       </c>
       <c r="H27" s="1"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -3753,7 +4188,7 @@
       </c>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -3776,7 +4211,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -3797,7 +4232,7 @@
       </c>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -3818,7 +4253,7 @@
       </c>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -3839,7 +4274,7 @@
       </c>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -3860,7 +4295,7 @@
       </c>
       <c r="H33" s="1"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -3881,7 +4316,7 @@
       </c>
       <c r="H34" s="1"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -3902,7 +4337,7 @@
       </c>
       <c r="H35" s="1"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -3923,7 +4358,7 @@
       </c>
       <c r="H36" s="1"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -3944,7 +4379,7 @@
       </c>
       <c r="H37" s="1"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -3965,7 +4400,7 @@
       </c>
       <c r="H38" s="1"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -3986,7 +4421,7 @@
       </c>
       <c r="H39" s="1"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -4007,7 +4442,7 @@
       </c>
       <c r="H40" s="1"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -4028,7 +4463,7 @@
       </c>
       <c r="H41" s="1"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -4049,7 +4484,7 @@
       </c>
       <c r="H42" s="1"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -4070,7 +4505,7 @@
       </c>
       <c r="H43" s="1"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -4091,7 +4526,7 @@
       </c>
       <c r="H44" s="1"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -4112,7 +4547,7 @@
       </c>
       <c r="H45" s="1"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -4133,7 +4568,7 @@
       </c>
       <c r="H46" s="1"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -4146,18 +4581,18 @@
       <c r="D47" t="s">
         <v>59</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="F47" s="3" t="s">
         <v>60</v>
       </c>
       <c r="G47" s="1">
         <v>46</v>
       </c>
       <c r="H47" s="1"/>
-      <c r="I47" s="9" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I47" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -4171,17 +4606,17 @@
         <v>11</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G48" s="1">
         <v>47</v>
       </c>
       <c r="H48" s="1"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -4195,14 +4630,14 @@
         <v>11</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G49" s="1">
         <v>48</v>
       </c>
       <c r="H49" s="1"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -4216,14 +4651,14 @@
         <v>11</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G50" s="1">
         <v>49</v>
       </c>
       <c r="H50" s="1"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -4237,14 +4672,14 @@
         <v>11</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G51" s="1">
         <v>50</v>
       </c>
       <c r="H51" s="1"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -4258,14 +4693,14 @@
         <v>11</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G52" s="1">
         <v>51</v>
       </c>
       <c r="H52" s="1"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -4279,14 +4714,14 @@
         <v>11</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G53" s="1">
         <v>52</v>
       </c>
       <c r="H53" s="1"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -4300,14 +4735,14 @@
         <v>18</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G54" s="1">
         <v>53</v>
       </c>
       <c r="H54" s="1"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -4321,14 +4756,14 @@
         <v>11</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G55" s="1">
         <v>54</v>
       </c>
       <c r="H55" s="1"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -4342,14 +4777,14 @@
         <v>11</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G56" s="1">
         <v>55</v>
       </c>
       <c r="H56" s="1"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -4363,14 +4798,14 @@
         <v>18</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G57" s="1">
         <v>57</v>
       </c>
       <c r="H57" s="1"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -4384,14 +4819,14 @@
         <v>18</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G58" s="1">
         <v>57</v>
       </c>
       <c r="H58" s="1"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -4405,14 +4840,14 @@
         <v>11</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G59" s="1">
         <v>58</v>
       </c>
       <c r="H59" s="1"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -4426,14 +4861,14 @@
         <v>11</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G60" s="1">
         <v>59</v>
       </c>
       <c r="H60" s="1"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -4446,18 +4881,18 @@
       <c r="D61" t="s">
         <v>59</v>
       </c>
-      <c r="F61" s="4" t="s">
-        <v>75</v>
+      <c r="F61" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="G61" s="1">
         <v>60</v>
       </c>
       <c r="H61" s="1"/>
-      <c r="I61" s="9" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I61" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -4471,17 +4906,17 @@
         <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G62" s="1">
         <v>61</v>
       </c>
       <c r="H62" s="1"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -4495,14 +4930,14 @@
         <v>11</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G63" s="1">
         <v>62</v>
       </c>
       <c r="H63" s="1"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -4516,14 +4951,14 @@
         <v>11</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G64" s="1">
         <v>63</v>
       </c>
       <c r="H64" s="1"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -4537,14 +4972,14 @@
         <v>11</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G65" s="1">
         <v>64</v>
       </c>
       <c r="H65" s="1"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -4558,14 +4993,14 @@
         <v>11</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G66" s="1">
         <v>65</v>
       </c>
       <c r="H66" s="1"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -4579,14 +5014,14 @@
         <v>11</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G67" s="1">
         <v>66</v>
       </c>
       <c r="H67" s="1"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -4600,17 +5035,17 @@
         <v>59</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G68" s="1">
         <v>67</v>
       </c>
       <c r="H68" s="1"/>
-      <c r="I68" s="9" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I68" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -4624,17 +5059,17 @@
         <v>18</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G69" s="1">
         <v>68</v>
       </c>
       <c r="H69" s="1"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -4648,7 +5083,7 @@
         <v>11</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G70" s="1">
         <v>69</v>
@@ -4657,7 +5092,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -4671,14 +5106,14 @@
         <v>11</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G71" s="1">
         <v>70</v>
       </c>
       <c r="H71" s="1"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -4692,14 +5127,14 @@
         <v>11</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G72" s="1">
         <v>71</v>
       </c>
       <c r="H72" s="1"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -4713,7 +5148,7 @@
         <v>11</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G73" s="1">
         <v>72</v>
@@ -4722,7 +5157,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -4736,7 +5171,7 @@
         <v>11</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G74" s="1">
         <v>73</v>
@@ -4745,7 +5180,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -4759,14 +5194,14 @@
         <v>11</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G75" s="1">
         <v>74</v>
       </c>
       <c r="H75" s="1"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -4779,18 +5214,18 @@
       <c r="D76" t="s">
         <v>59</v>
       </c>
-      <c r="F76" s="4" t="s">
-        <v>92</v>
+      <c r="F76" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="G76" s="1">
         <v>75</v>
       </c>
       <c r="H76" s="1"/>
-      <c r="I76" s="9" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I76" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -4804,17 +5239,17 @@
         <v>18</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G77" s="1">
         <v>76</v>
       </c>
       <c r="H77" s="1"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -4828,14 +5263,14 @@
         <v>11</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G78" s="1">
         <v>77</v>
       </c>
       <c r="H78" s="1"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -4849,7 +5284,7 @@
         <v>11</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G79" s="1">
         <v>78</v>
@@ -4858,7 +5293,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -4872,14 +5307,14 @@
         <v>11</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G80" s="1">
         <v>79</v>
       </c>
       <c r="H80" s="1"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -4893,14 +5328,14 @@
         <v>11</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G81" s="1">
         <v>80</v>
       </c>
       <c r="H81" s="1"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -4914,14 +5349,14 @@
         <v>11</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G82" s="1">
         <v>81</v>
       </c>
       <c r="H82" s="1"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -4935,7 +5370,7 @@
         <v>11</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G83" s="1">
         <v>82</v>
@@ -4944,7 +5379,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -4958,13 +5393,13 @@
         <v>11</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G84" s="1">
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -4978,13 +5413,13 @@
         <v>11</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G85" s="1">
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -4998,14 +5433,14 @@
         <v>11</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G86" s="1">
         <v>85</v>
       </c>
       <c r="H86" s="1"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -5019,13 +5454,13 @@
         <v>11</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G87" s="1">
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -5039,14 +5474,14 @@
         <v>11</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G88" s="1">
         <v>87</v>
       </c>
       <c r="H88" s="1"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -5060,7 +5495,7 @@
         <v>11</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G89" s="1">
         <v>88</v>
@@ -5069,7 +5504,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8">
       <c r="A90" s="1">
         <v>88</v>
       </c>
@@ -5083,14 +5518,14 @@
         <v>11</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G90" s="1">
         <v>89</v>
       </c>
       <c r="H90" s="1"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7">
       <c r="A91" s="1">
         <v>89</v>
       </c>
@@ -5104,13 +5539,13 @@
         <v>11</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G91" s="1">
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8">
       <c r="A92" s="1">
         <v>90</v>
       </c>
@@ -5124,7 +5559,7 @@
         <v>11</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G92" s="1">
         <v>91</v>
@@ -5133,7 +5568,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8">
       <c r="A93" s="1">
         <v>91</v>
       </c>
@@ -5147,14 +5582,14 @@
         <v>11</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G93" s="1">
         <v>92</v>
       </c>
       <c r="H93" s="1"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7">
       <c r="A94" s="1">
         <v>92</v>
       </c>
@@ -5168,13 +5603,13 @@
         <v>11</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G94" s="1">
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8">
       <c r="A95" s="1">
         <v>93</v>
       </c>
@@ -5188,14 +5623,14 @@
         <v>11</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G95" s="1">
         <v>94</v>
       </c>
       <c r="H95" s="1"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8">
       <c r="A96" s="1">
         <v>94</v>
       </c>
@@ -5209,14 +5644,14 @@
         <v>11</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G96" s="1">
         <v>95</v>
       </c>
       <c r="H96" s="1"/>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9">
       <c r="A97" s="1">
         <v>95</v>
       </c>
@@ -5229,18 +5664,18 @@
       <c r="D97" t="s">
         <v>59</v>
       </c>
-      <c r="F97" s="4" t="s">
-        <v>113</v>
+      <c r="F97" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="G97" s="1">
         <v>96</v>
       </c>
       <c r="H97" s="1"/>
-      <c r="I97" s="9" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I97" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
       <c r="A98" s="1">
         <v>96</v>
       </c>
@@ -5254,17 +5689,17 @@
         <v>18</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G98" s="1">
         <v>97</v>
       </c>
       <c r="H98" s="1"/>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8">
       <c r="A99" s="1">
         <v>97</v>
       </c>
@@ -5278,14 +5713,14 @@
         <v>11</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="G99" s="1">
         <v>98</v>
       </c>
       <c r="H99" s="1"/>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8">
       <c r="A100" s="1">
         <v>98</v>
       </c>
@@ -5299,14 +5734,14 @@
         <v>11</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G100" s="1">
         <v>99</v>
       </c>
       <c r="H100" s="1"/>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8">
       <c r="A101" s="1">
         <v>99</v>
       </c>
@@ -5320,14 +5755,14 @@
         <v>11</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="G101" s="1">
         <v>100</v>
       </c>
       <c r="H101" s="1"/>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8">
       <c r="A102" s="1">
         <v>100</v>
       </c>
@@ -5341,14 +5776,14 @@
         <v>11</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="G102" s="1">
         <v>101</v>
       </c>
       <c r="H102" s="1"/>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8">
       <c r="A103" s="1">
         <v>101</v>
       </c>
@@ -5362,14 +5797,14 @@
         <v>11</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G103" s="1">
         <v>102</v>
       </c>
       <c r="H103" s="1"/>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8">
       <c r="A104" s="1">
         <v>102</v>
       </c>
@@ -5383,14 +5818,14 @@
         <v>11</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G104" s="1">
         <v>103</v>
       </c>
       <c r="H104" s="1"/>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8">
       <c r="A105" s="1">
         <v>103</v>
       </c>
@@ -5404,14 +5839,14 @@
         <v>18</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G105" s="1">
         <v>104</v>
       </c>
       <c r="H105" s="1"/>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8">
       <c r="A106" s="1">
         <v>104</v>
       </c>
@@ -5425,14 +5860,14 @@
         <v>11</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="G106" s="1">
         <v>105</v>
       </c>
       <c r="H106" s="1"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8">
       <c r="A107" s="1">
         <v>105</v>
       </c>
@@ -5446,14 +5881,14 @@
         <v>11</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G107" s="1">
         <v>106</v>
       </c>
       <c r="H107" s="1"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8">
       <c r="A108" s="1">
         <v>106</v>
       </c>
@@ -5467,14 +5902,14 @@
         <v>11</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G108" s="1">
         <v>107</v>
       </c>
       <c r="H108" s="1"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8">
       <c r="A109" s="1">
         <v>107</v>
       </c>
@@ -5488,14 +5923,14 @@
         <v>11</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G109" s="1">
         <v>108</v>
       </c>
       <c r="H109" s="1"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8">
       <c r="A110" s="1">
         <v>108</v>
       </c>
@@ -5508,15 +5943,15 @@
       <c r="D110" t="s">
         <v>59</v>
       </c>
-      <c r="F110" s="6" t="s">
-        <v>127</v>
+      <c r="F110" s="10" t="s">
+        <v>132</v>
       </c>
       <c r="G110" s="1">
         <v>109</v>
       </c>
       <c r="H110" s="1"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8">
       <c r="A111" s="1">
         <v>109</v>
       </c>
@@ -5530,10 +5965,10 @@
         <v>18</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="G111" s="1">
         <v>110</v>
@@ -5542,7 +5977,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8">
       <c r="A112" s="1">
         <v>110</v>
       </c>
@@ -5556,7 +5991,7 @@
         <v>11</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G112" s="1">
         <v>111</v>
@@ -5565,7 +6000,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8">
       <c r="A113" s="1">
         <v>111</v>
       </c>
@@ -5579,7 +6014,7 @@
         <v>11</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="G113" s="1">
         <v>112</v>
@@ -5588,7 +6023,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8">
       <c r="A114" s="1">
         <v>112</v>
       </c>
@@ -5602,14 +6037,14 @@
         <v>11</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G114" s="1">
         <v>113</v>
       </c>
       <c r="H114" s="1"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8">
       <c r="A115" s="1">
         <v>113</v>
       </c>
@@ -5623,14 +6058,14 @@
         <v>11</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="G115" s="1">
         <v>114</v>
       </c>
       <c r="H115" s="1"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8">
       <c r="A116" s="1">
         <v>114</v>
       </c>
@@ -5644,14 +6079,14 @@
         <v>11</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G116" s="1">
         <v>115</v>
       </c>
       <c r="H116" s="1"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8">
       <c r="A117" s="1">
         <v>115</v>
       </c>
@@ -5665,14 +6100,14 @@
         <v>18</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="G117" s="1">
         <v>117</v>
       </c>
       <c r="H117" s="1"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8">
       <c r="A118" s="1">
         <v>116</v>
       </c>
@@ -5686,14 +6121,14 @@
         <v>18</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G118" s="1">
         <v>117</v>
       </c>
       <c r="H118" s="1"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8">
       <c r="A119" s="1">
         <v>117</v>
       </c>
@@ -5707,14 +6142,14 @@
         <v>11</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G119" s="1">
         <v>118</v>
       </c>
       <c r="H119" s="1"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8">
       <c r="A120" s="1">
         <v>118</v>
       </c>
@@ -5728,14 +6163,14 @@
         <v>11</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="G120" s="1">
         <v>119</v>
       </c>
       <c r="H120" s="1"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8">
       <c r="A121" s="1">
         <v>119</v>
       </c>
@@ -5749,14 +6184,14 @@
         <v>11</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G121" s="1">
         <v>120</v>
       </c>
       <c r="H121" s="1"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7">
       <c r="A122" s="1">
         <v>120</v>
       </c>
@@ -5770,13 +6205,13 @@
         <v>11</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G122" s="1">
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8">
       <c r="A123" s="1">
         <v>121</v>
       </c>
@@ -5790,14 +6225,14 @@
         <v>18</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="G123" s="1">
         <v>122</v>
       </c>
       <c r="H123" s="1"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8">
       <c r="A124" s="1">
         <v>122</v>
       </c>
@@ -5811,14 +6246,14 @@
         <v>11</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="G124" s="1">
         <v>123</v>
       </c>
       <c r="H124" s="1"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7">
       <c r="A125" s="1">
         <v>123</v>
       </c>
@@ -5832,13 +6267,13 @@
         <v>11</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="G125" s="1">
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7">
       <c r="A126" s="1">
         <v>124</v>
       </c>
@@ -5852,13 +6287,13 @@
         <v>11</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G126" s="1">
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8">
       <c r="A127" s="1">
         <v>125</v>
       </c>
@@ -5872,14 +6307,14 @@
         <v>11</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G127" s="1">
         <v>126</v>
       </c>
       <c r="H127" s="1"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8">
       <c r="A128" s="1">
         <v>126</v>
       </c>
@@ -5893,14 +6328,14 @@
         <v>11</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G128" s="1">
         <v>127</v>
       </c>
       <c r="H128" s="1"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8">
       <c r="A129" s="1">
         <v>127</v>
       </c>
@@ -5914,14 +6349,14 @@
         <v>11</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="G129" s="1">
         <v>128</v>
       </c>
       <c r="H129" s="1"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9">
       <c r="A130" s="1">
         <v>128</v>
       </c>
@@ -5934,18 +6369,18 @@
       <c r="D130" t="s">
         <v>59</v>
       </c>
-      <c r="F130" s="4" t="s">
-        <v>148</v>
+      <c r="F130" s="3" t="s">
+        <v>153</v>
       </c>
       <c r="G130" s="1">
         <v>129</v>
       </c>
       <c r="H130" s="1"/>
-      <c r="I130" s="9" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I130" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
       <c r="A131" s="1">
         <v>129</v>
       </c>
@@ -5959,17 +6394,17 @@
         <v>18</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="G131" s="1">
         <v>130</v>
       </c>
       <c r="H131" s="1"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8">
       <c r="A132" s="1">
         <v>130</v>
       </c>
@@ -5983,14 +6418,14 @@
         <v>11</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="G132" s="1">
         <v>131</v>
       </c>
       <c r="H132" s="1"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8">
       <c r="A133" s="1">
         <v>131</v>
       </c>
@@ -6004,14 +6439,14 @@
         <v>11</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="G133" s="1">
         <v>132</v>
       </c>
       <c r="H133" s="1"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8">
       <c r="A134" s="1">
         <v>132</v>
       </c>
@@ -6025,14 +6460,14 @@
         <v>11</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="G134" s="1">
         <v>133</v>
       </c>
       <c r="H134" s="1"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8">
       <c r="A135" s="1">
         <v>133</v>
       </c>
@@ -6046,14 +6481,14 @@
         <v>59</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="G135" s="1">
         <v>134</v>
       </c>
       <c r="H135" s="1"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8">
       <c r="A136" s="1">
         <v>134</v>
       </c>
@@ -6067,17 +6502,17 @@
         <v>11</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="G136" s="1">
         <v>135</v>
       </c>
       <c r="H136" s="1"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8">
       <c r="A137" s="1">
         <v>135</v>
       </c>
@@ -6091,14 +6526,14 @@
         <v>11</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="G137" s="1">
         <v>136</v>
       </c>
       <c r="H137" s="1"/>
     </row>
-    <row r="138" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+    <row r="138" ht="24" spans="1:9">
       <c r="A138" s="1">
         <v>136</v>
       </c>
@@ -6111,28 +6546,29 @@
       <c r="D138" t="s">
         <v>59</v>
       </c>
-      <c r="F138" s="7" t="s">
-        <v>158</v>
+      <c r="F138" s="11" t="s">
+        <v>164</v>
       </c>
       <c r="G138" s="1">
         <v>-1</v>
       </c>
       <c r="H138" s="1"/>
-      <c r="I138" s="9" t="s">
-        <v>292</v>
+      <c r="I138" s="4" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="12.75" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -6141,7 +6577,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6170,26 +6606,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>238</v>
+        <v>326</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>235</v>
+        <v>323</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>238</v>
+        <v>326</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -6198,18 +6634,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>239</v>
+        <v>327</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>238</v>
+        <v>326</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -6218,22 +6654,23 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>240</v>
+        <v>328</v>
       </c>
       <c r="G4" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -6242,7 +6679,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6271,26 +6708,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>241</v>
+        <v>329</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>235</v>
+        <v>323</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>241</v>
+        <v>329</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -6299,18 +6736,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>242</v>
+        <v>330</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>241</v>
+        <v>329</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -6319,18 +6756,18 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>243</v>
+        <v>331</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>241</v>
+        <v>329</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -6339,18 +6776,18 @@
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>244</v>
+        <v>332</v>
       </c>
       <c r="G5" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>241</v>
+        <v>329</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -6359,18 +6796,18 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>245</v>
+        <v>333</v>
       </c>
       <c r="G6" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>241</v>
+        <v>329</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -6379,18 +6816,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>246</v>
+        <v>334</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>241</v>
+        <v>329</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -6399,18 +6836,18 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>247</v>
+        <v>335</v>
       </c>
       <c r="G8" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>241</v>
+        <v>329</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -6419,22 +6856,23 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>248</v>
+        <v>336</v>
       </c>
       <c r="G9" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I32"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="24"/>
@@ -6443,7 +6881,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6472,26 +6910,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="G2" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -6500,18 +6938,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
@@ -6520,18 +6958,18 @@
         <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="G4" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -6540,18 +6978,18 @@
         <v>18</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="G5" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -6560,18 +6998,18 @@
         <v>11</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -6580,18 +7018,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -6600,18 +7038,18 @@
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -6620,64 +7058,64 @@
         <v>11</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
       </c>
       <c r="D10" t="s">
+        <v>173</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
         <v>166</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="G10" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>159</v>
-      </c>
       <c r="C11" t="s">
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="G11" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C12" t="s">
         <v>58</v>
@@ -6686,18 +7124,18 @@
         <v>59</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -6706,21 +7144,21 @@
         <v>11</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C14" t="s">
         <v>17</v>
@@ -6729,18 +7167,18 @@
         <v>18</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="G14" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C15" t="s">
         <v>10</v>
@@ -6749,21 +7187,21 @@
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="G15" s="1">
         <v>14</v>
       </c>
-      <c r="I15" s="9" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I15" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C16" t="s">
         <v>58</v>
@@ -6771,19 +7209,19 @@
       <c r="D16" t="s">
         <v>59</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>175</v>
+      <c r="F16" s="3" t="s">
+        <v>183</v>
       </c>
       <c r="G16" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
@@ -6792,21 +7230,21 @@
         <v>11</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="G17" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -6815,18 +7253,18 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="G18" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7">
       <c r="A19" s="1">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C19" t="s">
         <v>10</v>
@@ -6835,18 +7273,18 @@
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="G19" s="1">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8">
       <c r="A20" s="1">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
@@ -6854,20 +7292,20 @@
       <c r="D20" t="s">
         <v>11</v>
       </c>
-      <c r="F20" s="8" t="s">
-        <v>249</v>
+      <c r="F20" s="3" t="s">
+        <v>188</v>
       </c>
       <c r="G20" s="1">
         <v>19</v>
       </c>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8">
       <c r="A21" s="1">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C21" t="s">
         <v>10</v>
@@ -6875,20 +7313,20 @@
       <c r="D21" t="s">
         <v>11</v>
       </c>
-      <c r="F21" s="8" t="s">
-        <v>250</v>
+      <c r="F21" s="3" t="s">
+        <v>189</v>
       </c>
       <c r="G21" s="1">
         <v>20</v>
       </c>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7">
       <c r="A22" s="1">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C22" t="s">
         <v>10</v>
@@ -6897,18 +7335,18 @@
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="G22" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7">
       <c r="A23" s="1">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C23" t="s">
         <v>17</v>
@@ -6917,18 +7355,18 @@
         <v>18</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="G23" s="1">
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7">
       <c r="A24" s="1">
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C24" t="s">
         <v>17</v>
@@ -6937,18 +7375,18 @@
         <v>18</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="G24" s="1">
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7">
       <c r="A25" s="1">
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C25" t="s">
         <v>17</v>
@@ -6956,59 +7394,59 @@
       <c r="D25" t="s">
         <v>18</v>
       </c>
-      <c r="F25" s="8" t="s">
-        <v>251</v>
+      <c r="F25" s="3" t="s">
+        <v>193</v>
       </c>
       <c r="G25" s="1">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7">
       <c r="A26" s="1">
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C26" t="s">
         <v>17</v>
       </c>
-      <c r="D26" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>252</v>
+      <c r="D26" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>194</v>
       </c>
       <c r="G26" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7">
       <c r="A27" s="1">
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C27" t="s">
         <v>17</v>
       </c>
-      <c r="D27" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>253</v>
+      <c r="D27" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>195</v>
       </c>
       <c r="G27" s="1">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7">
       <c r="A28" s="1">
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C28" t="s">
         <v>10</v>
@@ -7017,18 +7455,18 @@
         <v>11</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="G28" s="1">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7">
       <c r="A29" s="1">
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C29" t="s">
         <v>10</v>
@@ -7037,18 +7475,18 @@
         <v>11</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="G29" s="1">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7">
       <c r="A30" s="1">
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C30" t="s">
         <v>10</v>
@@ -7057,18 +7495,18 @@
         <v>11</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="G30" s="1">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7">
       <c r="A31" s="1">
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C31" t="s">
         <v>58</v>
@@ -7077,34 +7515,35 @@
         <v>59</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="G31" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7">
       <c r="A32" s="1"/>
       <c r="G32" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF26B22E-2097-44D2-A335-C76ACA21E475}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="12.75"/>
   <cols>
-    <col min="2" max="2" width="13.109375" customWidth="1"/>
-    <col min="5" max="5" width="30.5546875" customWidth="1"/>
-    <col min="6" max="6" width="34.21875" customWidth="1"/>
+    <col min="2" max="2" width="13.1047619047619" customWidth="1"/>
+    <col min="5" max="5" width="30.552380952381" customWidth="1"/>
+    <col min="6" max="6" width="34.2190476190476" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7133,26 +7572,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>297</v>
+      <c r="B2" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="G2" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>296</v>
+      <c r="B3" s="4" t="s">
+        <v>200</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7160,19 +7599,19 @@
       <c r="D3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="10" t="s">
-        <v>298</v>
+      <c r="F3" s="2" t="s">
+        <v>202</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>294</v>
+      <c r="B4" s="4" t="s">
+        <v>200</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -7180,998 +7619,1000 @@
       <c r="D4" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>299</v>
+      <c r="F4" s="3" t="s">
+        <v>203</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>307</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>300</v>
+      <c r="B5" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>204</v>
       </c>
       <c r="G5" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>301</v>
+      <c r="B6" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>205</v>
       </c>
       <c r="G6" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>302</v>
+      <c r="B7" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>206</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>303</v>
+      <c r="B8" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>207</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>304</v>
+      <c r="B9" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>208</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>254</v>
+      <c r="B10" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="E10" s="3"/>
-      <c r="F10" s="10" t="s">
-        <v>305</v>
+      <c r="F10" s="2" t="s">
+        <v>209</v>
       </c>
       <c r="G10" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>274</v>
+      <c r="B11" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>59</v>
       </c>
       <c r="E11" s="3"/>
-      <c r="F11" s="10" t="s">
-        <v>308</v>
+      <c r="F11" s="2" t="s">
+        <v>210</v>
       </c>
       <c r="G11" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>309</v>
+      <c r="B12" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>211</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>312</v>
+      <c r="B13" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="E13" s="3"/>
-      <c r="F13" s="10" t="s">
-        <v>310</v>
+      <c r="F13" s="2" t="s">
+        <v>212</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>313</v>
+      <c r="B14" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>213</v>
       </c>
       <c r="G14" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9">
       <c r="A15" s="1"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="F15" s="10"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="F15" s="2"/>
       <c r="G15" s="1"/>
-      <c r="I15" s="5"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I15" s="4"/>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="1"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="F16" s="8"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="F16" s="3"/>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" s="1"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
       <c r="E17" s="3"/>
-      <c r="F17" s="10"/>
+      <c r="F17" s="2"/>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="1"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="F18" s="10"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="F18" s="2"/>
       <c r="G18" s="1"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7">
       <c r="A19" s="1"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="F19" s="10"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="F19" s="2"/>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8">
       <c r="A20" s="1"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="F20" s="10"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="F20" s="2"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8">
       <c r="A21" s="1"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="F21" s="8"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="F21" s="3"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7">
       <c r="A22" s="1"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="F22" s="10"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="F22" s="2"/>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7">
       <c r="A23" s="1"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="F23" s="10"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="F23" s="2"/>
       <c r="G23" s="1"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7">
       <c r="A24" s="1"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="F24" s="10"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="F24" s="2"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7">
       <c r="A25" s="1"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="F25" s="10"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="F25" s="2"/>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7">
       <c r="A26" s="1"/>
-      <c r="B26" s="9"/>
-      <c r="D26" s="9"/>
+      <c r="B26" s="4"/>
+      <c r="D26" s="4"/>
       <c r="F26" s="2"/>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7">
       <c r="A27" s="1"/>
-      <c r="B27" s="9"/>
-      <c r="D27" s="9"/>
+      <c r="B27" s="4"/>
+      <c r="D27" s="4"/>
       <c r="F27" s="2"/>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7">
       <c r="A28" s="1"/>
-      <c r="B28" s="9"/>
-      <c r="D28" s="9"/>
+      <c r="B28" s="4"/>
+      <c r="D28" s="4"/>
       <c r="F28" s="2"/>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7">
       <c r="A29" s="1"/>
-      <c r="B29" s="9"/>
-      <c r="D29" s="9"/>
+      <c r="B29" s="4"/>
+      <c r="D29" s="4"/>
       <c r="F29" s="2"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7">
       <c r="A30" s="1"/>
-      <c r="B30" s="9"/>
-      <c r="D30" s="9"/>
+      <c r="B30" s="4"/>
+      <c r="D30" s="4"/>
       <c r="F30" s="2"/>
       <c r="G30" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14D5AC1A-C19B-4034-9713-8C5FDC844D81}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="11"/>
-    <col min="2" max="2" width="13.109375" style="11" customWidth="1"/>
-    <col min="3" max="4" width="10.33203125" style="11"/>
-    <col min="5" max="5" width="30.5546875" style="11" customWidth="1"/>
-    <col min="6" max="6" width="57.88671875" style="11" customWidth="1"/>
-    <col min="7" max="16384" width="10.33203125" style="11"/>
+    <col min="1" max="1" width="10.3333333333333" style="5"/>
+    <col min="2" max="2" width="13.1047619047619" style="5" customWidth="1"/>
+    <col min="3" max="4" width="10.3333333333333" style="5"/>
+    <col min="5" max="5" width="30.552380952381" style="5" customWidth="1"/>
+    <col min="6" max="6" width="57.8857142857143" style="5" customWidth="1"/>
+    <col min="7" max="16384" width="10.3333333333333" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="12">
+    <row r="2" spans="1:7">
+      <c r="A2" s="6">
         <v>0</v>
       </c>
-      <c r="B2" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>317</v>
-      </c>
-      <c r="G2" s="12">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="12">
+      <c r="B2" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="G2" s="6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>333</v>
-      </c>
-      <c r="G3" s="12">
+      <c r="B3" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="G3" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
+    <row r="4" spans="1:7">
+      <c r="A4" s="6">
         <v>2</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>318</v>
-      </c>
-      <c r="G4" s="12">
+      <c r="B4" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="G4" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="12">
+    <row r="5" spans="1:7">
+      <c r="A5" s="6">
         <v>3</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>306</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>319</v>
-      </c>
-      <c r="G5" s="12">
+      <c r="B5" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="G5" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="12">
+    <row r="6" spans="1:7">
+      <c r="A6" s="6">
         <v>4</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>320</v>
-      </c>
-      <c r="G6" s="12">
+      <c r="B6" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="G6" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="12">
+    <row r="7" spans="1:7">
+      <c r="A7" s="6">
         <v>5</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>321</v>
-      </c>
-      <c r="G7" s="12">
+      <c r="B7" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="G7" s="6">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="12">
+    <row r="8" spans="1:8">
+      <c r="A8" s="6">
         <v>6</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>322</v>
-      </c>
-      <c r="G8" s="12">
+      <c r="B8" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="G8" s="6">
         <v>7</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="5">
         <v>1000</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="12">
+    <row r="9" spans="1:7">
+      <c r="A9" s="6">
         <v>7</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>325</v>
-      </c>
-      <c r="G9" s="12">
+      <c r="B9" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="G9" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="12">
+    <row r="10" spans="1:7">
+      <c r="A10" s="6">
         <v>8</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="E10" s="16"/>
-      <c r="F10" s="15" t="s">
-        <v>324</v>
-      </c>
-      <c r="G10" s="12">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="12">
-        <v>9</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="E11" s="16"/>
-      <c r="F11" s="15" t="s">
-        <v>323</v>
-      </c>
-      <c r="G11" s="12">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="12">
-        <v>10</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>311</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>326</v>
-      </c>
-      <c r="G12" s="12">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="12">
-        <v>11</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>311</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="E13" s="16"/>
-      <c r="F13" s="15" t="s">
-        <v>327</v>
-      </c>
-      <c r="G13" s="12">
+      <c r="B10" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="8"/>
+      <c r="F10" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="G10" s="6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="6">
+        <v>9</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="8"/>
+      <c r="F11" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="G11" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="6">
+        <v>10</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="G12" s="6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="6">
+        <v>11</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="8"/>
+      <c r="F13" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="G13" s="6">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="12">
+    <row r="14" spans="1:7">
+      <c r="A14" s="6">
         <v>12</v>
       </c>
-      <c r="B14" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>311</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>334</v>
-      </c>
-      <c r="G14" s="12">
+      <c r="B14" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="G14" s="6">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="12">
+    <row r="15" spans="1:9">
+      <c r="A15" s="6">
         <v>13</v>
       </c>
-      <c r="B15" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>330</v>
-      </c>
-      <c r="G15" s="12">
+      <c r="B15" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="G15" s="6">
         <v>14</v>
       </c>
-      <c r="I15" s="17"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="12">
+      <c r="I15" s="7"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="6">
         <v>14</v>
       </c>
-      <c r="B16" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>331</v>
-      </c>
-      <c r="G16" s="12">
+      <c r="B16" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="G16" s="6">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="12">
+    <row r="17" spans="1:7">
+      <c r="A17" s="6">
         <v>15</v>
       </c>
-      <c r="B17" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>332</v>
-      </c>
-      <c r="G17" s="12">
+      <c r="B17" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="G17" s="6">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="12">
+    <row r="18" spans="1:7">
+      <c r="A18" s="6">
         <v>16</v>
       </c>
-      <c r="B18" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="G18" s="12">
+      <c r="B18" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="12">
+      <c r="D18" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="G18" s="6">
         <v>17</v>
       </c>
-      <c r="B19" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="G19" s="12">
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="6">
+        <v>17</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="G19" s="6">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="12">
+    <row r="20" spans="1:7">
+      <c r="A20" s="6">
         <v>18</v>
       </c>
-      <c r="B20" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>341</v>
-      </c>
-      <c r="G20" s="12">
+      <c r="B20" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="G20" s="6">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="12">
+    <row r="21" spans="1:7">
+      <c r="A21" s="6">
         <v>19</v>
       </c>
-      <c r="B21" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>342</v>
-      </c>
-      <c r="G21" s="12">
+      <c r="B21" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="G21" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="12">
+    <row r="22" spans="1:8">
+      <c r="A22" s="6">
         <v>20</v>
       </c>
-      <c r="B22" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>335</v>
-      </c>
-      <c r="G22" s="12">
+      <c r="B22" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="G22" s="6">
         <v>22</v>
       </c>
-      <c r="H22" s="11">
+      <c r="H22" s="5">
         <v>3500</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="12">
+    <row r="23" spans="1:8">
+      <c r="A23" s="6">
         <v>21</v>
       </c>
-      <c r="B23" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>336</v>
-      </c>
-      <c r="G23" s="12">
+      <c r="B23" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="G23" s="6">
         <v>22</v>
       </c>
-      <c r="H23" s="11">
+      <c r="H23" s="5">
         <v>2000</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="12">
+    <row r="24" spans="1:8">
+      <c r="A24" s="6">
         <v>22</v>
       </c>
-      <c r="B24" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>274</v>
-      </c>
-      <c r="F24" s="15" t="s">
-        <v>337</v>
-      </c>
-      <c r="G24" s="12">
+      <c r="B24" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="G24" s="6">
         <v>23</v>
       </c>
-      <c r="H24" s="12"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="12">
+      <c r="H24" s="6"/>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="6">
         <v>23</v>
       </c>
-      <c r="B25" s="13" t="s">
-        <v>316</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>274</v>
-      </c>
-      <c r="F25" s="14" t="s">
-        <v>338</v>
-      </c>
-      <c r="G25" s="12">
+      <c r="B25" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="G25" s="6">
         <v>-1</v>
       </c>
-      <c r="H25" s="12"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="12">
+      <c r="H25" s="6"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="6">
         <v>24</v>
       </c>
-      <c r="B26" s="13" t="s">
-        <v>328</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>343</v>
-      </c>
-      <c r="G26" s="11">
+      <c r="B26" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="G26" s="5">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="12">
+    <row r="27" spans="1:7">
+      <c r="A27" s="6">
         <v>25</v>
       </c>
-      <c r="B27" s="13" t="s">
-        <v>329</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>344</v>
-      </c>
-      <c r="G27" s="11">
+      <c r="B27" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="G27" s="5">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="12">
+    <row r="28" spans="1:7">
+      <c r="A28" s="6">
         <v>26</v>
       </c>
-      <c r="B28" s="13" t="s">
-        <v>348</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>345</v>
-      </c>
-      <c r="G28" s="11">
+      <c r="B28" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="G28" s="5">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="12">
+    <row r="29" spans="1:7">
+      <c r="A29" s="6">
         <v>27</v>
       </c>
-      <c r="B29" s="13" t="s">
-        <v>349</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>274</v>
-      </c>
-      <c r="F29" s="15" t="s">
-        <v>347</v>
-      </c>
-      <c r="G29" s="11">
+      <c r="B29" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="G29" s="5">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="12">
+    <row r="30" spans="1:7">
+      <c r="A30" s="6">
         <v>28</v>
       </c>
-      <c r="B30" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>274</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>346</v>
-      </c>
-      <c r="G30" s="11">
+      <c r="B30" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="G30" s="5">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9720864F-1D73-4315-BBEE-79B914F8E21C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="12.75"/>
   <cols>
-    <col min="5" max="5" width="19.44140625" customWidth="1"/>
-    <col min="6" max="6" width="34.21875" customWidth="1"/>
+    <col min="5" max="5" width="19.4380952380952" customWidth="1"/>
+    <col min="6" max="6" width="34.2190476190476" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8200,26 +8641,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>260</v>
+      <c r="B2" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>251</v>
       </c>
       <c r="G2" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>255</v>
+      <c r="B3" s="4" t="s">
+        <v>250</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -8227,19 +8668,19 @@
       <c r="D3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="10" t="s">
-        <v>281</v>
+      <c r="F3" s="2" t="s">
+        <v>252</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>255</v>
+      <c r="B4" s="4" t="s">
+        <v>250</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -8247,19 +8688,19 @@
       <c r="D4" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>256</v>
+      <c r="F4" s="3" t="s">
+        <v>253</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>255</v>
+      <c r="B5" s="4" t="s">
+        <v>250</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -8267,109 +8708,109 @@
       <c r="D5" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="8" t="s">
-        <v>257</v>
+      <c r="F5" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="G5" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>280</v>
       </c>
       <c r="G6" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>276</v>
+      <c r="B7" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>256</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>263</v>
+      <c r="B8" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>257</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="B9" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>258</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>277</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>262</v>
+      <c r="B10" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="E10" s="3"/>
-      <c r="F10" s="10" t="s">
-        <v>278</v>
+      <c r="F10" s="2" t="s">
+        <v>259</v>
       </c>
       <c r="G10" s="1">
         <v>9</v>
@@ -8378,22 +8819,22 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>262</v>
+      <c r="B11" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="E11" s="3"/>
-      <c r="F11" s="10" t="s">
-        <v>264</v>
+      <c r="F11" s="2" t="s">
+        <v>260</v>
       </c>
       <c r="G11" s="1">
         <v>10</v>
@@ -8402,21 +8843,21 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8">
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="C12" s="9" t="s">
+      <c r="B12" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>261</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>265</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
@@ -8425,22 +8866,22 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8">
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="D13" s="9" t="s">
+      <c r="B13" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="10" t="s">
-        <v>266</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
@@ -8449,296 +8890,297 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>267</v>
+      <c r="B14" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>263</v>
       </c>
       <c r="G14" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9">
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>279</v>
+      <c r="B15" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>264</v>
       </c>
       <c r="G15" s="1">
         <v>14</v>
       </c>
-      <c r="I15" s="5"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I15" s="4"/>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>268</v>
+      <c r="B16" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>265</v>
       </c>
       <c r="G16" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>262</v>
+      <c r="B17" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="E17" s="3"/>
-      <c r="F17" s="10" t="s">
-        <v>269</v>
+      <c r="F17" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="G17" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>270</v>
+      <c r="B18" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>267</v>
       </c>
       <c r="G18" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7">
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>271</v>
+      <c r="B19" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>268</v>
       </c>
       <c r="G19" s="1">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8">
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>272</v>
+      <c r="B20" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>269</v>
       </c>
       <c r="G20" s="1">
         <v>19</v>
       </c>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8">
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>273</v>
+      <c r="B21" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>270</v>
       </c>
       <c r="G21" s="1">
         <v>20</v>
       </c>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7">
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>282</v>
+      <c r="B22" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>271</v>
       </c>
       <c r="G22" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7">
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>283</v>
+      <c r="B23" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>272</v>
       </c>
       <c r="G23" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7">
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>284</v>
+      <c r="B24" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="G24" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7">
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>285</v>
+      <c r="B25" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>274</v>
       </c>
       <c r="G25" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7">
       <c r="A26" s="1"/>
-      <c r="B26" s="9"/>
-      <c r="D26" s="9"/>
+      <c r="B26" s="4"/>
+      <c r="D26" s="4"/>
       <c r="F26" s="2"/>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7">
       <c r="A27" s="1"/>
-      <c r="B27" s="9"/>
-      <c r="D27" s="9"/>
+      <c r="B27" s="4"/>
+      <c r="D27" s="4"/>
       <c r="F27" s="2"/>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7">
       <c r="A28" s="1"/>
-      <c r="B28" s="9"/>
-      <c r="D28" s="9"/>
+      <c r="B28" s="4"/>
+      <c r="D28" s="4"/>
       <c r="F28" s="2"/>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7">
       <c r="A29" s="1"/>
-      <c r="B29" s="9"/>
-      <c r="D29" s="9"/>
+      <c r="B29" s="4"/>
+      <c r="D29" s="4"/>
       <c r="F29" s="2"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7">
       <c r="A30" s="1"/>
-      <c r="B30" s="9"/>
-      <c r="D30" s="9"/>
+      <c r="B30" s="4"/>
+      <c r="D30" s="4"/>
       <c r="F30" s="2"/>
       <c r="G30" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -8747,7 +9189,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8776,26 +9218,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>187</v>
+        <v>275</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>188</v>
+        <v>276</v>
       </c>
       <c r="G2" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>187</v>
+        <v>275</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -8804,18 +9246,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>189</v>
+        <v>277</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>187</v>
+        <v>275</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -8824,18 +9266,18 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>190</v>
+        <v>278</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>187</v>
+        <v>275</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -8844,18 +9286,18 @@
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>191</v>
+        <v>279</v>
       </c>
       <c r="G5" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>187</v>
+        <v>275</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -8864,18 +9306,18 @@
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>192</v>
+        <v>280</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>187</v>
+        <v>275</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -8884,18 +9326,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>193</v>
+        <v>281</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>187</v>
+        <v>275</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -8904,18 +9346,18 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>194</v>
+        <v>282</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>187</v>
+        <v>275</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -8924,18 +9366,18 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>195</v>
+        <v>283</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>187</v>
+        <v>275</v>
       </c>
       <c r="C10" t="s">
         <v>17</v>
@@ -8944,21 +9386,21 @@
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>196</v>
+        <v>284</v>
       </c>
       <c r="G10" s="1">
         <v>-1</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>187</v>
+        <v>275</v>
       </c>
       <c r="C11" t="s">
         <v>17</v>
@@ -8967,21 +9409,21 @@
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>198</v>
+        <v>286</v>
       </c>
       <c r="G11" s="1">
         <v>-1</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>187</v>
+        <v>275</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -8990,25 +9432,26 @@
         <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>199</v>
+        <v>287</v>
       </c>
       <c r="G12" s="1">
         <v>-1</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>197</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -9017,7 +9460,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9046,26 +9489,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>200</v>
+        <v>288</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>201</v>
+        <v>289</v>
       </c>
       <c r="G2" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>200</v>
+        <v>288</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -9074,18 +9517,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>202</v>
+        <v>290</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>200</v>
+        <v>288</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -9094,64 +9537,64 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>203</v>
+        <v>291</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>200</v>
+        <v>288</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>204</v>
+        <v>292</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>205</v>
+        <v>293</v>
       </c>
       <c r="G5" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>200</v>
+        <v>288</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>206</v>
+        <v>294</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>207</v>
+        <v>295</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>200</v>
+        <v>288</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -9160,18 +9603,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>208</v>
+        <v>296</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>200</v>
+        <v>288</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -9180,18 +9623,18 @@
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>209</v>
+        <v>297</v>
       </c>
       <c r="G8" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>200</v>
+        <v>288</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -9200,18 +9643,18 @@
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>210</v>
+        <v>298</v>
       </c>
       <c r="G9" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>200</v>
+        <v>288</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
@@ -9220,18 +9663,18 @@
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>211</v>
+        <v>299</v>
       </c>
       <c r="G10" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>200</v>
+        <v>288</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
@@ -9240,18 +9683,18 @@
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>212</v>
+        <v>300</v>
       </c>
       <c r="G11" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>200</v>
+        <v>288</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
@@ -9260,18 +9703,18 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>213</v>
+        <v>301</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>200</v>
+        <v>288</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -9280,18 +9723,18 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>214</v>
+        <v>302</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>200</v>
+        <v>288</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -9300,22 +9743,23 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>215</v>
+        <v>303</v>
       </c>
       <c r="G14" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -9324,7 +9768,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9353,26 +9797,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>216</v>
+        <v>304</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>217</v>
+        <v>305</v>
       </c>
       <c r="G2" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>216</v>
+        <v>304</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -9381,18 +9825,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>218</v>
+        <v>306</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>216</v>
+        <v>304</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -9401,18 +9845,18 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>219</v>
+        <v>307</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>216</v>
+        <v>304</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -9421,18 +9865,18 @@
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>220</v>
+        <v>308</v>
       </c>
       <c r="G5" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>216</v>
+        <v>304</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -9441,18 +9885,18 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>221</v>
+        <v>309</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>216</v>
+        <v>304</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -9461,18 +9905,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>222</v>
+        <v>310</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>216</v>
+        <v>304</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -9481,18 +9925,18 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>223</v>
+        <v>311</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>216</v>
+        <v>304</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -9501,64 +9945,64 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>224</v>
+        <v>312</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>216</v>
+        <v>304</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>204</v>
+        <v>292</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>225</v>
+        <v>313</v>
       </c>
       <c r="G10" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>216</v>
+        <v>304</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>206</v>
+        <v>294</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>226</v>
+        <v>314</v>
       </c>
       <c r="G11" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>216</v>
+        <v>304</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
@@ -9567,18 +10011,18 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>227</v>
+        <v>315</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>216</v>
+        <v>304</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -9587,18 +10031,18 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>228</v>
+        <v>316</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>216</v>
+        <v>304</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -9607,18 +10051,18 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>229</v>
+        <v>317</v>
       </c>
       <c r="G14" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>216</v>
+        <v>304</v>
       </c>
       <c r="C15" t="s">
         <v>58</v>
@@ -9627,18 +10071,18 @@
         <v>59</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>230</v>
+        <v>318</v>
       </c>
       <c r="G15" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>216</v>
+        <v>304</v>
       </c>
       <c r="C16" t="s">
         <v>10</v>
@@ -9647,18 +10091,18 @@
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>231</v>
+        <v>319</v>
       </c>
       <c r="G16" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>216</v>
+        <v>304</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
@@ -9667,18 +10111,18 @@
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>232</v>
+        <v>320</v>
       </c>
       <c r="G17" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>216</v>
+        <v>304</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -9687,22 +10131,23 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>233</v>
+        <v>321</v>
       </c>
       <c r="G18" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="12.75" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -9711,7 +10156,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9740,26 +10185,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>234</v>
+        <v>322</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>235</v>
+        <v>323</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>234</v>
+        <v>322</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -9768,18 +10213,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>236</v>
+        <v>324</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>234</v>
+        <v>322</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -9788,14 +10233,14 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>237</v>
+        <v>325</v>
       </c>
       <c r="G4" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Excel/ChatData.xlsx
+++ b/Assets/StreamingAssets/Excel/ChatData.xlsx
@@ -1616,7 +1616,7 @@
     <t>不研究修理_01</t>
   </si>
   <si>
-    <t>第一天5点时，未完成修理的研究</t>
+    <t>第一天5点时未完成修理的研究</t>
   </si>
   <si>
     <t>已经好久了</t>
@@ -1658,7 +1658,7 @@
     <t>不研究修理_02</t>
   </si>
   <si>
-    <t>第一天11点时，未完成修理的研究</t>
+    <t>第一天11点时未完成修理的研究</t>
   </si>
   <si>
     <t>那个……</t>
@@ -7676,8 +7676,8 @@
       <c r="C7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>18</v>
+      <c r="D7" t="s">
+        <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>206</v>
@@ -7717,7 +7717,7 @@
         <v>10</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>208</v>

--- a/Assets/StreamingAssets/Excel/ChatData.xlsx
+++ b/Assets/StreamingAssets/Excel/ChatData.xlsx
@@ -1,43 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FFEC38C-EC87-4EAF-B952-C449D9033FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="2"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="一切的开始" sheetId="1" r:id="rId1"/>
     <sheet name="修理研究完毕" sheetId="2" r:id="rId2"/>
     <sheet name="不研究修理_01" sheetId="11" r:id="rId3"/>
     <sheet name="不研究修理_02" sheetId="12" r:id="rId4"/>
-    <sheet name="堵住裂缝" sheetId="10" r:id="rId5"/>
-    <sheet name="死亡" sheetId="3" r:id="rId6"/>
-    <sheet name="第一次点开气密舱门" sheetId="4" r:id="rId7"/>
-    <sheet name="第一次进珊瑚礁海域" sheetId="5" r:id="rId8"/>
-    <sheet name="困了_01" sheetId="6" r:id="rId9"/>
-    <sheet name="困了_02" sheetId="7" r:id="rId10"/>
-    <sheet name="困了_03" sheetId="8" r:id="rId11"/>
+    <sheet name="水平面高度100" sheetId="13" r:id="rId5"/>
+    <sheet name="水平面高度70" sheetId="14" r:id="rId6"/>
+    <sheet name="堵住裂缝" sheetId="10" r:id="rId7"/>
+    <sheet name="死亡" sheetId="3" r:id="rId8"/>
+    <sheet name="第一次点开气密舱门" sheetId="4" r:id="rId9"/>
+    <sheet name="第一次进珊瑚礁海域" sheetId="5" r:id="rId10"/>
+    <sheet name="困了_01" sheetId="6" r:id="rId11"/>
+    <sheet name="困了_02" sheetId="7" r:id="rId12"/>
+    <sheet name="困了_03" sheetId="8" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1255" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1347" uniqueCount="369">
   <si>
     <t>小段</t>
   </si>
@@ -2393,20 +2388,148 @@
       </rPr>
       <t>嗯</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>其他_死亡</t>
+    </r>
+  </si>
+  <si>
+    <t>不……不不不……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>提示</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>求生系统</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>水平面高度100</t>
+  </si>
+  <si>
+    <t>真正该说对不起的人是我……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>………………</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>对话</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>麦麦</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>…………</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>对不起……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>再坚持一下</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>选项</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>别,一定还会有办法的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>脑子好乱……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>咳咳咳</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>水平面高度100</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>水平面高度达到100</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>水平面高度</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>水平面高度每次达到100</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>水平面高度70</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>水平面高度每次达到70</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>感觉在室内移动越来越费劲了</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>水平面高度70</t>
+  </si>
+  <si>
+    <t>哪怕是爬到最高处,水面也没过胸口了</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>没有多少时间</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>水平面高度71</t>
+  </si>
+  <si>
+    <t>如果有没堵上的裂缝应该尽快堵上</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>研究窗口中的"防涝"科技可解锁一些排水的建筑和工具</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>一旦水平面高度达到100,游戏就会结束</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.00_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="1">
+    <numFmt numFmtId="178" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -2426,352 +2549,43 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="10"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -2779,259 +2593,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -3040,16 +2612,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3064,90 +2630,171 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -3158,7 +2805,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -3186,154 +2833,40 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -3591,14 +3124,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I138"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="27"/>
@@ -3608,7 +3141,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3637,7 +3170,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -3649,7 +3182,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3670,7 +3203,7 @@
       </c>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -3691,7 +3224,7 @@
       </c>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -3711,7 +3244,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -3731,7 +3264,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -3752,7 +3285,7 @@
       </c>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -3773,7 +3306,7 @@
       </c>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -3794,7 +3327,7 @@
       </c>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -3815,7 +3348,7 @@
       </c>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -3836,7 +3369,7 @@
       </c>
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -3856,7 +3389,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -3877,7 +3410,7 @@
       </c>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -3897,7 +3430,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -3918,7 +3451,7 @@
       </c>
       <c r="H15" s="1"/>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -3939,7 +3472,7 @@
       </c>
       <c r="H16" s="1"/>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -3959,7 +3492,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -3979,7 +3512,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -4000,7 +3533,7 @@
       </c>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -4021,7 +3554,7 @@
       </c>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -4042,7 +3575,7 @@
       </c>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -4063,7 +3596,7 @@
       </c>
       <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -4084,7 +3617,7 @@
       </c>
       <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -4104,7 +3637,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -4125,7 +3658,7 @@
       </c>
       <c r="H25" s="1"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -4146,7 +3679,7 @@
       </c>
       <c r="H26" s="1"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -4167,7 +3700,7 @@
       </c>
       <c r="H27" s="1"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -4188,7 +3721,7 @@
       </c>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -4211,7 +3744,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -4232,7 +3765,7 @@
       </c>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -4253,7 +3786,7 @@
       </c>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -4274,7 +3807,7 @@
       </c>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -4295,7 +3828,7 @@
       </c>
       <c r="H33" s="1"/>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -4316,7 +3849,7 @@
       </c>
       <c r="H34" s="1"/>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -4337,7 +3870,7 @@
       </c>
       <c r="H35" s="1"/>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -4358,7 +3891,7 @@
       </c>
       <c r="H36" s="1"/>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -4379,7 +3912,7 @@
       </c>
       <c r="H37" s="1"/>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -4400,7 +3933,7 @@
       </c>
       <c r="H38" s="1"/>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -4421,7 +3954,7 @@
       </c>
       <c r="H39" s="1"/>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -4442,7 +3975,7 @@
       </c>
       <c r="H40" s="1"/>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -4463,7 +3996,7 @@
       </c>
       <c r="H41" s="1"/>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -4484,7 +4017,7 @@
       </c>
       <c r="H42" s="1"/>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -4505,7 +4038,7 @@
       </c>
       <c r="H43" s="1"/>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -4526,7 +4059,7 @@
       </c>
       <c r="H44" s="1"/>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -4547,7 +4080,7 @@
       </c>
       <c r="H45" s="1"/>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -4568,7 +4101,7 @@
       </c>
       <c r="H46" s="1"/>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -4588,11 +4121,11 @@
         <v>46</v>
       </c>
       <c r="H47" s="1"/>
-      <c r="I47" s="4" t="s">
+      <c r="I47" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -4616,7 +4149,7 @@
       </c>
       <c r="H48" s="1"/>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -4637,7 +4170,7 @@
       </c>
       <c r="H49" s="1"/>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -4658,7 +4191,7 @@
       </c>
       <c r="H50" s="1"/>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -4679,7 +4212,7 @@
       </c>
       <c r="H51" s="1"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -4700,7 +4233,7 @@
       </c>
       <c r="H52" s="1"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -4721,7 +4254,7 @@
       </c>
       <c r="H53" s="1"/>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -4742,7 +4275,7 @@
       </c>
       <c r="H54" s="1"/>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -4763,7 +4296,7 @@
       </c>
       <c r="H55" s="1"/>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -4784,7 +4317,7 @@
       </c>
       <c r="H56" s="1"/>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -4805,7 +4338,7 @@
       </c>
       <c r="H57" s="1"/>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -4826,7 +4359,7 @@
       </c>
       <c r="H58" s="1"/>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -4847,7 +4380,7 @@
       </c>
       <c r="H59" s="1"/>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -4868,7 +4401,7 @@
       </c>
       <c r="H60" s="1"/>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -4888,11 +4421,11 @@
         <v>60</v>
       </c>
       <c r="H61" s="1"/>
-      <c r="I61" s="4" t="s">
+      <c r="I61" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -4916,7 +4449,7 @@
       </c>
       <c r="H62" s="1"/>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -4937,7 +4470,7 @@
       </c>
       <c r="H63" s="1"/>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -4958,7 +4491,7 @@
       </c>
       <c r="H64" s="1"/>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -4979,7 +4512,7 @@
       </c>
       <c r="H65" s="1"/>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -5000,7 +4533,7 @@
       </c>
       <c r="H66" s="1"/>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -5021,7 +4554,7 @@
       </c>
       <c r="H67" s="1"/>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -5041,11 +4574,11 @@
         <v>67</v>
       </c>
       <c r="H68" s="1"/>
-      <c r="I68" s="4" t="s">
+      <c r="I68" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -5069,7 +4602,7 @@
       </c>
       <c r="H69" s="1"/>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -5092,7 +4625,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -5113,7 +4646,7 @@
       </c>
       <c r="H71" s="1"/>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -5134,7 +4667,7 @@
       </c>
       <c r="H72" s="1"/>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -5157,7 +4690,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -5180,7 +4713,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -5201,7 +4734,7 @@
       </c>
       <c r="H75" s="1"/>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -5221,11 +4754,11 @@
         <v>75</v>
       </c>
       <c r="H76" s="1"/>
-      <c r="I76" s="4" t="s">
+      <c r="I76" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -5249,7 +4782,7 @@
       </c>
       <c r="H77" s="1"/>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -5270,7 +4803,7 @@
       </c>
       <c r="H78" s="1"/>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -5293,7 +4826,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -5314,7 +4847,7 @@
       </c>
       <c r="H80" s="1"/>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -5335,7 +4868,7 @@
       </c>
       <c r="H81" s="1"/>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -5356,7 +4889,7 @@
       </c>
       <c r="H82" s="1"/>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -5379,7 +4912,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -5399,7 +4932,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -5419,7 +4952,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -5440,7 +4973,7 @@
       </c>
       <c r="H86" s="1"/>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -5460,7 +4993,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -5481,7 +5014,7 @@
       </c>
       <c r="H88" s="1"/>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -5504,7 +5037,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>88</v>
       </c>
@@ -5525,7 +5058,7 @@
       </c>
       <c r="H90" s="1"/>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>89</v>
       </c>
@@ -5545,7 +5078,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>90</v>
       </c>
@@ -5568,7 +5101,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>91</v>
       </c>
@@ -5589,7 +5122,7 @@
       </c>
       <c r="H93" s="1"/>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>92</v>
       </c>
@@ -5609,7 +5142,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>93</v>
       </c>
@@ -5630,7 +5163,7 @@
       </c>
       <c r="H95" s="1"/>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>94</v>
       </c>
@@ -5651,7 +5184,7 @@
       </c>
       <c r="H96" s="1"/>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>95</v>
       </c>
@@ -5671,11 +5204,11 @@
         <v>96</v>
       </c>
       <c r="H97" s="1"/>
-      <c r="I97" s="4" t="s">
+      <c r="I97" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>96</v>
       </c>
@@ -5699,7 +5232,7 @@
       </c>
       <c r="H98" s="1"/>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>97</v>
       </c>
@@ -5720,7 +5253,7 @@
       </c>
       <c r="H99" s="1"/>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>98</v>
       </c>
@@ -5741,7 +5274,7 @@
       </c>
       <c r="H100" s="1"/>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>99</v>
       </c>
@@ -5762,7 +5295,7 @@
       </c>
       <c r="H101" s="1"/>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>100</v>
       </c>
@@ -5783,7 +5316,7 @@
       </c>
       <c r="H102" s="1"/>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>101</v>
       </c>
@@ -5804,7 +5337,7 @@
       </c>
       <c r="H103" s="1"/>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>102</v>
       </c>
@@ -5825,7 +5358,7 @@
       </c>
       <c r="H104" s="1"/>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>103</v>
       </c>
@@ -5846,7 +5379,7 @@
       </c>
       <c r="H105" s="1"/>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>104</v>
       </c>
@@ -5867,7 +5400,7 @@
       </c>
       <c r="H106" s="1"/>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>105</v>
       </c>
@@ -5888,7 +5421,7 @@
       </c>
       <c r="H107" s="1"/>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>106</v>
       </c>
@@ -5909,7 +5442,7 @@
       </c>
       <c r="H108" s="1"/>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>107</v>
       </c>
@@ -5930,7 +5463,7 @@
       </c>
       <c r="H109" s="1"/>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>108</v>
       </c>
@@ -5943,7 +5476,7 @@
       <c r="D110" t="s">
         <v>59</v>
       </c>
-      <c r="F110" s="10" t="s">
+      <c r="F110" s="8" t="s">
         <v>132</v>
       </c>
       <c r="G110" s="1">
@@ -5951,7 +5484,7 @@
       </c>
       <c r="H110" s="1"/>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>109</v>
       </c>
@@ -5977,7 +5510,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>110</v>
       </c>
@@ -6000,7 +5533,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>111</v>
       </c>
@@ -6023,7 +5556,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>112</v>
       </c>
@@ -6044,7 +5577,7 @@
       </c>
       <c r="H114" s="1"/>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>113</v>
       </c>
@@ -6065,7 +5598,7 @@
       </c>
       <c r="H115" s="1"/>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>114</v>
       </c>
@@ -6086,7 +5619,7 @@
       </c>
       <c r="H116" s="1"/>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>115</v>
       </c>
@@ -6107,7 +5640,7 @@
       </c>
       <c r="H117" s="1"/>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>116</v>
       </c>
@@ -6128,7 +5661,7 @@
       </c>
       <c r="H118" s="1"/>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>117</v>
       </c>
@@ -6149,7 +5682,7 @@
       </c>
       <c r="H119" s="1"/>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>118</v>
       </c>
@@ -6170,7 +5703,7 @@
       </c>
       <c r="H120" s="1"/>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>119</v>
       </c>
@@ -6191,7 +5724,7 @@
       </c>
       <c r="H121" s="1"/>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>120</v>
       </c>
@@ -6211,7 +5744,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>121</v>
       </c>
@@ -6232,7 +5765,7 @@
       </c>
       <c r="H123" s="1"/>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>122</v>
       </c>
@@ -6253,7 +5786,7 @@
       </c>
       <c r="H124" s="1"/>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>123</v>
       </c>
@@ -6273,7 +5806,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>124</v>
       </c>
@@ -6293,7 +5826,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>125</v>
       </c>
@@ -6314,7 +5847,7 @@
       </c>
       <c r="H127" s="1"/>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>126</v>
       </c>
@@ -6335,7 +5868,7 @@
       </c>
       <c r="H128" s="1"/>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>127</v>
       </c>
@@ -6356,7 +5889,7 @@
       </c>
       <c r="H129" s="1"/>
     </row>
-    <row r="130" spans="1:9">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>128</v>
       </c>
@@ -6376,11 +5909,11 @@
         <v>129</v>
       </c>
       <c r="H130" s="1"/>
-      <c r="I130" s="4" t="s">
+      <c r="I130" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>129</v>
       </c>
@@ -6404,7 +5937,7 @@
       </c>
       <c r="H131" s="1"/>
     </row>
-    <row r="132" spans="1:8">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>130</v>
       </c>
@@ -6425,7 +5958,7 @@
       </c>
       <c r="H132" s="1"/>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>131</v>
       </c>
@@ -6446,7 +5979,7 @@
       </c>
       <c r="H133" s="1"/>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>132</v>
       </c>
@@ -6467,7 +6000,7 @@
       </c>
       <c r="H134" s="1"/>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>133</v>
       </c>
@@ -6488,7 +6021,7 @@
       </c>
       <c r="H135" s="1"/>
     </row>
-    <row r="136" spans="1:8">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>134</v>
       </c>
@@ -6512,7 +6045,7 @@
       </c>
       <c r="H136" s="1"/>
     </row>
-    <row r="137" spans="1:8">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>135</v>
       </c>
@@ -6533,7 +6066,7 @@
       </c>
       <c r="H137" s="1"/>
     </row>
-    <row r="138" ht="24" spans="1:9">
+    <row r="138" spans="1:9" ht="24" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>136</v>
       </c>
@@ -6546,29 +6079,28 @@
       <c r="D138" t="s">
         <v>59</v>
       </c>
-      <c r="F138" s="11" t="s">
+      <c r="F138" s="9" t="s">
         <v>164</v>
       </c>
       <c r="G138" s="1">
         <v>-1</v>
       </c>
       <c r="H138" s="1"/>
-      <c r="I138" s="4" t="s">
+      <c r="I138" t="s">
         <v>165</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="12.75" outlineLevelRow="3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -6577,7 +6109,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6606,26 +6138,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>326</v>
+        <v>304</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="G2" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>326</v>
+        <v>304</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -6634,18 +6166,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>327</v>
+        <v>306</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>326</v>
+        <v>304</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -6654,23 +6186,308 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>328</v>
+        <v>307</v>
       </c>
       <c r="G4" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="G5" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>304</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="G6" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>304</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="G7" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>304</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="G8" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>304</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="G9" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>304</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>173</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>304</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>173</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="G11" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>304</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="G12" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>304</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="G13" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>304</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="G14" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>304</v>
+      </c>
+      <c r="C15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="G15" s="1">
         <v>-1</v>
       </c>
     </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>304</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="G16" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>304</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="G17" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>304</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="G18" s="1">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="12.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -6679,7 +6496,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6708,12 +6525,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>323</v>
@@ -6722,11 +6539,213 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="G4" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="4" width="18"/>
+    <col min="5" max="5" width="10"/>
+    <col min="6" max="6" width="42"/>
+    <col min="7" max="8" width="10"/>
+    <col min="9" max="9" width="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>326</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="G2" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>326</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="G4" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="4" width="18"/>
+    <col min="5" max="5" width="10"/>
+    <col min="6" max="6" width="42"/>
+    <col min="7" max="8" width="10"/>
+    <col min="9" max="9" width="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="G2" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
         <v>329</v>
       </c>
       <c r="C3" t="s">
@@ -6742,7 +6761,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -6762,7 +6781,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -6782,7 +6801,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -6802,7 +6821,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -6822,7 +6841,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -6842,7 +6861,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -6863,16 +6882,15 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I32"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="24"/>
@@ -6881,7 +6899,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6910,7 +6928,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -6924,7 +6942,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -6944,7 +6962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -6964,7 +6982,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -6984,7 +7002,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -7004,7 +7022,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -7024,7 +7042,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -7044,7 +7062,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -7064,7 +7082,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -7087,7 +7105,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -7110,7 +7128,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -7130,7 +7148,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -7153,7 +7171,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -7173,7 +7191,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -7192,11 +7210,11 @@
       <c r="G15" s="1">
         <v>14</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -7216,7 +7234,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -7239,7 +7257,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -7259,7 +7277,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -7279,7 +7297,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -7300,7 +7318,7 @@
       </c>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -7321,7 +7339,7 @@
       </c>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -7341,7 +7359,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -7361,7 +7379,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -7381,7 +7399,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -7401,7 +7419,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -7411,7 +7429,7 @@
       <c r="C26" t="s">
         <v>17</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" t="s">
         <v>11</v>
       </c>
       <c r="F26" s="3" t="s">
@@ -7421,7 +7439,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -7431,7 +7449,7 @@
       <c r="C27" t="s">
         <v>17</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" t="s">
         <v>11</v>
       </c>
       <c r="F27" s="3" t="s">
@@ -7441,7 +7459,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -7461,7 +7479,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -7481,7 +7499,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -7501,7 +7519,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -7521,29 +7539,28 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="G32" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.1047619047619" customWidth="1"/>
-    <col min="5" max="5" width="30.552380952381" customWidth="1"/>
-    <col min="6" max="6" width="34.2190476190476" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" customWidth="1"/>
+    <col min="5" max="5" width="30.5546875" customWidth="1"/>
+    <col min="6" max="6" width="34.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7572,11 +7589,11 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" t="s">
         <v>200</v>
       </c>
       <c r="E2" s="3" t="s">
@@ -7586,11 +7603,11 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" t="s">
         <v>200</v>
       </c>
       <c r="C3" t="s">
@@ -7606,11 +7623,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" t="s">
         <v>200</v>
       </c>
       <c r="C4" t="s">
@@ -7626,17 +7643,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" t="s">
         <v>200</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="3" t="s">
@@ -7646,17 +7663,17 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" t="s">
         <v>200</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="3" t="s">
@@ -7666,14 +7683,14 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" t="s">
         <v>200</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" t="s">
         <v>10</v>
       </c>
       <c r="D7" t="s">
@@ -7686,17 +7703,17 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" t="s">
         <v>200</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="3" t="s">
@@ -7706,17 +7723,17 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" t="s">
         <v>200</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="3" t="s">
@@ -7726,17 +7743,17 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" t="s">
         <v>200</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
         <v>11</v>
       </c>
       <c r="E10" s="3"/>
@@ -7747,17 +7764,17 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" t="s">
         <v>200</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" t="s">
         <v>59</v>
       </c>
       <c r="E11" s="3"/>
@@ -7768,17 +7785,17 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" t="s">
         <v>200</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="3" t="s">
@@ -7788,17 +7805,17 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" t="s">
         <v>200</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
         <v>11</v>
       </c>
       <c r="E13" s="3"/>
@@ -7809,17 +7826,17 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" t="s">
         <v>200</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
@@ -7829,1358 +7846,1958 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
       <c r="F15" s="2"/>
       <c r="G15" s="1"/>
-      <c r="I15" s="4"/>
-    </row>
-    <row r="16" spans="1:7">
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
       <c r="F16" s="3"/>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
       <c r="E17" s="3"/>
       <c r="F17" s="2"/>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
       <c r="F18" s="2"/>
       <c r="G18" s="1"/>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
       <c r="F19" s="2"/>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
       <c r="F20" s="2"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
       <c r="F21" s="3"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
       <c r="F22" s="2"/>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
       <c r="F23" s="2"/>
       <c r="G23" s="1"/>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
       <c r="F24" s="2"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
       <c r="F25" s="2"/>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="4"/>
-      <c r="D26" s="4"/>
       <c r="F26" s="2"/>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
-      <c r="B27" s="4"/>
-      <c r="D27" s="4"/>
       <c r="F27" s="2"/>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="4"/>
-      <c r="D28" s="4"/>
       <c r="F28" s="2"/>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="B29" s="4"/>
-      <c r="D29" s="4"/>
       <c r="F29" s="2"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="4"/>
-      <c r="D30" s="4"/>
       <c r="F30" s="2"/>
       <c r="G30" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.3333333333333" style="5"/>
-    <col min="2" max="2" width="13.1047619047619" style="5" customWidth="1"/>
-    <col min="3" max="4" width="10.3333333333333" style="5"/>
-    <col min="5" max="5" width="30.552380952381" style="5" customWidth="1"/>
-    <col min="6" max="6" width="57.8857142857143" style="5" customWidth="1"/>
-    <col min="7" max="16384" width="10.3333333333333" style="5"/>
+    <col min="1" max="1" width="10.33203125" style="4"/>
+    <col min="2" max="2" width="13.109375" style="4" customWidth="1"/>
+    <col min="3" max="4" width="10.33203125" style="4"/>
+    <col min="5" max="5" width="30.5546875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="57.88671875" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="10.33203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="6">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="5">
         <v>0</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="G2" s="6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="6">
+      <c r="G2" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
         <v>1</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="9" t="s">
+      <c r="C3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="6">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
         <v>2</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="8" t="s">
+      <c r="C4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="6">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
         <v>3</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="6">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
         <v>4</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="6">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
         <v>5</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="9" t="s">
+      <c r="C7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="5">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="6">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
         <v>6</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="8" t="s">
+      <c r="C8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="5">
         <v>7</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="4">
         <v>1000</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="6">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
         <v>7</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="8" t="s">
+      <c r="C9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="5">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="6">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
         <v>8</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="9" t="s">
+      <c r="C10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="6"/>
+      <c r="F10" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="G10" s="6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="6">
-        <v>9</v>
-      </c>
-      <c r="B11" s="7" t="s">
+      <c r="G10" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="9" t="s">
+      <c r="D11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="6"/>
+      <c r="F11" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="G11" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="6">
-        <v>10</v>
-      </c>
-      <c r="B12" s="7" t="s">
+      <c r="G11" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <v>10</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="8" t="s">
+      <c r="C12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="G12" s="6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="6">
-        <v>11</v>
-      </c>
-      <c r="B13" s="7" t="s">
+      <c r="G12" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="7" t="s">
+      <c r="C13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="8"/>
-      <c r="F13" s="9" t="s">
+      <c r="E13" s="6"/>
+      <c r="F13" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="5">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="6">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
         <v>12</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="7" t="s">
+      <c r="C14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="5">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="6">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
         <v>13</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="9" t="s">
+      <c r="C15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="5">
         <v>14</v>
       </c>
-      <c r="I15" s="7"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="6">
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
         <v>14</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="9" t="s">
+      <c r="C16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="5">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="6">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
         <v>15</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="5">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="6">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="5">
         <v>16</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="7" t="s">
+      <c r="D18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="5">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="6">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
         <v>17</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="7" t="s">
+      <c r="D19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G19" s="5">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="6">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="5">
         <v>18</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D20" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="7" t="s">
+      <c r="D20" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G20" s="5">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="6">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="5">
         <v>19</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="7" t="s">
+      <c r="D21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G21" s="5">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="6">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="5">
         <v>20</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C22" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="9" t="s">
+      <c r="C22" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="G22" s="6">
+      <c r="G22" s="5">
         <v>22</v>
       </c>
-      <c r="H22" s="5">
+      <c r="H22" s="4">
         <v>3500</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="6">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
         <v>21</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="9" t="s">
+      <c r="C23" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="G23" s="6">
+      <c r="G23" s="5">
         <v>22</v>
       </c>
-      <c r="H23" s="5">
+      <c r="H23" s="4">
         <v>2000</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="6">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="5">
         <v>22</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="G24" s="6">
+      <c r="G24" s="5">
         <v>23</v>
       </c>
-      <c r="H24" s="6"/>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="6">
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="5">
         <v>23</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="G25" s="6">
+      <c r="G25" s="5">
         <v>-1</v>
       </c>
-      <c r="H25" s="6"/>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="6">
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="5">
         <v>24</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="7" t="s">
+      <c r="C26" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="G26" s="5">
+      <c r="G26" s="4">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="6">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="5">
         <v>25</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="C27" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="7" t="s">
+      <c r="C27" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="G27" s="5">
+      <c r="G27" s="4">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="6">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="5">
         <v>26</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="9" t="s">
+      <c r="C28" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="G28" s="5">
+      <c r="G28" s="4">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="6">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="5">
         <v>27</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="F29" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="G29" s="5">
+      <c r="G29" s="4">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="6">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="5">
         <v>28</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F30" s="9" t="s">
+      <c r="F30" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="G30" s="5">
+      <c r="G30" s="4">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE7E312D-F962-49D8-B0D5-21EC4E30030D}">
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="19.4380952380952" customWidth="1"/>
-    <col min="6" max="6" width="34.2190476190476" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" style="4"/>
+    <col min="2" max="2" width="13.109375" style="4" customWidth="1"/>
+    <col min="3" max="4" width="10.33203125" style="4"/>
+    <col min="5" max="5" width="30.5546875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="57.88671875" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="10.33203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="1">
+    <row r="2" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="G2" s="1">
+      <c r="B2" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="G2" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>1</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="G3" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="G4" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>353</v>
+      </c>
+      <c r="G5" s="4">
+        <v>4</v>
+      </c>
+      <c r="H5" s="4">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>4</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="G6" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>5</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="G7" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>6</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="G8" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>7</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="G9" s="4">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="G3" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="G4" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="G5" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="G6" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="G7" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="G8" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="G9" s="1">
+    <row r="10" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="G10" s="1">
-        <v>9</v>
-      </c>
-      <c r="H10">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="G11" s="1">
-        <v>10</v>
-      </c>
-      <c r="H11">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="G12" s="1">
-        <v>11</v>
-      </c>
-      <c r="H12">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="G13" s="1">
-        <v>12</v>
-      </c>
-      <c r="H13">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="G14" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G15" s="1">
-        <v>14</v>
-      </c>
-      <c r="I15" s="4"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="1">
-        <v>14</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="G16" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="1">
-        <v>15</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="G17" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="1">
-        <v>16</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="G18" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="1">
-        <v>17</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="G19" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="1">
-        <v>18</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="G20" s="1">
-        <v>19</v>
-      </c>
-      <c r="H20" s="1"/>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="1">
-        <v>19</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="G21" s="1">
-        <v>20</v>
-      </c>
-      <c r="H21" s="1"/>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="1">
-        <v>20</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="G22" s="1">
+      <c r="B10" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="G10" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>9</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="G11" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>10</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="G12" s="4">
         <v>-1</v>
       </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="1">
-        <v>21</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="G23" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="1">
-        <v>22</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="G24" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="1">
-        <v>23</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="G25" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="1"/>
-      <c r="B26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="1"/>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="1"/>
-      <c r="B27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="1"/>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="1"/>
-      <c r="B28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="1"/>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="1"/>
-      <c r="B29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="1"/>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="1"/>
-      <c r="B30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="1"/>
+      <c r="I12" s="11" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>11</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="G13" s="4">
+        <v>-1</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="5"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="5"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="5"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="5"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="5"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="5"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="5"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="5"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="5"/>
+      <c r="G18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="5"/>
+      <c r="G19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="5"/>
+      <c r="G20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="G21" s="5"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="5"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="5"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="5"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="5"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="5"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="5"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="5"/>
+      <c r="F28" s="7"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="5"/>
+      <c r="F29" s="7"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="5"/>
+      <c r="F30" s="7"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D385818A-0AD6-41B6-8DA0-2F40C85219EF}">
+  <dimension ref="A1:I30"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.33203125" style="4"/>
+    <col min="2" max="2" width="13.109375" style="4" customWidth="1"/>
+    <col min="3" max="4" width="10.33203125" style="4"/>
+    <col min="5" max="5" width="30.5546875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="57.88671875" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="10.33203125" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="5">
+        <v>0</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="G2" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>1</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="G3" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>2</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="G4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="G5" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>4</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="G6" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>5</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="G7" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>6</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="G8" s="5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="F9" s="12"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="F10" s="12"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="F11" s="12"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="F12" s="13"/>
+      <c r="I12" s="11"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="F13" s="10"/>
+      <c r="I13" s="11"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="5"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="5"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="5"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="5"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="5"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="5"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="5"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="5"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="5"/>
+      <c r="G18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="5"/>
+      <c r="G19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="5"/>
+      <c r="G20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="G21" s="5"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="5"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="5"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="5"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="5"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="5"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="5"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="5"/>
+      <c r="F28" s="7"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="5"/>
+      <c r="F29" s="7"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="5"/>
+      <c r="F30" s="7"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:I30"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="19.44140625" customWidth="1"/>
+    <col min="6" max="6" width="34.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="G2" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="G4" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G5" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G6" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>250</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="G7" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>250</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="G8" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>250</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="G9" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>250</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="G10" s="1">
+        <v>9</v>
+      </c>
+      <c r="H10">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>250</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="G11" s="1">
+        <v>10</v>
+      </c>
+      <c r="H11">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>250</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="G12" s="1">
+        <v>11</v>
+      </c>
+      <c r="H12">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>250</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="G13" s="1">
+        <v>12</v>
+      </c>
+      <c r="H13">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>250</v>
+      </c>
+      <c r="C14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="G14" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>250</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="G15" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>250</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G16" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>250</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="G17" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>250</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="G18" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>250</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="G19" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>250</v>
+      </c>
+      <c r="C20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="G20" s="1">
+        <v>19</v>
+      </c>
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>250</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="G21" s="1">
+        <v>20</v>
+      </c>
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>250</v>
+      </c>
+      <c r="C22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" t="s">
+        <v>59</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="G22" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>250</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="G23" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>250</v>
+      </c>
+      <c r="C24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="G24" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>250</v>
+      </c>
+      <c r="C25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="G25" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="1"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="1"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="1"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="1"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -9189,7 +9806,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9218,7 +9835,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -9232,7 +9849,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -9252,7 +9869,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -9272,7 +9889,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -9292,7 +9909,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -9312,7 +9929,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -9332,7 +9949,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -9352,7 +9969,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -9372,7 +9989,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -9395,7 +10012,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -9418,7 +10035,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -9442,16 +10059,15 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -9460,7 +10076,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9489,7 +10105,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -9503,7 +10119,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -9523,7 +10139,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -9543,7 +10159,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -9566,7 +10182,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -9589,7 +10205,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -9609,7 +10225,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -9629,7 +10245,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -9649,7 +10265,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -9669,7 +10285,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -9689,7 +10305,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -9709,7 +10325,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -9729,7 +10345,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -9750,497 +10366,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="12.75"/>
-  <cols>
-    <col min="1" max="4" width="18"/>
-    <col min="5" max="5" width="10"/>
-    <col min="6" max="6" width="42"/>
-    <col min="7" max="8" width="10"/>
-    <col min="9" max="9" width="18"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="1">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>304</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="G2" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>304</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="G3" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>304</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="G4" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>304</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="G5" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>304</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="G6" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>304</v>
-      </c>
-      <c r="C7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="G7" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>304</v>
-      </c>
-      <c r="C8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="G8" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>304</v>
-      </c>
-      <c r="C9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="G9" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>304</v>
-      </c>
-      <c r="C10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" t="s">
-        <v>173</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="G10" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>304</v>
-      </c>
-      <c r="C11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" t="s">
-        <v>173</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="G11" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>304</v>
-      </c>
-      <c r="C12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="G12" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s">
-        <v>304</v>
-      </c>
-      <c r="C13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="G13" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
-        <v>304</v>
-      </c>
-      <c r="C14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="G14" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s">
-        <v>304</v>
-      </c>
-      <c r="C15" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" t="s">
-        <v>59</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="G15" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="1">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>304</v>
-      </c>
-      <c r="C16" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="G16" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="1">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>304</v>
-      </c>
-      <c r="C17" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="G17" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="1">
-        <v>16</v>
-      </c>
-      <c r="B18" t="s">
-        <v>304</v>
-      </c>
-      <c r="C18" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="G18" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="12.75" outlineLevelRow="3"/>
-  <cols>
-    <col min="1" max="4" width="18"/>
-    <col min="5" max="5" width="10"/>
-    <col min="6" max="6" width="42"/>
-    <col min="7" max="8" width="10"/>
-    <col min="9" max="9" width="18"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="1">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>322</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="G2" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>322</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="G3" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>322</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="G4" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Excel/ChatData.xlsx
+++ b/Assets/StreamingAssets/Excel/ChatData.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FFEC38C-EC87-4EAF-B952-C449D9033FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="22188" windowHeight="9060" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="一切的开始" sheetId="1" r:id="rId1"/>
@@ -28,11 +22,24 @@
     <sheet name="困了_03" sheetId="8" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1347" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1347" uniqueCount="359">
   <si>
     <t>小段</t>
   </si>
@@ -1758,6 +1765,82 @@
     <t>接下来继续探索并为生存做准备吧</t>
   </si>
   <si>
+    <t>水平面高度100</t>
+  </si>
+  <si>
+    <t>水平面高度达到100</t>
+  </si>
+  <si>
+    <t>水平面高度</t>
+  </si>
+  <si>
+    <t>咳咳咳</t>
+  </si>
+  <si>
+    <t>脑子好乱……</t>
+  </si>
+  <si>
+    <t>别,一定还会有办法的</t>
+  </si>
+  <si>
+    <t>再坚持一下</t>
+  </si>
+  <si>
+    <t>对不起……</t>
+  </si>
+  <si>
+    <t>……</t>
+  </si>
+  <si>
+    <t>…………</t>
+  </si>
+  <si>
+    <t>………………</t>
+  </si>
+  <si>
+    <t>真正该说对不起的人是我……</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>其他_死亡</t>
+    </r>
+  </si>
+  <si>
+    <t>不……不不不……</t>
+  </si>
+  <si>
+    <t>水平面高度70</t>
+  </si>
+  <si>
+    <t>水平面高度每次达到70</t>
+  </si>
+  <si>
+    <t>感觉在室内移动越来越费劲了</t>
+  </si>
+  <si>
+    <t>哪怕是爬到最高处,水面也没过胸口了</t>
+  </si>
+  <si>
+    <t>没有多少时间</t>
+  </si>
+  <si>
+    <t>水平面高度71</t>
+  </si>
+  <si>
+    <t>如果有没堵上的裂缝应该尽快堵上</t>
+  </si>
+  <si>
+    <t>研究窗口中的"防涝"科技可解锁一些排水的建筑和工具</t>
+  </si>
+  <si>
+    <t>一旦水平面高度达到100,游戏就会结束</t>
+  </si>
+  <si>
     <t>堵住裂缝</t>
   </si>
   <si>
@@ -1932,16 +2015,6 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>其他_死亡</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>醒醒,再坚持一下,会有希望的</t>
     </r>
   </si>
@@ -2388,148 +2461,20 @@
       </rPr>
       <t>嗯</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>其他_死亡</t>
-    </r>
-  </si>
-  <si>
-    <t>不……不不不……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>提示</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>求生系统</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>水平面高度100</t>
-  </si>
-  <si>
-    <t>真正该说对不起的人是我……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>………………</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>对话</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>麦麦</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>…………</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>对不起……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>再坚持一下</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>选项</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>玩家</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>别,一定还会有办法的</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>脑子好乱……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>咳咳咳</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>水平面高度100</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>水平面高度达到100</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>水平面高度</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>水平面高度每次达到100</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>水平面高度70</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>水平面高度每次达到70</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>感觉在室内移动越来越费劲了</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>水平面高度70</t>
-  </si>
-  <si>
-    <t>哪怕是爬到最高处,水面也没过胸口了</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>没有多少时间</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>水平面高度71</t>
-  </si>
-  <si>
-    <t>如果有没堵上的裂缝应该尽快堵上</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>研究窗口中的"防涝"科技可解锁一些排水的建筑和工具</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>一旦水平面高度达到100,游戏就会结束</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="0.00_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="23">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -2549,43 +2494,352 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -2593,17 +2847,259 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2615,7 +3111,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2630,171 +3129,90 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -2805,7 +3223,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -2833,40 +3251,154 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -3124,14 +3656,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I138"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="27"/>
@@ -3141,7 +3673,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3170,7 +3702,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -3182,7 +3714,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3203,7 +3735,7 @@
       </c>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -3224,7 +3756,7 @@
       </c>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -3244,7 +3776,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -3264,7 +3796,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -3285,7 +3817,7 @@
       </c>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -3306,7 +3838,7 @@
       </c>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -3327,7 +3859,7 @@
       </c>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -3348,7 +3880,7 @@
       </c>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -3369,7 +3901,7 @@
       </c>
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -3389,7 +3921,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -3410,7 +3942,7 @@
       </c>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -3430,7 +3962,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -3451,7 +3983,7 @@
       </c>
       <c r="H15" s="1"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -3472,7 +4004,7 @@
       </c>
       <c r="H16" s="1"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -3492,7 +4024,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -3512,7 +4044,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -3533,7 +4065,7 @@
       </c>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -3554,7 +4086,7 @@
       </c>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -3575,7 +4107,7 @@
       </c>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -3596,7 +4128,7 @@
       </c>
       <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -3617,7 +4149,7 @@
       </c>
       <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -3637,7 +4169,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -3658,7 +4190,7 @@
       </c>
       <c r="H25" s="1"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -3679,7 +4211,7 @@
       </c>
       <c r="H26" s="1"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -3700,7 +4232,7 @@
       </c>
       <c r="H27" s="1"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -3721,7 +4253,7 @@
       </c>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -3744,7 +4276,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -3765,7 +4297,7 @@
       </c>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -3786,7 +4318,7 @@
       </c>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -3807,7 +4339,7 @@
       </c>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -3828,7 +4360,7 @@
       </c>
       <c r="H33" s="1"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -3849,7 +4381,7 @@
       </c>
       <c r="H34" s="1"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -3870,7 +4402,7 @@
       </c>
       <c r="H35" s="1"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -3891,7 +4423,7 @@
       </c>
       <c r="H36" s="1"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -3912,7 +4444,7 @@
       </c>
       <c r="H37" s="1"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -3933,7 +4465,7 @@
       </c>
       <c r="H38" s="1"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -3954,7 +4486,7 @@
       </c>
       <c r="H39" s="1"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -3975,7 +4507,7 @@
       </c>
       <c r="H40" s="1"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -3996,7 +4528,7 @@
       </c>
       <c r="H41" s="1"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -4017,7 +4549,7 @@
       </c>
       <c r="H42" s="1"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -4038,7 +4570,7 @@
       </c>
       <c r="H43" s="1"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -4059,7 +4591,7 @@
       </c>
       <c r="H44" s="1"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -4080,7 +4612,7 @@
       </c>
       <c r="H45" s="1"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -4101,7 +4633,7 @@
       </c>
       <c r="H46" s="1"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -4125,7 +4657,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -4149,7 +4681,7 @@
       </c>
       <c r="H48" s="1"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -4170,7 +4702,7 @@
       </c>
       <c r="H49" s="1"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -4191,7 +4723,7 @@
       </c>
       <c r="H50" s="1"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -4212,7 +4744,7 @@
       </c>
       <c r="H51" s="1"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -4233,7 +4765,7 @@
       </c>
       <c r="H52" s="1"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -4254,7 +4786,7 @@
       </c>
       <c r="H53" s="1"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -4275,7 +4807,7 @@
       </c>
       <c r="H54" s="1"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -4296,7 +4828,7 @@
       </c>
       <c r="H55" s="1"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -4317,7 +4849,7 @@
       </c>
       <c r="H56" s="1"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -4338,7 +4870,7 @@
       </c>
       <c r="H57" s="1"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -4359,7 +4891,7 @@
       </c>
       <c r="H58" s="1"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -4380,7 +4912,7 @@
       </c>
       <c r="H59" s="1"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -4401,7 +4933,7 @@
       </c>
       <c r="H60" s="1"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -4425,7 +4957,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -4449,7 +4981,7 @@
       </c>
       <c r="H62" s="1"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -4470,7 +5002,7 @@
       </c>
       <c r="H63" s="1"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -4491,7 +5023,7 @@
       </c>
       <c r="H64" s="1"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -4512,7 +5044,7 @@
       </c>
       <c r="H65" s="1"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -4533,7 +5065,7 @@
       </c>
       <c r="H66" s="1"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -4554,7 +5086,7 @@
       </c>
       <c r="H67" s="1"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -4578,7 +5110,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -4602,7 +5134,7 @@
       </c>
       <c r="H69" s="1"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -4625,7 +5157,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -4646,7 +5178,7 @@
       </c>
       <c r="H71" s="1"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -4667,7 +5199,7 @@
       </c>
       <c r="H72" s="1"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -4690,7 +5222,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -4713,7 +5245,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -4734,7 +5266,7 @@
       </c>
       <c r="H75" s="1"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -4758,7 +5290,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -4782,7 +5314,7 @@
       </c>
       <c r="H77" s="1"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -4803,7 +5335,7 @@
       </c>
       <c r="H78" s="1"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -4826,7 +5358,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -4847,7 +5379,7 @@
       </c>
       <c r="H80" s="1"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -4868,7 +5400,7 @@
       </c>
       <c r="H81" s="1"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -4889,7 +5421,7 @@
       </c>
       <c r="H82" s="1"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -4912,7 +5444,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -4932,7 +5464,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -4952,7 +5484,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -4973,7 +5505,7 @@
       </c>
       <c r="H86" s="1"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -4993,7 +5525,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -5014,7 +5546,7 @@
       </c>
       <c r="H88" s="1"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -5037,7 +5569,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8">
       <c r="A90" s="1">
         <v>88</v>
       </c>
@@ -5058,7 +5590,7 @@
       </c>
       <c r="H90" s="1"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7">
       <c r="A91" s="1">
         <v>89</v>
       </c>
@@ -5078,7 +5610,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8">
       <c r="A92" s="1">
         <v>90</v>
       </c>
@@ -5101,7 +5633,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8">
       <c r="A93" s="1">
         <v>91</v>
       </c>
@@ -5122,7 +5654,7 @@
       </c>
       <c r="H93" s="1"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7">
       <c r="A94" s="1">
         <v>92</v>
       </c>
@@ -5142,7 +5674,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8">
       <c r="A95" s="1">
         <v>93</v>
       </c>
@@ -5163,7 +5695,7 @@
       </c>
       <c r="H95" s="1"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8">
       <c r="A96" s="1">
         <v>94</v>
       </c>
@@ -5184,7 +5716,7 @@
       </c>
       <c r="H96" s="1"/>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9">
       <c r="A97" s="1">
         <v>95</v>
       </c>
@@ -5208,7 +5740,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8">
       <c r="A98" s="1">
         <v>96</v>
       </c>
@@ -5232,7 +5764,7 @@
       </c>
       <c r="H98" s="1"/>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8">
       <c r="A99" s="1">
         <v>97</v>
       </c>
@@ -5253,7 +5785,7 @@
       </c>
       <c r="H99" s="1"/>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8">
       <c r="A100" s="1">
         <v>98</v>
       </c>
@@ -5274,7 +5806,7 @@
       </c>
       <c r="H100" s="1"/>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8">
       <c r="A101" s="1">
         <v>99</v>
       </c>
@@ -5295,7 +5827,7 @@
       </c>
       <c r="H101" s="1"/>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8">
       <c r="A102" s="1">
         <v>100</v>
       </c>
@@ -5316,7 +5848,7 @@
       </c>
       <c r="H102" s="1"/>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8">
       <c r="A103" s="1">
         <v>101</v>
       </c>
@@ -5337,7 +5869,7 @@
       </c>
       <c r="H103" s="1"/>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8">
       <c r="A104" s="1">
         <v>102</v>
       </c>
@@ -5358,7 +5890,7 @@
       </c>
       <c r="H104" s="1"/>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8">
       <c r="A105" s="1">
         <v>103</v>
       </c>
@@ -5379,7 +5911,7 @@
       </c>
       <c r="H105" s="1"/>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8">
       <c r="A106" s="1">
         <v>104</v>
       </c>
@@ -5400,7 +5932,7 @@
       </c>
       <c r="H106" s="1"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8">
       <c r="A107" s="1">
         <v>105</v>
       </c>
@@ -5421,7 +5953,7 @@
       </c>
       <c r="H107" s="1"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8">
       <c r="A108" s="1">
         <v>106</v>
       </c>
@@ -5442,7 +5974,7 @@
       </c>
       <c r="H108" s="1"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8">
       <c r="A109" s="1">
         <v>107</v>
       </c>
@@ -5463,7 +5995,7 @@
       </c>
       <c r="H109" s="1"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8">
       <c r="A110" s="1">
         <v>108</v>
       </c>
@@ -5476,7 +6008,7 @@
       <c r="D110" t="s">
         <v>59</v>
       </c>
-      <c r="F110" s="8" t="s">
+      <c r="F110" s="9" t="s">
         <v>132</v>
       </c>
       <c r="G110" s="1">
@@ -5484,7 +6016,7 @@
       </c>
       <c r="H110" s="1"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8">
       <c r="A111" s="1">
         <v>109</v>
       </c>
@@ -5510,7 +6042,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8">
       <c r="A112" s="1">
         <v>110</v>
       </c>
@@ -5533,7 +6065,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8">
       <c r="A113" s="1">
         <v>111</v>
       </c>
@@ -5556,7 +6088,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8">
       <c r="A114" s="1">
         <v>112</v>
       </c>
@@ -5577,7 +6109,7 @@
       </c>
       <c r="H114" s="1"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8">
       <c r="A115" s="1">
         <v>113</v>
       </c>
@@ -5598,7 +6130,7 @@
       </c>
       <c r="H115" s="1"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8">
       <c r="A116" s="1">
         <v>114</v>
       </c>
@@ -5619,7 +6151,7 @@
       </c>
       <c r="H116" s="1"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8">
       <c r="A117" s="1">
         <v>115</v>
       </c>
@@ -5640,7 +6172,7 @@
       </c>
       <c r="H117" s="1"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8">
       <c r="A118" s="1">
         <v>116</v>
       </c>
@@ -5661,7 +6193,7 @@
       </c>
       <c r="H118" s="1"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8">
       <c r="A119" s="1">
         <v>117</v>
       </c>
@@ -5682,7 +6214,7 @@
       </c>
       <c r="H119" s="1"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8">
       <c r="A120" s="1">
         <v>118</v>
       </c>
@@ -5703,7 +6235,7 @@
       </c>
       <c r="H120" s="1"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8">
       <c r="A121" s="1">
         <v>119</v>
       </c>
@@ -5724,7 +6256,7 @@
       </c>
       <c r="H121" s="1"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7">
       <c r="A122" s="1">
         <v>120</v>
       </c>
@@ -5744,7 +6276,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8">
       <c r="A123" s="1">
         <v>121</v>
       </c>
@@ -5765,7 +6297,7 @@
       </c>
       <c r="H123" s="1"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8">
       <c r="A124" s="1">
         <v>122</v>
       </c>
@@ -5786,7 +6318,7 @@
       </c>
       <c r="H124" s="1"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7">
       <c r="A125" s="1">
         <v>123</v>
       </c>
@@ -5806,7 +6338,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7">
       <c r="A126" s="1">
         <v>124</v>
       </c>
@@ -5826,7 +6358,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8">
       <c r="A127" s="1">
         <v>125</v>
       </c>
@@ -5847,7 +6379,7 @@
       </c>
       <c r="H127" s="1"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8">
       <c r="A128" s="1">
         <v>126</v>
       </c>
@@ -5868,7 +6400,7 @@
       </c>
       <c r="H128" s="1"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8">
       <c r="A129" s="1">
         <v>127</v>
       </c>
@@ -5889,7 +6421,7 @@
       </c>
       <c r="H129" s="1"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9">
       <c r="A130" s="1">
         <v>128</v>
       </c>
@@ -5913,7 +6445,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8">
       <c r="A131" s="1">
         <v>129</v>
       </c>
@@ -5937,7 +6469,7 @@
       </c>
       <c r="H131" s="1"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8">
       <c r="A132" s="1">
         <v>130</v>
       </c>
@@ -5958,7 +6490,7 @@
       </c>
       <c r="H132" s="1"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8">
       <c r="A133" s="1">
         <v>131</v>
       </c>
@@ -5979,7 +6511,7 @@
       </c>
       <c r="H133" s="1"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8">
       <c r="A134" s="1">
         <v>132</v>
       </c>
@@ -6000,7 +6532,7 @@
       </c>
       <c r="H134" s="1"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8">
       <c r="A135" s="1">
         <v>133</v>
       </c>
@@ -6021,7 +6553,7 @@
       </c>
       <c r="H135" s="1"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8">
       <c r="A136" s="1">
         <v>134</v>
       </c>
@@ -6045,7 +6577,7 @@
       </c>
       <c r="H136" s="1"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8">
       <c r="A137" s="1">
         <v>135</v>
       </c>
@@ -6066,7 +6598,7 @@
       </c>
       <c r="H137" s="1"/>
     </row>
-    <row r="138" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+    <row r="138" ht="24" spans="1:9">
       <c r="A138" s="1">
         <v>136</v>
       </c>
@@ -6079,7 +6611,7 @@
       <c r="D138" t="s">
         <v>59</v>
       </c>
-      <c r="F138" s="9" t="s">
+      <c r="F138" s="10" t="s">
         <v>164</v>
       </c>
       <c r="G138" s="1">
@@ -6091,16 +6623,17 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -6109,7 +6642,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6138,26 +6671,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="G2" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -6166,18 +6699,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -6186,18 +6719,18 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -6206,18 +6739,18 @@
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="G5" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -6226,18 +6759,18 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -6246,18 +6779,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -6266,18 +6799,18 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -6286,18 +6819,18 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="G9" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
@@ -6306,21 +6839,21 @@
         <v>173</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="G10" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
@@ -6329,21 +6862,21 @@
         <v>173</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>294</v>
+        <v>316</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>314</v>
+        <v>336</v>
       </c>
       <c r="G11" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
@@ -6352,18 +6885,18 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>315</v>
+        <v>337</v>
       </c>
       <c r="G12" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -6372,18 +6905,18 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>316</v>
+        <v>338</v>
       </c>
       <c r="G13" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -6392,18 +6925,18 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="G14" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="C15" t="s">
         <v>58</v>
@@ -6412,18 +6945,18 @@
         <v>59</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="G15" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="C16" t="s">
         <v>10</v>
@@ -6432,18 +6965,18 @@
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="G16" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
@@ -6452,18 +6985,18 @@
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>320</v>
+        <v>342</v>
       </c>
       <c r="G17" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -6472,22 +7005,23 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>321</v>
+        <v>343</v>
       </c>
       <c r="G18" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -6496,7 +7030,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6525,26 +7059,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -6553,18 +7087,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>324</v>
+        <v>346</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -6573,22 +7107,23 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>325</v>
+        <v>347</v>
       </c>
       <c r="G4" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -6597,7 +7132,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6626,26 +7161,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -6654,18 +7189,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>327</v>
+        <v>349</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -6674,22 +7209,23 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="G4" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="10"/>
@@ -6698,7 +7234,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6727,26 +7263,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -6755,18 +7291,18 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -6775,18 +7311,18 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -6795,18 +7331,18 @@
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>332</v>
+        <v>354</v>
       </c>
       <c r="G5" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -6815,18 +7351,18 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="G6" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -6835,18 +7371,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -6855,18 +7391,18 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>335</v>
+        <v>357</v>
       </c>
       <c r="G8" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -6875,22 +7411,23 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>336</v>
+        <v>358</v>
       </c>
       <c r="G9" s="1">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I32"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="4" width="18"/>
     <col min="5" max="5" width="24"/>
@@ -6899,7 +7436,7 @@
     <col min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6928,7 +7465,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -6942,7 +7479,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -6962,7 +7499,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -6982,7 +7519,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -7002,7 +7539,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -7022,7 +7559,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -7042,7 +7579,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -7062,7 +7599,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -7082,7 +7619,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -7105,7 +7642,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -7128,7 +7665,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -7148,7 +7685,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -7171,7 +7708,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -7191,7 +7728,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -7214,7 +7751,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -7234,7 +7771,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -7257,7 +7794,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -7277,7 +7814,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -7297,7 +7834,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -7318,7 +7855,7 @@
       </c>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -7339,7 +7876,7 @@
       </c>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -7359,7 +7896,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -7379,7 +7916,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -7399,7 +7936,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -7419,7 +7956,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -7439,7 +7976,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -7459,7 +7996,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -7479,7 +8016,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -7499,7 +8036,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -7519,7 +8056,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -7539,28 +8076,29 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7">
       <c r="A32" s="1"/>
       <c r="G32" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheet